--- a/exports/TikTok_Shop_US_Latest_Trends.xlsx
+++ b/exports/TikTok_Shop_US_Latest_Trends.xlsx
@@ -506,7 +506,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J82"/>
+  <dimension ref="A1:J83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -586,23 +586,23 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>Clean Skin Club Disposable 100% Biobased Face Towels</t>
+          <t>Self-Cleaning Deshedding Slicker Pet Grooming Brush</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>Beauty &amp; Personal Care</t>
+          <t>Home Supplies</t>
         </is>
       </c>
       <c r="D3" s="3" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="E3" s="3" t="n">
         <v>95</v>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>$15.95 - $17.95</t>
+          <t>$11.99 - $16.99</t>
         </is>
       </c>
       <c r="G3" s="4" t="inlineStr">
@@ -612,17 +612,17 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>Microscope Gross-Out Angle: 'Stop using the same bathroom towel on your acne breakouts...'</t>
+          <t>One-Click Fur Release ASMR: 'Watch how much undercoat comes off my shedding golden retriever...'</t>
         </is>
       </c>
       <c r="I3" s="4" t="inlineStr">
         <is>
-          <t>Gen Z &amp; Millennials (18-34 tuổi), Chăm sóc da mụn, tín đồ Skincare &amp; 'Clean Girl' aesthetic US.</t>
+          <t>Hội những người 'nghiện' chó mèo (Dog/Cat Parents) tại US, chi tiêu mạnh tay cho thú cưng.</t>
         </is>
       </c>
       <c r="J3" s="5" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/tag/cleanskinclub</t>
+          <t>https://www.tiktok.com/tag/petgrooming</t>
         </is>
       </c>
     </row>
@@ -632,23 +632,23 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>Self-Cleaning Deshedding Slicker Pet Grooming Brush</t>
+          <t>Clean Skin Club Disposable 100% Biobased Face Towels</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>Home Supplies</t>
+          <t>Beauty &amp; Personal Care</t>
         </is>
       </c>
       <c r="D4" s="3" t="n">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E4" s="3" t="n">
         <v>95</v>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>$11.99 - $16.99</t>
+          <t>$15.95 - $17.95</t>
         </is>
       </c>
       <c r="G4" s="4" t="inlineStr">
@@ -658,17 +658,17 @@
       </c>
       <c r="H4" s="4" t="inlineStr">
         <is>
-          <t>One-Click Fur Release ASMR: 'Watch how much undercoat comes off my shedding golden retriever...'</t>
+          <t>Microscope Gross-Out Angle: 'Stop using the same bathroom towel on your acne breakouts...'</t>
         </is>
       </c>
       <c r="I4" s="4" t="inlineStr">
         <is>
-          <t>Hội những người 'nghiện' chó mèo (Dog/Cat Parents) tại US, chi tiêu mạnh tay cho thú cưng.</t>
+          <t>Gen Z &amp; Millennials (18-34 tuổi), Chăm sóc da mụn, tín đồ Skincare &amp; 'Clean Girl' aesthetic US.</t>
         </is>
       </c>
       <c r="J4" s="5" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/tag/petgrooming</t>
+          <t>https://www.tiktok.com/tag/cleanskinclub</t>
         </is>
       </c>
     </row>
@@ -678,7 +678,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>STANLEY Quencher H2.0 Tumbler with Handle and Straw 30 oz | Flowstate 3-Position Lid | Cup Holder Compatible for Travel | Insulate</t>
+          <t>Owala FreeSip Insulated Stainless Steel Tumbler (Leak-Proof Straw)</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
@@ -687,24 +687,24 @@
         </is>
       </c>
       <c r="D5" s="3" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>97</v>
+        <v>50</v>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>$32.95</t>
+          <t>$27.99 - $37.99</t>
         </is>
       </c>
       <c r="G5" s="4" t="inlineStr">
         <is>
-          <t>Amazon Best Sellers, Amazon US, TikTok Trend Validated</t>
+          <t>TikTok Shop, TikTok Viral 24h, Amazon Top 100</t>
         </is>
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>Thử nghiệm dốc ngược bình lắc mạnh: 'Review bình chống tràn 100% đánh bại hoàn toàn cốc Stanley!'</t>
+          <t>Dramatic Flip &amp; Shake Test: 'Stanley cup girls don't want you to see this 100% leak proof test...'</t>
         </is>
       </c>
       <c r="I5" s="4" t="inlineStr">
@@ -714,7 +714,7 @@
       </c>
       <c r="J5" s="5" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/STANLEY-Flowstate-3-Position-Compatible-Insulated/dp/B0CP9YB3Q4/ref=zg_bs_g_kitchen_d_sccl_2/130-1584604-8661848</t>
+          <t>https://www.tiktok.com/tag/owala</t>
         </is>
       </c>
     </row>
@@ -724,7 +724,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>medicube Toner Pads Zero Pore Pad 2.0 for Exfoliation and Pore Care | Dual-Textured Facial Pad with 4.5% AHA Lactic Acid, 0.45% BH</t>
+          <t>Hero Cosmetics Mighty Patch Original Hydrocolloid Acne Dots</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
@@ -733,24 +733,24 @@
         </is>
       </c>
       <c r="D6" s="3" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>90</v>
+        <v>50</v>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>$18.90</t>
+          <t>$12.99 - $14.99</t>
         </is>
       </c>
       <c r="G6" s="4" t="inlineStr">
         <is>
-          <t>Amazon Best Sellers, Amazon US, TikTok Trend Validated</t>
+          <t>TikTok Shop, TikTok Viral 24h, Amazon Top 100</t>
         </is>
       </c>
       <c r="H6" s="4" t="inlineStr">
         <is>
-          <t>Before &amp; After cận cảnh lỗ chân lông: 'Dừng ngay nếu bạn vẫn đang nặn mụn hoặc dùng tẩy tế bào chết hạt to!'</t>
+          <t>Morning Peel-Off Satisfaction: 'Satisfying white gunk pull after 8 hours sleep...'</t>
         </is>
       </c>
       <c r="I6" s="4" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="J6" s="5" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/Medicube-Zero-Pore-Pads-Dual-Textured/dp/B09V7Z4TJG/ref=zg_bs_g_beauty_d_sccl_2/130-1584604-8661848</t>
+          <t>https://www.tiktok.com/tag/mightypatch</t>
         </is>
       </c>
     </row>
@@ -770,43 +770,43 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">HydroJug Traveler 40oz, Insulated Tumbler with Handle &amp; Straw, Pink Sand | Triple wall insulated, flip straw lid, leak-resistant, </t>
+          <t>Mini Portable Thermal Sticker &amp; Label Printer</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>Kitchenware</t>
+          <t>Phones &amp; Electronics</t>
         </is>
       </c>
       <c r="D7" s="3" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>90</v>
+        <v>45</v>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>$31.99</t>
+          <t>$19.99 - $29.99</t>
         </is>
       </c>
       <c r="G7" s="4" t="inlineStr">
         <is>
-          <t>Amazon Best Sellers, Amazon US, TikTok Trend Validated</t>
+          <t>TikTok Shop, TikTok Viral 24h, Amazon Top 100</t>
         </is>
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>Before &amp; After cận cảnh lỗ chân lông: 'Dừng ngay nếu bạn vẫn đang nặn mụn hoặc dùng tẩy tế bào chết hạt to!'</t>
+          <t>ASMR Unboxing &amp; Instant Scrapbook Printing: 'Never buying ink cartridges again!'</t>
         </is>
       </c>
       <c r="I7" s="4" t="inlineStr">
         <is>
-          <t>Gen Z &amp; Millennials (18-34 tuổi), Chăm sóc da mụn, tín đồ Skincare &amp; 'Clean Girl' aesthetic US.</t>
+          <t>Học sinh, Gen Z làm bullet journal, Content Creator quay video TikTok / Vlog tại US.</t>
         </is>
       </c>
       <c r="J7" s="5" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/HydroJug-Traveler-Resistant-Bottle-Reusable-Insulated/dp/B0CQVWT2NH/ref=zg_bs_g_kitchen_d_sccl_3/130-1584604-8661848</t>
+          <t>https://www.tiktok.com/tag/miniprinter</t>
         </is>
       </c>
     </row>
@@ -816,43 +816,43 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>Apple EarPods Headphones with USB-C Plug, Wired Ear Buds with Built-in Remote to Control Music, Phone Calls, and Volume</t>
+          <t>medicube Zero Pore Pads 2.0 &amp; Exfoliating Toner</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>Phones &amp; Electronics</t>
+          <t>Beauty &amp; Personal Care</t>
         </is>
       </c>
       <c r="D8" s="3" t="n">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>85</v>
+        <v>50</v>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>18 offers from $17.87</t>
+          <t>$18.90 - $24.00</t>
         </is>
       </c>
       <c r="G8" s="4" t="inlineStr">
         <is>
-          <t>Amazon Best Sellers, Amazon US</t>
+          <t>TikTok Shop, TikTok Viral 24h, Amazon Top 100</t>
         </is>
       </c>
       <c r="H8" s="4" t="inlineStr">
         <is>
-          <t>Đặt câu hỏi trúng nỗi đau thường ngày: 'Tại sao không ai nói cho tôi biết món đồ này sớm hơn?!'</t>
+          <t>Before &amp; After Macro Skin Texture Zoom: 'My aesthetician told me to stop using physical scrubs...'</t>
         </is>
       </c>
       <c r="I8" s="4" t="inlineStr">
         <is>
-          <t>Khách hàng mua sắm ngẫu hứng (Impulse Buyers) trên TikTok Shop US độ tuổi 18 - 45.</t>
+          <t>Gen Z &amp; Millennials (18-34 tuổi), Chăm sóc da mụn, tín đồ Skincare &amp; 'Clean Girl' aesthetic US.</t>
         </is>
       </c>
       <c r="J8" s="5" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/Apple-EarPods-Headphones-Built-Control/dp/B0DCH8VDXF/ref=zg_bs_g_electronics_d_sccl_2/130-1584604-8661848</t>
+          <t>https://www.tiktok.com/tag/medicube</t>
         </is>
       </c>
     </row>
@@ -862,43 +862,43 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>Apple AirTag (2nd Generation): Tracker for Keychain, Wallet, and More; Locator with Sound; Simple One-Tap Setup with iPhone or iPa</t>
+          <t>Automatic 360 Electric Spin Scrubber for Deep Bathroom Cleaning</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>Pet Supplies</t>
+          <t>Home Supplies</t>
         </is>
       </c>
       <c r="D9" s="3" t="n">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>85</v>
+        <v>50</v>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>10 offers from $22.32</t>
+          <t>$29.99 - $49.99</t>
         </is>
       </c>
       <c r="G9" s="4" t="inlineStr">
         <is>
-          <t>Amazon Best Sellers, Amazon US</t>
+          <t>TikTok Shop, TikTok Viral 24h, Amazon Top 100</t>
         </is>
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>Âm thanh bấm nút nhả cả búi lông chó rụng chỉ trong 1 giây: 'Mùa rụng lông không còn là ác mộng!'</t>
+          <t>Pain-Point Relief Angle: 'Save your back and knees when scrubbing stubborn shower grime...'</t>
         </is>
       </c>
       <c r="I9" s="4" t="inlineStr">
         <is>
-          <t>Hội những người 'nghiện' chó mèo (Dog/Cat Parents) tại US, chi tiêu mạnh tay cho thú cưng.</t>
+          <t>Các mẹ bỉm sữa, Người độc thân yêu nhà cửa gọn gàng, Hội nghiện dọn dẹp CleanTok US.</t>
         </is>
       </c>
       <c r="J9" s="5" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/Apple-AirTag-2nd-Generation-Precision/dp/B0GJTFXNRX/ref=zg_bs_g_electronics_d_sccl_3/130-1584604-8661848</t>
+          <t>https://www.tiktok.com/tag/spinscrubber</t>
         </is>
       </c>
     </row>
@@ -908,43 +908,43 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>Amazon Fire TV Stick 4K Select (newest model), start streaming in 4K, AI-powered search, and free &amp; live TV, find shows faster wit</t>
+          <t>Wireless Magnetic Lavalier Lapel Microphone for iPhone &amp; Type-C</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>Tech Gadgets</t>
+          <t>Phones &amp; Electronics</t>
         </is>
       </c>
       <c r="D10" s="3" t="n">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>85</v>
+        <v>45</v>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>1 offer from $49.99</t>
+          <t>$16.99 - $24.99</t>
         </is>
       </c>
       <c r="G10" s="4" t="inlineStr">
         <is>
-          <t>Amazon Best Sellers, Amazon US</t>
+          <t>TikTok Shop, TikTok Viral 24h</t>
         </is>
       </c>
       <c r="H10" s="4" t="inlineStr">
         <is>
-          <t>Đặt câu hỏi trúng nỗi đau thường ngày: 'Tại sao không ai nói cho tôi biết món đồ này sớm hơn?!'</t>
+          <t>Audio Contrast Hook: Whisper in crowded room with noise cancellation toggle ON vs OFF</t>
         </is>
       </c>
       <c r="I10" s="4" t="inlineStr">
         <is>
-          <t>Khách hàng mua sắm ngẫu hứng (Impulse Buyers) trên TikTok Shop US độ tuổi 18 - 45.</t>
+          <t>Học sinh, Gen Z làm bullet journal, Content Creator quay video TikTok / Vlog tại US.</t>
         </is>
       </c>
       <c r="J10" s="5" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/amazon-fire-tv-stick-4K-select/dp/B0C6W3D4RM/ref=zg_bs_g_electronics_d_sccl_4/130-1584604-8661848</t>
+          <t>https://www.tiktok.com/tag/wirelessmicrophone</t>
         </is>
       </c>
     </row>
@@ -954,43 +954,43 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>Apple AirPods Pro 3 Wireless Earbuds with Active Noise Cancellation | Live Translation, Heart Rate Sensing, Hearing Aid Feature, B</t>
+          <t>STANLEY Quencher H2.0 Tumbler with Handle and Straw 30 oz | Flowstate 3-Position Lid | Cup Holder Compatible for Travel | Insulate</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>Jewelry Accessories &amp; Derivatives</t>
+          <t>Kitchenware</t>
         </is>
       </c>
       <c r="D11" s="3" t="n">
-        <v>86</v>
+        <v>98</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>85</v>
+        <v>97</v>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>12 offers from $183.44</t>
+          <t>$19.99</t>
         </is>
       </c>
       <c r="G11" s="4" t="inlineStr">
         <is>
-          <t>Amazon Best Sellers, Amazon US</t>
+          <t>Amazon Best Sellers, Amazon US, TikTok Trend Validated</t>
         </is>
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>So sánh âm thanh: 'Bật lọc tạp âm và nói chuyện giữa chợ ồn ào xem micro này xịn cỡ nào!'</t>
+          <t>Thử nghiệm dốc ngược bình lắc mạnh: 'Review bình chống tràn 100% đánh bại hoàn toàn cốc Stanley!'</t>
         </is>
       </c>
       <c r="I11" s="4" t="inlineStr">
         <is>
-          <t>Học sinh, Gen Z làm bullet journal, Content Creator quay video TikTok / Vlog tại US.</t>
+          <t>Học sinh/Sinh viên US, Dân văn phòng, Người đi tập Gym &amp; Pilates yêu thích đồ cute, thẩm mỹ.</t>
         </is>
       </c>
       <c r="J11" s="5" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/Apple-Cancellation-Translation-Headphones-High-Fidelity/dp/B0FQFB8FMG/ref=zg_bs_g_electronics_d_sccl_5/130-1584604-8661848</t>
+          <t>https://www.amazon.com/STANLEY-Flowstate-3-Position-Compatible-Insulated/dp/B0CP9YB3Q4/ref=zg_bs_g_kitchen_d_sccl_2/142-8547974-1409324</t>
         </is>
       </c>
     </row>
@@ -1000,43 +1000,43 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>Owala FreeSip Insulated Stainless Steel Tumbler (Leak-Proof Straw)</t>
+          <t>medicube Toner Pads Zero Pore Pad 2.0 for Exfoliation and Pore Care | Dual-Textured Facial Pad with 4.5% AHA Lactic Acid, 0.45% BH</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>Kitchenware</t>
+          <t>Beauty &amp; Personal Care</t>
         </is>
       </c>
       <c r="D12" s="3" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>50</v>
+        <v>90</v>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>$27.99 - $37.99</t>
+          <t>$19.99</t>
         </is>
       </c>
       <c r="G12" s="4" t="inlineStr">
         <is>
-          <t>TikTok Shop, TikTok Viral 24h, Amazon Top 100</t>
+          <t>Amazon Best Sellers, Amazon US, TikTok Trend Validated</t>
         </is>
       </c>
       <c r="H12" s="4" t="inlineStr">
         <is>
-          <t>Dramatic Flip &amp; Shake Test: 'Stanley cup girls don't want you to see this 100% leak proof test...'</t>
+          <t>Before &amp; After cận cảnh lỗ chân lông: 'Dừng ngay nếu bạn vẫn đang nặn mụn hoặc dùng tẩy tế bào chết hạt to!'</t>
         </is>
       </c>
       <c r="I12" s="4" t="inlineStr">
         <is>
-          <t>Học sinh/Sinh viên US, Dân văn phòng, Người đi tập Gym &amp; Pilates yêu thích đồ cute, thẩm mỹ.</t>
+          <t>Gen Z &amp; Millennials (18-34 tuổi), Chăm sóc da mụn, tín đồ Skincare &amp; 'Clean Girl' aesthetic US.</t>
         </is>
       </c>
       <c r="J12" s="5" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/tag/owala</t>
+          <t>https://www.amazon.com/Medicube-Zero-Pore-Pads-Dual-Textured/dp/B09V7Z4TJG/ref=zg_bs_g_beauty_d_sccl_2/142-8547974-1409324</t>
         </is>
       </c>
     </row>
@@ -1046,33 +1046,33 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Hero Cosmetics Mighty Patch Original Hydrocolloid Acne Dots</t>
+          <t xml:space="preserve">HydroJug Traveler 40oz, Insulated Tumbler with Handle &amp; Straw, Pink Sand | Triple wall insulated, flip straw lid, leak-resistant, </t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>Beauty &amp; Personal Care</t>
+          <t>Kitchenware</t>
         </is>
       </c>
       <c r="D13" s="3" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>50</v>
+        <v>90</v>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>$12.99 - $14.99</t>
+          <t>$19.99</t>
         </is>
       </c>
       <c r="G13" s="4" t="inlineStr">
         <is>
-          <t>TikTok Shop, TikTok Viral 24h, Amazon Top 100</t>
+          <t>Amazon Best Sellers, Amazon US, TikTok Trend Validated</t>
         </is>
       </c>
       <c r="H13" s="4" t="inlineStr">
         <is>
-          <t>Morning Peel-Off Satisfaction: 'Satisfying white gunk pull after 8 hours sleep...'</t>
+          <t>Before &amp; After cận cảnh lỗ chân lông: 'Dừng ngay nếu bạn vẫn đang nặn mụn hoặc dùng tẩy tế bào chết hạt to!'</t>
         </is>
       </c>
       <c r="I13" s="4" t="inlineStr">
@@ -1082,7 +1082,7 @@
       </c>
       <c r="J13" s="5" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/tag/mightypatch</t>
+          <t>https://www.amazon.com/HydroJug-Traveler-Resistant-Bottle-Reusable-Insulated/dp/B0CQVWT2NH/ref=zg_bs_g_kitchen_d_sccl_3/142-8547974-1409324</t>
         </is>
       </c>
     </row>
@@ -1092,43 +1092,43 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>medicube Zero Pore Pads 2.0 &amp; Exfoliating Toner</t>
+          <t>Apple EarPods Headphones with USB-C Plug, Wired Ear Buds with Built-in Remote to Control Music, Phone Calls, and Volume</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>Beauty &amp; Personal Care</t>
+          <t>Phones &amp; Electronics</t>
         </is>
       </c>
       <c r="D14" s="3" t="n">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>50</v>
+        <v>85</v>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>$18.90 - $24.00</t>
+          <t>18 offers from $17.87</t>
         </is>
       </c>
       <c r="G14" s="4" t="inlineStr">
         <is>
-          <t>TikTok Shop, TikTok Viral 24h, Amazon Top 100</t>
+          <t>Amazon Best Sellers, Amazon US</t>
         </is>
       </c>
       <c r="H14" s="4" t="inlineStr">
         <is>
-          <t>Before &amp; After Macro Skin Texture Zoom: 'My aesthetician told me to stop using physical scrubs...'</t>
+          <t>Đặt câu hỏi trúng nỗi đau thường ngày: 'Tại sao không ai nói cho tôi biết món đồ này sớm hơn?!'</t>
         </is>
       </c>
       <c r="I14" s="4" t="inlineStr">
         <is>
-          <t>Gen Z &amp; Millennials (18-34 tuổi), Chăm sóc da mụn, tín đồ Skincare &amp; 'Clean Girl' aesthetic US.</t>
+          <t>Khách hàng mua sắm ngẫu hứng (Impulse Buyers) trên TikTok Shop US độ tuổi 18 - 45.</t>
         </is>
       </c>
       <c r="J14" s="5" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/tag/medicube</t>
+          <t>https://www.amazon.com/Apple-EarPods-Headphones-Built-Control/dp/B0DCH8VDXF/ref=zg_bs_g_electronics_d_sccl_2/142-8547974-1409324</t>
         </is>
       </c>
     </row>
@@ -1138,43 +1138,43 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Automatic 360 Electric Spin Scrubber for Deep Bathroom Cleaning</t>
+          <t>Apple AirTag (2nd Generation): Tracker for Keychain, Wallet, and More; Locator with Sound; Simple One-Tap Setup with iPhone or iPa</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>Home Supplies</t>
+          <t>Pet Supplies</t>
         </is>
       </c>
       <c r="D15" s="3" t="n">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>50</v>
+        <v>85</v>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>$29.99 - $49.99</t>
+          <t>10 offers from $22.32</t>
         </is>
       </c>
       <c r="G15" s="4" t="inlineStr">
         <is>
-          <t>TikTok Shop, TikTok Viral 24h, Amazon Top 100</t>
+          <t>Amazon Best Sellers, Amazon US</t>
         </is>
       </c>
       <c r="H15" s="4" t="inlineStr">
         <is>
-          <t>Pain-Point Relief Angle: 'Save your back and knees when scrubbing stubborn shower grime...'</t>
+          <t>Âm thanh bấm nút nhả cả búi lông chó rụng chỉ trong 1 giây: 'Mùa rụng lông không còn là ác mộng!'</t>
         </is>
       </c>
       <c r="I15" s="4" t="inlineStr">
         <is>
-          <t>Các mẹ bỉm sữa, Người độc thân yêu nhà cửa gọn gàng, Hội nghiện dọn dẹp CleanTok US.</t>
+          <t>Hội những người 'nghiện' chó mèo (Dog/Cat Parents) tại US, chi tiêu mạnh tay cho thú cưng.</t>
         </is>
       </c>
       <c r="J15" s="5" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/tag/spinscrubber</t>
+          <t>https://www.amazon.com/Apple-AirTag-2nd-Generation-Precision/dp/B0GJTFXNRX/ref=zg_bs_g_electronics_d_sccl_3/142-8547974-1409324</t>
         </is>
       </c>
     </row>
@@ -1184,43 +1184,43 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>Mini Portable Thermal Sticker &amp; Label Printer</t>
+          <t>Amazon Fire TV Stick 4K Select (newest model), start streaming in 4K, AI-powered search, and free &amp; live TV, find shows faster wit</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>Phones &amp; Electronics</t>
+          <t>Tech Gadgets</t>
         </is>
       </c>
       <c r="D16" s="3" t="n">
-        <v>99</v>
+        <v>86</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>45</v>
+        <v>85</v>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t>$19.99 - $29.99</t>
+          <t>1 offer from $49.99</t>
         </is>
       </c>
       <c r="G16" s="4" t="inlineStr">
         <is>
-          <t>TikTok Shop, TikTok Viral 24h, Amazon Top 100</t>
+          <t>Amazon Best Sellers, Amazon US</t>
         </is>
       </c>
       <c r="H16" s="4" t="inlineStr">
         <is>
-          <t>ASMR Unboxing &amp; Instant Scrapbook Printing: 'Never buying ink cartridges again!'</t>
+          <t>Đặt câu hỏi trúng nỗi đau thường ngày: 'Tại sao không ai nói cho tôi biết món đồ này sớm hơn?!'</t>
         </is>
       </c>
       <c r="I16" s="4" t="inlineStr">
         <is>
-          <t>Học sinh, Gen Z làm bullet journal, Content Creator quay video TikTok / Vlog tại US.</t>
+          <t>Khách hàng mua sắm ngẫu hứng (Impulse Buyers) trên TikTok Shop US độ tuổi 18 - 45.</t>
         </is>
       </c>
       <c r="J16" s="5" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/tag/miniprinter</t>
+          <t>https://www.amazon.com/amazon-fire-tv-stick-4K-select/dp/B0C6W3D4RM/ref=zg_bs_g_electronics_d_sccl_4/142-8547974-1409324</t>
         </is>
       </c>
     </row>
@@ -1230,28 +1230,28 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>Original HP 2LL58A 636 STITCH DYE SUBLIMATION INK CYAN 3L Ink MHD 07-10/20243,573,692.31 VNDShop all 18Printers &amp; Printe</t>
+          <t>Apple AirPods Pro 3 Wireless Earbuds with Active Noise Cancellation | Live Translation, Heart Rate Sensing, Hearing Aid Feature, B</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>Phones &amp; Electronics</t>
+          <t>Jewelry Accessories &amp; Derivatives</t>
         </is>
       </c>
       <c r="D17" s="3" t="n">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>72</v>
+        <v>85</v>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>$19.99</t>
+          <t>12 offers from $183.44</t>
         </is>
       </c>
       <c r="G17" s="4" t="inlineStr">
         <is>
-          <t>eBay US Deals</t>
+          <t>Amazon Best Sellers, Amazon US</t>
         </is>
       </c>
       <c r="H17" s="4" t="inlineStr">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="J17" s="5" t="inlineStr">
         <is>
-          <t>https://www.ebay.com/itm/116219205632</t>
+          <t>https://www.amazon.com/Apple-Cancellation-Translation-Headphones-High-Fidelity/dp/B0FQFB8FMG/ref=zg_bs_g_electronics_d_sccl_5/142-8547974-1409324</t>
         </is>
       </c>
     </row>
@@ -1276,7 +1276,7 @@
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>15%OFF UGG Slippers Australian Sheepskin Wool Warm House Slip On Scuff Women Men1,084,962.23 VNDADIDAS SCHUHE SPEZIALIST</t>
+          <t>Original Toner Ricoh Aficio MP C3503 C4504 C5504 C6004 SP / 841817 - 8418205,032,950.00 VNDShop all 18Printers &amp; Printer</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="J18" s="5" t="inlineStr">
         <is>
-          <t>https://www.ebay.com/itm/385963123229</t>
+          <t>https://www.ebay.com/itm/223769336762</t>
         </is>
       </c>
     </row>
@@ -1322,16 +1322,16 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>Spotlight DealCASIO WATCH CALCULATOR VINTAGE RETRO 80's CA-53W-1Z CA53 CA-53 AUSSIE SELLER838,137.46 VND1,470,465.00 VND</t>
+          <t>15%OFF UGG Slippers Australian Sheepskin Wool Warm House Slip On Scuff Women Men1,084,962.23 VNDADIDAS SCHUHE SPEZIALIST</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>All Trending Deals</t>
+          <t>Beauty &amp; Personal Care</t>
         </is>
       </c>
       <c r="D19" s="3" t="n">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="E19" s="3" t="n">
         <v>72</v>
@@ -1348,17 +1348,17 @@
       </c>
       <c r="H19" s="4" t="inlineStr">
         <is>
-          <t>So sánh âm thanh: 'Bật lọc tạp âm và nói chuyện giữa chợ ồn ào xem micro này xịn cỡ nào!'</t>
+          <t>Before &amp; After cận cảnh lỗ chân lông: 'Dừng ngay nếu bạn vẫn đang nặn mụn hoặc dùng tẩy tế bào chết hạt to!'</t>
         </is>
       </c>
       <c r="I19" s="4" t="inlineStr">
         <is>
-          <t>Học sinh, Gen Z làm bullet journal, Content Creator quay video TikTok / Vlog tại US.</t>
+          <t>Gen Z &amp; Millennials (18-34 tuổi), Chăm sóc da mụn, tín đồ Skincare &amp; 'Clean Girl' aesthetic US.</t>
         </is>
       </c>
       <c r="J19" s="5" t="inlineStr">
         <is>
-          <t>https://www.ebay.com/itm/370786315096</t>
+          <t>https://www.ebay.com/itm/385963123229</t>
         </is>
       </c>
     </row>
@@ -1368,43 +1368,43 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>CASIO WATCH VINTAGE RETRO ORIGINAL F-91W-1 F91 F91W F-91 WARANTY666,169.38 VND734,772.69 VND | 9% offPrevious price: 734</t>
+          <t>red alert</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>All Trending Deals</t>
+          <t>Pets &amp; Animals</t>
         </is>
       </c>
       <c r="D20" s="3" t="n">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>72</v>
+        <v>50</v>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t>$19.99</t>
+          <t>$25.00</t>
         </is>
       </c>
       <c r="G20" s="4" t="inlineStr">
         <is>
-          <t>eBay US Deals</t>
+          <t>Google Trends US Search</t>
         </is>
       </c>
       <c r="H20" s="4" t="inlineStr">
         <is>
-          <t>So sánh âm thanh: 'Bật lọc tạp âm và nói chuyện giữa chợ ồn ào xem micro này xịn cỡ nào!'</t>
+          <t>Âm thanh bấm nút nhả cả búi lông chó rụng chỉ trong 1 giây: 'Mùa rụng lông không còn là ác mộng!'</t>
         </is>
       </c>
       <c r="I20" s="4" t="inlineStr">
         <is>
-          <t>Học sinh, Gen Z làm bullet journal, Content Creator quay video TikTok / Vlog tại US.</t>
+          <t>Hội những người 'nghiện' chó mèo (Dog/Cat Parents) tại US, chi tiêu mạnh tay cho thú cưng.</t>
         </is>
       </c>
       <c r="J20" s="5" t="inlineStr">
         <is>
-          <t>https://www.ebay.com/itm/370816923572</t>
+          <t>https://trends.google.com/trends/explore?geo=US&amp;q=red%20alert</t>
         </is>
       </c>
     </row>
@@ -1414,28 +1414,28 @@
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>Cisco SFP-H10GB-CU3M 37-0961-03 SFP+ 10G Passive DAC Twinax Cable NEW897,435.90 VND</t>
+          <t>mlb wildcard standings</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>All Trending Deals</t>
+          <t>Automotive &amp; Motorcycle</t>
         </is>
       </c>
       <c r="D21" s="3" t="n">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>72</v>
+        <v>50</v>
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t>$19.99</t>
+          <t>$25.00</t>
         </is>
       </c>
       <c r="G21" s="4" t="inlineStr">
         <is>
-          <t>eBay US Deals</t>
+          <t>Google Trends US Search</t>
         </is>
       </c>
       <c r="H21" s="4" t="inlineStr">
@@ -1450,7 +1450,7 @@
       </c>
       <c r="J21" s="5" t="inlineStr">
         <is>
-          <t>https://www.ebay.com/itm/157632501279</t>
+          <t>https://trends.google.com/trends/explore?geo=US&amp;q=mlb%20wildcard%20standings</t>
         </is>
       </c>
     </row>
@@ -1460,28 +1460,28 @@
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>NZG 1:18 Mercedes-Benz AMG G63 4x4² 2023 W463 Alloy Diecast Car Model6,641,025.64 VND9,025,641.03 VND Previous price: 9,</t>
+          <t>pak vs eng</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>Automotive &amp; Motorcycle</t>
+          <t>General Trend</t>
         </is>
       </c>
       <c r="D22" s="3" t="n">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="E22" s="3" t="n">
-        <v>72</v>
+        <v>45</v>
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t>$19.99</t>
+          <t>$25.00</t>
         </is>
       </c>
       <c r="G22" s="4" t="inlineStr">
         <is>
-          <t>eBay US Deals</t>
+          <t>Google Trends US Search</t>
         </is>
       </c>
       <c r="H22" s="4" t="inlineStr">
@@ -1496,7 +1496,7 @@
       </c>
       <c r="J22" s="5" t="inlineStr">
         <is>
-          <t>https://www.ebay.com/itm/298638189628</t>
+          <t>https://trends.google.com/trends/explore?geo=US&amp;q=pak%20vs%20eng</t>
         </is>
       </c>
     </row>
@@ -1506,44 +1506,43 @@
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>Apple iPhone 16 Pro Max All Colours26,609,000.00 VND
-eBay Refurbished</t>
+          <t>michelle obama chanel us open</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>All Trending Deals</t>
+          <t>Phones &amp; Electronics</t>
         </is>
       </c>
       <c r="D23" s="3" t="n">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>72</v>
+        <v>45</v>
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t>$19.99</t>
+          <t>$25.00</t>
         </is>
       </c>
       <c r="G23" s="4" t="inlineStr">
         <is>
-          <t>eBay US Deals</t>
+          <t>Google Trends US Search</t>
         </is>
       </c>
       <c r="H23" s="4" t="inlineStr">
         <is>
-          <t>Âm thanh bấm nút nhả cả búi lông chó rụng chỉ trong 1 giây: 'Mùa rụng lông không còn là ác mộng!'</t>
+          <t>So sánh âm thanh: 'Bật lọc tạp âm và nói chuyện giữa chợ ồn ào xem micro này xịn cỡ nào!'</t>
         </is>
       </c>
       <c r="I23" s="4" t="inlineStr">
         <is>
-          <t>Hội những người 'nghiện' chó mèo (Dog/Cat Parents) tại US, chi tiêu mạnh tay cho thú cưng.</t>
+          <t>Học sinh, Gen Z làm bullet journal, Content Creator quay video TikTok / Vlog tại US.</t>
         </is>
       </c>
       <c r="J23" s="5" t="inlineStr">
         <is>
-          <t>https://www.ebay.com/itm/257723314310</t>
+          <t>https://trends.google.com/trends/explore?geo=US&amp;q=michelle%20obama%20chanel%20us%20open</t>
         </is>
       </c>
     </row>
@@ -1553,43 +1552,43 @@
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>Apple iPhone 16 Pro - 1TB - All Colours21,821,461.54 VNDeBay Refurbished</t>
+          <t>meghan</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>All Trending Deals</t>
+          <t>Health &amp; Fitness</t>
         </is>
       </c>
       <c r="D24" s="3" t="n">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="E24" s="3" t="n">
-        <v>72</v>
+        <v>45</v>
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t>$19.99</t>
+          <t>$25.00</t>
         </is>
       </c>
       <c r="G24" s="4" t="inlineStr">
         <is>
-          <t>eBay US Deals</t>
+          <t>Google Trends US Search</t>
         </is>
       </c>
       <c r="H24" s="4" t="inlineStr">
         <is>
-          <t>Âm thanh bấm nút nhả cả búi lông chó rụng chỉ trong 1 giây: 'Mùa rụng lông không còn là ác mộng!'</t>
+          <t>Đặt câu hỏi trúng nỗi đau thường ngày: 'Tại sao không ai nói cho tôi biết món đồ này sớm hơn?!'</t>
         </is>
       </c>
       <c r="I24" s="4" t="inlineStr">
         <is>
-          <t>Hội những người 'nghiện' chó mèo (Dog/Cat Parents) tại US, chi tiêu mạnh tay cho thú cưng.</t>
+          <t>Khách hàng mua sắm ngẫu hứng (Impulse Buyers) trên TikTok Shop US độ tuổi 18 - 45.</t>
         </is>
       </c>
       <c r="J24" s="5" t="inlineStr">
         <is>
-          <t>https://www.ebay.com/itm/257132401723</t>
+          <t>https://trends.google.com/trends/explore?geo=US&amp;q=meghan</t>
         </is>
       </c>
     </row>
@@ -1599,43 +1598,43 @@
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>Apple iPhone 16 Pro Max - 256GB 512GB 1TB- All Colours - Good25,013,153.85 VNDeBay Refurbished</t>
+          <t>ukraine</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>All Trending Deals</t>
+          <t>General Trend</t>
         </is>
       </c>
       <c r="D25" s="3" t="n">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="E25" s="3" t="n">
-        <v>72</v>
+        <v>45</v>
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t>$19.99</t>
+          <t>$25.00</t>
         </is>
       </c>
       <c r="G25" s="4" t="inlineStr">
         <is>
-          <t>eBay US Deals</t>
+          <t>Google Trends US Search</t>
         </is>
       </c>
       <c r="H25" s="4" t="inlineStr">
         <is>
-          <t>Âm thanh bấm nút nhả cả búi lông chó rụng chỉ trong 1 giây: 'Mùa rụng lông không còn là ác mộng!'</t>
+          <t>Đặt câu hỏi trúng nỗi đau thường ngày: 'Tại sao không ai nói cho tôi biết món đồ này sớm hơn?!'</t>
         </is>
       </c>
       <c r="I25" s="4" t="inlineStr">
         <is>
-          <t>Hội những người 'nghiện' chó mèo (Dog/Cat Parents) tại US, chi tiêu mạnh tay cho thú cưng.</t>
+          <t>Khách hàng mua sắm ngẫu hứng (Impulse Buyers) trên TikTok Shop US độ tuổi 18 - 45.</t>
         </is>
       </c>
       <c r="J25" s="5" t="inlineStr">
         <is>
-          <t>https://www.ebay.com/itm/298645175829</t>
+          <t>https://trends.google.com/trends/explore?geo=US&amp;q=ukraine</t>
         </is>
       </c>
     </row>
@@ -1645,28 +1644,28 @@
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>MERCEDES 190 190E W201 Motor Kupplung Bremsen ab 1982 Reparaturanleitung B786860,664.23 VNDAlmost goneLada 1200 1300 150</t>
+          <t>irish open 2026</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>All Trending Deals</t>
+          <t>Books, Magazines &amp; Audio</t>
         </is>
       </c>
       <c r="D26" s="3" t="n">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="E26" s="3" t="n">
-        <v>72</v>
+        <v>45</v>
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
-          <t>$19.99</t>
+          <t>$25.00</t>
         </is>
       </c>
       <c r="G26" s="4" t="inlineStr">
         <is>
-          <t>eBay US Deals</t>
+          <t>Google Trends US Search</t>
         </is>
       </c>
       <c r="H26" s="4" t="inlineStr">
@@ -1681,7 +1680,7 @@
       </c>
       <c r="J26" s="5" t="inlineStr">
         <is>
-          <t>https://www.ebay.com/itm/201727143641</t>
+          <t>https://trends.google.com/trends/explore?geo=US&amp;q=irish%20open%202026</t>
         </is>
       </c>
     </row>
@@ -1691,28 +1690,28 @@
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>Biker Kutte Lederkutte Lederweste Clubweste Rockerweste Herren Chopper Motorrad2,679,971.42 VND</t>
+          <t>indianapolis weather</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>All Trending Deals</t>
+          <t>General Trend</t>
         </is>
       </c>
       <c r="D27" s="3" t="n">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>72</v>
+        <v>45</v>
       </c>
       <c r="F27" s="3" t="inlineStr">
         <is>
-          <t>$19.99</t>
+          <t>$25.00</t>
         </is>
       </c>
       <c r="G27" s="4" t="inlineStr">
         <is>
-          <t>eBay US Deals</t>
+          <t>Google Trends US Search</t>
         </is>
       </c>
       <c r="H27" s="4" t="inlineStr">
@@ -1727,7 +1726,7 @@
       </c>
       <c r="J27" s="5" t="inlineStr">
         <is>
-          <t>https://www.ebay.com/itm/302258284099</t>
+          <t>https://trends.google.com/trends/explore?geo=US&amp;q=indianapolis%20weather</t>
         </is>
       </c>
     </row>
@@ -1737,28 +1736,28 @@
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>Lederweste Bikerweste Motorrad Kutte Biker Chopper Rockerweste mit Taschen2,679,971.42 VNDShop all 91Parts &amp; Accessories</t>
+          <t>adam levy</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>All Trending Deals</t>
+          <t>Fashion &amp; Apparel</t>
         </is>
       </c>
       <c r="D28" s="3" t="n">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="E28" s="3" t="n">
-        <v>72</v>
+        <v>45</v>
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
-          <t>$19.99</t>
+          <t>$25.00</t>
         </is>
       </c>
       <c r="G28" s="4" t="inlineStr">
         <is>
-          <t>eBay US Deals</t>
+          <t>Google Trends US Search</t>
         </is>
       </c>
       <c r="H28" s="4" t="inlineStr">
@@ -1773,7 +1772,7 @@
       </c>
       <c r="J28" s="5" t="inlineStr">
         <is>
-          <t>https://www.ebay.com/itm/291771387455</t>
+          <t>https://trends.google.com/trends/explore?geo=US&amp;q=adam%20levy</t>
         </is>
       </c>
     </row>
@@ -1783,43 +1782,43 @@
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>CASIO WATCH SWIMMING 100 METRES WATER RESISTANT W-800 W-800H-1AV W8001,025,371.15 VND1,102,618.85 VND | 7% offPrevious p</t>
+          <t>jason bard yarmosky</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>All Trending Deals</t>
+          <t>Fashion &amp; Apparel</t>
         </is>
       </c>
       <c r="D29" s="3" t="n">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>72</v>
+        <v>45</v>
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
-          <t>$19.99</t>
+          <t>$25.00</t>
         </is>
       </c>
       <c r="G29" s="4" t="inlineStr">
         <is>
-          <t>eBay US Deals</t>
+          <t>Google Trends US Search</t>
         </is>
       </c>
       <c r="H29" s="4" t="inlineStr">
         <is>
-          <t>So sánh âm thanh: 'Bật lọc tạp âm và nói chuyện giữa chợ ồn ào xem micro này xịn cỡ nào!'</t>
+          <t>Đặt câu hỏi trúng nỗi đau thường ngày: 'Tại sao không ai nói cho tôi biết món đồ này sớm hơn?!'</t>
         </is>
       </c>
       <c r="I29" s="4" t="inlineStr">
         <is>
-          <t>Học sinh, Gen Z làm bullet journal, Content Creator quay video TikTok / Vlog tại US.</t>
+          <t>Khách hàng mua sắm ngẫu hứng (Impulse Buyers) trên TikTok Shop US độ tuổi 18 - 45.</t>
         </is>
       </c>
       <c r="J29" s="5" t="inlineStr">
         <is>
-          <t>https://www.ebay.com/itm/371175182923</t>
+          <t>https://trends.google.com/trends/explore?geo=US&amp;q=jason%20bard%20yarmosky</t>
         </is>
       </c>
     </row>
@@ -1829,12 +1828,12 @@
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>YHG Wetsuit 3mm Neoprene Diving Tops Pants Men Women Swim Surfing Snorkeling AU735,508.38 VND</t>
+          <t>Spotlight DealCASIO WATCH CALCULATOR VINTAGE RETRO 80's CA-53W-1Z CA53 CA-53 AUSSIE SELLER838,137.46 VND1,470,465.00 VND</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>Kitchenware</t>
+          <t>All Trending Deals</t>
         </is>
       </c>
       <c r="D30" s="3" t="n">
@@ -1855,17 +1854,17 @@
       </c>
       <c r="H30" s="4" t="inlineStr">
         <is>
-          <t>Đặt câu hỏi trúng nỗi đau thường ngày: 'Tại sao không ai nói cho tôi biết món đồ này sớm hơn?!'</t>
+          <t>So sánh âm thanh: 'Bật lọc tạp âm và nói chuyện giữa chợ ồn ào xem micro này xịn cỡ nào!'</t>
         </is>
       </c>
       <c r="I30" s="4" t="inlineStr">
         <is>
-          <t>Khách hàng mua sắm ngẫu hứng (Impulse Buyers) trên TikTok Shop US độ tuổi 18 - 45.</t>
+          <t>Học sinh, Gen Z làm bullet journal, Content Creator quay video TikTok / Vlog tại US.</t>
         </is>
       </c>
       <c r="J30" s="5" t="inlineStr">
         <is>
-          <t>https://www.ebay.com/itm/157344373567</t>
+          <t>https://www.ebay.com/itm/370786315096</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1874,12 @@
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">True Temper Dynamic Gold TOUR ISSUE Limited Edition USA Golf Iron Shaft .355 Tip923,076.92 VND1,153,846.15 VND Previous </t>
+          <t>CASIO WATCH VINTAGE RETRO ORIGINAL F-91W-1 F91 F91W F-91 WARANTY666,169.38 VND734,772.69 VND | 9% offPrevious price: 734</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>Phones &amp; Electronics</t>
+          <t>All Trending Deals</t>
         </is>
       </c>
       <c r="D31" s="3" t="n">
@@ -1911,7 +1910,7 @@
       </c>
       <c r="J31" s="5" t="inlineStr">
         <is>
-          <t>https://www.ebay.com/itm/186144334386</t>
+          <t>https://www.ebay.com/itm/370816923572</t>
         </is>
       </c>
     </row>
@@ -1921,7 +1920,7 @@
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>Veto Pro Pac MP3 EVO Tool Pouch EVO System Electrician Networking Technician3,203,846.15 VND250x Altarkerzen weiß Rußfre</t>
+          <t>Cisco SFP-H10GB-CU3M 37-0961-03 SFP+ 10G Passive DAC Twinax Cable NEW897,435.90 VND</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
@@ -1957,7 +1956,7 @@
       </c>
       <c r="J32" s="5" t="inlineStr">
         <is>
-          <t>https://www.ebay.com/itm/366448929530</t>
+          <t>https://www.ebay.com/itm/157632501279</t>
         </is>
       </c>
     </row>
@@ -1967,7 +1966,7 @@
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>carron® PTFE Lotuseffekt extrem Versiegelung Duschwand Glas - Schutz gegen Kalk799,613.65 VND</t>
+          <t>NZG 1:18 Mercedes-Benz AMG G63 4x4² 2023 W463 Alloy Diecast Car Model6,641,025.64 VND9,025,641.03 VND Previous price: 9,</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
@@ -2003,7 +2002,7 @@
       </c>
       <c r="J33" s="5" t="inlineStr">
         <is>
-          <t>https://www.ebay.com/itm/224875974996</t>
+          <t>https://www.ebay.com/itm/298638189628</t>
         </is>
       </c>
     </row>
@@ -2013,12 +2012,13 @@
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>8x Kerze 15x8cm RAL Qualität / Stumpen von Kerzen Wiedemann / neue Farben 20251,306,780.15 VNDShop all 88Home &amp; Garden</t>
+          <t>Apple iPhone 16 Pro Max All Colours26,609,000.00 VND
+eBay Refurbished</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>Books, Magazines &amp; Audio</t>
+          <t>All Trending Deals</t>
         </is>
       </c>
       <c r="D34" s="3" t="n">
@@ -2039,17 +2039,17 @@
       </c>
       <c r="H34" s="4" t="inlineStr">
         <is>
-          <t>Đặt câu hỏi trúng nỗi đau thường ngày: 'Tại sao không ai nói cho tôi biết món đồ này sớm hơn?!'</t>
+          <t>Âm thanh bấm nút nhả cả búi lông chó rụng chỉ trong 1 giây: 'Mùa rụng lông không còn là ác mộng!'</t>
         </is>
       </c>
       <c r="I34" s="4" t="inlineStr">
         <is>
-          <t>Khách hàng mua sắm ngẫu hứng (Impulse Buyers) trên TikTok Shop US độ tuổi 18 - 45.</t>
+          <t>Hội những người 'nghiện' chó mèo (Dog/Cat Parents) tại US, chi tiêu mạnh tay cho thú cưng.</t>
         </is>
       </c>
       <c r="J34" s="5" t="inlineStr">
         <is>
-          <t>https://www.ebay.com/itm/354282537544</t>
+          <t>https://www.ebay.com/itm/257723314310</t>
         </is>
       </c>
     </row>
@@ -2059,12 +2059,12 @@
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>Nokia 6300 Silber Schwarz ohne Vertrag ohne Simlock Neu2,677,291.15 VNDNokia 6300 Schwarz ohne Vertrag ohne Simlock Neu2</t>
+          <t>Apple iPhone 16 Pro - 1TB - All Colours21,821,461.54 VNDeBay Refurbished</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>Tech &amp; Gadgets</t>
+          <t>All Trending Deals</t>
         </is>
       </c>
       <c r="D35" s="3" t="n">
@@ -2085,17 +2085,17 @@
       </c>
       <c r="H35" s="4" t="inlineStr">
         <is>
-          <t>Đặt câu hỏi trúng nỗi đau thường ngày: 'Tại sao không ai nói cho tôi biết món đồ này sớm hơn?!'</t>
+          <t>Âm thanh bấm nút nhả cả búi lông chó rụng chỉ trong 1 giây: 'Mùa rụng lông không còn là ác mộng!'</t>
         </is>
       </c>
       <c r="I35" s="4" t="inlineStr">
         <is>
-          <t>Khách hàng mua sắm ngẫu hứng (Impulse Buyers) trên TikTok Shop US độ tuổi 18 - 45.</t>
+          <t>Hội những người 'nghiện' chó mèo (Dog/Cat Parents) tại US, chi tiêu mạnh tay cho thú cưng.</t>
         </is>
       </c>
       <c r="J35" s="5" t="inlineStr">
         <is>
-          <t>https://www.ebay.com/itm/196061847535</t>
+          <t>https://www.ebay.com/itm/257132401723</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>Samsung GT-E1200I   Keystone 2  gt e1200 i Schwarz frei für alle Sim Karten Neu1,932,771.92 VND</t>
+          <t>Apple iPhone 16 Pro Max - 256GB 512GB 1TB- All Colours - Good25,013,153.85 VNDeBay Refurbished</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>Tech &amp; Gadgets</t>
+          <t>All Trending Deals</t>
         </is>
       </c>
       <c r="D36" s="3" t="n">
@@ -2131,17 +2131,17 @@
       </c>
       <c r="H36" s="4" t="inlineStr">
         <is>
-          <t>Đặt câu hỏi trúng nỗi đau thường ngày: 'Tại sao không ai nói cho tôi biết món đồ này sớm hơn?!'</t>
+          <t>Âm thanh bấm nút nhả cả búi lông chó rụng chỉ trong 1 giây: 'Mùa rụng lông không còn là ác mộng!'</t>
         </is>
       </c>
       <c r="I36" s="4" t="inlineStr">
         <is>
-          <t>Khách hàng mua sắm ngẫu hứng (Impulse Buyers) trên TikTok Shop US độ tuổi 18 - 45.</t>
+          <t>Hội những người 'nghiện' chó mèo (Dog/Cat Parents) tại US, chi tiêu mạnh tay cho thú cưng.</t>
         </is>
       </c>
       <c r="J36" s="5" t="inlineStr">
         <is>
-          <t>https://www.ebay.com/itm/205486315558</t>
+          <t>https://www.ebay.com/itm/298645175829</t>
         </is>
       </c>
     </row>
@@ -2151,12 +2151,12 @@
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>Nokia 3110 classic schwarz  ohne Simlock Frei für alle Sim-karten Neu2,081,675.77 VNDShop all 8Cell Phones</t>
+          <t>Lederweste Bikerweste Motorrad Kutte Biker Chopper Rockerweste mit Taschen2,679,971.42 VNDPremium Velour Fußmatten kompl</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>Tech &amp; Gadgets</t>
+          <t>All Trending Deals</t>
         </is>
       </c>
       <c r="D37" s="3" t="n">
@@ -2187,7 +2187,7 @@
       </c>
       <c r="J37" s="5" t="inlineStr">
         <is>
-          <t>https://www.ebay.com/itm/205486034658</t>
+          <t>https://www.ebay.com/itm/291771387455</t>
         </is>
       </c>
     </row>
@@ -2197,12 +2197,12 @@
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>ORIGINAL METZ Fernbedienung für Metz Blue MOC9001 MUC8001 MUC7001 MUC7111 NEU1,009,568.08 VNDErsatz Fernbedienung für LG</t>
+          <t>Birne 6000K H13 E-PRÜFZEICHEN 12V 60/55W E-Prüfzeichen XENON SUPER WHITE HALOGEN625,693.96 VND</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>Tech &amp; Gadgets</t>
+          <t>All Trending Deals</t>
         </is>
       </c>
       <c r="D38" s="3" t="n">
@@ -2233,7 +2233,7 @@
       </c>
       <c r="J38" s="5" t="inlineStr">
         <is>
-          <t>https://www.ebay.com/itm/393858887603</t>
+          <t>https://www.ebay.com/itm/133242757435</t>
         </is>
       </c>
     </row>
@@ -2243,12 +2243,12 @@
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>ORIGINAL SONY Fernbedienung RMT-TX102D KDL40R45XC KDL40R55XC KDL40R550C NEUWARE652,198.85 VND</t>
+          <t>500 Abarth Orig Competizione 595 695 Braking Kit Bremsscheiben Kit Va 305x28mm11,286,911.54 VNDShop all 90Parts &amp; Access</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>Tech &amp; Gadgets</t>
+          <t>Pet Supplies</t>
         </is>
       </c>
       <c r="D39" s="3" t="n">
@@ -2269,17 +2269,17 @@
       </c>
       <c r="H39" s="4" t="inlineStr">
         <is>
-          <t>Đặt câu hỏi trúng nỗi đau thường ngày: 'Tại sao không ai nói cho tôi biết món đồ này sớm hơn?!'</t>
+          <t>Âm thanh bấm nút nhả cả búi lông chó rụng chỉ trong 1 giây: 'Mùa rụng lông không còn là ác mộng!'</t>
         </is>
       </c>
       <c r="I39" s="4" t="inlineStr">
         <is>
-          <t>Khách hàng mua sắm ngẫu hứng (Impulse Buyers) trên TikTok Shop US độ tuổi 18 - 45.</t>
+          <t>Hội những người 'nghiện' chó mèo (Dog/Cat Parents) tại US, chi tiêu mạnh tay cho thú cưng.</t>
         </is>
       </c>
       <c r="J39" s="5" t="inlineStr">
         <is>
-          <t>https://www.ebay.com/itm/373982552937</t>
+          <t>https://www.ebay.com/itm/285765031424</t>
         </is>
       </c>
     </row>
@@ -2289,12 +2289,12 @@
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>NEU ORIGINAL SAMSUNG Fernbedienung für UE40ES6100WXZG UE40ES6100 UE40ES6100W652,198.85 VNDShop all 7TV, Video &amp; Home Aud</t>
+          <t>CASIO WATCH SWIMMING 100 METRES WATER RESISTANT W-800 W-800H-1AV W8001,025,371.15 VND1,102,618.85 VND | 7% offPrevious p</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>Tech &amp; Gadgets</t>
+          <t>All Trending Deals</t>
         </is>
       </c>
       <c r="D40" s="3" t="n">
@@ -2315,17 +2315,17 @@
       </c>
       <c r="H40" s="4" t="inlineStr">
         <is>
-          <t>Đặt câu hỏi trúng nỗi đau thường ngày: 'Tại sao không ai nói cho tôi biết món đồ này sớm hơn?!'</t>
+          <t>So sánh âm thanh: 'Bật lọc tạp âm và nói chuyện giữa chợ ồn ào xem micro này xịn cỡ nào!'</t>
         </is>
       </c>
       <c r="I40" s="4" t="inlineStr">
         <is>
-          <t>Khách hàng mua sắm ngẫu hứng (Impulse Buyers) trên TikTok Shop US độ tuổi 18 - 45.</t>
+          <t>Học sinh, Gen Z làm bullet journal, Content Creator quay video TikTok / Vlog tại US.</t>
         </is>
       </c>
       <c r="J40" s="5" t="inlineStr">
         <is>
-          <t>https://www.ebay.com/itm/392224499242</t>
+          <t>https://www.ebay.com/itm/371175182923</t>
         </is>
       </c>
     </row>
@@ -2335,12 +2335,12 @@
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>Sony Playstation 5 Controller-TMR Sticks-Top Zustand-alle Farben2,380,972.50 VNDWii - Nintendo Wii Konsole Weiß mit Remo</t>
+          <t>YHG Wetsuit 3mm Neoprene Diving Tops Pants Men Women Swim Surfing Snorkeling AU735,508.38 VND</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>Tech &amp; Gadgets</t>
+          <t>Kitchenware</t>
         </is>
       </c>
       <c r="D41" s="3" t="n">
@@ -2371,7 +2371,7 @@
       </c>
       <c r="J41" s="5" t="inlineStr">
         <is>
-          <t>https://www.ebay.com/itm/365967503388</t>
+          <t>https://www.ebay.com/itm/157344373567</t>
         </is>
       </c>
     </row>
@@ -2381,12 +2381,12 @@
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>SW - Nintendo Switch-Konsole Neon-Rot/Neon-Blau (guter Zustand)5,656,857.12 VNDeBay Refurbished</t>
+          <t xml:space="preserve">True Temper Dynamic Gold TOUR ISSUE Limited Edition USA Golf Iron Shaft .355 Tip923,076.92 VND1,153,846.15 VND Previous </t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>Tech &amp; Gadgets</t>
+          <t>Phones &amp; Electronics</t>
         </is>
       </c>
       <c r="D42" s="3" t="n">
@@ -2407,17 +2407,17 @@
       </c>
       <c r="H42" s="4" t="inlineStr">
         <is>
-          <t>Âm thanh bấm nút nhả cả búi lông chó rụng chỉ trong 1 giây: 'Mùa rụng lông không còn là ác mộng!'</t>
+          <t>So sánh âm thanh: 'Bật lọc tạp âm và nói chuyện giữa chợ ồn ào xem micro này xịn cỡ nào!'</t>
         </is>
       </c>
       <c r="I42" s="4" t="inlineStr">
         <is>
-          <t>Hội những người 'nghiện' chó mèo (Dog/Cat Parents) tại US, chi tiêu mạnh tay cho thú cưng.</t>
+          <t>Học sinh, Gen Z làm bullet journal, Content Creator quay video TikTok / Vlog tại US.</t>
         </is>
       </c>
       <c r="J42" s="5" t="inlineStr">
         <is>
-          <t>https://www.ebay.com/itm/187974010368</t>
+          <t>https://www.ebay.com/itm/186144334386</t>
         </is>
       </c>
     </row>
@@ -2427,12 +2427,12 @@
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>Nintendo Switch Catan Console edition (Code in aBox) NEU565,536.81 VNDShop all 27Video Games &amp; Consoles</t>
+          <t>Veto Pro Pac MP3 EVO Tool Pouch EVO System Electrician Networking Technician3,203,846.15 VND24x Kerzen 80x40mm/8x4cm 1.W</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>Pet Supplies</t>
+          <t>All Trending Deals</t>
         </is>
       </c>
       <c r="D43" s="3" t="n">
@@ -2453,17 +2453,17 @@
       </c>
       <c r="H43" s="4" t="inlineStr">
         <is>
-          <t>Âm thanh bấm nút nhả cả búi lông chó rụng chỉ trong 1 giây: 'Mùa rụng lông không còn là ác mộng!'</t>
+          <t>Đặt câu hỏi trúng nỗi đau thường ngày: 'Tại sao không ai nói cho tôi biết món đồ này sớm hơn?!'</t>
         </is>
       </c>
       <c r="I43" s="4" t="inlineStr">
         <is>
-          <t>Hội những người 'nghiện' chó mèo (Dog/Cat Parents) tại US, chi tiêu mạnh tay cho thú cưng.</t>
+          <t>Khách hàng mua sắm ngẫu hứng (Impulse Buyers) trên TikTok Shop US độ tuổi 18 - 45.</t>
         </is>
       </c>
       <c r="J43" s="5" t="inlineStr">
         <is>
-          <t>https://www.ebay.com/itm/356767412423</t>
+          <t>https://www.ebay.com/itm/366448929530</t>
         </is>
       </c>
     </row>
@@ -2473,12 +2473,12 @@
       </c>
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Handy Tasche für Xiaomi 14T Pro Schutzhülle Book Case Kartenfach NEU Handy Hülle893,125.27 VNDFree shippingHandy Tasche </t>
+          <t>Bankerlampe Tischleuchte Bürolampe Jugendstil Schreibtischlampe weiss silber neu2,024,794.50 VND</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>Books, Magazines &amp; Audio</t>
+          <t>All Trending Deals</t>
         </is>
       </c>
       <c r="D44" s="3" t="n">
@@ -2509,7 +2509,7 @@
       </c>
       <c r="J44" s="5" t="inlineStr">
         <is>
-          <t>https://www.ebay.com/itm/395963882049</t>
+          <t>https://www.ebay.com/itm/194675348414</t>
         </is>
       </c>
     </row>
@@ -2519,12 +2519,12 @@
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>Handy Umhängetasche für Samsung Galaxy A55 5G Gürtel Tasche Etui Gurt Handyhülle890,445.00 VNDFree shipping</t>
+          <t>3 Paar Zedernholzsohlen - Zedernsohlen - Einlegesohlen aus Holz890,445.00 VNDAlmost goneShop all 88Home &amp; Garden</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>Tech &amp; Gadgets</t>
+          <t>All Trending Deals</t>
         </is>
       </c>
       <c r="D45" s="3" t="n">
@@ -2555,7 +2555,7 @@
       </c>
       <c r="J45" s="5" t="inlineStr">
         <is>
-          <t>https://www.ebay.com/itm/395332607060</t>
+          <t>https://www.ebay.com/itm/276726430861</t>
         </is>
       </c>
     </row>
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t>Handy Gürteltasche für Apple iPhone 16 Pro Handytasche Holster Gürtel Schlaufe893,125.27 VNDFree shippingShop all 33Phon</t>
+          <t xml:space="preserve">Opis PushMeFon mobile - Retro 2G Tischhandy Mobil-Telefon mit Metallklingel3,841,719.23 VNDNokia 6700 Classic 5MP Handy </t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
@@ -2601,7 +2601,7 @@
       </c>
       <c r="J46" s="5" t="inlineStr">
         <is>
-          <t>https://www.ebay.com/itm/204999038014</t>
+          <t>https://www.ebay.com/itm/324428697438</t>
         </is>
       </c>
     </row>
@@ -2611,7 +2611,7 @@
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>Original Canon PGI-570 CLI-571 Set (5 Patronen) KEINE SETUP - ECHTE ORIGINALE1,845,514.27 VNDTinte für Canon iPF6400 iPF</t>
+          <t>Nokia C2-01  (Ohne Simlock)  Frei für alle Sim-Karten Neu schwarz2,379,483.46 VND</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
@@ -2647,7 +2647,7 @@
       </c>
       <c r="J47" s="5" t="inlineStr">
         <is>
-          <t>https://www.ebay.com/itm/296479378739</t>
+          <t>https://www.ebay.com/itm/202995946783</t>
         </is>
       </c>
     </row>
@@ -2657,7 +2657,7 @@
       </c>
       <c r="B48" s="4" t="inlineStr">
         <is>
-          <t>Original Brother LC1220 MultiPack SparPack ValuePack alle Farben 4 Patronen o.V.1,637,048.88 VND</t>
+          <t>Opis 60s mobile - Das  Retro 2G Tischhandy mit Wählscheibe &amp; Metallklingel3,841,719.23 VNDShop all 8Cell Phones</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
@@ -2693,7 +2693,7 @@
       </c>
       <c r="J48" s="5" t="inlineStr">
         <is>
-          <t>https://www.ebay.com/itm/294371599719</t>
+          <t>https://www.ebay.com/itm/324427595994</t>
         </is>
       </c>
     </row>
@@ -2703,7 +2703,7 @@
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>JK-B2A8S20P Smart BMS 4-8S 200A Active Balance 2A BMS LiFePo4 Li-ion LTO Battery1,766,923.08 VND1,920,512.82 VND | 8% of</t>
+          <t>NEUWARE ORIGINAL METZ Fernbedienung RM18 RM 18 SCHNELLER VERSAND2,054,873.08 VNDAlmost goneORIGINAL SONY Fernbedienung R</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
@@ -2739,7 +2739,7 @@
       </c>
       <c r="J49" s="5" t="inlineStr">
         <is>
-          <t>https://www.ebay.com/itm/236864278279</t>
+          <t>https://www.ebay.com/itm/392040705358</t>
         </is>
       </c>
     </row>
@@ -2749,7 +2749,7 @@
       </c>
       <c r="B50" s="4" t="inlineStr">
         <is>
-          <t>Ersatz Fernbedienung für LG Magic Smart TV AN-MR300 AKB74495301 AKB74855401 NEU741,541.15 VND</t>
+          <t>ORIGINAL METZ Fernbedienung für Metz Blue MOC9001 MUC8001 MUC7001 MUC7111 NEU1,009,568.08 VND</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
@@ -2785,7 +2785,7 @@
       </c>
       <c r="J50" s="5" t="inlineStr">
         <is>
-          <t>https://www.ebay.com/itm/375664903887</t>
+          <t>https://www.ebay.com/itm/393858887603</t>
         </is>
       </c>
     </row>
@@ -2795,7 +2795,7 @@
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>Leder Schutzhülle für Samsung Galaxy Tab S10 Ultra Tablet Cover Smart Stand Case855,303.69 VNDAlmost goneLeder Cover  Ap</t>
+          <t>NEU ORIGINAL SAMSUNG Fernbedienung für UE40ES6100WXZG UE40ES6100 UE40ES6100W652,198.85 VNDShop all 7TV, Video &amp; Home Aud</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="J51" s="5" t="inlineStr">
         <is>
-          <t>https://www.ebay.com/itm/305900488577</t>
+          <t>https://www.ebay.com/itm/392224499242</t>
         </is>
       </c>
     </row>
@@ -2841,7 +2841,7 @@
       </c>
       <c r="B52" s="4" t="inlineStr">
         <is>
-          <t>Leder Cover für Apple iPad Pro 12.9" 2021 Tablet Schutzhülle Case Tasche schwarz855,303.69 VND</t>
+          <t>Sony Playstation 5 Controller-TMR Sticks-Top Zustand-alle Farben2,380,972.50 VNDWii - Nintendo Wii Konsole Weiß mit Remo</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
@@ -2877,7 +2877,7 @@
       </c>
       <c r="J52" s="5" t="inlineStr">
         <is>
-          <t>https://www.ebay.com/itm/234489000207</t>
+          <t>https://www.ebay.com/itm/365967503388</t>
         </is>
       </c>
     </row>
@@ -2887,7 +2887,7 @@
       </c>
       <c r="B53" s="4" t="inlineStr">
         <is>
-          <t>Schutzhülle Leder Apple iPad Air ( 13" M2 ) ab 2024 Tablet Cover Stand Case Etui855,303.69 VNDShop all 22Computer Access</t>
+          <t>SW - Nintendo Switch-Konsole Neon-Rot/Neon-Blau (guter Zustand)5,656,857.12 VNDeBay Refurbished</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
@@ -2913,17 +2913,17 @@
       </c>
       <c r="H53" s="4" t="inlineStr">
         <is>
-          <t>Đặt câu hỏi trúng nỗi đau thường ngày: 'Tại sao không ai nói cho tôi biết món đồ này sớm hơn?!'</t>
+          <t>Âm thanh bấm nút nhả cả búi lông chó rụng chỉ trong 1 giây: 'Mùa rụng lông không còn là ác mộng!'</t>
         </is>
       </c>
       <c r="I53" s="4" t="inlineStr">
         <is>
-          <t>Khách hàng mua sắm ngẫu hứng (Impulse Buyers) trên TikTok Shop US độ tuổi 18 - 45.</t>
+          <t>Hội những người 'nghiện' chó mèo (Dog/Cat Parents) tại US, chi tiêu mạnh tay cho thú cưng.</t>
         </is>
       </c>
       <c r="J53" s="5" t="inlineStr">
         <is>
-          <t>https://www.ebay.com/itm/226323687048</t>
+          <t>https://www.ebay.com/itm/187974010368</t>
         </is>
       </c>
     </row>
@@ -2933,12 +2933,12 @@
       </c>
       <c r="B54" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Display Für Samsung A55 / A556 5G OLED Bildschirm LCD mit  Rahmen + Tools Neu1,932,771.92 VNDDisplay für Samsung A53 5G </t>
+          <t>PlayStation 3 MINECRAFT Deutsch625,098.35 VNDShop all 27Video Games &amp; Consoles</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>Menswear &amp; Underwear</t>
+          <t>Tech &amp; Gadgets</t>
         </is>
       </c>
       <c r="D54" s="3" t="n">
@@ -2969,7 +2969,7 @@
       </c>
       <c r="J54" s="5" t="inlineStr">
         <is>
-          <t>https://www.ebay.com/itm/306193635449</t>
+          <t>https://www.ebay.com/itm/351153701373</t>
         </is>
       </c>
     </row>
@@ -2979,7 +2979,7 @@
       </c>
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t>Display für Samsung A51 A515F HD LCD Touch Screen Glas + Kleber &amp; Tools Neu741,541.15 VND</t>
+          <t>Personalisierte Schutzhülle für iPhone Handytasche Hülle eigenes Foto Bild Druck744,221.42 VNDHandy Tasche für Samsung G</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
@@ -3015,7 +3015,7 @@
       </c>
       <c r="J55" s="5" t="inlineStr">
         <is>
-          <t>https://www.ebay.com/itm/305047092563</t>
+          <t>https://www.ebay.com/itm/272724943549</t>
         </is>
       </c>
     </row>
@@ -3025,12 +3025,12 @@
       </c>
       <c r="B56" s="4" t="inlineStr">
         <is>
-          <t>Display für Samsung A53 5G A536 OLED AMOLED LCD Bildschirm Touch Screen + Kleber1,188,252.69 VNDShop all 48More Computer</t>
+          <t>Handy Tasche für Samsung Galaxy A55 5G Schutzhülle Book Case Dünn Handy Hülle774,002.19 VNDFree shipping</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>Tech &amp; Gadgets</t>
+          <t>Books, Magazines &amp; Audio</t>
         </is>
       </c>
       <c r="D56" s="3" t="n">
@@ -3061,7 +3061,7 @@
       </c>
       <c r="J56" s="5" t="inlineStr">
         <is>
-          <t>https://www.ebay.com/itm/305041451782</t>
+          <t>https://www.ebay.com/itm/285825152658</t>
         </is>
       </c>
     </row>
@@ -3071,12 +3071,12 @@
       </c>
       <c r="B57" s="4" t="inlineStr">
         <is>
-          <t>2 1/2ct Black Diamond Screw Back Studs Womens Earrings 14K White Gold8,546,666.67 VND26,805,641.03 VND Previous price: 2</t>
+          <t xml:space="preserve">Handy Hülle mit Band für Samsung Galaxy A55 5G Handy Kette Case zum Umhängen714,440.65 VNDFree shippingShop all 33Phone </t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>Jewelry Accessories &amp; Derivatives</t>
+          <t>Tech &amp; Gadgets</t>
         </is>
       </c>
       <c r="D57" s="3" t="n">
@@ -3107,7 +3107,7 @@
       </c>
       <c r="J57" s="5" t="inlineStr">
         <is>
-          <t>https://www.ebay.com/itm/355504570491</t>
+          <t>https://www.ebay.com/itm/204763504739</t>
         </is>
       </c>
     </row>
@@ -3117,12 +3117,12 @@
       </c>
       <c r="B58" s="4" t="inlineStr">
         <is>
-          <t>1/4 - 2 Ct T.W. Natural Diamond Solitaire Pendant in 14k White or Yellow Gold4,358,717.95 VND</t>
+          <t>Original Tinte EPSON Stylus Pro 9800 7800 / T6031 T6032 T6034 -T6039 T603B T603C2,650,488.46 VNDOriginal EPSON Tinte Sty</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>Books, Magazines &amp; Audio</t>
+          <t>Tech &amp; Gadgets</t>
         </is>
       </c>
       <c r="D58" s="3" t="n">
@@ -3153,7 +3153,7 @@
       </c>
       <c r="J58" s="5" t="inlineStr">
         <is>
-          <t>https://www.ebay.com/itm/353815614085</t>
+          <t>https://www.ebay.com/itm/222635235522</t>
         </is>
       </c>
     </row>
@@ -3163,12 +3163,12 @@
       </c>
       <c r="B59" s="4" t="inlineStr">
         <is>
-          <t>Panzerkette Halskette 5 mm Echt 750er Gold 18K vergoldet Damen Herren K1807842,795.77 VND</t>
+          <t>Tinte für Canon iPF6400 iPF6400S iPF6450 / PFI-206MBK 206BK 206GY 206C 206M 206Y2,677,291.15 VND</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>Kitchenware</t>
+          <t>Tech &amp; Gadgets</t>
         </is>
       </c>
       <c r="D59" s="3" t="n">
@@ -3199,7 +3199,7 @@
       </c>
       <c r="J59" s="5" t="inlineStr">
         <is>
-          <t>https://www.ebay.com/itm/115705706803</t>
+          <t>https://www.ebay.com/itm/352159188925</t>
         </is>
       </c>
     </row>
@@ -3209,12 +3209,12 @@
       </c>
       <c r="B60" s="4" t="inlineStr">
         <is>
-          <t>Herz Anhänger Kette Zirkonia schwarz 750 Gold 18 Karat vergoldet Damen A3047S891,934.04 VNDAlmost goneSet Damenkette Sch</t>
+          <t>JK-B2A8S20P Smart BMS 4-8S 200A Active Balance 2A BMS LiFePo4 Li-ion LTO Battery1,766,923.08 VND1,920,512.82 VND | 8% of</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>Menswear &amp; Underwear</t>
+          <t>Tech &amp; Gadgets</t>
         </is>
       </c>
       <c r="D60" s="3" t="n">
@@ -3245,7 +3245,7 @@
       </c>
       <c r="J60" s="5" t="inlineStr">
         <is>
-          <t>https://www.ebay.com/itm/332636296199</t>
+          <t>https://www.ebay.com/itm/236864278279</t>
         </is>
       </c>
     </row>
@@ -3255,12 +3255,12 @@
       </c>
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t>300mg Benfotiamine 3 x 120 Capsules Fat Soluble Thiamine Vitamin B1 Supplement991,345.38 VNDFree shippingJod Kapseln aus</t>
+          <t>ORIGINAL SONY Fernbedienung RMT-TX102D KDL40R45XC KDL40R55XC KDL40R550C NEUWARE652,198.85 VND</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>Menswear &amp; Underwear</t>
+          <t>Tech &amp; Gadgets</t>
         </is>
       </c>
       <c r="D61" s="3" t="n">
@@ -3291,7 +3291,7 @@
       </c>
       <c r="J61" s="5" t="inlineStr">
         <is>
-          <t>https://www.ebay.com/itm/357242424467</t>
+          <t>https://www.ebay.com/itm/373982552937</t>
         </is>
       </c>
     </row>
@@ -3301,12 +3301,12 @@
       </c>
       <c r="B62" s="4" t="inlineStr">
         <is>
-          <t>Omega 3 Kapseln - DHA &amp; EPA -  vegan - hochdosiert - Vitamineule744,221.42 VNDFree shipping</t>
+          <t>Für Xiaomi Redmi Pad Pro 12.1 Kontrast Robot Silikon Hybrid Hülle Blau / Schwarz713,249.42 VNDAlmost goneLeder Tablet Co</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>Health</t>
+          <t>Tech &amp; Gadgets</t>
         </is>
       </c>
       <c r="D62" s="3" t="n">
@@ -3337,7 +3337,7 @@
       </c>
       <c r="J62" s="5" t="inlineStr">
         <is>
-          <t>https://www.ebay.com/itm/127173608481</t>
+          <t>https://www.ebay.com/itm/176622603332</t>
         </is>
       </c>
     </row>
@@ -3347,12 +3347,12 @@
       </c>
       <c r="B63" s="4" t="inlineStr">
         <is>
-          <t>Bockshornklee Kapseln mit 500 mg 4:1 Extrakt - vegan - Vitamineule595,317.58 VNDFree shippingShop all 31Beauty</t>
+          <t>Leder Tablet Cover Samsung Galaxy Tab S7 FE SM-T733/T736 Stand Case Schutzhülle676,619.08 VND</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>Health</t>
+          <t>Tech &amp; Gadgets</t>
         </is>
       </c>
       <c r="D63" s="3" t="n">
@@ -3383,7 +3383,7 @@
       </c>
       <c r="J63" s="5" t="inlineStr">
         <is>
-          <t>https://www.ebay.com/itm/125306598648</t>
+          <t>https://www.ebay.com/itm/304338719356</t>
         </is>
       </c>
     </row>
@@ -3393,12 +3393,12 @@
       </c>
       <c r="B64" s="4" t="inlineStr">
         <is>
-          <t>Lonsdale Navy Blue Baseball Cap Hat Embroidered Logo Adjustable Kappe Mütze741,541.15 VND</t>
+          <t>Premium Leder Cover Apple iPad Pro 12.9"  2015-17 Tablet Schutzhülle Case Tasche729,033.23 VND828,501.00 VND | 12% offPr</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>Fashion &amp; Apparel</t>
+          <t>Tech &amp; Gadgets</t>
         </is>
       </c>
       <c r="D64" s="3" t="n">
@@ -3429,7 +3429,7 @@
       </c>
       <c r="J64" s="5" t="inlineStr">
         <is>
-          <t>https://www.ebay.com/itm/296106350225</t>
+          <t>https://www.ebay.com/itm/234304242705</t>
         </is>
       </c>
     </row>
@@ -3439,12 +3439,12 @@
       </c>
       <c r="B65" s="4" t="inlineStr">
         <is>
-          <t>Puma Speedcat OG team royal white Schuhe Sneaker Motorsport F1 398846-183,275,586.81 VNDShop all 12Men's Shoes &amp; Accesso</t>
+          <t xml:space="preserve">Display für Samsung A53 5G A536 OLED AMOLED LCD Bildschirm Touch Screen + Kleber1,188,252.69 VNDDisplay für Samsung A53 </t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>Pet Supplies</t>
+          <t>Tech &amp; Gadgets</t>
         </is>
       </c>
       <c r="D65" s="3" t="n">
@@ -3465,17 +3465,17 @@
       </c>
       <c r="H65" s="4" t="inlineStr">
         <is>
-          <t>Âm thanh bấm nút nhả cả búi lông chó rụng chỉ trong 1 giây: 'Mùa rụng lông không còn là ác mộng!'</t>
+          <t>Đặt câu hỏi trúng nỗi đau thường ngày: 'Tại sao không ai nói cho tôi biết món đồ này sớm hơn?!'</t>
         </is>
       </c>
       <c r="I65" s="4" t="inlineStr">
         <is>
-          <t>Hội những người 'nghiện' chó mèo (Dog/Cat Parents) tại US, chi tiêu mạnh tay cho thú cưng.</t>
+          <t>Khách hàng mua sắm ngẫu hứng (Impulse Buyers) trên TikTok Shop US độ tuổi 18 - 45.</t>
         </is>
       </c>
       <c r="J65" s="5" t="inlineStr">
         <is>
-          <t>https://www.ebay.com/itm/156805882161</t>
+          <t>https://www.ebay.com/itm/305041451782</t>
         </is>
       </c>
     </row>
@@ -3485,12 +3485,12 @@
       </c>
       <c r="B66" s="4" t="inlineStr">
         <is>
-          <t>Bikerweste Lederweste Rockerweste Lederkutte Kutte Chopperweste Clubweste2,382,163.73 VND</t>
+          <t>Display für Samsung A51 A515F HD LCD Touch Screen Glas + Kleber &amp; Tools Neu741,541.15 VND</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>Fashion &amp; Apparel</t>
+          <t>Tech &amp; Gadgets</t>
         </is>
       </c>
       <c r="D66" s="3" t="n">
@@ -3521,7 +3521,7 @@
       </c>
       <c r="J66" s="5" t="inlineStr">
         <is>
-          <t>https://www.ebay.com/itm/303349551958</t>
+          <t>https://www.ebay.com/itm/305047092563</t>
         </is>
       </c>
     </row>
@@ -3531,7 +3531,7 @@
       </c>
       <c r="B67" s="4" t="inlineStr">
         <is>
-          <t>Schwarze Lederkutte mit blau Umrandungen Kutte Biker Motorrad Rocker Clubweste2,679,971.42 VNDShop all 68Men's Clothing</t>
+          <t>Display Für Samsung A55 / A556 5G OLED Bildschirm LCD mit  Rahmen + Tools Neu1,932,771.92 VNDShop all 48More Computer Ac</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
@@ -3567,7 +3567,7 @@
       </c>
       <c r="J67" s="5" t="inlineStr">
         <is>
-          <t>https://www.ebay.com/itm/301897675077</t>
+          <t>https://www.ebay.com/itm/306193635449</t>
         </is>
       </c>
     </row>
@@ -3577,12 +3577,12 @@
       </c>
       <c r="B68" s="4" t="inlineStr">
         <is>
-          <t>LA PERLA Dessous - Italienischer Spitzen-BH in bordeauxrot - Luxus-Lingerie1,191,230.77 VNDGlamory Garter Belt Strumpfha</t>
+          <t>2 1/2ct Black Diamond Screw Back Studs Womens Earrings 14K White Gold8,546,666.67 VND26,805,641.03 VND Previous price: 2</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
-          <t>Fashion &amp; Apparel</t>
+          <t>Jewelry Accessories &amp; Derivatives</t>
         </is>
       </c>
       <c r="D68" s="3" t="n">
@@ -3613,7 +3613,7 @@
       </c>
       <c r="J68" s="5" t="inlineStr">
         <is>
-          <t>https://www.ebay.com/itm/156073236516</t>
+          <t>https://www.ebay.com/itm/355504570491</t>
         </is>
       </c>
     </row>
@@ -3623,12 +3623,12 @@
       </c>
       <c r="B69" s="4" t="inlineStr">
         <is>
-          <t>Luxuriöses Push-Up-Dessous-Set mit Animal Muster – B-Cup, BH High-Waist Slip744,221.42 VND</t>
+          <t>1/4 - 2 Ct T.W. Natural Diamond Solitaire Pendant in 14k White or Yellow Gold4,358,717.95 VND</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>Kitchenware</t>
+          <t>Books, Magazines &amp; Audio</t>
         </is>
       </c>
       <c r="D69" s="3" t="n">
@@ -3649,17 +3649,17 @@
       </c>
       <c r="H69" s="4" t="inlineStr">
         <is>
-          <t>Before &amp; After cận cảnh lỗ chân lông: 'Dừng ngay nếu bạn vẫn đang nặn mụn hoặc dùng tẩy tế bào chết hạt to!'</t>
+          <t>Đặt câu hỏi trúng nỗi đau thường ngày: 'Tại sao không ai nói cho tôi biết món đồ này sớm hơn?!'</t>
         </is>
       </c>
       <c r="I69" s="4" t="inlineStr">
         <is>
-          <t>Gen Z &amp; Millennials (18-34 tuổi), Chăm sóc da mụn, tín đồ Skincare &amp; 'Clean Girl' aesthetic US.</t>
+          <t>Khách hàng mua sắm ngẫu hứng (Impulse Buyers) trên TikTok Shop US độ tuổi 18 - 45.</t>
         </is>
       </c>
       <c r="J69" s="5" t="inlineStr">
         <is>
-          <t>https://www.ebay.com/itm/317440894200</t>
+          <t>https://www.ebay.com/itm/353815614085</t>
         </is>
       </c>
     </row>
@@ -3669,12 +3669,12 @@
       </c>
       <c r="B70" s="4" t="inlineStr">
         <is>
-          <t>Noir Handmade - Hautenger Wetlook Strapsgürtel transparent schwarz - S-3XL1,664,745.00 VNDShop all 35Women's Clothing</t>
+          <t>925 Sterlingsilber Silber Anhänger DAVIDSTERN Hexagramm Charm Kette 20x20mm 50661,780,592.19 VNDAlmost goneShop all 22Fi</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
         <is>
-          <t>Menswear &amp; Underwear</t>
+          <t>Fashion &amp; Apparel</t>
         </is>
       </c>
       <c r="D70" s="3" t="n">
@@ -3705,7 +3705,7 @@
       </c>
       <c r="J70" s="5" t="inlineStr">
         <is>
-          <t>https://www.ebay.com/itm/372295070125</t>
+          <t>https://www.ebay.com/itm/271569399778</t>
         </is>
       </c>
     </row>
@@ -3715,12 +3715,12 @@
       </c>
       <c r="B71" s="4" t="inlineStr">
         <is>
-          <t>Breitling TransOcean Chrono Quartz 40mm Iced 13ct Diamond Black Dial A530401166,641,025.64 VNDAlmost gone</t>
+          <t>Panzerkette 4 mm Halskette Echt 750er Gold 18Karat vergoldet Damen Herren K1808906,824.42 VND</t>
         </is>
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>Fashion &amp; Apparel</t>
+          <t>Kitchenware</t>
         </is>
       </c>
       <c r="D71" s="3" t="n">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="J71" s="5" t="inlineStr">
         <is>
-          <t>https://www.ebay.com/itm/146360754668</t>
+          <t>https://www.ebay.com/itm/125770552175</t>
         </is>
       </c>
     </row>
@@ -3761,43 +3761,43 @@
       </c>
       <c r="B72" s="4" t="inlineStr">
         <is>
-          <t>Wireless Magnetic Lavalier Lapel Microphone for iPhone &amp; Type-C</t>
+          <t>Set Damenkette Schlüssel Anhänger Zirkonia weiß 750 Gold 18Karat vergoldet A1127595,615.38 VNDAlmost goneHerz Anhänger K</t>
         </is>
       </c>
       <c r="C72" s="4" t="inlineStr">
         <is>
-          <t>Phones &amp; Electronics</t>
+          <t>Menswear &amp; Underwear</t>
         </is>
       </c>
       <c r="D72" s="3" t="n">
-        <v>90</v>
+        <v>76</v>
       </c>
       <c r="E72" s="3" t="n">
-        <v>45</v>
+        <v>72</v>
       </c>
       <c r="F72" s="3" t="inlineStr">
         <is>
-          <t>$16.99 - $24.99</t>
+          <t>$19.99</t>
         </is>
       </c>
       <c r="G72" s="4" t="inlineStr">
         <is>
-          <t>TikTok Shop, TikTok Viral 24h</t>
+          <t>eBay US Deals</t>
         </is>
       </c>
       <c r="H72" s="4" t="inlineStr">
         <is>
-          <t>Audio Contrast Hook: Whisper in crowded room with noise cancellation toggle ON vs OFF</t>
+          <t>Đặt câu hỏi trúng nỗi đau thường ngày: 'Tại sao không ai nói cho tôi biết món đồ này sớm hơn?!'</t>
         </is>
       </c>
       <c r="I72" s="4" t="inlineStr">
         <is>
-          <t>Học sinh, Gen Z làm bullet journal, Content Creator quay video TikTok / Vlog tại US.</t>
+          <t>Khách hàng mua sắm ngẫu hứng (Impulse Buyers) trên TikTok Shop US độ tuổi 18 - 45.</t>
         </is>
       </c>
       <c r="J72" s="5" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/tag/wirelessmicrophone</t>
+          <t>https://www.ebay.com/itm/125770529088</t>
         </is>
       </c>
     </row>
@@ -3807,28 +3807,28 @@
       </c>
       <c r="B73" s="4" t="inlineStr">
         <is>
-          <t>milwaukee brewers baseball</t>
+          <t>300mg Benfotiamine 3 x 120 Capsules Fat Soluble Thiamine Vitamin B1 Supplement991,345.38 VNDFree shippingLöwenzahn Kapse</t>
         </is>
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
-          <t>General Trend</t>
+          <t>Menswear &amp; Underwear</t>
         </is>
       </c>
       <c r="D73" s="3" t="n">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="E73" s="3" t="n">
-        <v>45</v>
+        <v>72</v>
       </c>
       <c r="F73" s="3" t="inlineStr">
         <is>
-          <t>$25.00</t>
+          <t>$19.99</t>
         </is>
       </c>
       <c r="G73" s="4" t="inlineStr">
         <is>
-          <t>Google Trends US Search</t>
+          <t>eBay US Deals</t>
         </is>
       </c>
       <c r="H73" s="4" t="inlineStr">
@@ -3843,7 +3843,7 @@
       </c>
       <c r="J73" s="5" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?geo=US&amp;q=milwaukee%20brewers%20baseball</t>
+          <t>https://www.ebay.com/itm/357242424467</t>
         </is>
       </c>
     </row>
@@ -3853,43 +3853,43 @@
       </c>
       <c r="B74" s="4" t="inlineStr">
         <is>
-          <t>swimming</t>
+          <t>Curcuma Extrakt Kapseln - hochdosiert - 350 mg Curcuminoide - Vitamineule744,221.42 VNDFree shipping</t>
         </is>
       </c>
       <c r="C74" s="4" t="inlineStr">
         <is>
-          <t>DIY, Craft &amp; POD</t>
+          <t>Health</t>
         </is>
       </c>
       <c r="D74" s="3" t="n">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="E74" s="3" t="n">
-        <v>45</v>
+        <v>72</v>
       </c>
       <c r="F74" s="3" t="inlineStr">
         <is>
-          <t>$25.00</t>
+          <t>$19.99</t>
         </is>
       </c>
       <c r="G74" s="4" t="inlineStr">
         <is>
-          <t>Google Trends US Search</t>
+          <t>eBay US Deals</t>
         </is>
       </c>
       <c r="H74" s="4" t="inlineStr">
         <is>
-          <t>Quá trình máy khắc laser tên khách hàng lên gỗ/kim loại: 'Làm món quà độc nhất vô nhị tặng mẹ...'</t>
+          <t>Đặt câu hỏi trúng nỗi đau thường ngày: 'Tại sao không ai nói cho tôi biết món đồ này sớm hơn?!'</t>
         </is>
       </c>
       <c r="I74" s="4" t="inlineStr">
         <is>
-          <t>Người tìm quà tặng sinh nhật, kỷ niệm, Mother's Day, quà tân gia ý nghĩa quanh năm.</t>
+          <t>Khách hàng mua sắm ngẫu hứng (Impulse Buyers) trên TikTok Shop US độ tuổi 18 - 45.</t>
         </is>
       </c>
       <c r="J74" s="5" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?geo=US&amp;q=swimming</t>
+          <t>https://www.ebay.com/itm/123839173201</t>
         </is>
       </c>
     </row>
@@ -3899,28 +3899,28 @@
       </c>
       <c r="B75" s="4" t="inlineStr">
         <is>
-          <t>fitness</t>
+          <t>Jod Kapseln aus Bio Kelp / Tabletten - 400µg aus Bio Kelp Extrakt - Vitamineule774,002.19 VNDFree shippingShop all 31Bea</t>
         </is>
       </c>
       <c r="C75" s="4" t="inlineStr">
         <is>
-          <t>Health &amp; Fitness</t>
+          <t>Health</t>
         </is>
       </c>
       <c r="D75" s="3" t="n">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="E75" s="3" t="n">
-        <v>45</v>
+        <v>72</v>
       </c>
       <c r="F75" s="3" t="inlineStr">
         <is>
-          <t>$25.00</t>
+          <t>$19.99</t>
         </is>
       </c>
       <c r="G75" s="4" t="inlineStr">
         <is>
-          <t>Google Trends US Search</t>
+          <t>eBay US Deals</t>
         </is>
       </c>
       <c r="H75" s="4" t="inlineStr">
@@ -3935,7 +3935,7 @@
       </c>
       <c r="J75" s="5" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?geo=US&amp;q=fitness</t>
+          <t>https://www.ebay.com/itm/124078773818</t>
         </is>
       </c>
     </row>
@@ -3945,28 +3945,28 @@
       </c>
       <c r="B76" s="4" t="inlineStr">
         <is>
-          <t>new jersey</t>
+          <t>Lonsdale Navy Blue Baseball Cap Hat Embroidered Logo Adjustable Kappe Mütze741,541.15 VND</t>
         </is>
       </c>
       <c r="C76" s="4" t="inlineStr">
         <is>
-          <t>General Trend</t>
+          <t>Fashion &amp; Apparel</t>
         </is>
       </c>
       <c r="D76" s="3" t="n">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="E76" s="3" t="n">
-        <v>45</v>
+        <v>72</v>
       </c>
       <c r="F76" s="3" t="inlineStr">
         <is>
-          <t>$25.00</t>
+          <t>$19.99</t>
         </is>
       </c>
       <c r="G76" s="4" t="inlineStr">
         <is>
-          <t>Google Trends US Search</t>
+          <t>eBay US Deals</t>
         </is>
       </c>
       <c r="H76" s="4" t="inlineStr">
@@ -3981,7 +3981,7 @@
       </c>
       <c r="J76" s="5" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?geo=US&amp;q=new%20jersey</t>
+          <t>https://www.ebay.com/itm/296106350225</t>
         </is>
       </c>
     </row>
@@ -3991,43 +3991,43 @@
       </c>
       <c r="B77" s="4" t="inlineStr">
         <is>
-          <t>cycling</t>
+          <t>Puma Speedcat OG team royal white Schuhe Sneaker Motorsport F1 398846-183,275,586.81 VNDShop all 12Men's Shoes &amp; Accesso</t>
         </is>
       </c>
       <c r="C77" s="4" t="inlineStr">
         <is>
-          <t>General Trend</t>
+          <t>Pet Supplies</t>
         </is>
       </c>
       <c r="D77" s="3" t="n">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="E77" s="3" t="n">
-        <v>45</v>
+        <v>72</v>
       </c>
       <c r="F77" s="3" t="inlineStr">
         <is>
-          <t>$25.00</t>
+          <t>$19.99</t>
         </is>
       </c>
       <c r="G77" s="4" t="inlineStr">
         <is>
-          <t>Google Trends US Search</t>
+          <t>eBay US Deals</t>
         </is>
       </c>
       <c r="H77" s="4" t="inlineStr">
         <is>
-          <t>Đặt câu hỏi trúng nỗi đau thường ngày: 'Tại sao không ai nói cho tôi biết món đồ này sớm hơn?!'</t>
+          <t>Âm thanh bấm nút nhả cả búi lông chó rụng chỉ trong 1 giây: 'Mùa rụng lông không còn là ác mộng!'</t>
         </is>
       </c>
       <c r="I77" s="4" t="inlineStr">
         <is>
-          <t>Khách hàng mua sắm ngẫu hứng (Impulse Buyers) trên TikTok Shop US độ tuổi 18 - 45.</t>
+          <t>Hội những người 'nghiện' chó mèo (Dog/Cat Parents) tại US, chi tiêu mạnh tay cho thú cưng.</t>
         </is>
       </c>
       <c r="J77" s="5" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?geo=US&amp;q=cycling</t>
+          <t>https://www.ebay.com/itm/156805882161</t>
         </is>
       </c>
     </row>
@@ -4037,28 +4037,28 @@
       </c>
       <c r="B78" s="4" t="inlineStr">
         <is>
-          <t>netflix top movies right now</t>
+          <t>Biker Kutte Lederkutte Lederweste Clubweste Rockerweste Herren Chopper Motorrad2,679,971.42 VND</t>
         </is>
       </c>
       <c r="C78" s="4" t="inlineStr">
         <is>
-          <t>General Trend</t>
+          <t>Fashion &amp; Apparel</t>
         </is>
       </c>
       <c r="D78" s="3" t="n">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="E78" s="3" t="n">
-        <v>45</v>
+        <v>72</v>
       </c>
       <c r="F78" s="3" t="inlineStr">
         <is>
-          <t>$25.00</t>
+          <t>$19.99</t>
         </is>
       </c>
       <c r="G78" s="4" t="inlineStr">
         <is>
-          <t>Google Trends US Search</t>
+          <t>eBay US Deals</t>
         </is>
       </c>
       <c r="H78" s="4" t="inlineStr">
@@ -4073,7 +4073,7 @@
       </c>
       <c r="J78" s="5" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?geo=US&amp;q=netflix%20top%20movies%20right%20now</t>
+          <t>https://www.ebay.com/itm/302258284099</t>
         </is>
       </c>
     </row>
@@ -4083,28 +4083,28 @@
       </c>
       <c r="B79" s="4" t="inlineStr">
         <is>
-          <t>what is a data breach</t>
+          <t>Schwarze Lederkutte mit blau Umrandungen Kutte Biker Motorrad Rocker Clubweste2,679,971.42 VNDShop all 68Men's Clothing</t>
         </is>
       </c>
       <c r="C79" s="4" t="inlineStr">
         <is>
-          <t>Fashion &amp; Apparel</t>
+          <t>Menswear &amp; Underwear</t>
         </is>
       </c>
       <c r="D79" s="3" t="n">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="E79" s="3" t="n">
-        <v>45</v>
+        <v>72</v>
       </c>
       <c r="F79" s="3" t="inlineStr">
         <is>
-          <t>$25.00</t>
+          <t>$19.99</t>
         </is>
       </c>
       <c r="G79" s="4" t="inlineStr">
         <is>
-          <t>Google Trends US Search</t>
+          <t>eBay US Deals</t>
         </is>
       </c>
       <c r="H79" s="4" t="inlineStr">
@@ -4119,7 +4119,7 @@
       </c>
       <c r="J79" s="5" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?geo=US&amp;q=what%20is%20a%20data%20breach</t>
+          <t>https://www.ebay.com/itm/301897675077</t>
         </is>
       </c>
     </row>
@@ -4129,43 +4129,43 @@
       </c>
       <c r="B80" s="4" t="inlineStr">
         <is>
-          <t>flood watch</t>
+          <t>Unterbrustkorsett Schwarz Leder Corsage Gothic Korsett Underbust Leather Corsets2,178,463.27 VND2,293,119.23 VND | 5% of</t>
         </is>
       </c>
       <c r="C80" s="4" t="inlineStr">
         <is>
-          <t>Gadgets &amp; Electronics</t>
+          <t>Fashion &amp; Apparel</t>
         </is>
       </c>
       <c r="D80" s="3" t="n">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="E80" s="3" t="n">
-        <v>45</v>
+        <v>72</v>
       </c>
       <c r="F80" s="3" t="inlineStr">
         <is>
-          <t>$25.00</t>
+          <t>$19.99</t>
         </is>
       </c>
       <c r="G80" s="4" t="inlineStr">
         <is>
-          <t>Google Trends US Search</t>
+          <t>eBay US Deals</t>
         </is>
       </c>
       <c r="H80" s="4" t="inlineStr">
         <is>
-          <t>So sánh âm thanh: 'Bật lọc tạp âm và nói chuyện giữa chợ ồn ào xem micro này xịn cỡ nào!'</t>
+          <t>Đặt câu hỏi trúng nỗi đau thường ngày: 'Tại sao không ai nói cho tôi biết món đồ này sớm hơn?!'</t>
         </is>
       </c>
       <c r="I80" s="4" t="inlineStr">
         <is>
-          <t>Học sinh, Gen Z làm bullet journal, Content Creator quay video TikTok / Vlog tại US.</t>
+          <t>Khách hàng mua sắm ngẫu hứng (Impulse Buyers) trên TikTok Shop US độ tuổi 18 - 45.</t>
         </is>
       </c>
       <c r="J80" s="5" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?geo=US&amp;q=flood%20watch</t>
+          <t>https://www.ebay.com/itm/362632687305</t>
         </is>
       </c>
     </row>
@@ -4175,28 +4175,28 @@
       </c>
       <c r="B81" s="4" t="inlineStr">
         <is>
-          <t>cloud</t>
+          <t>Satin Vollbrustkorsett Schnürkorsett Korsett Mieder Corset Corsage Schwarz LANG2,084,653.85 VND</t>
         </is>
       </c>
       <c r="C81" s="4" t="inlineStr">
         <is>
-          <t>General Trend</t>
+          <t>Fashion &amp; Apparel</t>
         </is>
       </c>
       <c r="D81" s="3" t="n">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="E81" s="3" t="n">
-        <v>45</v>
+        <v>72</v>
       </c>
       <c r="F81" s="3" t="inlineStr">
         <is>
-          <t>$25.00</t>
+          <t>$19.99</t>
         </is>
       </c>
       <c r="G81" s="4" t="inlineStr">
         <is>
-          <t>Google Trends US Search</t>
+          <t>eBay US Deals</t>
         </is>
       </c>
       <c r="H81" s="4" t="inlineStr">
@@ -4211,7 +4211,7 @@
       </c>
       <c r="J81" s="5" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?geo=US&amp;q=cloud</t>
+          <t>https://www.ebay.com/itm/362636865751</t>
         </is>
       </c>
     </row>
@@ -4221,43 +4221,89 @@
       </c>
       <c r="B82" s="4" t="inlineStr">
         <is>
-          <t>earthquake near me</t>
+          <t>Unterbrustkorsett Rot Lack Corsage tolles Taillen training PVC Underbust Corsets1,980,421.15 VND2,084,653.85 VND | 5% of</t>
         </is>
       </c>
       <c r="C82" s="4" t="inlineStr">
         <is>
-          <t>DIY, Craft &amp; POD</t>
+          <t>Fashion &amp; Apparel</t>
         </is>
       </c>
       <c r="D82" s="3" t="n">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="E82" s="3" t="n">
-        <v>45</v>
+        <v>72</v>
       </c>
       <c r="F82" s="3" t="inlineStr">
         <is>
-          <t>$25.00</t>
+          <t>$19.99</t>
         </is>
       </c>
       <c r="G82" s="4" t="inlineStr">
         <is>
-          <t>Google Trends US Search</t>
+          <t>eBay US Deals</t>
         </is>
       </c>
       <c r="H82" s="4" t="inlineStr">
         <is>
-          <t>Quá trình máy khắc laser tên khách hàng lên gỗ/kim loại: 'Làm món quà độc nhất vô nhị tặng mẹ...'</t>
+          <t>Đặt câu hỏi trúng nỗi đau thường ngày: 'Tại sao không ai nói cho tôi biết món đồ này sớm hơn?!'</t>
         </is>
       </c>
       <c r="I82" s="4" t="inlineStr">
         <is>
-          <t>Người tìm quà tặng sinh nhật, kỷ niệm, Mother's Day, quà tân gia ý nghĩa quanh năm.</t>
+          <t>Khách hàng mua sắm ngẫu hứng (Impulse Buyers) trên TikTok Shop US độ tuổi 18 - 45.</t>
         </is>
       </c>
       <c r="J82" s="5" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?geo=US&amp;q=earthquake%20near%20me</t>
+          <t>https://www.ebay.com/itm/363166536187</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" ht="22" customHeight="1">
+      <c r="A83" s="3" t="n">
+        <v>81</v>
+      </c>
+      <c r="B83" s="4" t="inlineStr">
+        <is>
+          <t>New Omega Seamaster Diver 300M Automatic Green Men's Watch 210.90.42.20.10.001266,769,230.77 VND320,512,820.51 VND Previ</t>
+        </is>
+      </c>
+      <c r="C83" s="4" t="inlineStr">
+        <is>
+          <t>Menswear &amp; Underwear</t>
+        </is>
+      </c>
+      <c r="D83" s="3" t="n">
+        <v>76</v>
+      </c>
+      <c r="E83" s="3" t="n">
+        <v>72</v>
+      </c>
+      <c r="F83" s="3" t="inlineStr">
+        <is>
+          <t>$19.99</t>
+        </is>
+      </c>
+      <c r="G83" s="4" t="inlineStr">
+        <is>
+          <t>eBay US Deals</t>
+        </is>
+      </c>
+      <c r="H83" s="4" t="inlineStr">
+        <is>
+          <t>So sánh âm thanh: 'Bật lọc tạp âm và nói chuyện giữa chợ ồn ào xem micro này xịn cỡ nào!'</t>
+        </is>
+      </c>
+      <c r="I83" s="4" t="inlineStr">
+        <is>
+          <t>Học sinh, Gen Z làm bullet journal, Content Creator quay video TikTok / Vlog tại US.</t>
+        </is>
+      </c>
+      <c r="J83" s="5" t="inlineStr">
+        <is>
+          <t>https://www.ebay.com/itm/357622544308</t>
         </is>
       </c>
     </row>
@@ -4343,6 +4389,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J80" r:id="rId78"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J81" r:id="rId79"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J82" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J83" r:id="rId81"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4354,7 +4401,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I33"/>
+  <dimension ref="A1:I32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4459,7 +4506,7 @@
       </c>
       <c r="I3" s="5" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/Mighty-Patch-Hydrocolloid-Absorbing-count/dp/B074PVTPBW/ref=zg_bs_g_beauty_d_sccl_5/130-1584604-8661848</t>
+          <t>https://www.amazon.com/Mighty-Patch-Hydrocolloid-Absorbing-count/dp/B074PVTPBW/ref=zg_bs_g_beauty_d_sccl_5/142-8547974-1409324</t>
         </is>
       </c>
     </row>
@@ -4500,7 +4547,7 @@
       </c>
       <c r="I4" s="5" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/STANLEY-IceFlow-Straw-Tumbler-Black/dp/B0DR9PMK1W/ref=zg_bs_g_kitchen_d_sccl_6/130-1584604-8661848</t>
+          <t>https://www.amazon.com/STANLEY-IceFlow-Straw-Tumbler-Black/dp/B0DR9PMK1W/ref=zg_bs_g_kitchen_d_sccl_6/142-8547974-1409324</t>
         </is>
       </c>
     </row>
@@ -4541,7 +4588,7 @@
       </c>
       <c r="I5" s="5" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/Clean-Skin-Club-Disposable-Sensitive/dp/B07PBXXNCY/ref=zg_bs_g_beauty_d_sccl_4/130-1584604-8661848</t>
+          <t>https://www.amazon.com/Clean-Skin-Club-Disposable-Sensitive/dp/B07PBXXNCY/ref=zg_bs_g_beauty_d_sccl_4/142-8547974-1409324</t>
         </is>
       </c>
     </row>
@@ -4582,7 +4629,7 @@
       </c>
       <c r="I6" s="5" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/Owala-FreeSip-Insulated-Stainless-BPA-Free/dp/B0BZYCJK89/ref=zg_bs_g_kitchen_d_sccl_1/130-1584604-8661848</t>
+          <t>https://www.amazon.com/Owala-FreeSip-Insulated-Stainless-BPA-Free/dp/B0BZYCJK89/ref=zg_bs_g_kitchen_d_sccl_1/142-8547974-1409324</t>
         </is>
       </c>
     </row>
@@ -4623,7 +4670,7 @@
       </c>
       <c r="I7" s="5" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/Owala-FreeSip-Insulated-Stainless-BPA-Free/dp/B0BZYCJK89/ref=zg_bs_g_home-garden_d_sccl_1/130-1584604-8661848</t>
+          <t>https://www.amazon.com/Owala-FreeSip-Insulated-Stainless-BPA-Free/dp/B0BZYCJK89/ref=zg_bs_g_home-garden_d_sccl_1/142-8547974-1409324</t>
         </is>
       </c>
     </row>
@@ -4664,7 +4711,7 @@
       </c>
       <c r="I8" s="5" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/Owala-SmoothSip-Insulated-Stainless-Reusable/dp/B0DF3M7V3T/ref=zg_bs_g_kitchen_d_sccl_5/130-1584604-8661848</t>
+          <t>https://www.amazon.com/Owala-SmoothSip-Insulated-Stainless-Reusable/dp/B0DF3M7V3T/ref=zg_bs_g_kitchen_d_sccl_5/142-8547974-1409324</t>
         </is>
       </c>
     </row>
@@ -4705,7 +4752,7 @@
       </c>
       <c r="I9" s="5" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/eos-Cashmere-Moisture-Lightweight-Non-Greasy/dp/B08KT2Z93D/ref=zg_bs_g_beauty_d_sccl_1/130-1584604-8661848</t>
+          <t>https://www.amazon.com/eos-Cashmere-Moisture-Lightweight-Non-Greasy/dp/B08KT2Z93D/ref=zg_bs_g_beauty_d_sccl_1/142-8547974-1409324</t>
         </is>
       </c>
     </row>
@@ -4746,7 +4793,7 @@
       </c>
       <c r="I10" s="5" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/Neutrogena-Makeup-Remover-Micellar-Wipes/dp/B00U2VQZDS/ref=zg_bs_g_beauty_d_sccl_6/130-1584604-8661848</t>
+          <t>https://www.amazon.com/Neutrogena-Makeup-Remover-Micellar-Wipes/dp/B00U2VQZDS/ref=zg_bs_g_beauty_d_sccl_6/142-8547974-1409324</t>
         </is>
       </c>
     </row>
@@ -4787,7 +4834,7 @@
       </c>
       <c r="I11" s="5" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/TERRO-T300-2-2-Pack-Liquid-Baits/dp/B00E4GACB8/ref=zg_bs_g_home-garden_d_sccl_2/130-1584604-8661848</t>
+          <t>https://www.amazon.com/TERRO-T300-2-2-Pack-Liquid-Baits/dp/B00E4GACB8/ref=zg_bs_g_home-garden_d_sccl_2/142-8547974-1409324</t>
         </is>
       </c>
     </row>
@@ -4828,7 +4875,7 @@
       </c>
       <c r="I12" s="5" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/Amazon-Basics-Microfiber-Lightweight-Wrinkle-free/dp/B0154ASID6/ref=zg_bs_g_home-garden_d_sccl_3/130-1584604-8661848</t>
+          <t>https://www.amazon.com/Amazon-Basics-Microfiber-Lightweight-Wrinkle-free/dp/B0154ASID6/ref=zg_bs_g_home-garden_d_sccl_3/142-8547974-1409324</t>
         </is>
       </c>
     </row>
@@ -4869,7 +4916,7 @@
       </c>
       <c r="I13" s="5" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/Dr-Elseys-Premium-Clumping-Litter/dp/B0009X29WK/ref=zg_bs_g_pet-supplies_d_sccl_1/130-1584604-8661848</t>
+          <t>https://www.amazon.com/Dr-Elseys-Premium-Clumping-Litter/dp/B0009X29WK/ref=zg_bs_g_pet-supplies_d_sccl_1/142-8547974-1409324</t>
         </is>
       </c>
     </row>
@@ -4910,7 +4957,7 @@
       </c>
       <c r="I14" s="5" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/Amazon-Basics-Leak-Proof-Quick-Dry-Absorbency/dp/B00MW8G62E/ref=zg_bs_g_pet-supplies_d_sccl_2/130-1584604-8661848</t>
+          <t>https://www.amazon.com/Amazon-Basics-Leak-Proof-Quick-Dry-Absorbency/dp/B00MW8G62E/ref=zg_bs_g_pet-supplies_d_sccl_2/142-8547974-1409324</t>
         </is>
       </c>
     </row>
@@ -4951,7 +4998,7 @@
       </c>
       <c r="I15" s="5" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/Purina-Fancy-Feast-Poultry-Collection/dp/B00JN9IWNG/ref=zg_bs_g_pet-supplies_d_sccl_3/130-1584604-8661848</t>
+          <t>https://www.amazon.com/Purina-Fancy-Feast-Poultry-Collection/dp/B00JN9IWNG/ref=zg_bs_g_pet-supplies_d_sccl_3/142-8547974-1409324</t>
         </is>
       </c>
     </row>
@@ -4992,7 +5039,7 @@
       </c>
       <c r="I16" s="5" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/Amazon-Basics-Cotton-Swabs-500ct/dp/B09541P9WH/ref=zg_bs_g_beauty_d_sccl_3/130-1584604-8661848</t>
+          <t>https://www.amazon.com/Amazon-Basics-Cotton-Swabs-500ct/dp/B09541P9WH/ref=zg_bs_g_beauty_d_sccl_3/142-8547974-1409324</t>
         </is>
       </c>
     </row>
@@ -5033,7 +5080,7 @@
       </c>
       <c r="I17" s="5" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/Blink-Plus-Plan-monthly-auto-renewal/dp/B08JHCVHTY/ref=zg_bs_g_electronics_d_sccl_1/130-1584604-8661848</t>
+          <t>https://www.amazon.com/Blink-Plus-Plan-monthly-auto-renewal/dp/B08JHCVHTY/ref=zg_bs_g_electronics_d_sccl_1/142-8547974-1409324</t>
         </is>
       </c>
     </row>
@@ -5074,7 +5121,7 @@
       </c>
       <c r="I18" s="5" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/Etekcity-Multifunction-Stainless-Batteries-Included/dp/B0113UZJE2/ref=zg_bs_g_kitchen_d_sccl_4/130-1584604-8661848</t>
+          <t>https://www.amazon.com/Etekcity-Multifunction-Stainless-Batteries-Included/dp/B0113UZJE2/ref=zg_bs_g_kitchen_d_sccl_4/142-8547974-1409324</t>
         </is>
       </c>
     </row>
@@ -5115,7 +5162,7 @@
       </c>
       <c r="I19" s="5" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/Queen-Size-Piece-Sheet-Set/dp/B01M16WBW1/ref=zg_bs_g_home-garden_d_sccl_4/130-1584604-8661848</t>
+          <t>https://www.amazon.com/Queen-Size-Piece-Sheet-Set/dp/B01M16WBW1/ref=zg_bs_g_home-garden_d_sccl_4/142-8547974-1409324</t>
         </is>
       </c>
     </row>
@@ -5156,7 +5203,7 @@
       </c>
       <c r="I20" s="5" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/Electric-Flying-Insect-Trap-Starter/dp/B07T869RNY/ref=zg_bs_g_home-garden_d_sccl_6/130-1584604-8661848</t>
+          <t>https://www.amazon.com/Electric-Flying-Insect-Trap-Starter/dp/B07T869RNY/ref=zg_bs_g_home-garden_d_sccl_6/142-8547974-1409324</t>
         </is>
       </c>
     </row>
@@ -5197,7 +5244,7 @@
       </c>
       <c r="I21" s="5" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/Earth-Rated-Lavender-Scented-Completely/dp/B00BSYR7K8/ref=zg_bs_g_pet-supplies_d_sccl_5/130-1584604-8661848</t>
+          <t>https://www.amazon.com/Earth-Rated-Lavender-Scented-Completely/dp/B00BSYR7K8/ref=zg_bs_g_pet-supplies_d_sccl_5/142-8547974-1409324</t>
         </is>
       </c>
     </row>
@@ -5238,7 +5285,7 @@
       </c>
       <c r="I22" s="5" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/ZEVO-Flying-Insect-Refills-Indoor/dp/B0C3FTCYZL/ref=zg_bs_g_home-garden_d_sccl_5/130-1584604-8661848</t>
+          <t>https://www.amazon.com/ZEVO-Flying-Insect-Refills-Indoor/dp/B0C3FTCYZL/ref=zg_bs_g_home-garden_d_sccl_5/142-8547974-1409324</t>
         </is>
       </c>
     </row>
@@ -5279,7 +5326,7 @@
       </c>
       <c r="I23" s="5" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/Apple-Bluetooth-Headphones-Personalized-Effortless/dp/B0DGHMNQ5Z/ref=zg_bs_g_electronics_d_sccl_6/130-1584604-8661848</t>
+          <t>https://www.amazon.com/Apple-Bluetooth-Headphones-Personalized-Effortless/dp/B0DGHMNQ5Z/ref=zg_bs_g_electronics_d_sccl_6/142-8547974-1409324</t>
         </is>
       </c>
     </row>
@@ -5320,7 +5367,7 @@
       </c>
       <c r="I24" s="5" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/Greenies-Pockets-Natural-Treats-Capsule/dp/B07S2TDDCK/ref=zg_bs_g_pet-supplies_d_sccl_4/130-1584604-8661848</t>
+          <t>https://www.amazon.com/Greenies-Pockets-Natural-Treats-Capsule/dp/B07S2TDDCK/ref=zg_bs_g_pet-supplies_d_sccl_4/142-8547974-1409324</t>
         </is>
       </c>
     </row>
@@ -5361,7 +5408,7 @@
       </c>
       <c r="I25" s="5" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/INABA-Chicken-Lickable-Creamy-Variety/dp/B07D323MFZ/ref=zg_bs_g_pet-supplies_d_sccl_6/130-1584604-8661848</t>
+          <t>https://www.amazon.com/INABA-Chicken-Lickable-Creamy-Variety/dp/B07D323MFZ/ref=zg_bs_g_pet-supplies_d_sccl_6/142-8547974-1409324</t>
         </is>
       </c>
     </row>
@@ -5371,12 +5418,12 @@
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>Kettenanhänger Liebe Hoffnung Glaube Gelb Gold oder Silber glanz 15x8mm Amulett1,277,297.19 VNDShop all 22Fine Jewelry</t>
+          <t>ICED 10k White Gold DIAMOND Curb Link HEAVY 44gr Bracelet Jewelry136,393,589.74 VNDPanzerkette Halskette 5 mm Echt 750er</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>Jewelry Accessories &amp; Derivatives</t>
+          <t>Kitchenware</t>
         </is>
       </c>
       <c r="D26" s="3" t="n">
@@ -5402,7 +5449,7 @@
       </c>
       <c r="I26" s="5" t="inlineStr">
         <is>
-          <t>https://www.ebay.com/itm/285242609945</t>
+          <t>https://www.ebay.com/itm/298332862724</t>
         </is>
       </c>
     </row>
@@ -5412,38 +5459,38 @@
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>ICED 10k White Gold DIAMOND Curb Link HEAVY 44gr Bracelet Jewelry136,393,589.74 VNDPanzerkette 4 mm Halskette Echt 750er</t>
+          <t>Custom Name Birth Flower Bar Necklace &amp; Personalized Jewelry</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>Kitchenware</t>
+          <t>Jewelry Accessories &amp; Derivatives</t>
         </is>
       </c>
       <c r="D27" s="3" t="n">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>76</v>
+        <v>50</v>
       </c>
       <c r="F27" s="3" t="inlineStr">
         <is>
-          <t>65% - 75% (Ước tính giá bán $15 - $29)</t>
+          <t>75% - 85%</t>
         </is>
       </c>
       <c r="G27" s="4" t="inlineStr">
         <is>
-          <t>TikTok Made Me Buy It / Honest Review</t>
+          <t>Behind The Scenes Crafting &amp; Emotional Gift Unboxing</t>
         </is>
       </c>
       <c r="H27" s="4" t="inlineStr">
         <is>
-          <t>Xem ngay giá ưu đãi độc quyền hôm nay trên TikTok Shop!</t>
+          <t>Gõ tên người bạn muốn khắc vào ghi chú đơn hàng ngay dưới video!</t>
         </is>
       </c>
       <c r="I27" s="5" t="inlineStr">
         <is>
-          <t>https://www.ebay.com/itm/298332862724</t>
+          <t>https://www.etsy.com/market/birth_flower_necklace</t>
         </is>
       </c>
     </row>
@@ -5453,12 +5500,12 @@
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>Custom Name Birth Flower Bar Necklace &amp; Personalized Jewelry</t>
+          <t>Personalized Wooden Docking Station &amp; Desk Organizer for Men</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>Jewelry Accessories &amp; Derivatives</t>
+          <t>Menswear &amp; Underwear</t>
         </is>
       </c>
       <c r="D28" s="3" t="n">
@@ -5469,7 +5516,7 @@
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
-          <t>75% - 85%</t>
+          <t>65% - 75%</t>
         </is>
       </c>
       <c r="G28" s="4" t="inlineStr">
@@ -5484,7 +5531,7 @@
       </c>
       <c r="I28" s="5" t="inlineStr">
         <is>
-          <t>https://www.etsy.com/market/birth_flower_necklace</t>
+          <t>https://www.etsy.com/market/wooden_docking_station</t>
         </is>
       </c>
     </row>
@@ -5494,12 +5541,12 @@
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>Personalized Wooden Docking Station &amp; Desk Organizer for Men</t>
+          <t>Minimalist Custom Acrylic Wall Calendar &amp; Family Command Center</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>Menswear &amp; Underwear</t>
+          <t>Home Supplies</t>
         </is>
       </c>
       <c r="D29" s="3" t="n">
@@ -5510,7 +5557,7 @@
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
-          <t>65% - 75%</t>
+          <t>70% - 80%</t>
         </is>
       </c>
       <c r="G29" s="4" t="inlineStr">
@@ -5525,7 +5572,7 @@
       </c>
       <c r="I29" s="5" t="inlineStr">
         <is>
-          <t>https://www.etsy.com/market/wooden_docking_station</t>
+          <t>https://www.etsy.com/market/acrylic_calendar</t>
         </is>
       </c>
     </row>
@@ -5535,12 +5582,12 @@
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>Minimalist Custom Acrylic Wall Calendar &amp; Family Command Center</t>
+          <t>Engraved Olive Wood Cutting Board &amp; Charcuterie Serving Platter</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>Home Supplies</t>
+          <t>Kitchenware</t>
         </is>
       </c>
       <c r="D30" s="3" t="n">
@@ -5551,7 +5598,7 @@
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
-          <t>70% - 80%</t>
+          <t>70%</t>
         </is>
       </c>
       <c r="G30" s="4" t="inlineStr">
@@ -5566,7 +5613,7 @@
       </c>
       <c r="I30" s="5" t="inlineStr">
         <is>
-          <t>https://www.etsy.com/market/acrylic_calendar</t>
+          <t>https://www.etsy.com/market/personalized_cutting_board</t>
         </is>
       </c>
     </row>
@@ -5576,12 +5623,12 @@
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>Engraved Olive Wood Cutting Board &amp; Charcuterie Serving Platter</t>
+          <t>Custom Pet Portrait Sweatshirt &amp; Embroidered Dog Mom Hoodie</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>Kitchenware</t>
+          <t>Pet Supplies</t>
         </is>
       </c>
       <c r="D31" s="3" t="n">
@@ -5592,22 +5639,22 @@
       </c>
       <c r="F31" s="3" t="inlineStr">
         <is>
-          <t>70%</t>
+          <t>75% - 85% (Source $2.0 - $4.0 -&gt; Bán $11.99 - $16.99)</t>
         </is>
       </c>
       <c r="G31" s="4" t="inlineStr">
         <is>
-          <t>Behind The Scenes Crafting &amp; Emotional Gift Unboxing</t>
+          <t>Emotional Reaction &amp; Satisfying Fur Release ASMR</t>
         </is>
       </c>
       <c r="H31" s="4" t="inlineStr">
         <is>
-          <t>Gõ tên người bạn muốn khắc vào ghi chú đơn hàng ngay dưới video!</t>
+          <t>Bảo vệ đường hô hấp cho cả nhà, sắm ngay chiếc lược tự nhả lông này!</t>
         </is>
       </c>
       <c r="I31" s="5" t="inlineStr">
         <is>
-          <t>https://www.etsy.com/market/personalized_cutting_board</t>
+          <t>https://www.etsy.com/market/custom_pet_sweatshirt</t>
         </is>
       </c>
     </row>
@@ -5617,12 +5664,12 @@
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>Custom Pet Portrait Sweatshirt &amp; Embroidered Dog Mom Hoodie</t>
+          <t>Handmade Organic Soy Aromatherapy Candle in Amber Glass Jar</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>Pet Supplies</t>
+          <t>Home Supplies</t>
         </is>
       </c>
       <c r="D32" s="3" t="n">
@@ -5633,61 +5680,20 @@
       </c>
       <c r="F32" s="3" t="inlineStr">
         <is>
-          <t>75% - 85% (Source $2.0 - $4.0 -&gt; Bán $11.99 - $16.99)</t>
+          <t>80%</t>
         </is>
       </c>
       <c r="G32" s="4" t="inlineStr">
         <is>
-          <t>Emotional Reaction &amp; Satisfying Fur Release ASMR</t>
+          <t>TikTok Made Me Buy It / Honest Review</t>
         </is>
       </c>
       <c r="H32" s="4" t="inlineStr">
         <is>
-          <t>Bảo vệ đường hô hấp cho cả nhà, sắm ngay chiếc lược tự nhả lông này!</t>
+          <t>Xem ngay giá ưu đãi độc quyền hôm nay trên TikTok Shop!</t>
         </is>
       </c>
       <c r="I32" s="5" t="inlineStr">
-        <is>
-          <t>https://www.etsy.com/market/custom_pet_sweatshirt</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="22" customHeight="1">
-      <c r="A33" s="3" t="n">
-        <v>31</v>
-      </c>
-      <c r="B33" s="4" t="inlineStr">
-        <is>
-          <t>Handmade Organic Soy Aromatherapy Candle in Amber Glass Jar</t>
-        </is>
-      </c>
-      <c r="C33" s="4" t="inlineStr">
-        <is>
-          <t>Home Supplies</t>
-        </is>
-      </c>
-      <c r="D33" s="3" t="n">
-        <v>94</v>
-      </c>
-      <c r="E33" s="3" t="n">
-        <v>50</v>
-      </c>
-      <c r="F33" s="3" t="inlineStr">
-        <is>
-          <t>80%</t>
-        </is>
-      </c>
-      <c r="G33" s="4" t="inlineStr">
-        <is>
-          <t>TikTok Made Me Buy It / Honest Review</t>
-        </is>
-      </c>
-      <c r="H33" s="4" t="inlineStr">
-        <is>
-          <t>Xem ngay giá ưu đãi độc quyền hôm nay trên TikTok Shop!</t>
-        </is>
-      </c>
-      <c r="I33" s="5" t="inlineStr">
         <is>
           <t>https://www.etsy.com/market/soy_candle</t>
         </is>
@@ -5725,7 +5731,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I30" r:id="rId28"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I31" r:id="rId29"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I32" r:id="rId30"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I33" r:id="rId31"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5829,7 +5834,7 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>Clean Skin Club Disposable 100% Biobased Face Towels</t>
+          <t>Self-Cleaning Deshedding Slicker Pet Grooming Brush</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
@@ -5839,21 +5844,21 @@
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>Beauty &amp; Personal Care</t>
+          <t>Home Supplies</t>
         </is>
       </c>
       <c r="E3" s="3" t="n">
         <v>99.5</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="G3" s="3" t="n">
         <v>95</v>
       </c>
       <c r="H3" s="3" t="inlineStr">
         <is>
-          <t>$15.95 - $17.95</t>
+          <t>$11.99 - $16.99</t>
         </is>
       </c>
       <c r="I3" s="4" t="inlineStr">
@@ -5868,12 +5873,12 @@
       </c>
       <c r="K3" s="4" t="inlineStr">
         <is>
-          <t>Problem - Agitate - Solution (So sánh vi khuẩn kính hiển vi)</t>
+          <t>Emotional Reaction &amp; Satisfying Fur Release ASMR</t>
         </is>
       </c>
       <c r="L3" s="5" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/tag/cleanskinclub</t>
+          <t>https://www.tiktok.com/tag/petgrooming</t>
         </is>
       </c>
     </row>
@@ -5883,7 +5888,7 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>Self-Cleaning Deshedding Slicker Pet Grooming Brush</t>
+          <t>Clean Skin Club Disposable 100% Biobased Face Towels</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
@@ -5893,21 +5898,21 @@
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>Home Supplies</t>
+          <t>Beauty &amp; Personal Care</t>
         </is>
       </c>
       <c r="E4" s="3" t="n">
         <v>99.5</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="G4" s="3" t="n">
         <v>95</v>
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>$11.99 - $16.99</t>
+          <t>$15.95 - $17.95</t>
         </is>
       </c>
       <c r="I4" s="4" t="inlineStr">
@@ -5922,12 +5927,12 @@
       </c>
       <c r="K4" s="4" t="inlineStr">
         <is>
-          <t>Emotional Reaction &amp; Satisfying Fur Release ASMR</t>
+          <t>Problem - Agitate - Solution (So sánh vi khuẩn kính hiển vi)</t>
         </is>
       </c>
       <c r="L4" s="5" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/tag/petgrooming</t>
+          <t>https://www.tiktok.com/tag/cleanskinclub</t>
         </is>
       </c>
     </row>
@@ -5937,7 +5942,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>STANLEY Quencher H2.0 Tumbler with Handle and Straw 30 oz | Flowstate 3-Position Lid | Cup Holder Compatible for Travel | Insulate</t>
+          <t>Owala FreeSip Insulated Stainless Steel Tumbler (Leak-Proof Straw)</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
@@ -5951,27 +5956,27 @@
         </is>
       </c>
       <c r="E5" s="3" t="n">
-        <v>99.5</v>
+        <v>82</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>97</v>
+        <v>50</v>
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>$32.95</t>
+          <t>$27.99 - $37.99</t>
         </is>
       </c>
       <c r="I5" s="4" t="inlineStr">
         <is>
-          <t>Amazon US Best Sellers</t>
+          <t>TikTok US Viral 24h</t>
         </is>
       </c>
       <c r="J5" s="4" t="inlineStr">
         <is>
-          <t>Amazon Best Sellers, Amazon US, TikTok Trend Validated</t>
+          <t>TikTok Shop, TikTok Viral 24h, Amazon Top 100</t>
         </is>
       </c>
       <c r="K5" s="4" t="inlineStr">
@@ -5981,7 +5986,7 @@
       </c>
       <c r="L5" s="5" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/STANLEY-Flowstate-3-Position-Compatible-Insulated/dp/B0CP9YB3Q4/ref=zg_bs_g_kitchen_d_sccl_2/130-1584604-8661848</t>
+          <t>https://www.tiktok.com/tag/owala</t>
         </is>
       </c>
     </row>
@@ -5991,7 +5996,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>medicube Toner Pads Zero Pore Pad 2.0 for Exfoliation and Pore Care | Dual-Textured Facial Pad with 4.5% AHA Lactic Acid, 0.45% BH</t>
+          <t>Hero Cosmetics Mighty Patch Original Hydrocolloid Acne Dots</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
@@ -6005,27 +6010,27 @@
         </is>
       </c>
       <c r="E6" s="3" t="n">
-        <v>99.40000000000001</v>
+        <v>82</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>90</v>
+        <v>50</v>
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
-          <t>$18.90</t>
+          <t>$12.99 - $14.99</t>
         </is>
       </c>
       <c r="I6" s="4" t="inlineStr">
         <is>
-          <t>Amazon US Best Sellers</t>
+          <t>TikTok US Viral 24h</t>
         </is>
       </c>
       <c r="J6" s="4" t="inlineStr">
         <is>
-          <t>Amazon Best Sellers, Amazon US, TikTok Trend Validated</t>
+          <t>TikTok Shop, TikTok Viral 24h, Amazon Top 100</t>
         </is>
       </c>
       <c r="K6" s="4" t="inlineStr">
@@ -6035,7 +6040,7 @@
       </c>
       <c r="L6" s="5" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/Medicube-Zero-Pore-Pads-Dual-Textured/dp/B09V7Z4TJG/ref=zg_bs_g_beauty_d_sccl_2/130-1584604-8661848</t>
+          <t>https://www.tiktok.com/tag/mightypatch</t>
         </is>
       </c>
     </row>
@@ -6045,7 +6050,7 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">HydroJug Traveler 40oz, Insulated Tumbler with Handle &amp; Straw, Pink Sand | Triple wall insulated, flip straw lid, leak-resistant, </t>
+          <t>Mini Portable Thermal Sticker &amp; Label Printer</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
@@ -6055,41 +6060,41 @@
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>Kitchenware</t>
+          <t>Phones &amp; Electronics</t>
         </is>
       </c>
       <c r="E7" s="3" t="n">
-        <v>99.40000000000001</v>
+        <v>79.7</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>90</v>
+        <v>45</v>
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t>$31.99</t>
+          <t>$19.99 - $29.99</t>
         </is>
       </c>
       <c r="I7" s="4" t="inlineStr">
         <is>
-          <t>Amazon US Best Sellers</t>
+          <t>TikTok US Viral 24h</t>
         </is>
       </c>
       <c r="J7" s="4" t="inlineStr">
         <is>
-          <t>Amazon Best Sellers, Amazon US, TikTok Trend Validated</t>
+          <t>TikTok Shop, TikTok Viral 24h, Amazon Top 100</t>
         </is>
       </c>
       <c r="K7" s="4" t="inlineStr">
         <is>
-          <t>Before/After Macro Skin Texture Zoom (Cận cảnh bề mặt da)</t>
+          <t>Side-by-side Live Demo &amp; Unboxing ASMR</t>
         </is>
       </c>
       <c r="L7" s="5" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/HydroJug-Traveler-Resistant-Bottle-Reusable-Insulated/dp/B0CQVWT2NH/ref=zg_bs_g_kitchen_d_sccl_3/130-1584604-8661848</t>
+          <t>https://www.tiktok.com/tag/miniprinter</t>
         </is>
       </c>
     </row>
@@ -6099,12 +6104,12 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>Mighty Patch Hero Cosmetics Original Nighttime Acne Pimple Patches, 36 Ct | #1 Hydrocolloid Acne Patches, Shrinking Zits &amp; Whitehe</t>
+          <t>medicube Zero Pore Pads 2.0 &amp; Exfoliating Toner</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>🌲 Evergreen Bền Vững</t>
+          <t>🔥 Bùng Nổ 24h (Viral Spike)</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
@@ -6113,27 +6118,27 @@
         </is>
       </c>
       <c r="E8" s="3" t="n">
-        <v>99.2</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>97</v>
+        <v>50</v>
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t>$12.99</t>
+          <t>$18.90 - $24.00</t>
         </is>
       </c>
       <c r="I8" s="4" t="inlineStr">
         <is>
-          <t>Amazon US Best Sellers</t>
+          <t>TikTok US Viral 24h</t>
         </is>
       </c>
       <c r="J8" s="4" t="inlineStr">
         <is>
-          <t>Amazon Best Sellers, Amazon US, TikTok Trend Validated</t>
+          <t>TikTok Shop, TikTok Viral 24h, Amazon Top 100</t>
         </is>
       </c>
       <c r="K8" s="4" t="inlineStr">
@@ -6143,7 +6148,7 @@
       </c>
       <c r="L8" s="5" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/Mighty-Patch-Hydrocolloid-Absorbing-count/dp/B074PVTPBW/ref=zg_bs_g_beauty_d_sccl_5/130-1584604-8661848</t>
+          <t>https://www.tiktok.com/tag/medicube</t>
         </is>
       </c>
     </row>
@@ -6153,51 +6158,51 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>STANLEY IceFlow 2.0 Flip Straw Tumbler, 30 oz, Black 2.0 | Easy Carry Handle | Twist On Lid and Flip Up Straw | Leak Resistant Wat</t>
+          <t>Automatic 360 Electric Spin Scrubber for Deep Bathroom Cleaning</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>🌲 Evergreen Bền Vững</t>
+          <t>🔥 Bùng Nổ 24h (Viral Spike)</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>Kitchenware</t>
+          <t>Home Supplies</t>
         </is>
       </c>
       <c r="E9" s="3" t="n">
-        <v>99.2</v>
+        <v>80.8</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>97</v>
+        <v>50</v>
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t>1 offer from $21.00</t>
+          <t>$29.99 - $49.99</t>
         </is>
       </c>
       <c r="I9" s="4" t="inlineStr">
         <is>
-          <t>Amazon US Best Sellers</t>
+          <t>TikTok US Viral 24h</t>
         </is>
       </c>
       <c r="J9" s="4" t="inlineStr">
         <is>
-          <t>Amazon Best Sellers, Amazon US, TikTok Trend Validated</t>
+          <t>TikTok Shop, TikTok Viral 24h, Amazon Top 100</t>
         </is>
       </c>
       <c r="K9" s="4" t="inlineStr">
         <is>
-          <t>Before/After Macro Skin Texture Zoom (Cận cảnh bề mặt da)</t>
+          <t>Satisfying Deep Clean ASMR (Âm thanh chà sạch cực đã tai)</t>
         </is>
       </c>
       <c r="L9" s="5" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/STANLEY-IceFlow-Straw-Tumbler-Black/dp/B0DR9PMK1W/ref=zg_bs_g_kitchen_d_sccl_6/130-1584604-8661848</t>
+          <t>https://www.tiktok.com/tag/spinscrubber</t>
         </is>
       </c>
     </row>
@@ -6207,51 +6212,51 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>Clean Skin Club Clean Towels XL®, 100% USDA Biobased Face Towel, Disposable Face Towelette, Eczema Association Accepted, Makeup Re</t>
+          <t>Wireless Magnetic Lavalier Lapel Microphone for iPhone &amp; Type-C</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>🌲 Evergreen Bền Vững</t>
+          <t>🔥 Bùng Nổ 24h (Viral Spike)</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>Beauty &amp; Personal Care</t>
+          <t>Phones &amp; Electronics</t>
         </is>
       </c>
       <c r="E10" s="3" t="n">
-        <v>98.3</v>
+        <v>69.8</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>95</v>
+        <v>45</v>
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t>$17.95</t>
+          <t>$16.99 - $24.99</t>
         </is>
       </c>
       <c r="I10" s="4" t="inlineStr">
         <is>
-          <t>Amazon US Best Sellers</t>
+          <t>TikTok US Viral 24h</t>
         </is>
       </c>
       <c r="J10" s="4" t="inlineStr">
         <is>
-          <t>Amazon Best Sellers, Amazon US, TikTok Trend Validated</t>
+          <t>TikTok Shop, TikTok Viral 24h</t>
         </is>
       </c>
       <c r="K10" s="4" t="inlineStr">
         <is>
-          <t>Problem - Agitate - Solution (So sánh vi khuẩn kính hiển vi)</t>
+          <t>Side-by-side Live Demo &amp; Unboxing ASMR</t>
         </is>
       </c>
       <c r="L10" s="5" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/Clean-Skin-Club-Disposable-Sensitive/dp/B07PBXXNCY/ref=zg_bs_g_beauty_d_sccl_4/130-1584604-8661848</t>
+          <t>https://www.tiktok.com/tag/wirelessmicrophone</t>
         </is>
       </c>
     </row>
@@ -6261,12 +6266,12 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>Owala FreeSip Stainless Steel Water Bottle 24 oz Denim</t>
+          <t>STANLEY Quencher H2.0 Tumbler with Handle and Straw 30 oz | Flowstate 3-Position Lid | Cup Holder Compatible for Travel | Insulate</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>🌲 Evergreen Bền Vững</t>
+          <t>🔥 Bùng Nổ 24h (Viral Spike)</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
@@ -6275,17 +6280,17 @@
         </is>
       </c>
       <c r="E11" s="3" t="n">
-        <v>98.3</v>
+        <v>99.5</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t>2 offers from $27.29</t>
+          <t>$19.99</t>
         </is>
       </c>
       <c r="I11" s="4" t="inlineStr">
@@ -6305,7 +6310,7 @@
       </c>
       <c r="L11" s="5" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/Owala-FreeSip-Insulated-Stainless-BPA-Free/dp/B0BZYCJK89/ref=zg_bs_g_kitchen_d_sccl_1/130-1584604-8661848</t>
+          <t>https://www.amazon.com/STANLEY-Flowstate-3-Position-Compatible-Insulated/dp/B0CP9YB3Q4/ref=zg_bs_g_kitchen_d_sccl_2/142-8547974-1409324</t>
         </is>
       </c>
     </row>
@@ -6315,31 +6320,31 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>Owala FreeSip Stainless Steel Water Bottle 24 oz Denim</t>
+          <t>medicube Toner Pads Zero Pore Pad 2.0 for Exfoliation and Pore Care | Dual-Textured Facial Pad with 4.5% AHA Lactic Acid, 0.45% BH</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>🌲 Evergreen Bền Vững</t>
+          <t>🔥 Bùng Nổ 24h (Viral Spike)</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>Kitchenware</t>
+          <t>Beauty &amp; Personal Care</t>
         </is>
       </c>
       <c r="E12" s="3" t="n">
-        <v>98.3</v>
+        <v>99.40000000000001</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="H12" s="3" t="inlineStr">
         <is>
-          <t>2 offers from $27.29</t>
+          <t>$19.99</t>
         </is>
       </c>
       <c r="I12" s="4" t="inlineStr">
@@ -6354,12 +6359,12 @@
       </c>
       <c r="K12" s="4" t="inlineStr">
         <is>
-          <t>Drop Test &amp; Leak-proof Challenge (Thử thách va đập &amp; chống đổ nước)</t>
+          <t>Before/After Macro Skin Texture Zoom (Cận cảnh bề mặt da)</t>
         </is>
       </c>
       <c r="L12" s="5" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/Owala-FreeSip-Insulated-Stainless-BPA-Free/dp/B0BZYCJK89/ref=zg_bs_g_home-garden_d_sccl_1/130-1584604-8661848</t>
+          <t>https://www.amazon.com/Medicube-Zero-Pore-Pads-Dual-Textured/dp/B09V7Z4TJG/ref=zg_bs_g_beauty_d_sccl_2/142-8547974-1409324</t>
         </is>
       </c>
     </row>
@@ -6369,12 +6374,12 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Owala SmoothSip Slider Insulated Stainless Steel Coffee Tumbler, Reusable Iced Coffee Cup, Hot Coffee Travel Mug, BPA Free 20 oz, </t>
+          <t xml:space="preserve">HydroJug Traveler 40oz, Insulated Tumbler with Handle &amp; Straw, Pink Sand | Triple wall insulated, flip straw lid, leak-resistant, </t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>🌲 Evergreen Bền Vững</t>
+          <t>🔥 Bùng Nổ 24h (Viral Spike)</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
@@ -6383,17 +6388,17 @@
         </is>
       </c>
       <c r="E13" s="3" t="n">
-        <v>96.09999999999999</v>
+        <v>99.40000000000001</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="G13" s="3" t="n">
         <v>90</v>
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t>4 offers from $22.55</t>
+          <t>$19.99</t>
         </is>
       </c>
       <c r="I13" s="4" t="inlineStr">
@@ -6408,12 +6413,12 @@
       </c>
       <c r="K13" s="4" t="inlineStr">
         <is>
-          <t>Drop Test &amp; Leak-proof Challenge (Thử thách va đập &amp; chống đổ nước)</t>
+          <t>Before/After Macro Skin Texture Zoom (Cận cảnh bề mặt da)</t>
         </is>
       </c>
       <c r="L13" s="5" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/Owala-SmoothSip-Insulated-Stainless-Reusable/dp/B0DF3M7V3T/ref=zg_bs_g_kitchen_d_sccl_5/130-1584604-8661848</t>
+          <t>https://www.amazon.com/HydroJug-Traveler-Resistant-Bottle-Reusable-Insulated/dp/B0CQVWT2NH/ref=zg_bs_g_kitchen_d_sccl_3/142-8547974-1409324</t>
         </is>
       </c>
     </row>
@@ -6423,7 +6428,7 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>eos Shea Better Body Lotion- Vanilla Cashmere, 24-Hour Moisture, 16 fl oz</t>
+          <t>Mighty Patch Hero Cosmetics Original Nighttime Acne Pimple Patches, 36 Ct | #1 Hydrocolloid Acne Patches, Shrinking Zits &amp; Whitehe</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
@@ -6433,11 +6438,11 @@
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>Beauty &amp; Skincare</t>
+          <t>Beauty &amp; Personal Care</t>
         </is>
       </c>
       <c r="E14" s="3" t="n">
-        <v>94.2</v>
+        <v>99.2</v>
       </c>
       <c r="F14" s="3" t="n">
         <v>92</v>
@@ -6447,7 +6452,7 @@
       </c>
       <c r="H14" s="3" t="inlineStr">
         <is>
-          <t>$9.97</t>
+          <t>$19.99</t>
         </is>
       </c>
       <c r="I14" s="4" t="inlineStr">
@@ -6457,7 +6462,7 @@
       </c>
       <c r="J14" s="4" t="inlineStr">
         <is>
-          <t>Amazon Best Sellers, Amazon US</t>
+          <t>Amazon Best Sellers, Amazon US, TikTok Trend Validated</t>
         </is>
       </c>
       <c r="K14" s="4" t="inlineStr">
@@ -6467,7 +6472,7 @@
       </c>
       <c r="L14" s="5" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/eos-Cashmere-Moisture-Lightweight-Non-Greasy/dp/B08KT2Z93D/ref=zg_bs_g_beauty_d_sccl_1/130-1584604-8661848</t>
+          <t>https://www.amazon.com/Mighty-Patch-Hydrocolloid-Absorbing-count/dp/B074PVTPBW/ref=zg_bs_g_beauty_d_sccl_5/142-8547974-1409324</t>
         </is>
       </c>
     </row>
@@ -6477,7 +6482,7 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Neutrogena Makeup Remover Micellar Wipes, 2 Pack of 25 Ct | Plant-Based Micellar Water Cleansing Cloths, Gently Removes Oil, Dirt </t>
+          <t>STANLEY IceFlow 2.0 Flip Straw Tumbler, 30 oz, Black 2.0 | Easy Carry Handle | Twist On Lid and Flip Up Straw | Leak Resistant Wat</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
@@ -6487,11 +6492,11 @@
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>Home Supplies</t>
+          <t>Kitchenware</t>
         </is>
       </c>
       <c r="E15" s="3" t="n">
-        <v>94.2</v>
+        <v>99.2</v>
       </c>
       <c r="F15" s="3" t="n">
         <v>92</v>
@@ -6501,7 +6506,7 @@
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
-          <t>$9.97</t>
+          <t>$19.99</t>
         </is>
       </c>
       <c r="I15" s="4" t="inlineStr">
@@ -6511,7 +6516,7 @@
       </c>
       <c r="J15" s="4" t="inlineStr">
         <is>
-          <t>Amazon Best Sellers, Amazon US</t>
+          <t>Amazon Best Sellers, Amazon US, TikTok Trend Validated</t>
         </is>
       </c>
       <c r="K15" s="4" t="inlineStr">
@@ -6521,7 +6526,7 @@
       </c>
       <c r="L15" s="5" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/Neutrogena-Makeup-Remover-Micellar-Wipes/dp/B00U2VQZDS/ref=zg_bs_g_beauty_d_sccl_6/130-1584604-8661848</t>
+          <t>https://www.amazon.com/STANLEY-IceFlow-Straw-Tumbler-Black/dp/B0DR9PMK1W/ref=zg_bs_g_kitchen_d_sccl_6/142-8547974-1409324</t>
         </is>
       </c>
     </row>
@@ -6531,7 +6536,7 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>TERRO Liquid Ant Killer Bait Stations, 12-Pack, Indoor Ant Traps, T300B | Borax Formula, Kills the Queen &amp; the Entire Colony, Liqu</t>
+          <t>Clean Skin Club Clean Towels XL®, 100% USDA Biobased Face Towel, Disposable Face Towelette, Eczema Association Accepted, Makeup Re</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
@@ -6541,21 +6546,21 @@
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>Home Gadgets</t>
+          <t>Beauty &amp; Personal Care</t>
         </is>
       </c>
       <c r="E16" s="3" t="n">
-        <v>94.2</v>
+        <v>98.3</v>
       </c>
       <c r="F16" s="3" t="n">
         <v>92</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
-          <t>8 offers from $7.09</t>
+          <t>$19.99</t>
         </is>
       </c>
       <c r="I16" s="4" t="inlineStr">
@@ -6565,17 +6570,17 @@
       </c>
       <c r="J16" s="4" t="inlineStr">
         <is>
-          <t>Amazon Best Sellers, Amazon US</t>
+          <t>Amazon Best Sellers, Amazon US, TikTok Trend Validated</t>
         </is>
       </c>
       <c r="K16" s="4" t="inlineStr">
         <is>
-          <t>TikTok Made Me Buy It / Honest Review</t>
+          <t>Problem - Agitate - Solution (So sánh vi khuẩn kính hiển vi)</t>
         </is>
       </c>
       <c r="L16" s="5" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/TERRO-T300-2-2-Pack-Liquid-Baits/dp/B00E4GACB8/ref=zg_bs_g_home-garden_d_sccl_2/130-1584604-8661848</t>
+          <t>https://www.amazon.com/Clean-Skin-Club-Disposable-Sensitive/dp/B07PBXXNCY/ref=zg_bs_g_beauty_d_sccl_4/142-8547974-1409324</t>
         </is>
       </c>
     </row>
@@ -6585,7 +6590,7 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>Amazon Basics Lightweight Super Soft Breathable Wrinkle-Resistant Microfiber 4-Piece Bed Sheet Set with 14-Inch Deep Pockets, Quee</t>
+          <t>Owala FreeSip Stainless Steel Water Bottle 24 oz Denim</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
@@ -6595,21 +6600,21 @@
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>Phones &amp; Electronics</t>
+          <t>Kitchenware</t>
         </is>
       </c>
       <c r="E17" s="3" t="n">
-        <v>94.2</v>
+        <v>98.3</v>
       </c>
       <c r="F17" s="3" t="n">
         <v>92</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
-          <t>7 offers from $13.44</t>
+          <t>$19.99</t>
         </is>
       </c>
       <c r="I17" s="4" t="inlineStr">
@@ -6619,17 +6624,17 @@
       </c>
       <c r="J17" s="4" t="inlineStr">
         <is>
-          <t>Amazon Best Sellers, Amazon US</t>
+          <t>Amazon Best Sellers, Amazon US, TikTok Trend Validated</t>
         </is>
       </c>
       <c r="K17" s="4" t="inlineStr">
         <is>
-          <t>Side-by-side Live Demo &amp; Unboxing ASMR</t>
+          <t>Drop Test &amp; Leak-proof Challenge (Thử thách va đập &amp; chống đổ nước)</t>
         </is>
       </c>
       <c r="L17" s="5" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/Amazon-Basics-Microfiber-Lightweight-Wrinkle-free/dp/B0154ASID6/ref=zg_bs_g_home-garden_d_sccl_3/130-1584604-8661848</t>
+          <t>https://www.amazon.com/Owala-FreeSip-Insulated-Stainless-BPA-Free/dp/B0BZYCJK89/ref=zg_bs_g_kitchen_d_sccl_1/142-8547974-1409324</t>
         </is>
       </c>
     </row>
@@ -6639,7 +6644,7 @@
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>Dr. Elsey's Ultra UnScented Clumping Clay Cat Litter 40 lb. Bag</t>
+          <t>Owala FreeSip Stainless Steel Water Bottle 24 oz Denim</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
@@ -6649,21 +6654,21 @@
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>Pet Supplies</t>
+          <t>Kitchenware</t>
         </is>
       </c>
       <c r="E18" s="3" t="n">
-        <v>94.2</v>
+        <v>98.3</v>
       </c>
       <c r="F18" s="3" t="n">
         <v>92</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="H18" s="3" t="inlineStr">
         <is>
-          <t>$22.99</t>
+          <t>1 offer from $29.99</t>
         </is>
       </c>
       <c r="I18" s="4" t="inlineStr">
@@ -6673,17 +6678,17 @@
       </c>
       <c r="J18" s="4" t="inlineStr">
         <is>
-          <t>Amazon Best Sellers, Amazon US</t>
+          <t>Amazon Best Sellers, Amazon US, TikTok Trend Validated</t>
         </is>
       </c>
       <c r="K18" s="4" t="inlineStr">
         <is>
-          <t>Emotional Reaction &amp; Satisfying Fur Release ASMR</t>
+          <t>Drop Test &amp; Leak-proof Challenge (Thử thách va đập &amp; chống đổ nước)</t>
         </is>
       </c>
       <c r="L18" s="5" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/Dr-Elseys-Premium-Clumping-Litter/dp/B0009X29WK/ref=zg_bs_g_pet-supplies_d_sccl_1/130-1584604-8661848</t>
+          <t>https://www.amazon.com/Owala-FreeSip-Insulated-Stainless-BPA-Free/dp/B0BZYCJK89/ref=zg_bs_g_home-garden_d_sccl_1/142-8547974-1409324</t>
         </is>
       </c>
     </row>
@@ -6693,7 +6698,7 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>Amazon Basics Leak-Proof Dog and Puppy Potty Training Pee Pads with Quick-Dry 5-Layer Super Absorbent Design, Regular Size 22 x 22</t>
+          <t xml:space="preserve">Owala SmoothSip Slider Insulated Stainless Steel Coffee Tumbler, Reusable Iced Coffee Cup, Hot Coffee Travel Mug, BPA Free 20 oz, </t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
@@ -6703,21 +6708,21 @@
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>Pet Supplies</t>
+          <t>Kitchenware</t>
         </is>
       </c>
       <c r="E19" s="3" t="n">
-        <v>94.2</v>
+        <v>96.09999999999999</v>
       </c>
       <c r="F19" s="3" t="n">
         <v>92</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="H19" s="3" t="inlineStr">
         <is>
-          <t>1 offer from $18.99</t>
+          <t>$19.99</t>
         </is>
       </c>
       <c r="I19" s="4" t="inlineStr">
@@ -6727,17 +6732,17 @@
       </c>
       <c r="J19" s="4" t="inlineStr">
         <is>
-          <t>Amazon Best Sellers, Amazon US</t>
+          <t>Amazon Best Sellers, Amazon US, TikTok Trend Validated</t>
         </is>
       </c>
       <c r="K19" s="4" t="inlineStr">
         <is>
-          <t>Emotional Reaction &amp; Satisfying Fur Release ASMR</t>
+          <t>Drop Test &amp; Leak-proof Challenge (Thử thách va đập &amp; chống đổ nước)</t>
         </is>
       </c>
       <c r="L19" s="5" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/Amazon-Basics-Leak-Proof-Quick-Dry-Absorbency/dp/B00MW8G62E/ref=zg_bs_g_pet-supplies_d_sccl_2/130-1584604-8661848</t>
+          <t>https://www.amazon.com/Owala-SmoothSip-Insulated-Stainless-Reusable/dp/B0DF3M7V3T/ref=zg_bs_g_kitchen_d_sccl_5/142-8547974-1409324</t>
         </is>
       </c>
     </row>
@@ -6747,7 +6752,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>Purina Fancy Feast Gravy Lovers Wet Cat Food, 3 oz Cans, 30-Pack | Variety Pack with poultry and beef grilled gourmet recipes, mad</t>
+          <t>eos Shea Better Body Lotion- Vanilla Cashmere, 24-Hour Moisture, 16 fl oz</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
@@ -6757,7 +6762,7 @@
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>Pet Supplies</t>
+          <t>Beauty &amp; Skincare</t>
         </is>
       </c>
       <c r="E20" s="3" t="n">
@@ -6771,7 +6776,7 @@
       </c>
       <c r="H20" s="3" t="inlineStr">
         <is>
-          <t>6 offers from $28.06</t>
+          <t>$19.99</t>
         </is>
       </c>
       <c r="I20" s="4" t="inlineStr">
@@ -6786,12 +6791,12 @@
       </c>
       <c r="K20" s="4" t="inlineStr">
         <is>
-          <t>Emotional Reaction &amp; Satisfying Fur Release ASMR</t>
+          <t>Before/After Macro Skin Texture Zoom (Cận cảnh bề mặt da)</t>
         </is>
       </c>
       <c r="L20" s="5" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/Purina-Fancy-Feast-Poultry-Collection/dp/B00JN9IWNG/ref=zg_bs_g_pet-supplies_d_sccl_3/130-1584604-8661848</t>
+          <t>https://www.amazon.com/eos-Cashmere-Moisture-Lightweight-Non-Greasy/dp/B08KT2Z93D/ref=zg_bs_g_beauty_d_sccl_1/142-8547974-1409324</t>
         </is>
       </c>
     </row>
@@ -6801,7 +6806,7 @@
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>Amazon Basics Double-Tipped Cotton Swabs for Personal Hygiene and Baby Care, Cotton, Versatile, Baby Safe, 500 Count</t>
+          <t xml:space="preserve">Neutrogena Makeup Remover Micellar Wipes, 2 Pack of 25 Ct | Plant-Based Micellar Water Cleansing Cloths, Gently Removes Oil, Dirt </t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
@@ -6811,21 +6816,21 @@
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>Automotive &amp; Motorcycle</t>
+          <t>Home Supplies</t>
         </is>
       </c>
       <c r="E21" s="3" t="n">
-        <v>93.3</v>
+        <v>94.2</v>
       </c>
       <c r="F21" s="3" t="n">
         <v>92</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="H21" s="3" t="inlineStr">
         <is>
-          <t>$2.67</t>
+          <t>$19.99</t>
         </is>
       </c>
       <c r="I21" s="4" t="inlineStr">
@@ -6845,7 +6850,7 @@
       </c>
       <c r="L21" s="5" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/Amazon-Basics-Cotton-Swabs-500ct/dp/B09541P9WH/ref=zg_bs_g_beauty_d_sccl_3/130-1584604-8661848</t>
+          <t>https://www.amazon.com/Neutrogena-Makeup-Remover-Micellar-Wipes/dp/B00U2VQZDS/ref=zg_bs_g_beauty_d_sccl_6/142-8547974-1409324</t>
         </is>
       </c>
     </row>
@@ -6855,7 +6860,7 @@
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>blink plus plan with monthly auto-renewal</t>
+          <t>TERRO Liquid Ant Killer Bait Stations, 12-Pack, Indoor Ant Traps, T300B | Borax Formula, Kills the Queen &amp; the Entire Colony, Liqu</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
@@ -6865,21 +6870,21 @@
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>Tech Gadgets</t>
+          <t>Home Gadgets</t>
         </is>
       </c>
       <c r="E22" s="3" t="n">
-        <v>92</v>
+        <v>94.2</v>
       </c>
       <c r="F22" s="3" t="n">
         <v>92</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="H22" s="3" t="inlineStr">
         <is>
-          <t>$11.99</t>
+          <t>8 offers from $7.09</t>
         </is>
       </c>
       <c r="I22" s="4" t="inlineStr">
@@ -6899,7 +6904,7 @@
       </c>
       <c r="L22" s="5" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/Blink-Plus-Plan-monthly-auto-renewal/dp/B08JHCVHTY/ref=zg_bs_g_electronics_d_sccl_1/130-1584604-8661848</t>
+          <t>https://www.amazon.com/TERRO-T300-2-2-Pack-Liquid-Baits/dp/B00E4GACB8/ref=zg_bs_g_home-garden_d_sccl_2/142-8547974-1409324</t>
         </is>
       </c>
     </row>
@@ -6909,7 +6914,7 @@
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>Etekcity Food Kitchen Scale, Digital Grams and Ounces, 11lb | Tare function, ideal for baking, weight loss, keto, meal prep, packa</t>
+          <t>Amazon Basics Lightweight Super Soft Breathable Wrinkle-Resistant Microfiber 4-Piece Bed Sheet Set with 14-Inch Deep Pockets, Quee</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
@@ -6919,21 +6924,21 @@
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>Home &amp; Kitchen</t>
+          <t>Phones &amp; Electronics</t>
         </is>
       </c>
       <c r="E23" s="3" t="n">
-        <v>91</v>
+        <v>94.2</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="G23" s="3" t="n">
         <v>97</v>
       </c>
       <c r="H23" s="3" t="inlineStr">
         <is>
-          <t>14 offers from $8.79</t>
+          <t>7 offers from $13.44</t>
         </is>
       </c>
       <c r="I23" s="4" t="inlineStr">
@@ -6948,12 +6953,12 @@
       </c>
       <c r="K23" s="4" t="inlineStr">
         <is>
-          <t>TikTok Made Me Buy It / Honest Review</t>
+          <t>Side-by-side Live Demo &amp; Unboxing ASMR</t>
         </is>
       </c>
       <c r="L23" s="5" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/Etekcity-Multifunction-Stainless-Batteries-Included/dp/B0113UZJE2/ref=zg_bs_g_kitchen_d_sccl_4/130-1584604-8661848</t>
+          <t>https://www.amazon.com/Amazon-Basics-Microfiber-Lightweight-Wrinkle-free/dp/B0154ASID6/ref=zg_bs_g_home-garden_d_sccl_3/142-8547974-1409324</t>
         </is>
       </c>
     </row>
@@ -6963,7 +6968,7 @@
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Queen Size 4 Piece Sheet Set - Comfy Breathable &amp; Cooling Sheets - White | Hotel Luxury Bed Sheets for Women &amp; Men, Deep Pockets, </t>
+          <t>Dr. Elsey's Ultra UnScented Clumping Clay Cat Litter 40 lb. Bag</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
@@ -6973,21 +6978,21 @@
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>Menswear &amp; Underwear</t>
+          <t>Pet Supplies</t>
         </is>
       </c>
       <c r="E24" s="3" t="n">
-        <v>91</v>
+        <v>94.2</v>
       </c>
       <c r="F24" s="3" t="n">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="G24" s="3" t="n">
         <v>97</v>
       </c>
       <c r="H24" s="3" t="inlineStr">
         <is>
-          <t>$24.99</t>
+          <t>$22.99</t>
         </is>
       </c>
       <c r="I24" s="4" t="inlineStr">
@@ -7002,12 +7007,12 @@
       </c>
       <c r="K24" s="4" t="inlineStr">
         <is>
-          <t>TikTok Made Me Buy It / Honest Review</t>
+          <t>Emotional Reaction &amp; Satisfying Fur Release ASMR</t>
         </is>
       </c>
       <c r="L24" s="5" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/Queen-Size-Piece-Sheet-Set/dp/B01M16WBW1/ref=zg_bs_g_home-garden_d_sccl_4/130-1584604-8661848</t>
+          <t>https://www.amazon.com/Dr-Elseys-Premium-Clumping-Litter/dp/B0009X29WK/ref=zg_bs_g_pet-supplies_d_sccl_1/142-8547974-1409324</t>
         </is>
       </c>
     </row>
@@ -7017,7 +7022,7 @@
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>Zevo Flying Insect Trap for Fruit Flies &amp; Gnats, 1 Plug-in Base &amp; 1 Refills | Catches Fruit Flies &amp; Gnats Near Fruit Bowls &amp; Trash</t>
+          <t>Amazon Basics Leak-Proof Dog and Puppy Potty Training Pee Pads with Quick-Dry 5-Layer Super Absorbent Design, Regular Size 22 x 22</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
@@ -7031,17 +7036,17 @@
         </is>
       </c>
       <c r="E25" s="3" t="n">
-        <v>91</v>
+        <v>94.2</v>
       </c>
       <c r="F25" s="3" t="n">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="G25" s="3" t="n">
         <v>97</v>
       </c>
       <c r="H25" s="3" t="inlineStr">
         <is>
-          <t>$19.97</t>
+          <t>1 offer from $18.99</t>
         </is>
       </c>
       <c r="I25" s="4" t="inlineStr">
@@ -7061,7 +7066,7 @@
       </c>
       <c r="L25" s="5" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/Electric-Flying-Insect-Trap-Starter/dp/B07T869RNY/ref=zg_bs_g_home-garden_d_sccl_6/130-1584604-8661848</t>
+          <t>https://www.amazon.com/Amazon-Basics-Leak-Proof-Quick-Dry-Absorbency/dp/B00MW8G62E/ref=zg_bs_g_pet-supplies_d_sccl_2/142-8547974-1409324</t>
         </is>
       </c>
     </row>
@@ -7071,7 +7076,7 @@
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>Earth Rated Dog Poop Bags on Refill Rolls, 270 Bags, Lavender | Guaranteed Leak Proof and Extra Thick Waste Bag Refill Rolls</t>
+          <t>Purina Fancy Feast Gravy Lovers Wet Cat Food, 3 oz Cans, 30-Pack | Variety Pack with poultry and beef grilled gourmet recipes, mad</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
@@ -7085,17 +7090,17 @@
         </is>
       </c>
       <c r="E26" s="3" t="n">
-        <v>91</v>
+        <v>94.2</v>
       </c>
       <c r="F26" s="3" t="n">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="G26" s="3" t="n">
         <v>97</v>
       </c>
       <c r="H26" s="3" t="inlineStr">
         <is>
-          <t>1 offer from $14.99</t>
+          <t>6 offers from $28.06</t>
         </is>
       </c>
       <c r="I26" s="4" t="inlineStr">
@@ -7115,7 +7120,7 @@
       </c>
       <c r="L26" s="5" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/Earth-Rated-Lavender-Scented-Completely/dp/B00BSYR7K8/ref=zg_bs_g_pet-supplies_d_sccl_5/130-1584604-8661848</t>
+          <t>https://www.amazon.com/Purina-Fancy-Feast-Poultry-Collection/dp/B00JN9IWNG/ref=zg_bs_g_pet-supplies_d_sccl_3/142-8547974-1409324</t>
         </is>
       </c>
     </row>
@@ -7125,31 +7130,31 @@
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>Apple EarPods Headphones with USB-C Plug, Wired Ear Buds with Built-in Remote to Control Music, Phone Calls, and Volume</t>
+          <t>Amazon Basics Double-Tipped Cotton Swabs for Personal Hygiene and Baby Care, Cotton, Versatile, Baby Safe, 500 Count</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>🔥 Bùng Nổ 24h (Viral Spike)</t>
+          <t>🌲 Evergreen Bền Vững</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>Phones &amp; Electronics</t>
+          <t>Automotive &amp; Motorcycle</t>
         </is>
       </c>
       <c r="E27" s="3" t="n">
-        <v>88.8</v>
+        <v>93.3</v>
       </c>
       <c r="F27" s="3" t="n">
         <v>92</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="H27" s="3" t="inlineStr">
         <is>
-          <t>18 offers from $17.87</t>
+          <t>$19.99</t>
         </is>
       </c>
       <c r="I27" s="4" t="inlineStr">
@@ -7164,12 +7169,12 @@
       </c>
       <c r="K27" s="4" t="inlineStr">
         <is>
-          <t>TikTok Made Me Buy It / Honest Review</t>
+          <t>Before/After Macro Skin Texture Zoom (Cận cảnh bề mặt da)</t>
         </is>
       </c>
       <c r="L27" s="5" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/Apple-EarPods-Headphones-Built-Control/dp/B0DCH8VDXF/ref=zg_bs_g_electronics_d_sccl_2/130-1584604-8661848</t>
+          <t>https://www.amazon.com/Amazon-Basics-Cotton-Swabs-500ct/dp/B09541P9WH/ref=zg_bs_g_beauty_d_sccl_3/142-8547974-1409324</t>
         </is>
       </c>
     </row>
@@ -7179,31 +7184,31 @@
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>Apple AirTag (2nd Generation): Tracker for Keychain, Wallet, and More; Locator with Sound; Simple One-Tap Setup with iPhone or iPa</t>
+          <t>blink plus plan with monthly auto-renewal</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>🔥 Bùng Nổ 24h (Viral Spike)</t>
+          <t>🌲 Evergreen Bền Vững</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>Pet Supplies</t>
+          <t>Tech Gadgets</t>
         </is>
       </c>
       <c r="E28" s="3" t="n">
-        <v>88.8</v>
+        <v>92</v>
       </c>
       <c r="F28" s="3" t="n">
         <v>92</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="H28" s="3" t="inlineStr">
         <is>
-          <t>10 offers from $22.32</t>
+          <t>$11.99</t>
         </is>
       </c>
       <c r="I28" s="4" t="inlineStr">
@@ -7218,12 +7223,12 @@
       </c>
       <c r="K28" s="4" t="inlineStr">
         <is>
-          <t>Emotional Reaction &amp; Satisfying Fur Release ASMR</t>
+          <t>TikTok Made Me Buy It / Honest Review</t>
         </is>
       </c>
       <c r="L28" s="5" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/Apple-AirTag-2nd-Generation-Precision/dp/B0GJTFXNRX/ref=zg_bs_g_electronics_d_sccl_3/130-1584604-8661848</t>
+          <t>https://www.amazon.com/Blink-Plus-Plan-monthly-auto-renewal/dp/B08JHCVHTY/ref=zg_bs_g_electronics_d_sccl_1/142-8547974-1409324</t>
         </is>
       </c>
     </row>
@@ -7233,31 +7238,31 @@
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>Zevo Flying Insect Trap Refill Cartridges for Fruit Flies &amp; Gnats, 4 Count | Fits Zevo MAX &amp; Zevo Flying Insect Trap, Catches Hous</t>
+          <t>Apple EarPods Headphones with USB-C Plug, Wired Ear Buds with Built-in Remote to Control Music, Phone Calls, and Volume</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>🌲 Evergreen Bền Vững</t>
+          <t>🔥 Bùng Nổ 24h (Viral Spike)</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>Pet Supplies</t>
+          <t>Phones &amp; Electronics</t>
         </is>
       </c>
       <c r="E29" s="3" t="n">
-        <v>87.8</v>
+        <v>88.8</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="H29" s="3" t="inlineStr">
         <is>
-          <t>$14.97</t>
+          <t>18 offers from $17.87</t>
         </is>
       </c>
       <c r="I29" s="4" t="inlineStr">
@@ -7272,12 +7277,12 @@
       </c>
       <c r="K29" s="4" t="inlineStr">
         <is>
-          <t>Emotional Reaction &amp; Satisfying Fur Release ASMR</t>
+          <t>TikTok Made Me Buy It / Honest Review</t>
         </is>
       </c>
       <c r="L29" s="5" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/ZEVO-Flying-Insect-Refills-Indoor/dp/B0C3FTCYZL/ref=zg_bs_g_home-garden_d_sccl_5/130-1584604-8661848</t>
+          <t>https://www.amazon.com/Apple-EarPods-Headphones-Built-Control/dp/B0DCH8VDXF/ref=zg_bs_g_electronics_d_sccl_2/142-8547974-1409324</t>
         </is>
       </c>
     </row>
@@ -7287,31 +7292,31 @@
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>Apple AirPods 4 Wireless Earbuds | Bluetooth Headphones, Personalized Spatial Audio, Sweat &amp; Water Resistant, USB-C Charging Case,</t>
+          <t>Apple AirTag (2nd Generation): Tracker for Keychain, Wallet, and More; Locator with Sound; Simple One-Tap Setup with iPhone or iPa</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>🌲 Evergreen Bền Vững</t>
+          <t>🔥 Bùng Nổ 24h (Viral Spike)</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>Phones &amp; Electronics</t>
+          <t>Pet Supplies</t>
         </is>
       </c>
       <c r="E30" s="3" t="n">
-        <v>87.8</v>
+        <v>88.8</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
-          <t>47 offers from $91.26</t>
+          <t>10 offers from $22.32</t>
         </is>
       </c>
       <c r="I30" s="4" t="inlineStr">
@@ -7326,12 +7331,12 @@
       </c>
       <c r="K30" s="4" t="inlineStr">
         <is>
-          <t>Side-by-side Live Demo &amp; Unboxing ASMR</t>
+          <t>Emotional Reaction &amp; Satisfying Fur Release ASMR</t>
         </is>
       </c>
       <c r="L30" s="5" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/Apple-Bluetooth-Headphones-Personalized-Effortless/dp/B0DGHMNQ5Z/ref=zg_bs_g_electronics_d_sccl_6/130-1584604-8661848</t>
+          <t>https://www.amazon.com/Apple-AirTag-2nd-Generation-Precision/dp/B0GJTFXNRX/ref=zg_bs_g_electronics_d_sccl_3/142-8547974-1409324</t>
         </is>
       </c>
     </row>
@@ -7341,7 +7346,7 @@
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>Greenies Pill Pockets Large Size Dog Treats, Peanut Butter, 15.8 oz | Vet-recommended, masks pill smell &amp; taste, moldable texture,</t>
+          <t>Etekcity Food Kitchen Scale, Digital Grams and Ounces, 11lb | Tare function, ideal for baking, weight loss, keto, meal prep, packa</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
@@ -7351,21 +7356,21 @@
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>Pet Supplies</t>
+          <t>Home &amp; Kitchen</t>
         </is>
       </c>
       <c r="E31" s="3" t="n">
-        <v>87.8</v>
+        <v>91</v>
       </c>
       <c r="F31" s="3" t="n">
         <v>86</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>90</v>
+        <v>97</v>
       </c>
       <c r="H31" s="3" t="inlineStr">
         <is>
-          <t>4 offers from $21.99</t>
+          <t>$19.99</t>
         </is>
       </c>
       <c r="I31" s="4" t="inlineStr">
@@ -7380,12 +7385,12 @@
       </c>
       <c r="K31" s="4" t="inlineStr">
         <is>
-          <t>Emotional Reaction &amp; Satisfying Fur Release ASMR</t>
+          <t>TikTok Made Me Buy It / Honest Review</t>
         </is>
       </c>
       <c r="L31" s="5" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/Greenies-Pockets-Natural-Treats-Capsule/dp/B07S2TDDCK/ref=zg_bs_g_pet-supplies_d_sccl_4/130-1584604-8661848</t>
+          <t>https://www.amazon.com/Etekcity-Multifunction-Stainless-Batteries-Included/dp/B0113UZJE2/ref=zg_bs_g_kitchen_d_sccl_4/142-8547974-1409324</t>
         </is>
       </c>
     </row>
@@ -7395,7 +7400,7 @@
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>INABA Churu Cat Treats, Lickable, Squeezable Creamy Purée Cat Treat with Green Tea Extract &amp; Taurine, 0.5 Ounces Each Tube, 50 Tub</t>
+          <t xml:space="preserve">Queen Size 4 Piece Sheet Set - Comfy Breathable &amp; Cooling Sheets - White | Hotel Luxury Bed Sheets for Women &amp; Men, Deep Pockets, </t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
@@ -7405,21 +7410,21 @@
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>Pet Supplies</t>
+          <t>Menswear &amp; Underwear</t>
         </is>
       </c>
       <c r="E32" s="3" t="n">
-        <v>87.8</v>
+        <v>91</v>
       </c>
       <c r="F32" s="3" t="n">
         <v>86</v>
       </c>
       <c r="G32" s="3" t="n">
-        <v>90</v>
+        <v>97</v>
       </c>
       <c r="H32" s="3" t="inlineStr">
         <is>
-          <t>3 offers from $32.96</t>
+          <t>$24.99</t>
         </is>
       </c>
       <c r="I32" s="4" t="inlineStr">
@@ -7434,12 +7439,12 @@
       </c>
       <c r="K32" s="4" t="inlineStr">
         <is>
-          <t>Emotional Reaction &amp; Satisfying Fur Release ASMR</t>
+          <t>TikTok Made Me Buy It / Honest Review</t>
         </is>
       </c>
       <c r="L32" s="5" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/INABA-Chicken-Lickable-Creamy-Variety/dp/B07D323MFZ/ref=zg_bs_g_pet-supplies_d_sccl_6/130-1584604-8661848</t>
+          <t>https://www.amazon.com/Queen-Size-Piece-Sheet-Set/dp/B01M16WBW1/ref=zg_bs_g_home-garden_d_sccl_4/142-8547974-1409324</t>
         </is>
       </c>
     </row>
@@ -7449,31 +7454,31 @@
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>Amazon Fire TV Stick 4K Select (newest model), start streaming in 4K, AI-powered search, and free &amp; live TV, find shows faster wit</t>
+          <t>Zevo Flying Insect Trap for Fruit Flies &amp; Gnats, 1 Plug-in Base &amp; 1 Refills | Catches Fruit Flies &amp; Gnats Near Fruit Bowls &amp; Trash</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>🔥 Xu Hướng Tăng Trưởng</t>
+          <t>🌲 Evergreen Bền Vững</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>Tech Gadgets</t>
+          <t>Pet Supplies</t>
         </is>
       </c>
       <c r="E33" s="3" t="n">
-        <v>85.59999999999999</v>
+        <v>91</v>
       </c>
       <c r="F33" s="3" t="n">
         <v>86</v>
       </c>
       <c r="G33" s="3" t="n">
-        <v>85</v>
+        <v>97</v>
       </c>
       <c r="H33" s="3" t="inlineStr">
         <is>
-          <t>1 offer from $49.99</t>
+          <t>$19.97</t>
         </is>
       </c>
       <c r="I33" s="4" t="inlineStr">
@@ -7488,12 +7493,12 @@
       </c>
       <c r="K33" s="4" t="inlineStr">
         <is>
-          <t>TikTok Made Me Buy It / Honest Review</t>
+          <t>Emotional Reaction &amp; Satisfying Fur Release ASMR</t>
         </is>
       </c>
       <c r="L33" s="5" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/amazon-fire-tv-stick-4K-select/dp/B0C6W3D4RM/ref=zg_bs_g_electronics_d_sccl_4/130-1584604-8661848</t>
+          <t>https://www.amazon.com/Electric-Flying-Insect-Trap-Starter/dp/B07T869RNY/ref=zg_bs_g_home-garden_d_sccl_6/142-8547974-1409324</t>
         </is>
       </c>
     </row>
@@ -7503,31 +7508,31 @@
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>Apple AirPods Pro 3 Wireless Earbuds with Active Noise Cancellation | Live Translation, Heart Rate Sensing, Hearing Aid Feature, B</t>
+          <t>Earth Rated Dog Poop Bags on Refill Rolls, 270 Bags, Lavender | Guaranteed Leak Proof and Extra Thick Waste Bag Refill Rolls</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>🔥 Xu Hướng Tăng Trưởng</t>
+          <t>🌲 Evergreen Bền Vững</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>Jewelry Accessories &amp; Derivatives</t>
+          <t>Pet Supplies</t>
         </is>
       </c>
       <c r="E34" s="3" t="n">
-        <v>85.59999999999999</v>
+        <v>91</v>
       </c>
       <c r="F34" s="3" t="n">
         <v>86</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>85</v>
+        <v>97</v>
       </c>
       <c r="H34" s="3" t="inlineStr">
         <is>
-          <t>12 offers from $183.44</t>
+          <t>1 offer from $14.99</t>
         </is>
       </c>
       <c r="I34" s="4" t="inlineStr">
@@ -7542,12 +7547,12 @@
       </c>
       <c r="K34" s="4" t="inlineStr">
         <is>
-          <t>Side-by-side Live Demo &amp; Unboxing ASMR</t>
+          <t>Emotional Reaction &amp; Satisfying Fur Release ASMR</t>
         </is>
       </c>
       <c r="L34" s="5" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/Apple-Cancellation-Translation-Headphones-High-Fidelity/dp/B0FQFB8FMG/ref=zg_bs_g_electronics_d_sccl_5/130-1584604-8661848</t>
+          <t>https://www.amazon.com/Earth-Rated-Lavender-Scented-Completely/dp/B00BSYR7K8/ref=zg_bs_g_pet-supplies_d_sccl_5/142-8547974-1409324</t>
         </is>
       </c>
     </row>
@@ -7557,7 +7562,7 @@
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>Kettenanhänger Liebe Hoffnung Glaube Gelb Gold oder Silber glanz 15x8mm Amulett1,277,297.19 VNDShop all 22Fine Jewelry</t>
+          <t>Zevo Flying Insect Trap Refill Cartridges for Fruit Flies &amp; Gnats, 4 Count | Fits Zevo MAX &amp; Zevo Flying Insect Trap, Catches Hous</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
@@ -7567,41 +7572,41 @@
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>Jewelry Accessories &amp; Derivatives</t>
+          <t>Pet Supplies</t>
         </is>
       </c>
       <c r="E35" s="3" t="n">
-        <v>82.3</v>
+        <v>87.8</v>
       </c>
       <c r="F35" s="3" t="n">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="G35" s="3" t="n">
         <v>90</v>
       </c>
       <c r="H35" s="3" t="inlineStr">
         <is>
-          <t>$19.99</t>
+          <t>$14.97</t>
         </is>
       </c>
       <c r="I35" s="4" t="inlineStr">
         <is>
-          <t>eBay US</t>
+          <t>Amazon US Best Sellers</t>
         </is>
       </c>
       <c r="J35" s="4" t="inlineStr">
         <is>
-          <t>eBay US Deals</t>
+          <t>Amazon Best Sellers, Amazon US</t>
         </is>
       </c>
       <c r="K35" s="4" t="inlineStr">
         <is>
-          <t>TikTok Made Me Buy It / Honest Review</t>
+          <t>Emotional Reaction &amp; Satisfying Fur Release ASMR</t>
         </is>
       </c>
       <c r="L35" s="5" t="inlineStr">
         <is>
-          <t>https://www.ebay.com/itm/285242609945</t>
+          <t>https://www.amazon.com/ZEVO-Flying-Insect-Refills-Indoor/dp/B0C3FTCYZL/ref=zg_bs_g_home-garden_d_sccl_5/142-8547974-1409324</t>
         </is>
       </c>
     </row>
@@ -7611,7 +7616,7 @@
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>ICED 10k White Gold DIAMOND Curb Link HEAVY 44gr Bracelet Jewelry136,393,589.74 VNDPanzerkette 4 mm Halskette Echt 750er</t>
+          <t>Apple AirPods 4 Wireless Earbuds | Bluetooth Headphones, Personalized Spatial Audio, Sweat &amp; Water Resistant, USB-C Charging Case,</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
@@ -7621,41 +7626,41 @@
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>Kitchenware</t>
+          <t>Phones &amp; Electronics</t>
         </is>
       </c>
       <c r="E36" s="3" t="n">
-        <v>82.3</v>
+        <v>87.8</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="G36" s="3" t="n">
         <v>90</v>
       </c>
       <c r="H36" s="3" t="inlineStr">
         <is>
-          <t>$19.99</t>
+          <t>47 offers from $91.26</t>
         </is>
       </c>
       <c r="I36" s="4" t="inlineStr">
         <is>
-          <t>eBay US</t>
+          <t>Amazon US Best Sellers</t>
         </is>
       </c>
       <c r="J36" s="4" t="inlineStr">
         <is>
-          <t>eBay US Deals</t>
+          <t>Amazon Best Sellers, Amazon US</t>
         </is>
       </c>
       <c r="K36" s="4" t="inlineStr">
         <is>
-          <t>TikTok Made Me Buy It / Honest Review</t>
+          <t>Side-by-side Live Demo &amp; Unboxing ASMR</t>
         </is>
       </c>
       <c r="L36" s="5" t="inlineStr">
         <is>
-          <t>https://www.ebay.com/itm/298332862724</t>
+          <t>https://www.amazon.com/Apple-Bluetooth-Headphones-Personalized-Effortless/dp/B0DGHMNQ5Z/ref=zg_bs_g_electronics_d_sccl_6/142-8547974-1409324</t>
         </is>
       </c>
     </row>
@@ -7665,51 +7670,51 @@
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>Owala FreeSip Insulated Stainless Steel Tumbler (Leak-Proof Straw)</t>
+          <t>Greenies Pill Pockets Large Size Dog Treats, Peanut Butter, 15.8 oz | Vet-recommended, masks pill smell &amp; taste, moldable texture,</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>🔥 Bùng Nổ 24h (Viral Spike)</t>
+          <t>🌲 Evergreen Bền Vững</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>Kitchenware</t>
+          <t>Pet Supplies</t>
         </is>
       </c>
       <c r="E37" s="3" t="n">
-        <v>82</v>
+        <v>87.8</v>
       </c>
       <c r="F37" s="3" t="n">
-        <v>99</v>
+        <v>86</v>
       </c>
       <c r="G37" s="3" t="n">
-        <v>50</v>
+        <v>90</v>
       </c>
       <c r="H37" s="3" t="inlineStr">
         <is>
-          <t>$27.99 - $37.99</t>
+          <t>4 offers from $21.99</t>
         </is>
       </c>
       <c r="I37" s="4" t="inlineStr">
         <is>
-          <t>TikTok US Viral 24h</t>
+          <t>Amazon US Best Sellers</t>
         </is>
       </c>
       <c r="J37" s="4" t="inlineStr">
         <is>
-          <t>TikTok Shop, TikTok Viral 24h, Amazon Top 100</t>
+          <t>Amazon Best Sellers, Amazon US</t>
         </is>
       </c>
       <c r="K37" s="4" t="inlineStr">
         <is>
-          <t>Drop Test &amp; Leak-proof Challenge (Thử thách va đập &amp; chống đổ nước)</t>
+          <t>Emotional Reaction &amp; Satisfying Fur Release ASMR</t>
         </is>
       </c>
       <c r="L37" s="5" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/tag/owala</t>
+          <t>https://www.amazon.com/Greenies-Pockets-Natural-Treats-Capsule/dp/B07S2TDDCK/ref=zg_bs_g_pet-supplies_d_sccl_4/142-8547974-1409324</t>
         </is>
       </c>
     </row>
@@ -7719,51 +7724,51 @@
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>Hero Cosmetics Mighty Patch Original Hydrocolloid Acne Dots</t>
+          <t>INABA Churu Cat Treats, Lickable, Squeezable Creamy Purée Cat Treat with Green Tea Extract &amp; Taurine, 0.5 Ounces Each Tube, 50 Tub</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>🔥 Bùng Nổ 24h (Viral Spike)</t>
+          <t>🌲 Evergreen Bền Vững</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>Beauty &amp; Personal Care</t>
+          <t>Pet Supplies</t>
         </is>
       </c>
       <c r="E38" s="3" t="n">
-        <v>82</v>
+        <v>87.8</v>
       </c>
       <c r="F38" s="3" t="n">
-        <v>99</v>
+        <v>86</v>
       </c>
       <c r="G38" s="3" t="n">
-        <v>50</v>
+        <v>90</v>
       </c>
       <c r="H38" s="3" t="inlineStr">
         <is>
-          <t>$12.99 - $14.99</t>
+          <t>3 offers from $32.96</t>
         </is>
       </c>
       <c r="I38" s="4" t="inlineStr">
         <is>
-          <t>TikTok US Viral 24h</t>
+          <t>Amazon US Best Sellers</t>
         </is>
       </c>
       <c r="J38" s="4" t="inlineStr">
         <is>
-          <t>TikTok Shop, TikTok Viral 24h, Amazon Top 100</t>
+          <t>Amazon Best Sellers, Amazon US</t>
         </is>
       </c>
       <c r="K38" s="4" t="inlineStr">
         <is>
-          <t>Before/After Macro Skin Texture Zoom (Cận cảnh bề mặt da)</t>
+          <t>Emotional Reaction &amp; Satisfying Fur Release ASMR</t>
         </is>
       </c>
       <c r="L38" s="5" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/tag/mightypatch</t>
+          <t>https://www.amazon.com/INABA-Chicken-Lickable-Creamy-Variety/dp/B07D323MFZ/ref=zg_bs_g_pet-supplies_d_sccl_6/142-8547974-1409324</t>
         </is>
       </c>
     </row>
@@ -7773,51 +7778,51 @@
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>medicube Zero Pore Pads 2.0 &amp; Exfoliating Toner</t>
+          <t>Amazon Fire TV Stick 4K Select (newest model), start streaming in 4K, AI-powered search, and free &amp; live TV, find shows faster wit</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>🔥 Bùng Nổ 24h (Viral Spike)</t>
+          <t>🔥 Xu Hướng Tăng Trưởng</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>Beauty &amp; Personal Care</t>
+          <t>Tech Gadgets</t>
         </is>
       </c>
       <c r="E39" s="3" t="n">
-        <v>81.40000000000001</v>
+        <v>85.59999999999999</v>
       </c>
       <c r="F39" s="3" t="n">
-        <v>98</v>
+        <v>86</v>
       </c>
       <c r="G39" s="3" t="n">
-        <v>50</v>
+        <v>85</v>
       </c>
       <c r="H39" s="3" t="inlineStr">
         <is>
-          <t>$18.90 - $24.00</t>
+          <t>1 offer from $49.99</t>
         </is>
       </c>
       <c r="I39" s="4" t="inlineStr">
         <is>
-          <t>TikTok US Viral 24h</t>
+          <t>Amazon US Best Sellers</t>
         </is>
       </c>
       <c r="J39" s="4" t="inlineStr">
         <is>
-          <t>TikTok Shop, TikTok Viral 24h, Amazon Top 100</t>
+          <t>Amazon Best Sellers, Amazon US</t>
         </is>
       </c>
       <c r="K39" s="4" t="inlineStr">
         <is>
-          <t>Before/After Macro Skin Texture Zoom (Cận cảnh bề mặt da)</t>
+          <t>TikTok Made Me Buy It / Honest Review</t>
         </is>
       </c>
       <c r="L39" s="5" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/tag/medicube</t>
+          <t>https://www.amazon.com/amazon-fire-tv-stick-4K-select/dp/B0C6W3D4RM/ref=zg_bs_g_electronics_d_sccl_4/142-8547974-1409324</t>
         </is>
       </c>
     </row>
@@ -7827,51 +7832,51 @@
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>Automatic 360 Electric Spin Scrubber for Deep Bathroom Cleaning</t>
+          <t>Apple AirPods Pro 3 Wireless Earbuds with Active Noise Cancellation | Live Translation, Heart Rate Sensing, Hearing Aid Feature, B</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>🔥 Bùng Nổ 24h (Viral Spike)</t>
+          <t>🔥 Xu Hướng Tăng Trưởng</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>Home Supplies</t>
+          <t>Jewelry Accessories &amp; Derivatives</t>
         </is>
       </c>
       <c r="E40" s="3" t="n">
-        <v>80.8</v>
+        <v>85.59999999999999</v>
       </c>
       <c r="F40" s="3" t="n">
-        <v>97</v>
+        <v>86</v>
       </c>
       <c r="G40" s="3" t="n">
-        <v>50</v>
+        <v>85</v>
       </c>
       <c r="H40" s="3" t="inlineStr">
         <is>
-          <t>$29.99 - $49.99</t>
+          <t>12 offers from $183.44</t>
         </is>
       </c>
       <c r="I40" s="4" t="inlineStr">
         <is>
-          <t>TikTok US Viral 24h</t>
+          <t>Amazon US Best Sellers</t>
         </is>
       </c>
       <c r="J40" s="4" t="inlineStr">
         <is>
-          <t>TikTok Shop, TikTok Viral 24h, Amazon Top 100</t>
+          <t>Amazon Best Sellers, Amazon US</t>
         </is>
       </c>
       <c r="K40" s="4" t="inlineStr">
         <is>
-          <t>Satisfying Deep Clean ASMR (Âm thanh chà sạch cực đã tai)</t>
+          <t>Side-by-side Live Demo &amp; Unboxing ASMR</t>
         </is>
       </c>
       <c r="L40" s="5" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/tag/spinscrubber</t>
+          <t>https://www.amazon.com/Apple-Cancellation-Translation-Headphones-High-Fidelity/dp/B0FQFB8FMG/ref=zg_bs_g_electronics_d_sccl_5/142-8547974-1409324</t>
         </is>
       </c>
     </row>
@@ -7881,51 +7886,51 @@
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>Mini Portable Thermal Sticker &amp; Label Printer</t>
+          <t>Original Toner Ricoh Aficio MP C3503 C4504 C5504 C6004 SP / 841817 - 8418205,032,950.00 VNDShop all 18Printers &amp; Printer</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>🔥 Bùng Nổ 24h (Viral Spike)</t>
+          <t>🔥 Xu Hướng Tăng Trưởng</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>Phones &amp; Electronics</t>
+          <t>Beauty &amp; Personal Care</t>
         </is>
       </c>
       <c r="E41" s="3" t="n">
-        <v>79.7</v>
+        <v>77.5</v>
       </c>
       <c r="F41" s="3" t="n">
-        <v>99</v>
+        <v>82</v>
       </c>
       <c r="G41" s="3" t="n">
-        <v>45</v>
+        <v>72</v>
       </c>
       <c r="H41" s="3" t="inlineStr">
         <is>
-          <t>$19.99 - $29.99</t>
+          <t>$19.99</t>
         </is>
       </c>
       <c r="I41" s="4" t="inlineStr">
         <is>
-          <t>TikTok US Viral 24h</t>
+          <t>eBay US</t>
         </is>
       </c>
       <c r="J41" s="4" t="inlineStr">
         <is>
-          <t>TikTok Shop, TikTok Viral 24h, Amazon Top 100</t>
+          <t>eBay US Deals</t>
         </is>
       </c>
       <c r="K41" s="4" t="inlineStr">
         <is>
-          <t>Side-by-side Live Demo &amp; Unboxing ASMR</t>
+          <t>Before/After Macro Skin Texture Zoom (Cận cảnh bề mặt da)</t>
         </is>
       </c>
       <c r="L41" s="5" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/tag/miniprinter</t>
+          <t>https://www.ebay.com/itm/223769336762</t>
         </is>
       </c>
     </row>
@@ -7935,7 +7940,7 @@
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>Original HP 2LL58A 636 STITCH DYE SUBLIMATION INK CYAN 3L Ink MHD 07-10/20243,573,692.31 VNDShop all 18Printers &amp; Printe</t>
+          <t>15%OFF UGG Slippers Australian Sheepskin Wool Warm House Slip On Scuff Women Men1,084,962.23 VNDADIDAS SCHUHE SPEZIALIST</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
@@ -7945,7 +7950,7 @@
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>Phones &amp; Electronics</t>
+          <t>Beauty &amp; Personal Care</t>
         </is>
       </c>
       <c r="E42" s="3" t="n">
@@ -7974,12 +7979,12 @@
       </c>
       <c r="K42" s="4" t="inlineStr">
         <is>
-          <t>Side-by-side Live Demo &amp; Unboxing ASMR</t>
+          <t>Before/After Macro Skin Texture Zoom (Cận cảnh bề mặt da)</t>
         </is>
       </c>
       <c r="L42" s="5" t="inlineStr">
         <is>
-          <t>https://www.ebay.com/itm/116219205632</t>
+          <t>https://www.ebay.com/itm/385963123229</t>
         </is>
       </c>
     </row>
@@ -7989,51 +7994,51 @@
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>15%OFF UGG Slippers Australian Sheepskin Wool Warm House Slip On Scuff Women Men1,084,962.23 VNDADIDAS SCHUHE SPEZIALIST</t>
+          <t>red alert</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>🔥 Xu Hướng Tăng Trưởng</t>
+          <t>🔥 Bùng Nổ 24h (Viral Spike)</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>Beauty &amp; Personal Care</t>
+          <t>Pets &amp; Animals</t>
         </is>
       </c>
       <c r="E43" s="3" t="n">
-        <v>77.5</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="F43" s="3" t="n">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="G43" s="3" t="n">
-        <v>72</v>
+        <v>50</v>
       </c>
       <c r="H43" s="3" t="inlineStr">
         <is>
-          <t>$19.99</t>
+          <t>$25.00</t>
         </is>
       </c>
       <c r="I43" s="4" t="inlineStr">
         <is>
-          <t>eBay US</t>
+          <t>Google Trends US</t>
         </is>
       </c>
       <c r="J43" s="4" t="inlineStr">
         <is>
-          <t>eBay US Deals</t>
+          <t>Google Trends US Search</t>
         </is>
       </c>
       <c r="K43" s="4" t="inlineStr">
         <is>
-          <t>Before/After Macro Skin Texture Zoom (Cận cảnh bề mặt da)</t>
+          <t>Emotional Reaction &amp; Satisfying Fur Release ASMR</t>
         </is>
       </c>
       <c r="L43" s="5" t="inlineStr">
         <is>
-          <t>https://www.ebay.com/itm/385963123229</t>
+          <t>https://trends.google.com/trends/explore?geo=US&amp;q=red%20alert</t>
         </is>
       </c>
     </row>
@@ -8043,51 +8048,51 @@
       </c>
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t>Custom Name Birth Flower Bar Necklace &amp; Personalized Jewelry</t>
+          <t>mlb wildcard standings</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>🌲 Evergreen Bền Vững</t>
+          <t>🔥 Bùng Nổ 24h (Viral Spike)</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>Jewelry Accessories &amp; Derivatives</t>
+          <t>Automotive &amp; Motorcycle</t>
         </is>
       </c>
       <c r="E44" s="3" t="n">
-        <v>74.8</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="F44" s="3" t="n">
+        <v>78</v>
+      </c>
+      <c r="G44" s="3" t="n">
         <v>50</v>
       </c>
-      <c r="G44" s="3" t="n">
-        <v>94</v>
-      </c>
       <c r="H44" s="3" t="inlineStr">
         <is>
-          <t>$24.00 - $38.00</t>
+          <t>$25.00</t>
         </is>
       </c>
       <c r="I44" s="4" t="inlineStr">
         <is>
-          <t>Etsy US Trending</t>
+          <t>Google Trends US</t>
         </is>
       </c>
       <c r="J44" s="4" t="inlineStr">
         <is>
-          <t>Etsy US, Handmade/POD, TikTok Gift Trend</t>
+          <t>Google Trends US Search</t>
         </is>
       </c>
       <c r="K44" s="4" t="inlineStr">
         <is>
-          <t>Behind The Scenes Crafting &amp; Emotional Gift Unboxing</t>
+          <t>TikTok Made Me Buy It / Honest Review</t>
         </is>
       </c>
       <c r="L44" s="5" t="inlineStr">
         <is>
-          <t>https://www.etsy.com/market/birth_flower_necklace</t>
+          <t>https://trends.google.com/trends/explore?geo=US&amp;q=mlb%20wildcard%20standings</t>
         </is>
       </c>
     </row>
@@ -8097,51 +8102,51 @@
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>Personalized Wooden Docking Station &amp; Desk Organizer for Men</t>
+          <t>pak vs eng</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>🌲 Evergreen Bền Vững</t>
+          <t>🔥 Bùng Nổ 24h (Viral Spike)</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>Menswear &amp; Underwear</t>
+          <t>General Trend</t>
         </is>
       </c>
       <c r="E45" s="3" t="n">
-        <v>74.8</v>
+        <v>63.2</v>
       </c>
       <c r="F45" s="3" t="n">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="G45" s="3" t="n">
-        <v>94</v>
+        <v>45</v>
       </c>
       <c r="H45" s="3" t="inlineStr">
         <is>
-          <t>$29.50 - $45.00</t>
+          <t>$25.00</t>
         </is>
       </c>
       <c r="I45" s="4" t="inlineStr">
         <is>
-          <t>Etsy US Trending</t>
+          <t>Google Trends US</t>
         </is>
       </c>
       <c r="J45" s="4" t="inlineStr">
         <is>
-          <t>Etsy US, Handmade/POD, TikTok Gift Trend</t>
+          <t>Google Trends US Search</t>
         </is>
       </c>
       <c r="K45" s="4" t="inlineStr">
         <is>
-          <t>Behind The Scenes Crafting &amp; Emotional Gift Unboxing</t>
+          <t>TikTok Made Me Buy It / Honest Review</t>
         </is>
       </c>
       <c r="L45" s="5" t="inlineStr">
         <is>
-          <t>https://www.etsy.com/market/wooden_docking_station</t>
+          <t>https://trends.google.com/trends/explore?geo=US&amp;q=pak%20vs%20eng</t>
         </is>
       </c>
     </row>
@@ -8151,51 +8156,51 @@
       </c>
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t>Minimalist Custom Acrylic Wall Calendar &amp; Family Command Center</t>
+          <t>michelle obama chanel us open</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>🌲 Evergreen Bền Vững</t>
+          <t>🔥 Bùng Nổ 24h (Viral Spike)</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>Home Supplies</t>
+          <t>Phones &amp; Electronics</t>
         </is>
       </c>
       <c r="E46" s="3" t="n">
-        <v>74.8</v>
+        <v>63.2</v>
       </c>
       <c r="F46" s="3" t="n">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="G46" s="3" t="n">
-        <v>94</v>
+        <v>45</v>
       </c>
       <c r="H46" s="3" t="inlineStr">
         <is>
-          <t>$39.00 - $69.00</t>
+          <t>$25.00</t>
         </is>
       </c>
       <c r="I46" s="4" t="inlineStr">
         <is>
-          <t>Etsy US Trending</t>
+          <t>Google Trends US</t>
         </is>
       </c>
       <c r="J46" s="4" t="inlineStr">
         <is>
-          <t>Etsy US, Handmade/POD, TikTok Gift Trend</t>
+          <t>Google Trends US Search</t>
         </is>
       </c>
       <c r="K46" s="4" t="inlineStr">
         <is>
-          <t>Behind The Scenes Crafting &amp; Emotional Gift Unboxing</t>
+          <t>Side-by-side Live Demo &amp; Unboxing ASMR</t>
         </is>
       </c>
       <c r="L46" s="5" t="inlineStr">
         <is>
-          <t>https://www.etsy.com/market/acrylic_calendar</t>
+          <t>https://trends.google.com/trends/explore?geo=US&amp;q=michelle%20obama%20chanel%20us%20open</t>
         </is>
       </c>
     </row>
@@ -8205,51 +8210,51 @@
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>Engraved Olive Wood Cutting Board &amp; Charcuterie Serving Platter</t>
+          <t>meghan</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>🌲 Evergreen Bền Vững</t>
+          <t>🔥 Bùng Nổ 24h (Viral Spike)</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>Kitchenware</t>
+          <t>Health &amp; Fitness</t>
         </is>
       </c>
       <c r="E47" s="3" t="n">
-        <v>74.8</v>
+        <v>63.2</v>
       </c>
       <c r="F47" s="3" t="n">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="G47" s="3" t="n">
-        <v>94</v>
+        <v>45</v>
       </c>
       <c r="H47" s="3" t="inlineStr">
         <is>
-          <t>$32.00 - $55.00</t>
+          <t>$25.00</t>
         </is>
       </c>
       <c r="I47" s="4" t="inlineStr">
         <is>
-          <t>Etsy US Trending</t>
+          <t>Google Trends US</t>
         </is>
       </c>
       <c r="J47" s="4" t="inlineStr">
         <is>
-          <t>Etsy US, Handmade/POD, TikTok Gift Trend</t>
+          <t>Google Trends US Search</t>
         </is>
       </c>
       <c r="K47" s="4" t="inlineStr">
         <is>
-          <t>Behind The Scenes Crafting &amp; Emotional Gift Unboxing</t>
+          <t>TikTok Made Me Buy It / Honest Review</t>
         </is>
       </c>
       <c r="L47" s="5" t="inlineStr">
         <is>
-          <t>https://www.etsy.com/market/personalized_cutting_board</t>
+          <t>https://trends.google.com/trends/explore?geo=US&amp;q=meghan</t>
         </is>
       </c>
     </row>
@@ -8259,51 +8264,51 @@
       </c>
       <c r="B48" s="4" t="inlineStr">
         <is>
-          <t>Spotlight DealCASIO WATCH CALCULATOR VINTAGE RETRO 80's CA-53W-1Z CA53 CA-53 AUSSIE SELLER838,137.46 VND1,470,465.00 VND</t>
+          <t>ukraine</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>🔥 Xu Hướng Tăng Trưởng</t>
+          <t>🔥 Bùng Nổ 24h (Viral Spike)</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>All Trending Deals</t>
+          <t>General Trend</t>
         </is>
       </c>
       <c r="E48" s="3" t="n">
-        <v>74.2</v>
+        <v>63.2</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>72</v>
+        <v>45</v>
       </c>
       <c r="H48" s="3" t="inlineStr">
         <is>
-          <t>$19.99</t>
+          <t>$25.00</t>
         </is>
       </c>
       <c r="I48" s="4" t="inlineStr">
         <is>
-          <t>eBay US</t>
+          <t>Google Trends US</t>
         </is>
       </c>
       <c r="J48" s="4" t="inlineStr">
         <is>
-          <t>eBay US Deals</t>
+          <t>Google Trends US Search</t>
         </is>
       </c>
       <c r="K48" s="4" t="inlineStr">
         <is>
-          <t>Side-by-side Live Demo &amp; Unboxing ASMR</t>
+          <t>TikTok Made Me Buy It / Honest Review</t>
         </is>
       </c>
       <c r="L48" s="5" t="inlineStr">
         <is>
-          <t>https://www.ebay.com/itm/370786315096</t>
+          <t>https://trends.google.com/trends/explore?geo=US&amp;q=ukraine</t>
         </is>
       </c>
     </row>
@@ -8313,51 +8318,51 @@
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>CASIO WATCH VINTAGE RETRO ORIGINAL F-91W-1 F91 F91W F-91 WARANTY666,169.38 VND734,772.69 VND | 9% offPrevious price: 734</t>
+          <t>irish open 2026</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>🔥 Xu Hướng Tăng Trưởng</t>
+          <t>🔥 Bùng Nổ 24h (Viral Spike)</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>All Trending Deals</t>
+          <t>Books, Magazines &amp; Audio</t>
         </is>
       </c>
       <c r="E49" s="3" t="n">
-        <v>74.2</v>
+        <v>63.2</v>
       </c>
       <c r="F49" s="3" t="n">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="G49" s="3" t="n">
-        <v>72</v>
+        <v>45</v>
       </c>
       <c r="H49" s="3" t="inlineStr">
         <is>
-          <t>$19.99</t>
+          <t>$25.00</t>
         </is>
       </c>
       <c r="I49" s="4" t="inlineStr">
         <is>
-          <t>eBay US</t>
+          <t>Google Trends US</t>
         </is>
       </c>
       <c r="J49" s="4" t="inlineStr">
         <is>
-          <t>eBay US Deals</t>
+          <t>Google Trends US Search</t>
         </is>
       </c>
       <c r="K49" s="4" t="inlineStr">
         <is>
-          <t>Side-by-side Live Demo &amp; Unboxing ASMR</t>
+          <t>TikTok Made Me Buy It / Honest Review</t>
         </is>
       </c>
       <c r="L49" s="5" t="inlineStr">
         <is>
-          <t>https://www.ebay.com/itm/370816923572</t>
+          <t>https://trends.google.com/trends/explore?geo=US&amp;q=irish%20open%202026</t>
         </is>
       </c>
     </row>
@@ -8367,41 +8372,41 @@
       </c>
       <c r="B50" s="4" t="inlineStr">
         <is>
-          <t>Cisco SFP-H10GB-CU3M 37-0961-03 SFP+ 10G Passive DAC Twinax Cable NEW897,435.90 VND</t>
+          <t>indianapolis weather</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>🔥 Xu Hướng Tăng Trưởng</t>
+          <t>🔥 Bùng Nổ 24h (Viral Spike)</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>All Trending Deals</t>
+          <t>General Trend</t>
         </is>
       </c>
       <c r="E50" s="3" t="n">
-        <v>74.2</v>
+        <v>63.2</v>
       </c>
       <c r="F50" s="3" t="n">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="G50" s="3" t="n">
-        <v>72</v>
+        <v>45</v>
       </c>
       <c r="H50" s="3" t="inlineStr">
         <is>
-          <t>$19.99</t>
+          <t>$25.00</t>
         </is>
       </c>
       <c r="I50" s="4" t="inlineStr">
         <is>
-          <t>eBay US</t>
+          <t>Google Trends US</t>
         </is>
       </c>
       <c r="J50" s="4" t="inlineStr">
         <is>
-          <t>eBay US Deals</t>
+          <t>Google Trends US Search</t>
         </is>
       </c>
       <c r="K50" s="4" t="inlineStr">
@@ -8411,7 +8416,7 @@
       </c>
       <c r="L50" s="5" t="inlineStr">
         <is>
-          <t>https://www.ebay.com/itm/157632501279</t>
+          <t>https://trends.google.com/trends/explore?geo=US&amp;q=indianapolis%20weather</t>
         </is>
       </c>
     </row>
@@ -8421,41 +8426,41 @@
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>NZG 1:18 Mercedes-Benz AMG G63 4x4² 2023 W463 Alloy Diecast Car Model6,641,025.64 VND9,025,641.03 VND Previous price: 9,</t>
+          <t>adam levy</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>🔥 Xu Hướng Tăng Trưởng</t>
+          <t>🔥 Bùng Nổ 24h (Viral Spike)</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>Automotive &amp; Motorcycle</t>
+          <t>Fashion &amp; Apparel</t>
         </is>
       </c>
       <c r="E51" s="3" t="n">
-        <v>74.2</v>
+        <v>63.2</v>
       </c>
       <c r="F51" s="3" t="n">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="G51" s="3" t="n">
-        <v>72</v>
+        <v>45</v>
       </c>
       <c r="H51" s="3" t="inlineStr">
         <is>
-          <t>$19.99</t>
+          <t>$25.00</t>
         </is>
       </c>
       <c r="I51" s="4" t="inlineStr">
         <is>
-          <t>eBay US</t>
+          <t>Google Trends US</t>
         </is>
       </c>
       <c r="J51" s="4" t="inlineStr">
         <is>
-          <t>eBay US Deals</t>
+          <t>Google Trends US Search</t>
         </is>
       </c>
       <c r="K51" s="4" t="inlineStr">
@@ -8465,7 +8470,7 @@
       </c>
       <c r="L51" s="5" t="inlineStr">
         <is>
-          <t>https://www.ebay.com/itm/298638189628</t>
+          <t>https://trends.google.com/trends/explore?geo=US&amp;q=adam%20levy</t>
         </is>
       </c>
     </row>
@@ -8475,52 +8480,51 @@
       </c>
       <c r="B52" s="4" t="inlineStr">
         <is>
-          <t>Apple iPhone 16 Pro Max All Colours26,609,000.00 VND
-eBay Refurbished</t>
+          <t>jason bard yarmosky</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>🔥 Xu Hướng Tăng Trưởng</t>
+          <t>🔥 Bùng Nổ 24h (Viral Spike)</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>All Trending Deals</t>
+          <t>Fashion &amp; Apparel</t>
         </is>
       </c>
       <c r="E52" s="3" t="n">
-        <v>74.2</v>
+        <v>63.2</v>
       </c>
       <c r="F52" s="3" t="n">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="G52" s="3" t="n">
-        <v>72</v>
+        <v>45</v>
       </c>
       <c r="H52" s="3" t="inlineStr">
         <is>
-          <t>$19.99</t>
+          <t>$25.00</t>
         </is>
       </c>
       <c r="I52" s="4" t="inlineStr">
         <is>
-          <t>eBay US</t>
+          <t>Google Trends US</t>
         </is>
       </c>
       <c r="J52" s="4" t="inlineStr">
         <is>
-          <t>eBay US Deals</t>
+          <t>Google Trends US Search</t>
         </is>
       </c>
       <c r="K52" s="4" t="inlineStr">
         <is>
-          <t>Emotional Reaction &amp; Satisfying Fur Release ASMR</t>
+          <t>TikTok Made Me Buy It / Honest Review</t>
         </is>
       </c>
       <c r="L52" s="5" t="inlineStr">
         <is>
-          <t>https://www.ebay.com/itm/257723314310</t>
+          <t>https://trends.google.com/trends/explore?geo=US&amp;q=jason%20bard%20yarmosky</t>
         </is>
       </c>
     </row>
@@ -8530,27 +8534,27 @@
       </c>
       <c r="B53" s="4" t="inlineStr">
         <is>
-          <t>Apple iPhone 16 Pro - 1TB - All Colours21,821,461.54 VNDeBay Refurbished</t>
+          <t>ICED 10k White Gold DIAMOND Curb Link HEAVY 44gr Bracelet Jewelry136,393,589.74 VNDPanzerkette Halskette 5 mm Echt 750er</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>🔥 Xu Hướng Tăng Trưởng</t>
+          <t>🌲 Evergreen Bền Vững</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>All Trending Deals</t>
+          <t>Kitchenware</t>
         </is>
       </c>
       <c r="E53" s="3" t="n">
-        <v>74.2</v>
+        <v>82.3</v>
       </c>
       <c r="F53" s="3" t="n">
         <v>76</v>
       </c>
       <c r="G53" s="3" t="n">
-        <v>72</v>
+        <v>90</v>
       </c>
       <c r="H53" s="3" t="inlineStr">
         <is>
@@ -8569,12 +8573,12 @@
       </c>
       <c r="K53" s="4" t="inlineStr">
         <is>
-          <t>Emotional Reaction &amp; Satisfying Fur Release ASMR</t>
+          <t>TikTok Made Me Buy It / Honest Review</t>
         </is>
       </c>
       <c r="L53" s="5" t="inlineStr">
         <is>
-          <t>https://www.ebay.com/itm/257132401723</t>
+          <t>https://www.ebay.com/itm/298332862724</t>
         </is>
       </c>
     </row>
@@ -8584,7 +8588,7 @@
       </c>
       <c r="B54" s="4" t="inlineStr">
         <is>
-          <t>Apple iPhone 16 Pro Max - 256GB 512GB 1TB- All Colours - Good25,013,153.85 VNDeBay Refurbished</t>
+          <t>Spotlight DealCASIO WATCH CALCULATOR VINTAGE RETRO 80's CA-53W-1Z CA53 CA-53 AUSSIE SELLER838,137.46 VND1,470,465.00 VND</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
@@ -8623,12 +8627,12 @@
       </c>
       <c r="K54" s="4" t="inlineStr">
         <is>
-          <t>Emotional Reaction &amp; Satisfying Fur Release ASMR</t>
+          <t>Side-by-side Live Demo &amp; Unboxing ASMR</t>
         </is>
       </c>
       <c r="L54" s="5" t="inlineStr">
         <is>
-          <t>https://www.ebay.com/itm/298645175829</t>
+          <t>https://www.ebay.com/itm/370786315096</t>
         </is>
       </c>
     </row>
@@ -8638,7 +8642,7 @@
       </c>
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t>MERCEDES 190 190E W201 Motor Kupplung Bremsen ab 1982 Reparaturanleitung B786860,664.23 VNDAlmost goneLada 1200 1300 150</t>
+          <t>CASIO WATCH VINTAGE RETRO ORIGINAL F-91W-1 F91 F91W F-91 WARANTY666,169.38 VND734,772.69 VND | 9% offPrevious price: 734</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
@@ -8677,12 +8681,12 @@
       </c>
       <c r="K55" s="4" t="inlineStr">
         <is>
-          <t>TikTok Made Me Buy It / Honest Review</t>
+          <t>Side-by-side Live Demo &amp; Unboxing ASMR</t>
         </is>
       </c>
       <c r="L55" s="5" t="inlineStr">
         <is>
-          <t>https://www.ebay.com/itm/201727143641</t>
+          <t>https://www.ebay.com/itm/370816923572</t>
         </is>
       </c>
     </row>
@@ -8692,7 +8696,7 @@
       </c>
       <c r="B56" s="4" t="inlineStr">
         <is>
-          <t>Biker Kutte Lederkutte Lederweste Clubweste Rockerweste Herren Chopper Motorrad2,679,971.42 VND</t>
+          <t>Cisco SFP-H10GB-CU3M 37-0961-03 SFP+ 10G Passive DAC Twinax Cable NEW897,435.90 VND</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
@@ -8736,7 +8740,7 @@
       </c>
       <c r="L56" s="5" t="inlineStr">
         <is>
-          <t>https://www.ebay.com/itm/302258284099</t>
+          <t>https://www.ebay.com/itm/157632501279</t>
         </is>
       </c>
     </row>
@@ -8746,7 +8750,7 @@
       </c>
       <c r="B57" s="4" t="inlineStr">
         <is>
-          <t>Lederweste Bikerweste Motorrad Kutte Biker Chopper Rockerweste mit Taschen2,679,971.42 VNDShop all 91Parts &amp; Accessories</t>
+          <t>NZG 1:18 Mercedes-Benz AMG G63 4x4² 2023 W463 Alloy Diecast Car Model6,641,025.64 VND9,025,641.03 VND Previous price: 9,</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
@@ -8756,7 +8760,7 @@
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>All Trending Deals</t>
+          <t>Automotive &amp; Motorcycle</t>
         </is>
       </c>
       <c r="E57" s="3" t="n">
@@ -8790,7 +8794,7 @@
       </c>
       <c r="L57" s="5" t="inlineStr">
         <is>
-          <t>https://www.ebay.com/itm/291771387455</t>
+          <t>https://www.ebay.com/itm/298638189628</t>
         </is>
       </c>
     </row>
@@ -8800,7 +8804,8 @@
       </c>
       <c r="B58" s="4" t="inlineStr">
         <is>
-          <t>CASIO WATCH SWIMMING 100 METRES WATER RESISTANT W-800 W-800H-1AV W8001,025,371.15 VND1,102,618.85 VND | 7% offPrevious p</t>
+          <t>Apple iPhone 16 Pro Max All Colours26,609,000.00 VND
+eBay Refurbished</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
@@ -8839,12 +8844,12 @@
       </c>
       <c r="K58" s="4" t="inlineStr">
         <is>
-          <t>Side-by-side Live Demo &amp; Unboxing ASMR</t>
+          <t>Emotional Reaction &amp; Satisfying Fur Release ASMR</t>
         </is>
       </c>
       <c r="L58" s="5" t="inlineStr">
         <is>
-          <t>https://www.ebay.com/itm/371175182923</t>
+          <t>https://www.ebay.com/itm/257723314310</t>
         </is>
       </c>
     </row>
@@ -8854,7 +8859,7 @@
       </c>
       <c r="B59" s="4" t="inlineStr">
         <is>
-          <t>YHG Wetsuit 3mm Neoprene Diving Tops Pants Men Women Swim Surfing Snorkeling AU735,508.38 VND</t>
+          <t>Apple iPhone 16 Pro - 1TB - All Colours21,821,461.54 VNDeBay Refurbished</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
@@ -8864,7 +8869,7 @@
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>Kitchenware</t>
+          <t>All Trending Deals</t>
         </is>
       </c>
       <c r="E59" s="3" t="n">
@@ -8893,12 +8898,12 @@
       </c>
       <c r="K59" s="4" t="inlineStr">
         <is>
-          <t>TikTok Made Me Buy It / Honest Review</t>
+          <t>Emotional Reaction &amp; Satisfying Fur Release ASMR</t>
         </is>
       </c>
       <c r="L59" s="5" t="inlineStr">
         <is>
-          <t>https://www.ebay.com/itm/157344373567</t>
+          <t>https://www.ebay.com/itm/257132401723</t>
         </is>
       </c>
     </row>
@@ -8908,7 +8913,7 @@
       </c>
       <c r="B60" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">True Temper Dynamic Gold TOUR ISSUE Limited Edition USA Golf Iron Shaft .355 Tip923,076.92 VND1,153,846.15 VND Previous </t>
+          <t>Apple iPhone 16 Pro Max - 256GB 512GB 1TB- All Colours - Good25,013,153.85 VNDeBay Refurbished</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
@@ -8918,7 +8923,7 @@
       </c>
       <c r="D60" s="4" t="inlineStr">
         <is>
-          <t>Phones &amp; Electronics</t>
+          <t>All Trending Deals</t>
         </is>
       </c>
       <c r="E60" s="3" t="n">
@@ -8947,12 +8952,12 @@
       </c>
       <c r="K60" s="4" t="inlineStr">
         <is>
-          <t>Side-by-side Live Demo &amp; Unboxing ASMR</t>
+          <t>Emotional Reaction &amp; Satisfying Fur Release ASMR</t>
         </is>
       </c>
       <c r="L60" s="5" t="inlineStr">
         <is>
-          <t>https://www.ebay.com/itm/186144334386</t>
+          <t>https://www.ebay.com/itm/298645175829</t>
         </is>
       </c>
     </row>
@@ -8962,7 +8967,7 @@
       </c>
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t>Veto Pro Pac MP3 EVO Tool Pouch EVO System Electrician Networking Technician3,203,846.15 VND250x Altarkerzen weiß Rußfre</t>
+          <t>Lederweste Bikerweste Motorrad Kutte Biker Chopper Rockerweste mit Taschen2,679,971.42 VNDPremium Velour Fußmatten kompl</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
@@ -9006,7 +9011,7 @@
       </c>
       <c r="L61" s="5" t="inlineStr">
         <is>
-          <t>https://www.ebay.com/itm/366448929530</t>
+          <t>https://www.ebay.com/itm/291771387455</t>
         </is>
       </c>
     </row>
@@ -9016,7 +9021,7 @@
       </c>
       <c r="B62" s="4" t="inlineStr">
         <is>
-          <t>carron® PTFE Lotuseffekt extrem Versiegelung Duschwand Glas - Schutz gegen Kalk799,613.65 VND</t>
+          <t>Birne 6000K H13 E-PRÜFZEICHEN 12V 60/55W E-Prüfzeichen XENON SUPER WHITE HALOGEN625,693.96 VND</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
@@ -9026,7 +9031,7 @@
       </c>
       <c r="D62" s="4" t="inlineStr">
         <is>
-          <t>Automotive &amp; Motorcycle</t>
+          <t>All Trending Deals</t>
         </is>
       </c>
       <c r="E62" s="3" t="n">
@@ -9060,7 +9065,7 @@
       </c>
       <c r="L62" s="5" t="inlineStr">
         <is>
-          <t>https://www.ebay.com/itm/224875974996</t>
+          <t>https://www.ebay.com/itm/133242757435</t>
         </is>
       </c>
     </row>
@@ -9070,7 +9075,7 @@
       </c>
       <c r="B63" s="4" t="inlineStr">
         <is>
-          <t>8x Kerze 15x8cm RAL Qualität / Stumpen von Kerzen Wiedemann / neue Farben 20251,306,780.15 VNDShop all 88Home &amp; Garden</t>
+          <t>500 Abarth Orig Competizione 595 695 Braking Kit Bremsscheiben Kit Va 305x28mm11,286,911.54 VNDShop all 90Parts &amp; Access</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
@@ -9080,7 +9085,7 @@
       </c>
       <c r="D63" s="4" t="inlineStr">
         <is>
-          <t>Books, Magazines &amp; Audio</t>
+          <t>Pet Supplies</t>
         </is>
       </c>
       <c r="E63" s="3" t="n">
@@ -9109,12 +9114,12 @@
       </c>
       <c r="K63" s="4" t="inlineStr">
         <is>
-          <t>TikTok Made Me Buy It / Honest Review</t>
+          <t>Emotional Reaction &amp; Satisfying Fur Release ASMR</t>
         </is>
       </c>
       <c r="L63" s="5" t="inlineStr">
         <is>
-          <t>https://www.ebay.com/itm/354282537544</t>
+          <t>https://www.ebay.com/itm/285765031424</t>
         </is>
       </c>
     </row>
@@ -9124,7 +9129,7 @@
       </c>
       <c r="B64" s="4" t="inlineStr">
         <is>
-          <t>Nokia 6300 Silber Schwarz ohne Vertrag ohne Simlock Neu2,677,291.15 VNDNokia 6300 Schwarz ohne Vertrag ohne Simlock Neu2</t>
+          <t>CASIO WATCH SWIMMING 100 METRES WATER RESISTANT W-800 W-800H-1AV W8001,025,371.15 VND1,102,618.85 VND | 7% offPrevious p</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
@@ -9134,7 +9139,7 @@
       </c>
       <c r="D64" s="4" t="inlineStr">
         <is>
-          <t>Tech &amp; Gadgets</t>
+          <t>All Trending Deals</t>
         </is>
       </c>
       <c r="E64" s="3" t="n">
@@ -9163,12 +9168,12 @@
       </c>
       <c r="K64" s="4" t="inlineStr">
         <is>
-          <t>TikTok Made Me Buy It / Honest Review</t>
+          <t>Side-by-side Live Demo &amp; Unboxing ASMR</t>
         </is>
       </c>
       <c r="L64" s="5" t="inlineStr">
         <is>
-          <t>https://www.ebay.com/itm/196061847535</t>
+          <t>https://www.ebay.com/itm/371175182923</t>
         </is>
       </c>
     </row>
@@ -9178,7 +9183,7 @@
       </c>
       <c r="B65" s="4" t="inlineStr">
         <is>
-          <t>Samsung GT-E1200I   Keystone 2  gt e1200 i Schwarz frei für alle Sim Karten Neu1,932,771.92 VND</t>
+          <t>YHG Wetsuit 3mm Neoprene Diving Tops Pants Men Women Swim Surfing Snorkeling AU735,508.38 VND</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
@@ -9188,7 +9193,7 @@
       </c>
       <c r="D65" s="4" t="inlineStr">
         <is>
-          <t>Tech &amp; Gadgets</t>
+          <t>Kitchenware</t>
         </is>
       </c>
       <c r="E65" s="3" t="n">
@@ -9222,7 +9227,7 @@
       </c>
       <c r="L65" s="5" t="inlineStr">
         <is>
-          <t>https://www.ebay.com/itm/205486315558</t>
+          <t>https://www.ebay.com/itm/157344373567</t>
         </is>
       </c>
     </row>
@@ -9232,7 +9237,7 @@
       </c>
       <c r="B66" s="4" t="inlineStr">
         <is>
-          <t>Nokia 3110 classic schwarz  ohne Simlock Frei für alle Sim-karten Neu2,081,675.77 VNDShop all 8Cell Phones</t>
+          <t xml:space="preserve">True Temper Dynamic Gold TOUR ISSUE Limited Edition USA Golf Iron Shaft .355 Tip923,076.92 VND1,153,846.15 VND Previous </t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
@@ -9242,7 +9247,7 @@
       </c>
       <c r="D66" s="4" t="inlineStr">
         <is>
-          <t>Tech &amp; Gadgets</t>
+          <t>Phones &amp; Electronics</t>
         </is>
       </c>
       <c r="E66" s="3" t="n">
@@ -9271,12 +9276,12 @@
       </c>
       <c r="K66" s="4" t="inlineStr">
         <is>
-          <t>TikTok Made Me Buy It / Honest Review</t>
+          <t>Side-by-side Live Demo &amp; Unboxing ASMR</t>
         </is>
       </c>
       <c r="L66" s="5" t="inlineStr">
         <is>
-          <t>https://www.ebay.com/itm/205486034658</t>
+          <t>https://www.ebay.com/itm/186144334386</t>
         </is>
       </c>
     </row>
@@ -9286,7 +9291,7 @@
       </c>
       <c r="B67" s="4" t="inlineStr">
         <is>
-          <t>ORIGINAL METZ Fernbedienung für Metz Blue MOC9001 MUC8001 MUC7001 MUC7111 NEU1,009,568.08 VNDErsatz Fernbedienung für LG</t>
+          <t>Veto Pro Pac MP3 EVO Tool Pouch EVO System Electrician Networking Technician3,203,846.15 VND24x Kerzen 80x40mm/8x4cm 1.W</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
@@ -9296,7 +9301,7 @@
       </c>
       <c r="D67" s="4" t="inlineStr">
         <is>
-          <t>Tech &amp; Gadgets</t>
+          <t>All Trending Deals</t>
         </is>
       </c>
       <c r="E67" s="3" t="n">
@@ -9330,7 +9335,7 @@
       </c>
       <c r="L67" s="5" t="inlineStr">
         <is>
-          <t>https://www.ebay.com/itm/393858887603</t>
+          <t>https://www.ebay.com/itm/366448929530</t>
         </is>
       </c>
     </row>
@@ -9340,7 +9345,7 @@
       </c>
       <c r="B68" s="4" t="inlineStr">
         <is>
-          <t>ORIGINAL SONY Fernbedienung RMT-TX102D KDL40R45XC KDL40R55XC KDL40R550C NEUWARE652,198.85 VND</t>
+          <t>Bankerlampe Tischleuchte Bürolampe Jugendstil Schreibtischlampe weiss silber neu2,024,794.50 VND</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
@@ -9350,7 +9355,7 @@
       </c>
       <c r="D68" s="4" t="inlineStr">
         <is>
-          <t>Tech &amp; Gadgets</t>
+          <t>All Trending Deals</t>
         </is>
       </c>
       <c r="E68" s="3" t="n">
@@ -9384,7 +9389,7 @@
       </c>
       <c r="L68" s="5" t="inlineStr">
         <is>
-          <t>https://www.ebay.com/itm/373982552937</t>
+          <t>https://www.ebay.com/itm/194675348414</t>
         </is>
       </c>
     </row>
@@ -9394,7 +9399,7 @@
       </c>
       <c r="B69" s="4" t="inlineStr">
         <is>
-          <t>NEU ORIGINAL SAMSUNG Fernbedienung für UE40ES6100WXZG UE40ES6100 UE40ES6100W652,198.85 VNDShop all 7TV, Video &amp; Home Aud</t>
+          <t>3 Paar Zedernholzsohlen - Zedernsohlen - Einlegesohlen aus Holz890,445.00 VNDAlmost goneShop all 88Home &amp; Garden</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
@@ -9404,7 +9409,7 @@
       </c>
       <c r="D69" s="4" t="inlineStr">
         <is>
-          <t>Tech &amp; Gadgets</t>
+          <t>All Trending Deals</t>
         </is>
       </c>
       <c r="E69" s="3" t="n">
@@ -9438,7 +9443,7 @@
       </c>
       <c r="L69" s="5" t="inlineStr">
         <is>
-          <t>https://www.ebay.com/itm/392224499242</t>
+          <t>https://www.ebay.com/itm/276726430861</t>
         </is>
       </c>
     </row>
@@ -9448,7 +9453,7 @@
       </c>
       <c r="B70" s="4" t="inlineStr">
         <is>
-          <t>Sony Playstation 5 Controller-TMR Sticks-Top Zustand-alle Farben2,380,972.50 VNDWii - Nintendo Wii Konsole Weiß mit Remo</t>
+          <t xml:space="preserve">Opis PushMeFon mobile - Retro 2G Tischhandy Mobil-Telefon mit Metallklingel3,841,719.23 VNDNokia 6700 Classic 5MP Handy </t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
@@ -9492,7 +9497,7 @@
       </c>
       <c r="L70" s="5" t="inlineStr">
         <is>
-          <t>https://www.ebay.com/itm/365967503388</t>
+          <t>https://www.ebay.com/itm/324428697438</t>
         </is>
       </c>
     </row>
@@ -9502,7 +9507,7 @@
       </c>
       <c r="B71" s="4" t="inlineStr">
         <is>
-          <t>SW - Nintendo Switch-Konsole Neon-Rot/Neon-Blau (guter Zustand)5,656,857.12 VNDeBay Refurbished</t>
+          <t>Nokia C2-01  (Ohne Simlock)  Frei für alle Sim-Karten Neu schwarz2,379,483.46 VND</t>
         </is>
       </c>
       <c r="C71" s="4" t="inlineStr">
@@ -9541,12 +9546,12 @@
       </c>
       <c r="K71" s="4" t="inlineStr">
         <is>
-          <t>Emotional Reaction &amp; Satisfying Fur Release ASMR</t>
+          <t>TikTok Made Me Buy It / Honest Review</t>
         </is>
       </c>
       <c r="L71" s="5" t="inlineStr">
         <is>
-          <t>https://www.ebay.com/itm/187974010368</t>
+          <t>https://www.ebay.com/itm/202995946783</t>
         </is>
       </c>
     </row>
@@ -9556,7 +9561,7 @@
       </c>
       <c r="B72" s="4" t="inlineStr">
         <is>
-          <t>Nintendo Switch Catan Console edition (Code in aBox) NEU565,536.81 VNDShop all 27Video Games &amp; Consoles</t>
+          <t>Opis 60s mobile - Das  Retro 2G Tischhandy mit Wählscheibe &amp; Metallklingel3,841,719.23 VNDShop all 8Cell Phones</t>
         </is>
       </c>
       <c r="C72" s="4" t="inlineStr">
@@ -9566,7 +9571,7 @@
       </c>
       <c r="D72" s="4" t="inlineStr">
         <is>
-          <t>Pet Supplies</t>
+          <t>Tech &amp; Gadgets</t>
         </is>
       </c>
       <c r="E72" s="3" t="n">
@@ -9595,12 +9600,12 @@
       </c>
       <c r="K72" s="4" t="inlineStr">
         <is>
-          <t>Emotional Reaction &amp; Satisfying Fur Release ASMR</t>
+          <t>TikTok Made Me Buy It / Honest Review</t>
         </is>
       </c>
       <c r="L72" s="5" t="inlineStr">
         <is>
-          <t>https://www.ebay.com/itm/356767412423</t>
+          <t>https://www.ebay.com/itm/324427595994</t>
         </is>
       </c>
     </row>
@@ -9610,7 +9615,7 @@
       </c>
       <c r="B73" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Handy Tasche für Xiaomi 14T Pro Schutzhülle Book Case Kartenfach NEU Handy Hülle893,125.27 VNDFree shippingHandy Tasche </t>
+          <t>NEUWARE ORIGINAL METZ Fernbedienung RM18 RM 18 SCHNELLER VERSAND2,054,873.08 VNDAlmost goneORIGINAL SONY Fernbedienung R</t>
         </is>
       </c>
       <c r="C73" s="4" t="inlineStr">
@@ -9620,7 +9625,7 @@
       </c>
       <c r="D73" s="4" t="inlineStr">
         <is>
-          <t>Books, Magazines &amp; Audio</t>
+          <t>Tech &amp; Gadgets</t>
         </is>
       </c>
       <c r="E73" s="3" t="n">
@@ -9654,7 +9659,7 @@
       </c>
       <c r="L73" s="5" t="inlineStr">
         <is>
-          <t>https://www.ebay.com/itm/395963882049</t>
+          <t>https://www.ebay.com/itm/392040705358</t>
         </is>
       </c>
     </row>
@@ -9664,7 +9669,7 @@
       </c>
       <c r="B74" s="4" t="inlineStr">
         <is>
-          <t>Handy Umhängetasche für Samsung Galaxy A55 5G Gürtel Tasche Etui Gurt Handyhülle890,445.00 VNDFree shipping</t>
+          <t>ORIGINAL METZ Fernbedienung für Metz Blue MOC9001 MUC8001 MUC7001 MUC7111 NEU1,009,568.08 VND</t>
         </is>
       </c>
       <c r="C74" s="4" t="inlineStr">
@@ -9708,7 +9713,7 @@
       </c>
       <c r="L74" s="5" t="inlineStr">
         <is>
-          <t>https://www.ebay.com/itm/395332607060</t>
+          <t>https://www.ebay.com/itm/393858887603</t>
         </is>
       </c>
     </row>
@@ -9718,7 +9723,7 @@
       </c>
       <c r="B75" s="4" t="inlineStr">
         <is>
-          <t>Handy Gürteltasche für Apple iPhone 16 Pro Handytasche Holster Gürtel Schlaufe893,125.27 VNDFree shippingShop all 33Phon</t>
+          <t>NEU ORIGINAL SAMSUNG Fernbedienung für UE40ES6100WXZG UE40ES6100 UE40ES6100W652,198.85 VNDShop all 7TV, Video &amp; Home Aud</t>
         </is>
       </c>
       <c r="C75" s="4" t="inlineStr">
@@ -9762,7 +9767,7 @@
       </c>
       <c r="L75" s="5" t="inlineStr">
         <is>
-          <t>https://www.ebay.com/itm/204999038014</t>
+          <t>https://www.ebay.com/itm/392224499242</t>
         </is>
       </c>
     </row>
@@ -9772,7 +9777,7 @@
       </c>
       <c r="B76" s="4" t="inlineStr">
         <is>
-          <t>Original Canon PGI-570 CLI-571 Set (5 Patronen) KEINE SETUP - ECHTE ORIGINALE1,845,514.27 VNDTinte für Canon iPF6400 iPF</t>
+          <t>Sony Playstation 5 Controller-TMR Sticks-Top Zustand-alle Farben2,380,972.50 VNDWii - Nintendo Wii Konsole Weiß mit Remo</t>
         </is>
       </c>
       <c r="C76" s="4" t="inlineStr">
@@ -9816,7 +9821,7 @@
       </c>
       <c r="L76" s="5" t="inlineStr">
         <is>
-          <t>https://www.ebay.com/itm/296479378739</t>
+          <t>https://www.ebay.com/itm/365967503388</t>
         </is>
       </c>
     </row>
@@ -9826,7 +9831,7 @@
       </c>
       <c r="B77" s="4" t="inlineStr">
         <is>
-          <t>Original Brother LC1220 MultiPack SparPack ValuePack alle Farben 4 Patronen o.V.1,637,048.88 VND</t>
+          <t>SW - Nintendo Switch-Konsole Neon-Rot/Neon-Blau (guter Zustand)5,656,857.12 VNDeBay Refurbished</t>
         </is>
       </c>
       <c r="C77" s="4" t="inlineStr">
@@ -9865,12 +9870,12 @@
       </c>
       <c r="K77" s="4" t="inlineStr">
         <is>
-          <t>TikTok Made Me Buy It / Honest Review</t>
+          <t>Emotional Reaction &amp; Satisfying Fur Release ASMR</t>
         </is>
       </c>
       <c r="L77" s="5" t="inlineStr">
         <is>
-          <t>https://www.ebay.com/itm/294371599719</t>
+          <t>https://www.ebay.com/itm/187974010368</t>
         </is>
       </c>
     </row>
@@ -9880,7 +9885,7 @@
       </c>
       <c r="B78" s="4" t="inlineStr">
         <is>
-          <t>JK-B2A8S20P Smart BMS 4-8S 200A Active Balance 2A BMS LiFePo4 Li-ion LTO Battery1,766,923.08 VND1,920,512.82 VND | 8% of</t>
+          <t>PlayStation 3 MINECRAFT Deutsch625,098.35 VNDShop all 27Video Games &amp; Consoles</t>
         </is>
       </c>
       <c r="C78" s="4" t="inlineStr">
@@ -9924,7 +9929,7 @@
       </c>
       <c r="L78" s="5" t="inlineStr">
         <is>
-          <t>https://www.ebay.com/itm/236864278279</t>
+          <t>https://www.ebay.com/itm/351153701373</t>
         </is>
       </c>
     </row>
@@ -9934,7 +9939,7 @@
       </c>
       <c r="B79" s="4" t="inlineStr">
         <is>
-          <t>Ersatz Fernbedienung für LG Magic Smart TV AN-MR300 AKB74495301 AKB74855401 NEU741,541.15 VND</t>
+          <t>Personalisierte Schutzhülle für iPhone Handytasche Hülle eigenes Foto Bild Druck744,221.42 VNDHandy Tasche für Samsung G</t>
         </is>
       </c>
       <c r="C79" s="4" t="inlineStr">
@@ -9978,7 +9983,7 @@
       </c>
       <c r="L79" s="5" t="inlineStr">
         <is>
-          <t>https://www.ebay.com/itm/375664903887</t>
+          <t>https://www.ebay.com/itm/272724943549</t>
         </is>
       </c>
     </row>
@@ -9988,7 +9993,7 @@
       </c>
       <c r="B80" s="4" t="inlineStr">
         <is>
-          <t>Leder Schutzhülle für Samsung Galaxy Tab S10 Ultra Tablet Cover Smart Stand Case855,303.69 VNDAlmost goneLeder Cover  Ap</t>
+          <t>Handy Tasche für Samsung Galaxy A55 5G Schutzhülle Book Case Dünn Handy Hülle774,002.19 VNDFree shipping</t>
         </is>
       </c>
       <c r="C80" s="4" t="inlineStr">
@@ -9998,7 +10003,7 @@
       </c>
       <c r="D80" s="4" t="inlineStr">
         <is>
-          <t>Tech &amp; Gadgets</t>
+          <t>Books, Magazines &amp; Audio</t>
         </is>
       </c>
       <c r="E80" s="3" t="n">
@@ -10032,7 +10037,7 @@
       </c>
       <c r="L80" s="5" t="inlineStr">
         <is>
-          <t>https://www.ebay.com/itm/305900488577</t>
+          <t>https://www.ebay.com/itm/285825152658</t>
         </is>
       </c>
     </row>
@@ -10042,7 +10047,7 @@
       </c>
       <c r="B81" s="4" t="inlineStr">
         <is>
-          <t>Leder Cover für Apple iPad Pro 12.9" 2021 Tablet Schutzhülle Case Tasche schwarz855,303.69 VND</t>
+          <t xml:space="preserve">Handy Hülle mit Band für Samsung Galaxy A55 5G Handy Kette Case zum Umhängen714,440.65 VNDFree shippingShop all 33Phone </t>
         </is>
       </c>
       <c r="C81" s="4" t="inlineStr">
@@ -10086,7 +10091,7 @@
       </c>
       <c r="L81" s="5" t="inlineStr">
         <is>
-          <t>https://www.ebay.com/itm/234489000207</t>
+          <t>https://www.ebay.com/itm/204763504739</t>
         </is>
       </c>
     </row>
@@ -10096,7 +10101,7 @@
       </c>
       <c r="B82" s="4" t="inlineStr">
         <is>
-          <t>Schutzhülle Leder Apple iPad Air ( 13" M2 ) ab 2024 Tablet Cover Stand Case Etui855,303.69 VNDShop all 22Computer Access</t>
+          <t>Original Tinte EPSON Stylus Pro 9800 7800 / T6031 T6032 T6034 -T6039 T603B T603C2,650,488.46 VNDOriginal EPSON Tinte Sty</t>
         </is>
       </c>
       <c r="C82" s="4" t="inlineStr">
@@ -10140,7 +10145,7 @@
       </c>
       <c r="L82" s="5" t="inlineStr">
         <is>
-          <t>https://www.ebay.com/itm/226323687048</t>
+          <t>https://www.ebay.com/itm/222635235522</t>
         </is>
       </c>
     </row>
@@ -10150,7 +10155,7 @@
       </c>
       <c r="B83" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Display Für Samsung A55 / A556 5G OLED Bildschirm LCD mit  Rahmen + Tools Neu1,932,771.92 VNDDisplay für Samsung A53 5G </t>
+          <t>Tinte für Canon iPF6400 iPF6400S iPF6450 / PFI-206MBK 206BK 206GY 206C 206M 206Y2,677,291.15 VND</t>
         </is>
       </c>
       <c r="C83" s="4" t="inlineStr">
@@ -10160,7 +10165,7 @@
       </c>
       <c r="D83" s="4" t="inlineStr">
         <is>
-          <t>Menswear &amp; Underwear</t>
+          <t>Tech &amp; Gadgets</t>
         </is>
       </c>
       <c r="E83" s="3" t="n">
@@ -10194,7 +10199,7 @@
       </c>
       <c r="L83" s="5" t="inlineStr">
         <is>
-          <t>https://www.ebay.com/itm/306193635449</t>
+          <t>https://www.ebay.com/itm/352159188925</t>
         </is>
       </c>
     </row>
@@ -10204,7 +10209,7 @@
       </c>
       <c r="B84" s="4" t="inlineStr">
         <is>
-          <t>Display für Samsung A51 A515F HD LCD Touch Screen Glas + Kleber &amp; Tools Neu741,541.15 VND</t>
+          <t>JK-B2A8S20P Smart BMS 4-8S 200A Active Balance 2A BMS LiFePo4 Li-ion LTO Battery1,766,923.08 VND1,920,512.82 VND | 8% of</t>
         </is>
       </c>
       <c r="C84" s="4" t="inlineStr">
@@ -10248,7 +10253,7 @@
       </c>
       <c r="L84" s="5" t="inlineStr">
         <is>
-          <t>https://www.ebay.com/itm/305047092563</t>
+          <t>https://www.ebay.com/itm/236864278279</t>
         </is>
       </c>
     </row>
@@ -10258,7 +10263,7 @@
       </c>
       <c r="B85" s="4" t="inlineStr">
         <is>
-          <t>Display für Samsung A53 5G A536 OLED AMOLED LCD Bildschirm Touch Screen + Kleber1,188,252.69 VNDShop all 48More Computer</t>
+          <t>ORIGINAL SONY Fernbedienung RMT-TX102D KDL40R45XC KDL40R55XC KDL40R550C NEUWARE652,198.85 VND</t>
         </is>
       </c>
       <c r="C85" s="4" t="inlineStr">
@@ -10302,7 +10307,7 @@
       </c>
       <c r="L85" s="5" t="inlineStr">
         <is>
-          <t>https://www.ebay.com/itm/305041451782</t>
+          <t>https://www.ebay.com/itm/373982552937</t>
         </is>
       </c>
     </row>
@@ -10312,7 +10317,7 @@
       </c>
       <c r="B86" s="4" t="inlineStr">
         <is>
-          <t>2 1/2ct Black Diamond Screw Back Studs Womens Earrings 14K White Gold8,546,666.67 VND26,805,641.03 VND Previous price: 2</t>
+          <t>Für Xiaomi Redmi Pad Pro 12.1 Kontrast Robot Silikon Hybrid Hülle Blau / Schwarz713,249.42 VNDAlmost goneLeder Tablet Co</t>
         </is>
       </c>
       <c r="C86" s="4" t="inlineStr">
@@ -10322,7 +10327,7 @@
       </c>
       <c r="D86" s="4" t="inlineStr">
         <is>
-          <t>Jewelry Accessories &amp; Derivatives</t>
+          <t>Tech &amp; Gadgets</t>
         </is>
       </c>
       <c r="E86" s="3" t="n">
@@ -10356,7 +10361,7 @@
       </c>
       <c r="L86" s="5" t="inlineStr">
         <is>
-          <t>https://www.ebay.com/itm/355504570491</t>
+          <t>https://www.ebay.com/itm/176622603332</t>
         </is>
       </c>
     </row>
@@ -10366,7 +10371,7 @@
       </c>
       <c r="B87" s="4" t="inlineStr">
         <is>
-          <t>1/4 - 2 Ct T.W. Natural Diamond Solitaire Pendant in 14k White or Yellow Gold4,358,717.95 VND</t>
+          <t>Leder Tablet Cover Samsung Galaxy Tab S7 FE SM-T733/T736 Stand Case Schutzhülle676,619.08 VND</t>
         </is>
       </c>
       <c r="C87" s="4" t="inlineStr">
@@ -10376,7 +10381,7 @@
       </c>
       <c r="D87" s="4" t="inlineStr">
         <is>
-          <t>Books, Magazines &amp; Audio</t>
+          <t>Tech &amp; Gadgets</t>
         </is>
       </c>
       <c r="E87" s="3" t="n">
@@ -10410,7 +10415,7 @@
       </c>
       <c r="L87" s="5" t="inlineStr">
         <is>
-          <t>https://www.ebay.com/itm/353815614085</t>
+          <t>https://www.ebay.com/itm/304338719356</t>
         </is>
       </c>
     </row>
@@ -10420,7 +10425,7 @@
       </c>
       <c r="B88" s="4" t="inlineStr">
         <is>
-          <t>Panzerkette Halskette 5 mm Echt 750er Gold 18K vergoldet Damen Herren K1807842,795.77 VND</t>
+          <t>Premium Leder Cover Apple iPad Pro 12.9"  2015-17 Tablet Schutzhülle Case Tasche729,033.23 VND828,501.00 VND | 12% offPr</t>
         </is>
       </c>
       <c r="C88" s="4" t="inlineStr">
@@ -10430,7 +10435,7 @@
       </c>
       <c r="D88" s="4" t="inlineStr">
         <is>
-          <t>Kitchenware</t>
+          <t>Tech &amp; Gadgets</t>
         </is>
       </c>
       <c r="E88" s="3" t="n">
@@ -10464,7 +10469,7 @@
       </c>
       <c r="L88" s="5" t="inlineStr">
         <is>
-          <t>https://www.ebay.com/itm/115705706803</t>
+          <t>https://www.ebay.com/itm/234304242705</t>
         </is>
       </c>
     </row>
@@ -10474,7 +10479,7 @@
       </c>
       <c r="B89" s="4" t="inlineStr">
         <is>
-          <t>Herz Anhänger Kette Zirkonia schwarz 750 Gold 18 Karat vergoldet Damen A3047S891,934.04 VNDAlmost goneSet Damenkette Sch</t>
+          <t xml:space="preserve">Display für Samsung A53 5G A536 OLED AMOLED LCD Bildschirm Touch Screen + Kleber1,188,252.69 VNDDisplay für Samsung A53 </t>
         </is>
       </c>
       <c r="C89" s="4" t="inlineStr">
@@ -10484,7 +10489,7 @@
       </c>
       <c r="D89" s="4" t="inlineStr">
         <is>
-          <t>Menswear &amp; Underwear</t>
+          <t>Tech &amp; Gadgets</t>
         </is>
       </c>
       <c r="E89" s="3" t="n">
@@ -10518,7 +10523,7 @@
       </c>
       <c r="L89" s="5" t="inlineStr">
         <is>
-          <t>https://www.ebay.com/itm/332636296199</t>
+          <t>https://www.ebay.com/itm/305041451782</t>
         </is>
       </c>
     </row>
@@ -10528,7 +10533,7 @@
       </c>
       <c r="B90" s="4" t="inlineStr">
         <is>
-          <t>300mg Benfotiamine 3 x 120 Capsules Fat Soluble Thiamine Vitamin B1 Supplement991,345.38 VNDFree shippingJod Kapseln aus</t>
+          <t>Display für Samsung A51 A515F HD LCD Touch Screen Glas + Kleber &amp; Tools Neu741,541.15 VND</t>
         </is>
       </c>
       <c r="C90" s="4" t="inlineStr">
@@ -10538,7 +10543,7 @@
       </c>
       <c r="D90" s="4" t="inlineStr">
         <is>
-          <t>Menswear &amp; Underwear</t>
+          <t>Tech &amp; Gadgets</t>
         </is>
       </c>
       <c r="E90" s="3" t="n">
@@ -10572,7 +10577,7 @@
       </c>
       <c r="L90" s="5" t="inlineStr">
         <is>
-          <t>https://www.ebay.com/itm/357242424467</t>
+          <t>https://www.ebay.com/itm/305047092563</t>
         </is>
       </c>
     </row>
@@ -10582,7 +10587,7 @@
       </c>
       <c r="B91" s="4" t="inlineStr">
         <is>
-          <t>Omega 3 Kapseln - DHA &amp; EPA -  vegan - hochdosiert - Vitamineule744,221.42 VNDFree shipping</t>
+          <t>Display Für Samsung A55 / A556 5G OLED Bildschirm LCD mit  Rahmen + Tools Neu1,932,771.92 VNDShop all 48More Computer Ac</t>
         </is>
       </c>
       <c r="C91" s="4" t="inlineStr">
@@ -10592,7 +10597,7 @@
       </c>
       <c r="D91" s="4" t="inlineStr">
         <is>
-          <t>Health</t>
+          <t>Menswear &amp; Underwear</t>
         </is>
       </c>
       <c r="E91" s="3" t="n">
@@ -10626,7 +10631,7 @@
       </c>
       <c r="L91" s="5" t="inlineStr">
         <is>
-          <t>https://www.ebay.com/itm/127173608481</t>
+          <t>https://www.ebay.com/itm/306193635449</t>
         </is>
       </c>
     </row>
@@ -10636,7 +10641,7 @@
       </c>
       <c r="B92" s="4" t="inlineStr">
         <is>
-          <t>Bockshornklee Kapseln mit 500 mg 4:1 Extrakt - vegan - Vitamineule595,317.58 VNDFree shippingShop all 31Beauty</t>
+          <t>2 1/2ct Black Diamond Screw Back Studs Womens Earrings 14K White Gold8,546,666.67 VND26,805,641.03 VND Previous price: 2</t>
         </is>
       </c>
       <c r="C92" s="4" t="inlineStr">
@@ -10646,7 +10651,7 @@
       </c>
       <c r="D92" s="4" t="inlineStr">
         <is>
-          <t>Health</t>
+          <t>Jewelry Accessories &amp; Derivatives</t>
         </is>
       </c>
       <c r="E92" s="3" t="n">
@@ -10680,7 +10685,7 @@
       </c>
       <c r="L92" s="5" t="inlineStr">
         <is>
-          <t>https://www.ebay.com/itm/125306598648</t>
+          <t>https://www.ebay.com/itm/355504570491</t>
         </is>
       </c>
     </row>
@@ -10690,7 +10695,7 @@
       </c>
       <c r="B93" s="4" t="inlineStr">
         <is>
-          <t>Lonsdale Navy Blue Baseball Cap Hat Embroidered Logo Adjustable Kappe Mütze741,541.15 VND</t>
+          <t>1/4 - 2 Ct T.W. Natural Diamond Solitaire Pendant in 14k White or Yellow Gold4,358,717.95 VND</t>
         </is>
       </c>
       <c r="C93" s="4" t="inlineStr">
@@ -10700,7 +10705,7 @@
       </c>
       <c r="D93" s="4" t="inlineStr">
         <is>
-          <t>Fashion &amp; Apparel</t>
+          <t>Books, Magazines &amp; Audio</t>
         </is>
       </c>
       <c r="E93" s="3" t="n">
@@ -10734,7 +10739,7 @@
       </c>
       <c r="L93" s="5" t="inlineStr">
         <is>
-          <t>https://www.ebay.com/itm/296106350225</t>
+          <t>https://www.ebay.com/itm/353815614085</t>
         </is>
       </c>
     </row>
@@ -10744,7 +10749,7 @@
       </c>
       <c r="B94" s="4" t="inlineStr">
         <is>
-          <t>Puma Speedcat OG team royal white Schuhe Sneaker Motorsport F1 398846-183,275,586.81 VNDShop all 12Men's Shoes &amp; Accesso</t>
+          <t>925 Sterlingsilber Silber Anhänger DAVIDSTERN Hexagramm Charm Kette 20x20mm 50661,780,592.19 VNDAlmost goneShop all 22Fi</t>
         </is>
       </c>
       <c r="C94" s="4" t="inlineStr">
@@ -10754,7 +10759,7 @@
       </c>
       <c r="D94" s="4" t="inlineStr">
         <is>
-          <t>Pet Supplies</t>
+          <t>Fashion &amp; Apparel</t>
         </is>
       </c>
       <c r="E94" s="3" t="n">
@@ -10783,12 +10788,12 @@
       </c>
       <c r="K94" s="4" t="inlineStr">
         <is>
-          <t>Emotional Reaction &amp; Satisfying Fur Release ASMR</t>
+          <t>TikTok Made Me Buy It / Honest Review</t>
         </is>
       </c>
       <c r="L94" s="5" t="inlineStr">
         <is>
-          <t>https://www.ebay.com/itm/156805882161</t>
+          <t>https://www.ebay.com/itm/271569399778</t>
         </is>
       </c>
     </row>
@@ -10798,7 +10803,7 @@
       </c>
       <c r="B95" s="4" t="inlineStr">
         <is>
-          <t>Bikerweste Lederweste Rockerweste Lederkutte Kutte Chopperweste Clubweste2,382,163.73 VND</t>
+          <t>Panzerkette 4 mm Halskette Echt 750er Gold 18Karat vergoldet Damen Herren K1808906,824.42 VND</t>
         </is>
       </c>
       <c r="C95" s="4" t="inlineStr">
@@ -10808,7 +10813,7 @@
       </c>
       <c r="D95" s="4" t="inlineStr">
         <is>
-          <t>Fashion &amp; Apparel</t>
+          <t>Kitchenware</t>
         </is>
       </c>
       <c r="E95" s="3" t="n">
@@ -10842,7 +10847,7 @@
       </c>
       <c r="L95" s="5" t="inlineStr">
         <is>
-          <t>https://www.ebay.com/itm/303349551958</t>
+          <t>https://www.ebay.com/itm/125770552175</t>
         </is>
       </c>
     </row>
@@ -10852,7 +10857,7 @@
       </c>
       <c r="B96" s="4" t="inlineStr">
         <is>
-          <t>Schwarze Lederkutte mit blau Umrandungen Kutte Biker Motorrad Rocker Clubweste2,679,971.42 VNDShop all 68Men's Clothing</t>
+          <t>Set Damenkette Schlüssel Anhänger Zirkonia weiß 750 Gold 18Karat vergoldet A1127595,615.38 VNDAlmost goneHerz Anhänger K</t>
         </is>
       </c>
       <c r="C96" s="4" t="inlineStr">
@@ -10896,7 +10901,7 @@
       </c>
       <c r="L96" s="5" t="inlineStr">
         <is>
-          <t>https://www.ebay.com/itm/301897675077</t>
+          <t>https://www.ebay.com/itm/125770529088</t>
         </is>
       </c>
     </row>
@@ -10906,7 +10911,7 @@
       </c>
       <c r="B97" s="4" t="inlineStr">
         <is>
-          <t>LA PERLA Dessous - Italienischer Spitzen-BH in bordeauxrot - Luxus-Lingerie1,191,230.77 VNDGlamory Garter Belt Strumpfha</t>
+          <t>300mg Benfotiamine 3 x 120 Capsules Fat Soluble Thiamine Vitamin B1 Supplement991,345.38 VNDFree shippingLöwenzahn Kapse</t>
         </is>
       </c>
       <c r="C97" s="4" t="inlineStr">
@@ -10916,7 +10921,7 @@
       </c>
       <c r="D97" s="4" t="inlineStr">
         <is>
-          <t>Fashion &amp; Apparel</t>
+          <t>Menswear &amp; Underwear</t>
         </is>
       </c>
       <c r="E97" s="3" t="n">
@@ -10950,7 +10955,7 @@
       </c>
       <c r="L97" s="5" t="inlineStr">
         <is>
-          <t>https://www.ebay.com/itm/156073236516</t>
+          <t>https://www.ebay.com/itm/357242424467</t>
         </is>
       </c>
     </row>
@@ -10960,7 +10965,7 @@
       </c>
       <c r="B98" s="4" t="inlineStr">
         <is>
-          <t>Luxuriöses Push-Up-Dessous-Set mit Animal Muster – B-Cup, BH High-Waist Slip744,221.42 VND</t>
+          <t>Curcuma Extrakt Kapseln - hochdosiert - 350 mg Curcuminoide - Vitamineule744,221.42 VNDFree shipping</t>
         </is>
       </c>
       <c r="C98" s="4" t="inlineStr">
@@ -10970,7 +10975,7 @@
       </c>
       <c r="D98" s="4" t="inlineStr">
         <is>
-          <t>Kitchenware</t>
+          <t>Health</t>
         </is>
       </c>
       <c r="E98" s="3" t="n">
@@ -10999,12 +11004,12 @@
       </c>
       <c r="K98" s="4" t="inlineStr">
         <is>
-          <t>Before/After Macro Skin Texture Zoom (Cận cảnh bề mặt da)</t>
+          <t>TikTok Made Me Buy It / Honest Review</t>
         </is>
       </c>
       <c r="L98" s="5" t="inlineStr">
         <is>
-          <t>https://www.ebay.com/itm/317440894200</t>
+          <t>https://www.ebay.com/itm/123839173201</t>
         </is>
       </c>
     </row>
@@ -11014,7 +11019,7 @@
       </c>
       <c r="B99" s="4" t="inlineStr">
         <is>
-          <t>Noir Handmade - Hautenger Wetlook Strapsgürtel transparent schwarz - S-3XL1,664,745.00 VNDShop all 35Women's Clothing</t>
+          <t>Jod Kapseln aus Bio Kelp / Tabletten - 400µg aus Bio Kelp Extrakt - Vitamineule774,002.19 VNDFree shippingShop all 31Bea</t>
         </is>
       </c>
       <c r="C99" s="4" t="inlineStr">
@@ -11024,7 +11029,7 @@
       </c>
       <c r="D99" s="4" t="inlineStr">
         <is>
-          <t>Menswear &amp; Underwear</t>
+          <t>Health</t>
         </is>
       </c>
       <c r="E99" s="3" t="n">
@@ -11058,7 +11063,7 @@
       </c>
       <c r="L99" s="5" t="inlineStr">
         <is>
-          <t>https://www.ebay.com/itm/372295070125</t>
+          <t>https://www.ebay.com/itm/124078773818</t>
         </is>
       </c>
     </row>
@@ -11068,7 +11073,7 @@
       </c>
       <c r="B100" s="4" t="inlineStr">
         <is>
-          <t>Breitling TransOcean Chrono Quartz 40mm Iced 13ct Diamond Black Dial A530401166,641,025.64 VNDAlmost gone</t>
+          <t>Lonsdale Navy Blue Baseball Cap Hat Embroidered Logo Adjustable Kappe Mütze741,541.15 VND</t>
         </is>
       </c>
       <c r="C100" s="4" t="inlineStr">
@@ -11112,7 +11117,7 @@
       </c>
       <c r="L100" s="5" t="inlineStr">
         <is>
-          <t>https://www.ebay.com/itm/146360754668</t>
+          <t>https://www.ebay.com/itm/296106350225</t>
         </is>
       </c>
     </row>
@@ -11122,51 +11127,51 @@
       </c>
       <c r="B101" s="4" t="inlineStr">
         <is>
-          <t>Wireless Magnetic Lavalier Lapel Microphone for iPhone &amp; Type-C</t>
+          <t>Puma Speedcat OG team royal white Schuhe Sneaker Motorsport F1 398846-183,275,586.81 VNDShop all 12Men's Shoes &amp; Accesso</t>
         </is>
       </c>
       <c r="C101" s="4" t="inlineStr">
         <is>
-          <t>🔥 Bùng Nổ 24h (Viral Spike)</t>
+          <t>🔥 Xu Hướng Tăng Trưởng</t>
         </is>
       </c>
       <c r="D101" s="4" t="inlineStr">
         <is>
-          <t>Phones &amp; Electronics</t>
+          <t>Pet Supplies</t>
         </is>
       </c>
       <c r="E101" s="3" t="n">
-        <v>69.8</v>
+        <v>74.2</v>
       </c>
       <c r="F101" s="3" t="n">
-        <v>90</v>
+        <v>76</v>
       </c>
       <c r="G101" s="3" t="n">
-        <v>45</v>
+        <v>72</v>
       </c>
       <c r="H101" s="3" t="inlineStr">
         <is>
-          <t>$16.99 - $24.99</t>
+          <t>$19.99</t>
         </is>
       </c>
       <c r="I101" s="4" t="inlineStr">
         <is>
-          <t>TikTok US Viral 24h</t>
+          <t>eBay US</t>
         </is>
       </c>
       <c r="J101" s="4" t="inlineStr">
         <is>
-          <t>TikTok Shop, TikTok Viral 24h</t>
+          <t>eBay US Deals</t>
         </is>
       </c>
       <c r="K101" s="4" t="inlineStr">
         <is>
-          <t>Side-by-side Live Demo &amp; Unboxing ASMR</t>
+          <t>Emotional Reaction &amp; Satisfying Fur Release ASMR</t>
         </is>
       </c>
       <c r="L101" s="5" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/tag/wirelessmicrophone</t>
+          <t>https://www.ebay.com/itm/156805882161</t>
         </is>
       </c>
     </row>
@@ -11176,51 +11181,51 @@
       </c>
       <c r="B102" s="4" t="inlineStr">
         <is>
-          <t>Custom Pet Portrait Sweatshirt &amp; Embroidered Dog Mom Hoodie</t>
+          <t>Biker Kutte Lederkutte Lederweste Clubweste Rockerweste Herren Chopper Motorrad2,679,971.42 VND</t>
         </is>
       </c>
       <c r="C102" s="4" t="inlineStr">
         <is>
-          <t>🌲 Evergreen Bền Vững</t>
+          <t>🔥 Xu Hướng Tăng Trưởng</t>
         </is>
       </c>
       <c r="D102" s="4" t="inlineStr">
         <is>
-          <t>Pet Supplies</t>
+          <t>Fashion &amp; Apparel</t>
         </is>
       </c>
       <c r="E102" s="3" t="n">
-        <v>69.8</v>
+        <v>74.2</v>
       </c>
       <c r="F102" s="3" t="n">
-        <v>50</v>
+        <v>76</v>
       </c>
       <c r="G102" s="3" t="n">
-        <v>94</v>
+        <v>72</v>
       </c>
       <c r="H102" s="3" t="inlineStr">
         <is>
-          <t>$34.00 - $48.00</t>
+          <t>$19.99</t>
         </is>
       </c>
       <c r="I102" s="4" t="inlineStr">
         <is>
-          <t>Etsy US Trending</t>
+          <t>eBay US</t>
         </is>
       </c>
       <c r="J102" s="4" t="inlineStr">
         <is>
-          <t>Etsy US, Handmade/POD</t>
+          <t>eBay US Deals</t>
         </is>
       </c>
       <c r="K102" s="4" t="inlineStr">
         <is>
-          <t>Emotional Reaction &amp; Satisfying Fur Release ASMR</t>
+          <t>TikTok Made Me Buy It / Honest Review</t>
         </is>
       </c>
       <c r="L102" s="5" t="inlineStr">
         <is>
-          <t>https://www.etsy.com/market/custom_pet_sweatshirt</t>
+          <t>https://www.ebay.com/itm/302258284099</t>
         </is>
       </c>
     </row>
@@ -11230,41 +11235,41 @@
       </c>
       <c r="B103" s="4" t="inlineStr">
         <is>
-          <t>Handmade Organic Soy Aromatherapy Candle in Amber Glass Jar</t>
+          <t>Schwarze Lederkutte mit blau Umrandungen Kutte Biker Motorrad Rocker Clubweste2,679,971.42 VNDShop all 68Men's Clothing</t>
         </is>
       </c>
       <c r="C103" s="4" t="inlineStr">
         <is>
-          <t>🌲 Evergreen Bền Vững</t>
+          <t>🔥 Xu Hướng Tăng Trưởng</t>
         </is>
       </c>
       <c r="D103" s="4" t="inlineStr">
         <is>
-          <t>Home Supplies</t>
+          <t>Menswear &amp; Underwear</t>
         </is>
       </c>
       <c r="E103" s="3" t="n">
-        <v>69.8</v>
+        <v>74.2</v>
       </c>
       <c r="F103" s="3" t="n">
-        <v>50</v>
+        <v>76</v>
       </c>
       <c r="G103" s="3" t="n">
-        <v>94</v>
+        <v>72</v>
       </c>
       <c r="H103" s="3" t="inlineStr">
         <is>
-          <t>$18.00 - $26.00</t>
+          <t>$19.99</t>
         </is>
       </c>
       <c r="I103" s="4" t="inlineStr">
         <is>
-          <t>Etsy US Trending</t>
+          <t>eBay US</t>
         </is>
       </c>
       <c r="J103" s="4" t="inlineStr">
         <is>
-          <t>Etsy US, Handmade/POD</t>
+          <t>eBay US Deals</t>
         </is>
       </c>
       <c r="K103" s="4" t="inlineStr">
@@ -11274,7 +11279,7 @@
       </c>
       <c r="L103" s="5" t="inlineStr">
         <is>
-          <t>https://www.etsy.com/market/soy_candle</t>
+          <t>https://www.ebay.com/itm/301897675077</t>
         </is>
       </c>
     </row>
@@ -11284,41 +11289,41 @@
       </c>
       <c r="B104" s="4" t="inlineStr">
         <is>
-          <t>milwaukee brewers baseball</t>
+          <t>Unterbrustkorsett Schwarz Leder Corsage Gothic Korsett Underbust Leather Corsets2,178,463.27 VND2,293,119.23 VND | 5% of</t>
         </is>
       </c>
       <c r="C104" s="4" t="inlineStr">
         <is>
-          <t>🔥 Bùng Nổ 24h (Viral Spike)</t>
+          <t>🔥 Xu Hướng Tăng Trưởng</t>
         </is>
       </c>
       <c r="D104" s="4" t="inlineStr">
         <is>
-          <t>General Trend</t>
+          <t>Fashion &amp; Apparel</t>
         </is>
       </c>
       <c r="E104" s="3" t="n">
-        <v>68.7</v>
+        <v>74.2</v>
       </c>
       <c r="F104" s="3" t="n">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="G104" s="3" t="n">
-        <v>45</v>
+        <v>72</v>
       </c>
       <c r="H104" s="3" t="inlineStr">
         <is>
-          <t>$25.00</t>
+          <t>$19.99</t>
         </is>
       </c>
       <c r="I104" s="4" t="inlineStr">
         <is>
-          <t>Google Trends US</t>
+          <t>eBay US</t>
         </is>
       </c>
       <c r="J104" s="4" t="inlineStr">
         <is>
-          <t>Google Trends US Search</t>
+          <t>eBay US Deals</t>
         </is>
       </c>
       <c r="K104" s="4" t="inlineStr">
@@ -11328,7 +11333,7 @@
       </c>
       <c r="L104" s="5" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?geo=US&amp;q=milwaukee%20brewers%20baseball</t>
+          <t>https://www.ebay.com/itm/362632687305</t>
         </is>
       </c>
     </row>
@@ -11338,51 +11343,51 @@
       </c>
       <c r="B105" s="4" t="inlineStr">
         <is>
-          <t>swimming</t>
+          <t>Satin Vollbrustkorsett Schnürkorsett Korsett Mieder Corset Corsage Schwarz LANG2,084,653.85 VND</t>
         </is>
       </c>
       <c r="C105" s="4" t="inlineStr">
         <is>
-          <t>🔥 Bùng Nổ 24h (Viral Spike)</t>
+          <t>🔥 Xu Hướng Tăng Trưởng</t>
         </is>
       </c>
       <c r="D105" s="4" t="inlineStr">
         <is>
-          <t>DIY, Craft &amp; POD</t>
+          <t>Fashion &amp; Apparel</t>
         </is>
       </c>
       <c r="E105" s="3" t="n">
-        <v>63.2</v>
+        <v>74.2</v>
       </c>
       <c r="F105" s="3" t="n">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="G105" s="3" t="n">
-        <v>45</v>
+        <v>72</v>
       </c>
       <c r="H105" s="3" t="inlineStr">
         <is>
-          <t>$25.00</t>
+          <t>$19.99</t>
         </is>
       </c>
       <c r="I105" s="4" t="inlineStr">
         <is>
-          <t>Google Trends US</t>
+          <t>eBay US</t>
         </is>
       </c>
       <c r="J105" s="4" t="inlineStr">
         <is>
-          <t>Google Trends US Search</t>
+          <t>eBay US Deals</t>
         </is>
       </c>
       <c r="K105" s="4" t="inlineStr">
         <is>
-          <t>Behind The Scenes Crafting &amp; Emotional Gift Unboxing</t>
+          <t>TikTok Made Me Buy It / Honest Review</t>
         </is>
       </c>
       <c r="L105" s="5" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?geo=US&amp;q=swimming</t>
+          <t>https://www.ebay.com/itm/362636865751</t>
         </is>
       </c>
     </row>
@@ -11392,41 +11397,41 @@
       </c>
       <c r="B106" s="4" t="inlineStr">
         <is>
-          <t>fitness</t>
+          <t>Unterbrustkorsett Rot Lack Corsage tolles Taillen training PVC Underbust Corsets1,980,421.15 VND2,084,653.85 VND | 5% of</t>
         </is>
       </c>
       <c r="C106" s="4" t="inlineStr">
         <is>
-          <t>🔥 Bùng Nổ 24h (Viral Spike)</t>
+          <t>🔥 Xu Hướng Tăng Trưởng</t>
         </is>
       </c>
       <c r="D106" s="4" t="inlineStr">
         <is>
-          <t>Health &amp; Fitness</t>
+          <t>Fashion &amp; Apparel</t>
         </is>
       </c>
       <c r="E106" s="3" t="n">
-        <v>63.2</v>
+        <v>74.2</v>
       </c>
       <c r="F106" s="3" t="n">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="G106" s="3" t="n">
-        <v>45</v>
+        <v>72</v>
       </c>
       <c r="H106" s="3" t="inlineStr">
         <is>
-          <t>$25.00</t>
+          <t>$19.99</t>
         </is>
       </c>
       <c r="I106" s="4" t="inlineStr">
         <is>
-          <t>Google Trends US</t>
+          <t>eBay US</t>
         </is>
       </c>
       <c r="J106" s="4" t="inlineStr">
         <is>
-          <t>Google Trends US Search</t>
+          <t>eBay US Deals</t>
         </is>
       </c>
       <c r="K106" s="4" t="inlineStr">
@@ -11436,7 +11441,7 @@
       </c>
       <c r="L106" s="5" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?geo=US&amp;q=fitness</t>
+          <t>https://www.ebay.com/itm/363166536187</t>
         </is>
       </c>
     </row>
@@ -11446,51 +11451,51 @@
       </c>
       <c r="B107" s="4" t="inlineStr">
         <is>
-          <t>new jersey</t>
+          <t>New Omega Seamaster Diver 300M Automatic Green Men's Watch 210.90.42.20.10.001266,769,230.77 VND320,512,820.51 VND Previ</t>
         </is>
       </c>
       <c r="C107" s="4" t="inlineStr">
         <is>
-          <t>🔥 Bùng Nổ 24h (Viral Spike)</t>
+          <t>🔥 Xu Hướng Tăng Trưởng</t>
         </is>
       </c>
       <c r="D107" s="4" t="inlineStr">
         <is>
-          <t>General Trend</t>
+          <t>Menswear &amp; Underwear</t>
         </is>
       </c>
       <c r="E107" s="3" t="n">
-        <v>63.2</v>
+        <v>74.2</v>
       </c>
       <c r="F107" s="3" t="n">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="G107" s="3" t="n">
-        <v>45</v>
+        <v>72</v>
       </c>
       <c r="H107" s="3" t="inlineStr">
         <is>
-          <t>$25.00</t>
+          <t>$19.99</t>
         </is>
       </c>
       <c r="I107" s="4" t="inlineStr">
         <is>
-          <t>Google Trends US</t>
+          <t>eBay US</t>
         </is>
       </c>
       <c r="J107" s="4" t="inlineStr">
         <is>
-          <t>Google Trends US Search</t>
+          <t>eBay US Deals</t>
         </is>
       </c>
       <c r="K107" s="4" t="inlineStr">
         <is>
-          <t>TikTok Made Me Buy It / Honest Review</t>
+          <t>Side-by-side Live Demo &amp; Unboxing ASMR</t>
         </is>
       </c>
       <c r="L107" s="5" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?geo=US&amp;q=new%20jersey</t>
+          <t>https://www.ebay.com/itm/357622544308</t>
         </is>
       </c>
     </row>
@@ -11500,51 +11505,51 @@
       </c>
       <c r="B108" s="4" t="inlineStr">
         <is>
-          <t>cycling</t>
+          <t>Custom Name Birth Flower Bar Necklace &amp; Personalized Jewelry</t>
         </is>
       </c>
       <c r="C108" s="4" t="inlineStr">
         <is>
-          <t>🔥 Bùng Nổ 24h (Viral Spike)</t>
+          <t>🌲 Evergreen Bền Vững</t>
         </is>
       </c>
       <c r="D108" s="4" t="inlineStr">
         <is>
-          <t>General Trend</t>
+          <t>Jewelry Accessories &amp; Derivatives</t>
         </is>
       </c>
       <c r="E108" s="3" t="n">
-        <v>63.2</v>
+        <v>74.8</v>
       </c>
       <c r="F108" s="3" t="n">
-        <v>78</v>
+        <v>50</v>
       </c>
       <c r="G108" s="3" t="n">
-        <v>45</v>
+        <v>94</v>
       </c>
       <c r="H108" s="3" t="inlineStr">
         <is>
-          <t>$25.00</t>
+          <t>$24.00 - $38.00</t>
         </is>
       </c>
       <c r="I108" s="4" t="inlineStr">
         <is>
-          <t>Google Trends US</t>
+          <t>Etsy US Trending</t>
         </is>
       </c>
       <c r="J108" s="4" t="inlineStr">
         <is>
-          <t>Google Trends US Search</t>
+          <t>Etsy US, Handmade/POD, TikTok Gift Trend</t>
         </is>
       </c>
       <c r="K108" s="4" t="inlineStr">
         <is>
-          <t>TikTok Made Me Buy It / Honest Review</t>
+          <t>Behind The Scenes Crafting &amp; Emotional Gift Unboxing</t>
         </is>
       </c>
       <c r="L108" s="5" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?geo=US&amp;q=cycling</t>
+          <t>https://www.etsy.com/market/birth_flower_necklace</t>
         </is>
       </c>
     </row>
@@ -11554,51 +11559,51 @@
       </c>
       <c r="B109" s="4" t="inlineStr">
         <is>
-          <t>netflix top movies right now</t>
+          <t>Personalized Wooden Docking Station &amp; Desk Organizer for Men</t>
         </is>
       </c>
       <c r="C109" s="4" t="inlineStr">
         <is>
-          <t>🔥 Bùng Nổ 24h (Viral Spike)</t>
+          <t>🌲 Evergreen Bền Vững</t>
         </is>
       </c>
       <c r="D109" s="4" t="inlineStr">
         <is>
-          <t>General Trend</t>
+          <t>Menswear &amp; Underwear</t>
         </is>
       </c>
       <c r="E109" s="3" t="n">
-        <v>63.2</v>
+        <v>74.8</v>
       </c>
       <c r="F109" s="3" t="n">
-        <v>78</v>
+        <v>50</v>
       </c>
       <c r="G109" s="3" t="n">
-        <v>45</v>
+        <v>94</v>
       </c>
       <c r="H109" s="3" t="inlineStr">
         <is>
-          <t>$25.00</t>
+          <t>$29.50 - $45.00</t>
         </is>
       </c>
       <c r="I109" s="4" t="inlineStr">
         <is>
-          <t>Google Trends US</t>
+          <t>Etsy US Trending</t>
         </is>
       </c>
       <c r="J109" s="4" t="inlineStr">
         <is>
-          <t>Google Trends US Search</t>
+          <t>Etsy US, Handmade/POD, TikTok Gift Trend</t>
         </is>
       </c>
       <c r="K109" s="4" t="inlineStr">
         <is>
-          <t>TikTok Made Me Buy It / Honest Review</t>
+          <t>Behind The Scenes Crafting &amp; Emotional Gift Unboxing</t>
         </is>
       </c>
       <c r="L109" s="5" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?geo=US&amp;q=netflix%20top%20movies%20right%20now</t>
+          <t>https://www.etsy.com/market/wooden_docking_station</t>
         </is>
       </c>
     </row>
@@ -11608,51 +11613,51 @@
       </c>
       <c r="B110" s="4" t="inlineStr">
         <is>
-          <t>what is a data breach</t>
+          <t>Minimalist Custom Acrylic Wall Calendar &amp; Family Command Center</t>
         </is>
       </c>
       <c r="C110" s="4" t="inlineStr">
         <is>
-          <t>🔥 Bùng Nổ 24h (Viral Spike)</t>
+          <t>🌲 Evergreen Bền Vững</t>
         </is>
       </c>
       <c r="D110" s="4" t="inlineStr">
         <is>
-          <t>Fashion &amp; Apparel</t>
+          <t>Home Supplies</t>
         </is>
       </c>
       <c r="E110" s="3" t="n">
-        <v>63.2</v>
+        <v>74.8</v>
       </c>
       <c r="F110" s="3" t="n">
-        <v>78</v>
+        <v>50</v>
       </c>
       <c r="G110" s="3" t="n">
-        <v>45</v>
+        <v>94</v>
       </c>
       <c r="H110" s="3" t="inlineStr">
         <is>
-          <t>$25.00</t>
+          <t>$39.00 - $69.00</t>
         </is>
       </c>
       <c r="I110" s="4" t="inlineStr">
         <is>
-          <t>Google Trends US</t>
+          <t>Etsy US Trending</t>
         </is>
       </c>
       <c r="J110" s="4" t="inlineStr">
         <is>
-          <t>Google Trends US Search</t>
+          <t>Etsy US, Handmade/POD, TikTok Gift Trend</t>
         </is>
       </c>
       <c r="K110" s="4" t="inlineStr">
         <is>
-          <t>TikTok Made Me Buy It / Honest Review</t>
+          <t>Behind The Scenes Crafting &amp; Emotional Gift Unboxing</t>
         </is>
       </c>
       <c r="L110" s="5" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?geo=US&amp;q=what%20is%20a%20data%20breach</t>
+          <t>https://www.etsy.com/market/acrylic_calendar</t>
         </is>
       </c>
     </row>
@@ -11662,51 +11667,51 @@
       </c>
       <c r="B111" s="4" t="inlineStr">
         <is>
-          <t>flood watch</t>
+          <t>Engraved Olive Wood Cutting Board &amp; Charcuterie Serving Platter</t>
         </is>
       </c>
       <c r="C111" s="4" t="inlineStr">
         <is>
-          <t>🔥 Bùng Nổ 24h (Viral Spike)</t>
+          <t>🌲 Evergreen Bền Vững</t>
         </is>
       </c>
       <c r="D111" s="4" t="inlineStr">
         <is>
-          <t>Gadgets &amp; Electronics</t>
+          <t>Kitchenware</t>
         </is>
       </c>
       <c r="E111" s="3" t="n">
-        <v>63.2</v>
+        <v>74.8</v>
       </c>
       <c r="F111" s="3" t="n">
-        <v>78</v>
+        <v>50</v>
       </c>
       <c r="G111" s="3" t="n">
-        <v>45</v>
+        <v>94</v>
       </c>
       <c r="H111" s="3" t="inlineStr">
         <is>
-          <t>$25.00</t>
+          <t>$32.00 - $55.00</t>
         </is>
       </c>
       <c r="I111" s="4" t="inlineStr">
         <is>
-          <t>Google Trends US</t>
+          <t>Etsy US Trending</t>
         </is>
       </c>
       <c r="J111" s="4" t="inlineStr">
         <is>
-          <t>Google Trends US Search</t>
+          <t>Etsy US, Handmade/POD, TikTok Gift Trend</t>
         </is>
       </c>
       <c r="K111" s="4" t="inlineStr">
         <is>
-          <t>Side-by-side Live Demo &amp; Unboxing ASMR</t>
+          <t>Behind The Scenes Crafting &amp; Emotional Gift Unboxing</t>
         </is>
       </c>
       <c r="L111" s="5" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?geo=US&amp;q=flood%20watch</t>
+          <t>https://www.etsy.com/market/personalized_cutting_board</t>
         </is>
       </c>
     </row>
@@ -11716,51 +11721,51 @@
       </c>
       <c r="B112" s="4" t="inlineStr">
         <is>
-          <t>cloud</t>
+          <t>Custom Pet Portrait Sweatshirt &amp; Embroidered Dog Mom Hoodie</t>
         </is>
       </c>
       <c r="C112" s="4" t="inlineStr">
         <is>
-          <t>🔥 Bùng Nổ 24h (Viral Spike)</t>
+          <t>🌲 Evergreen Bền Vững</t>
         </is>
       </c>
       <c r="D112" s="4" t="inlineStr">
         <is>
-          <t>General Trend</t>
+          <t>Pet Supplies</t>
         </is>
       </c>
       <c r="E112" s="3" t="n">
-        <v>63.2</v>
+        <v>69.8</v>
       </c>
       <c r="F112" s="3" t="n">
-        <v>78</v>
+        <v>50</v>
       </c>
       <c r="G112" s="3" t="n">
-        <v>45</v>
+        <v>94</v>
       </c>
       <c r="H112" s="3" t="inlineStr">
         <is>
-          <t>$25.00</t>
+          <t>$34.00 - $48.00</t>
         </is>
       </c>
       <c r="I112" s="4" t="inlineStr">
         <is>
-          <t>Google Trends US</t>
+          <t>Etsy US Trending</t>
         </is>
       </c>
       <c r="J112" s="4" t="inlineStr">
         <is>
-          <t>Google Trends US Search</t>
+          <t>Etsy US, Handmade/POD</t>
         </is>
       </c>
       <c r="K112" s="4" t="inlineStr">
         <is>
-          <t>TikTok Made Me Buy It / Honest Review</t>
+          <t>Emotional Reaction &amp; Satisfying Fur Release ASMR</t>
         </is>
       </c>
       <c r="L112" s="5" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?geo=US&amp;q=cloud</t>
+          <t>https://www.etsy.com/market/custom_pet_sweatshirt</t>
         </is>
       </c>
     </row>
@@ -11770,51 +11775,51 @@
       </c>
       <c r="B113" s="4" t="inlineStr">
         <is>
-          <t>earthquake near me</t>
+          <t>Handmade Organic Soy Aromatherapy Candle in Amber Glass Jar</t>
         </is>
       </c>
       <c r="C113" s="4" t="inlineStr">
         <is>
-          <t>🔥 Bùng Nổ 24h (Viral Spike)</t>
+          <t>🌲 Evergreen Bền Vững</t>
         </is>
       </c>
       <c r="D113" s="4" t="inlineStr">
         <is>
-          <t>DIY, Craft &amp; POD</t>
+          <t>Home Supplies</t>
         </is>
       </c>
       <c r="E113" s="3" t="n">
-        <v>63.2</v>
+        <v>69.8</v>
       </c>
       <c r="F113" s="3" t="n">
-        <v>78</v>
+        <v>50</v>
       </c>
       <c r="G113" s="3" t="n">
-        <v>45</v>
+        <v>94</v>
       </c>
       <c r="H113" s="3" t="inlineStr">
         <is>
-          <t>$25.00</t>
+          <t>$18.00 - $26.00</t>
         </is>
       </c>
       <c r="I113" s="4" t="inlineStr">
         <is>
-          <t>Google Trends US</t>
+          <t>Etsy US Trending</t>
         </is>
       </c>
       <c r="J113" s="4" t="inlineStr">
         <is>
-          <t>Google Trends US Search</t>
+          <t>Etsy US, Handmade/POD</t>
         </is>
       </c>
       <c r="K113" s="4" t="inlineStr">
         <is>
-          <t>Behind The Scenes Crafting &amp; Emotional Gift Unboxing</t>
+          <t>TikTok Made Me Buy It / Honest Review</t>
         </is>
       </c>
       <c r="L113" s="5" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?geo=US&amp;q=earthquake%20near%20me</t>
+          <t>https://www.etsy.com/market/soy_candle</t>
         </is>
       </c>
     </row>
@@ -11949,7 +11954,7 @@
     <col width="48" customWidth="1" min="2" max="2"/>
     <col width="26" customWidth="1" min="3" max="3"/>
     <col width="31" customWidth="1" min="4" max="4"/>
-    <col width="29" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
     <col width="23" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
     <col width="13" customWidth="1" min="8" max="8"/>
@@ -12049,7 +12054,7 @@
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>Sarah Potempa | Beachwaver</t>
+          <t>TheBeachwaver</t>
         </is>
       </c>
       <c r="F3" s="4" t="inlineStr">
@@ -12082,7 +12087,7 @@
       </c>
       <c r="L3" s="5" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@thebeachwaver/video/7325595304670678315</t>
+          <t>https://www.tiktok.com/@thebeachwaver/video/7356017048943643950</t>
         </is>
       </c>
     </row>
@@ -12107,7 +12112,7 @@
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>GuruNanda Official</t>
+          <t>GuruNanda LLC</t>
         </is>
       </c>
       <c r="F4" s="4" t="inlineStr">
@@ -12140,7 +12145,7 @@
       </c>
       <c r="L4" s="5" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@gurunanda.official/video/7279326442644262187</t>
+          <t>https://www.tiktok.com/@gurunanda.official/video/7429800163327102251</t>
         </is>
       </c>
     </row>
@@ -12165,7 +12170,7 @@
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>Clean Skin Club</t>
+          <t>Skinfluencer</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
@@ -12198,7 +12203,7 @@
       </c>
       <c r="L5" s="5" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@cleanskinclub/video/7289524021272743210</t>
+          <t>https://www.tiktok.com/@yurileeeee/video/7221620810480487723</t>
         </is>
       </c>
     </row>
@@ -12223,7 +12228,7 @@
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>Wavytalk Official</t>
+          <t>Julissa Guillen</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr">
@@ -12256,7 +12261,7 @@
       </c>
       <c r="L6" s="5" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@wavytalkofficial/video/7308119047976193322</t>
+          <t>https://www.tiktok.com/@julissa_guillen/video/7472807429730798879</t>
         </is>
       </c>
     </row>
@@ -12281,7 +12286,7 @@
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>Halara Official</t>
+          <t>marteenredman</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
@@ -12314,7 +12319,7 @@
       </c>
       <c r="L7" s="5" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@halara_official/video/7285141029838327072</t>
+          <t>https://www.tiktok.com/@marteen2003/video/7439055743417863467</t>
         </is>
       </c>
     </row>
@@ -12339,7 +12344,7 @@
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>Tarte Cosmetics</t>
+          <t>Anna Volpi</t>
         </is>
       </c>
       <c r="F8" s="4" t="inlineStr">
@@ -12372,7 +12377,7 @@
       </c>
       <c r="L8" s="5" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@tartecosmetics/video/7298642398453075246</t>
+          <t>https://www.tiktok.com/@volpi_nana/video/7339999772620623137</t>
         </is>
       </c>
     </row>
@@ -12397,7 +12402,7 @@
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>Medicube Official</t>
+          <t>medicube global</t>
         </is>
       </c>
       <c r="F9" s="4" t="inlineStr">
@@ -12430,7 +12435,7 @@
       </c>
       <c r="L9" s="5" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@medicube_official/video/7311749814400781570</t>
+          <t>https://www.tiktok.com/@medicube_official/video/7620065284086402317</t>
         </is>
       </c>
     </row>
@@ -12488,7 +12493,7 @@
       </c>
       <c r="L10" s="5" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@owalalife/video/7264875328905628974</t>
+          <t>https://www.tiktok.com/@owala/video/7221286918594546986</t>
         </is>
       </c>
     </row>
@@ -12513,7 +12518,7 @@
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>The Pink Stuff USA</t>
+          <t>The Pink Stuff</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
@@ -12546,7 +12551,7 @@
       </c>
       <c r="L11" s="5" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@thepinkstuff_us/video/7258380299836378410</t>
+          <t>https://www.tiktok.com/@cleanwithpinkstuff/video/7202974721091112198</t>
         </is>
       </c>
     </row>
@@ -12571,7 +12576,7 @@
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>Anker Official</t>
+          <t>ANKER</t>
         </is>
       </c>
       <c r="F12" s="4" t="inlineStr">
@@ -12604,7 +12609,7 @@
       </c>
       <c r="L12" s="5" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@anker_official/video/7302485601248054570</t>
+          <t>https://www.tiktok.com/@ankerofficial/video/7414300606036200734</t>
         </is>
       </c>
     </row>
@@ -12629,7 +12634,7 @@
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>MicroTouch Grooming</t>
+          <t>JG</t>
         </is>
       </c>
       <c r="F13" s="4" t="inlineStr">
@@ -12662,7 +12667,7 @@
       </c>
       <c r="L13" s="5" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@microtouch_official/video/7294520938453075211</t>
+          <t>https://www.tiktok.com/@itsjgbaby/video/7633124615593807135</t>
         </is>
       </c>
     </row>
@@ -12687,7 +12692,7 @@
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>Aumuca Pet</t>
+          <t>Aumuca Pet Official</t>
         </is>
       </c>
       <c r="F14" s="4" t="inlineStr">
@@ -12720,7 +12725,7 @@
       </c>
       <c r="L14" s="5" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@aumucapet/video/7272991044875750698</t>
+          <t>https://www.tiktok.com/@aumucapet</t>
         </is>
       </c>
     </row>
@@ -12745,12 +12750,12 @@
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>Ryse Fuel &amp; Supps</t>
+          <t>RYSE Supplements</t>
         </is>
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>@rysesupps</t>
+          <t>@ryse_supps</t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr">
@@ -12778,7 +12783,7 @@
       </c>
       <c r="L15" s="5" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@rysesupps/video/7315682947198274858</t>
+          <t>https://www.tiktok.com/@ryse_supps</t>
         </is>
       </c>
     </row>
@@ -12803,7 +12808,7 @@
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>Bloom Nutrition</t>
+          <t>Sammie Head</t>
         </is>
       </c>
       <c r="F16" s="4" t="inlineStr">
@@ -12836,7 +12841,7 @@
       </c>
       <c r="L16" s="5" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@bloomnu/video/7289567845123891498</t>
+          <t>https://www.tiktok.com/@sammie_head/video/7427978403812281631</t>
         </is>
       </c>
     </row>
@@ -12861,7 +12866,7 @@
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>Solawave Skincare</t>
+          <t>Krista Stucchio</t>
         </is>
       </c>
       <c r="F17" s="4" t="inlineStr">
@@ -12894,7 +12899,7 @@
       </c>
       <c r="L17" s="5" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@solawave/video/7274567891234567890</t>
+          <t>https://www.tiktok.com/@kristastucchio/video/7444008146323983646</t>
         </is>
       </c>
     </row>
@@ -12919,12 +12924,12 @@
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>DriveSmart US</t>
+          <t>Fanttik</t>
         </is>
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>@drivesmart_us</t>
+          <t>@fanttik_official</t>
         </is>
       </c>
       <c r="G18" s="3" t="inlineStr">
@@ -12952,7 +12957,7 @@
       </c>
       <c r="L18" s="5" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@cleanwith_heidi/video/7389146461942484257</t>
+          <t>https://www.tiktok.com/@fanttik_official/video/7563514320575892766</t>
         </is>
       </c>
     </row>

--- a/exports/TikTok_Shop_US_Latest_Trends.xlsx
+++ b/exports/TikTok_Shop_US_Latest_Trends.xlsx
@@ -514,7 +514,7 @@
     <col width="36" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="25" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
     <col width="48" customWidth="1" min="7" max="7"/>
     <col width="48" customWidth="1" min="8" max="8"/>
     <col width="48" customWidth="1" min="9" max="9"/>
@@ -954,7 +954,7 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>STANLEY Quencher H2.0 Tumbler with Handle and Straw 30 oz | Flowstate 3-Position Lid | Cup Holder Compatible for Travel | Insulate</t>
+          <t>STANLEY Quencher H2.0 Flow State Tumbler, 40 oz, Rose Quartz 2.0 | Handle and Straw | 3-Position Lid | Cup Holder Compatible for T</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
@@ -990,7 +990,7 @@
       </c>
       <c r="J11" s="5" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/STANLEY-Flowstate-3-Position-Compatible-Insulated/dp/B0CP9YB3Q4/ref=zg_bs_g_kitchen_d_sccl_2/142-8547974-1409324</t>
+          <t>https://www.amazon.com/STANLEY-Quencher-State-Tumbler-Quartz/dp/B0CP9Z56SW/ref=zg_bs_g_kitchen_d_sccl_2/134-1887633-9887334</t>
         </is>
       </c>
     </row>
@@ -1036,7 +1036,7 @@
       </c>
       <c r="J12" s="5" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/Medicube-Zero-Pore-Pads-Dual-Textured/dp/B09V7Z4TJG/ref=zg_bs_g_beauty_d_sccl_2/142-8547974-1409324</t>
+          <t>https://www.amazon.com/Medicube-Zero-Pore-Pads-Dual-Textured/dp/B09V7Z4TJG/ref=zg_bs_g_beauty_d_sccl_2/134-1887633-9887334</t>
         </is>
       </c>
     </row>
@@ -1082,7 +1082,7 @@
       </c>
       <c r="J13" s="5" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/HydroJug-Traveler-Resistant-Bottle-Reusable-Insulated/dp/B0CQVWT2NH/ref=zg_bs_g_kitchen_d_sccl_3/142-8547974-1409324</t>
+          <t>https://www.amazon.com/HydroJug-Traveler-Resistant-Bottle-Reusable-Insulated/dp/B0CQVWT2NH/ref=zg_bs_g_kitchen_d_sccl_3/134-1887633-9887334</t>
         </is>
       </c>
     </row>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>18 offers from $17.87</t>
+          <t>$19.99</t>
         </is>
       </c>
       <c r="G14" s="4" t="inlineStr">
@@ -1128,7 +1128,7 @@
       </c>
       <c r="J14" s="5" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/Apple-EarPods-Headphones-Built-Control/dp/B0DCH8VDXF/ref=zg_bs_g_electronics_d_sccl_2/142-8547974-1409324</t>
+          <t>https://www.amazon.com/Apple-EarPods-Headphones-Built-Control/dp/B0DCH8VDXF/ref=zg_bs_g_electronics_d_sccl_2/134-1887633-9887334</t>
         </is>
       </c>
     </row>
@@ -1154,7 +1154,7 @@
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>10 offers from $22.32</t>
+          <t>$19.99</t>
         </is>
       </c>
       <c r="G15" s="4" t="inlineStr">
@@ -1174,7 +1174,7 @@
       </c>
       <c r="J15" s="5" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/Apple-AirTag-2nd-Generation-Precision/dp/B0GJTFXNRX/ref=zg_bs_g_electronics_d_sccl_3/142-8547974-1409324</t>
+          <t>https://www.amazon.com/Apple-AirTag-2nd-Generation-Precision/dp/B0GJTFXNRX/ref=zg_bs_g_electronics_d_sccl_3/134-1887633-9887334</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>Amazon Fire TV Stick 4K Select (newest model), start streaming in 4K, AI-powered search, and free &amp; live TV, find shows faster wit</t>
+          <t>Apple AirPods Pro 3 Wireless Earbuds with Active Noise Cancellation | Live Translation, Heart Rate Sensing, Hearing Aid Feature, B</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>Tech Gadgets</t>
+          <t>Jewelry Accessories &amp; Derivatives</t>
         </is>
       </c>
       <c r="D16" s="3" t="n">
@@ -1200,7 +1200,7 @@
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t>1 offer from $49.99</t>
+          <t>$19.99</t>
         </is>
       </c>
       <c r="G16" s="4" t="inlineStr">
@@ -1210,17 +1210,17 @@
       </c>
       <c r="H16" s="4" t="inlineStr">
         <is>
-          <t>Đặt câu hỏi trúng nỗi đau thường ngày: 'Tại sao không ai nói cho tôi biết món đồ này sớm hơn?!'</t>
+          <t>So sánh âm thanh: 'Bật lọc tạp âm và nói chuyện giữa chợ ồn ào xem micro này xịn cỡ nào!'</t>
         </is>
       </c>
       <c r="I16" s="4" t="inlineStr">
         <is>
-          <t>Khách hàng mua sắm ngẫu hứng (Impulse Buyers) trên TikTok Shop US độ tuổi 18 - 45.</t>
+          <t>Học sinh, Gen Z làm bullet journal, Content Creator quay video TikTok / Vlog tại US.</t>
         </is>
       </c>
       <c r="J16" s="5" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/amazon-fire-tv-stick-4K-select/dp/B0C6W3D4RM/ref=zg_bs_g_electronics_d_sccl_4/142-8547974-1409324</t>
+          <t>https://www.amazon.com/Apple-Cancellation-Translation-Headphones-High-Fidelity/dp/B0FQFB8FMG/ref=zg_bs_g_electronics_d_sccl_4/134-1887633-9887334</t>
         </is>
       </c>
     </row>
@@ -1230,12 +1230,12 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>Apple AirPods Pro 3 Wireless Earbuds with Active Noise Cancellation | Live Translation, Heart Rate Sensing, Hearing Aid Feature, B</t>
+          <t xml:space="preserve">Roku Streaming Stick HD with Voice Remote | Compact 4K Streaming Device for TV with Roku Voice Remote &amp; Long-Range Wi-Fi - Free &amp; </t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>Jewelry Accessories &amp; Derivatives</t>
+          <t>Tech Gadgets</t>
         </is>
       </c>
       <c r="D17" s="3" t="n">
@@ -1246,7 +1246,7 @@
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>12 offers from $183.44</t>
+          <t>$19.99</t>
         </is>
       </c>
       <c r="G17" s="4" t="inlineStr">
@@ -1256,17 +1256,17 @@
       </c>
       <c r="H17" s="4" t="inlineStr">
         <is>
-          <t>So sánh âm thanh: 'Bật lọc tạp âm và nói chuyện giữa chợ ồn ào xem micro này xịn cỡ nào!'</t>
+          <t>Đặt câu hỏi trúng nỗi đau thường ngày: 'Tại sao không ai nói cho tôi biết món đồ này sớm hơn?!'</t>
         </is>
       </c>
       <c r="I17" s="4" t="inlineStr">
         <is>
-          <t>Học sinh, Gen Z làm bullet journal, Content Creator quay video TikTok / Vlog tại US.</t>
+          <t>Khách hàng mua sắm ngẫu hứng (Impulse Buyers) trên TikTok Shop US độ tuổi 18 - 45.</t>
         </is>
       </c>
       <c r="J17" s="5" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/Apple-Cancellation-Translation-Headphones-High-Fidelity/dp/B0FQFB8FMG/ref=zg_bs_g_electronics_d_sccl_5/142-8547974-1409324</t>
+          <t>https://www.amazon.com/Roku-Streaming-Stick-HD-2025/dp/B0DXXYS4BJ/ref=zg_bs_g_electronics_d_sccl_5/134-1887633-9887334</t>
         </is>
       </c>
     </row>
@@ -1276,19 +1276,19 @@
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>Original Toner Ricoh Aficio MP C3503 C4504 C5504 C6004 SP / 841817 - 8418205,032,950.00 VNDShop all 18Printers &amp; Printer</t>
+          <t>Amazon Fire TV Stick 4K Select (newest model), start streaming in 4K, AI-powered search, and free &amp; live TV, find shows faster wit</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>Beauty &amp; Personal Care</t>
+          <t>Tech Gadgets</t>
         </is>
       </c>
       <c r="D18" s="3" t="n">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>72</v>
+        <v>85</v>
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
@@ -1297,22 +1297,22 @@
       </c>
       <c r="G18" s="4" t="inlineStr">
         <is>
-          <t>eBay US Deals</t>
+          <t>Amazon Best Sellers, Amazon US</t>
         </is>
       </c>
       <c r="H18" s="4" t="inlineStr">
         <is>
-          <t>Before &amp; After cận cảnh lỗ chân lông: 'Dừng ngay nếu bạn vẫn đang nặn mụn hoặc dùng tẩy tế bào chết hạt to!'</t>
+          <t>Đặt câu hỏi trúng nỗi đau thường ngày: 'Tại sao không ai nói cho tôi biết món đồ này sớm hơn?!'</t>
         </is>
       </c>
       <c r="I18" s="4" t="inlineStr">
         <is>
-          <t>Gen Z &amp; Millennials (18-34 tuổi), Chăm sóc da mụn, tín đồ Skincare &amp; 'Clean Girl' aesthetic US.</t>
+          <t>Khách hàng mua sắm ngẫu hứng (Impulse Buyers) trên TikTok Shop US độ tuổi 18 - 45.</t>
         </is>
       </c>
       <c r="J18" s="5" t="inlineStr">
         <is>
-          <t>https://www.ebay.com/itm/223769336762</t>
+          <t>https://www.amazon.com/amazon-fire-tv-stick-4K-select/dp/B0C6W3D4RM/ref=zg_bs_g_electronics_d_sccl_6/134-1887633-9887334</t>
         </is>
       </c>
     </row>
@@ -1322,7 +1322,7 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>15%OFF UGG Slippers Australian Sheepskin Wool Warm House Slip On Scuff Women Men1,084,962.23 VNDADIDAS SCHUHE SPEZIALIST</t>
+          <t>Original Toner Ricoh Aficio MP C3503 C4504 C5504 C6004 SP / 841817 - 8418205,032,950.00 VNDShop all 18Printers &amp; Printer</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
@@ -1358,7 +1358,7 @@
       </c>
       <c r="J19" s="5" t="inlineStr">
         <is>
-          <t>https://www.ebay.com/itm/385963123229</t>
+          <t>https://www.ebay.com/itm/223769336762</t>
         </is>
       </c>
     </row>
@@ -1368,43 +1368,43 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>red alert</t>
+          <t>Womens Mens UGG Mini Short Tall Classic Boots Chestnut Genuine Sheepskin Wool1,636,731.46 VNDADIDAS SCHUHE SPEZIALIST 42</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>Pets &amp; Animals</t>
+          <t>Beauty &amp; Personal Care</t>
         </is>
       </c>
       <c r="D20" s="3" t="n">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>50</v>
+        <v>72</v>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t>$25.00</t>
+          <t>$19.99</t>
         </is>
       </c>
       <c r="G20" s="4" t="inlineStr">
         <is>
-          <t>Google Trends US Search</t>
+          <t>eBay US Deals</t>
         </is>
       </c>
       <c r="H20" s="4" t="inlineStr">
         <is>
-          <t>Âm thanh bấm nút nhả cả búi lông chó rụng chỉ trong 1 giây: 'Mùa rụng lông không còn là ác mộng!'</t>
+          <t>Đặt câu hỏi trúng nỗi đau thường ngày: 'Tại sao không ai nói cho tôi biết món đồ này sớm hơn?!'</t>
         </is>
       </c>
       <c r="I20" s="4" t="inlineStr">
         <is>
-          <t>Hội những người 'nghiện' chó mèo (Dog/Cat Parents) tại US, chi tiêu mạnh tay cho thú cưng.</t>
+          <t>Khách hàng mua sắm ngẫu hứng (Impulse Buyers) trên TikTok Shop US độ tuổi 18 - 45.</t>
         </is>
       </c>
       <c r="J20" s="5" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?geo=US&amp;q=red%20alert</t>
+          <t>https://www.ebay.com/itm/385738675527</t>
         </is>
       </c>
     </row>
@@ -1414,19 +1414,19 @@
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>mlb wildcard standings</t>
+          <t>erin napier</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>Automotive &amp; Motorcycle</t>
+          <t>General Trend</t>
         </is>
       </c>
       <c r="D21" s="3" t="n">
         <v>78</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
@@ -1450,7 +1450,7 @@
       </c>
       <c r="J21" s="5" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?geo=US&amp;q=mlb%20wildcard%20standings</t>
+          <t>https://trends.google.com/trends/explore?geo=US&amp;q=erin%20napier</t>
         </is>
       </c>
     </row>
@@ -1460,7 +1460,7 @@
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>pak vs eng</t>
+          <t>blake lively</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
@@ -1496,7 +1496,7 @@
       </c>
       <c r="J22" s="5" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?geo=US&amp;q=pak%20vs%20eng</t>
+          <t>https://trends.google.com/trends/explore?geo=US&amp;q=blake%20lively</t>
         </is>
       </c>
     </row>
@@ -1506,12 +1506,12 @@
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>michelle obama chanel us open</t>
+          <t>mitch mcconnell</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>Phones &amp; Electronics</t>
+          <t>Fashion &amp; Apparel</t>
         </is>
       </c>
       <c r="D23" s="3" t="n">
@@ -1532,17 +1532,17 @@
       </c>
       <c r="H23" s="4" t="inlineStr">
         <is>
-          <t>So sánh âm thanh: 'Bật lọc tạp âm và nói chuyện giữa chợ ồn ào xem micro này xịn cỡ nào!'</t>
+          <t>Đặt câu hỏi trúng nỗi đau thường ngày: 'Tại sao không ai nói cho tôi biết món đồ này sớm hơn?!'</t>
         </is>
       </c>
       <c r="I23" s="4" t="inlineStr">
         <is>
-          <t>Học sinh, Gen Z làm bullet journal, Content Creator quay video TikTok / Vlog tại US.</t>
+          <t>Khách hàng mua sắm ngẫu hứng (Impulse Buyers) trên TikTok Shop US độ tuổi 18 - 45.</t>
         </is>
       </c>
       <c r="J23" s="5" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?geo=US&amp;q=michelle%20obama%20chanel%20us%20open</t>
+          <t>https://trends.google.com/trends/explore?geo=US&amp;q=mitch%20mcconnell</t>
         </is>
       </c>
     </row>
@@ -1552,12 +1552,12 @@
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>meghan</t>
+          <t>the falling man</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>Health &amp; Fitness</t>
+          <t>Fashion &amp; Apparel</t>
         </is>
       </c>
       <c r="D24" s="3" t="n">
@@ -1588,7 +1588,7 @@
       </c>
       <c r="J24" s="5" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?geo=US&amp;q=meghan</t>
+          <t>https://trends.google.com/trends/explore?geo=US&amp;q=the%20falling%20man</t>
         </is>
       </c>
     </row>
@@ -1598,12 +1598,12 @@
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>ukraine</t>
+          <t>gas prices</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>General Trend</t>
+          <t>Fashion &amp; Apparel</t>
         </is>
       </c>
       <c r="D25" s="3" t="n">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="J25" s="5" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?geo=US&amp;q=ukraine</t>
+          <t>https://trends.google.com/trends/explore?geo=US&amp;q=gas%20prices</t>
         </is>
       </c>
     </row>
@@ -1644,12 +1644,12 @@
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>irish open 2026</t>
+          <t>weather today</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>Books, Magazines &amp; Audio</t>
+          <t>General Trend</t>
         </is>
       </c>
       <c r="D26" s="3" t="n">
@@ -1680,7 +1680,7 @@
       </c>
       <c r="J26" s="5" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?geo=US&amp;q=irish%20open%202026</t>
+          <t>https://trends.google.com/trends/explore?geo=US&amp;q=weather%20today</t>
         </is>
       </c>
     </row>
@@ -1690,7 +1690,7 @@
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>indianapolis weather</t>
+          <t>spacex</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
@@ -1726,7 +1726,7 @@
       </c>
       <c r="J27" s="5" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?geo=US&amp;q=indianapolis%20weather</t>
+          <t>https://trends.google.com/trends/explore?geo=US&amp;q=spacex</t>
         </is>
       </c>
     </row>
@@ -1736,12 +1736,12 @@
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>adam levy</t>
+          <t>costco rationing oil</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>Fashion &amp; Apparel</t>
+          <t>Beauty &amp; Personal Care</t>
         </is>
       </c>
       <c r="D28" s="3" t="n">
@@ -1762,17 +1762,17 @@
       </c>
       <c r="H28" s="4" t="inlineStr">
         <is>
-          <t>Đặt câu hỏi trúng nỗi đau thường ngày: 'Tại sao không ai nói cho tôi biết món đồ này sớm hơn?!'</t>
+          <t>Before &amp; After cận cảnh lỗ chân lông: 'Dừng ngay nếu bạn vẫn đang nặn mụn hoặc dùng tẩy tế bào chết hạt to!'</t>
         </is>
       </c>
       <c r="I28" s="4" t="inlineStr">
         <is>
-          <t>Khách hàng mua sắm ngẫu hứng (Impulse Buyers) trên TikTok Shop US độ tuổi 18 - 45.</t>
+          <t>Gen Z &amp; Millennials (18-34 tuổi), Chăm sóc da mụn, tín đồ Skincare &amp; 'Clean Girl' aesthetic US.</t>
         </is>
       </c>
       <c r="J28" s="5" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?geo=US&amp;q=adam%20levy</t>
+          <t>https://trends.google.com/trends/explore?geo=US&amp;q=costco%20rationing%20oil</t>
         </is>
       </c>
     </row>
@@ -1782,12 +1782,12 @@
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>jason bard yarmosky</t>
+          <t>sharon horgan</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>Fashion &amp; Apparel</t>
+          <t>General Trend</t>
         </is>
       </c>
       <c r="D29" s="3" t="n">
@@ -1818,7 +1818,7 @@
       </c>
       <c r="J29" s="5" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?geo=US&amp;q=jason%20bard%20yarmosky</t>
+          <t>https://trends.google.com/trends/explore?geo=US&amp;q=sharon%20horgan</t>
         </is>
       </c>
     </row>
@@ -1828,43 +1828,43 @@
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>Spotlight DealCASIO WATCH CALCULATOR VINTAGE RETRO 80's CA-53W-1Z CA53 CA-53 AUSSIE SELLER838,137.46 VND1,470,465.00 VND</t>
+          <t>the walking dead: dead city</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>All Trending Deals</t>
+          <t>Gadgets &amp; Electronics</t>
         </is>
       </c>
       <c r="D30" s="3" t="n">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>72</v>
+        <v>45</v>
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
-          <t>$19.99</t>
+          <t>$25.00</t>
         </is>
       </c>
       <c r="G30" s="4" t="inlineStr">
         <is>
-          <t>eBay US Deals</t>
+          <t>Google Trends US Search</t>
         </is>
       </c>
       <c r="H30" s="4" t="inlineStr">
         <is>
-          <t>So sánh âm thanh: 'Bật lọc tạp âm và nói chuyện giữa chợ ồn ào xem micro này xịn cỡ nào!'</t>
+          <t>Đặt câu hỏi trúng nỗi đau thường ngày: 'Tại sao không ai nói cho tôi biết món đồ này sớm hơn?!'</t>
         </is>
       </c>
       <c r="I30" s="4" t="inlineStr">
         <is>
-          <t>Học sinh, Gen Z làm bullet journal, Content Creator quay video TikTok / Vlog tại US.</t>
+          <t>Khách hàng mua sắm ngẫu hứng (Impulse Buyers) trên TikTok Shop US độ tuổi 18 - 45.</t>
         </is>
       </c>
       <c r="J30" s="5" t="inlineStr">
         <is>
-          <t>https://www.ebay.com/itm/370786315096</t>
+          <t>https://trends.google.com/trends/explore?geo=US&amp;q=the%20walking%20dead%3A%20dead%20city</t>
         </is>
       </c>
     </row>
@@ -1874,7 +1874,7 @@
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>CASIO WATCH VINTAGE RETRO ORIGINAL F-91W-1 F91 F91W F-91 WARANTY666,169.38 VND734,772.69 VND | 9% offPrevious price: 734</t>
+          <t>Spotlight DealGE ECG Leadwire Set 3 Lead Grabber AHA 51in REF 2106390-0021,538,461.54 VND</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
@@ -1900,17 +1900,17 @@
       </c>
       <c r="H31" s="4" t="inlineStr">
         <is>
-          <t>So sánh âm thanh: 'Bật lọc tạp âm và nói chuyện giữa chợ ồn ào xem micro này xịn cỡ nào!'</t>
+          <t>Đặt câu hỏi trúng nỗi đau thường ngày: 'Tại sao không ai nói cho tôi biết món đồ này sớm hơn?!'</t>
         </is>
       </c>
       <c r="I31" s="4" t="inlineStr">
         <is>
-          <t>Học sinh, Gen Z làm bullet journal, Content Creator quay video TikTok / Vlog tại US.</t>
+          <t>Khách hàng mua sắm ngẫu hứng (Impulse Buyers) trên TikTok Shop US độ tuổi 18 - 45.</t>
         </is>
       </c>
       <c r="J31" s="5" t="inlineStr">
         <is>
-          <t>https://www.ebay.com/itm/370816923572</t>
+          <t>https://www.ebay.com/itm/178382893222</t>
         </is>
       </c>
     </row>
@@ -1920,7 +1920,7 @@
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>Cisco SFP-H10GB-CU3M 37-0961-03 SFP+ 10G Passive DAC Twinax Cable NEW897,435.90 VND</t>
+          <t>CASIO WATCH CALCULATOR VINTAGE RETRO 80's CA-53W-1Z CA53 CA-53 AUSSIE SELLER838,137.46 VND1,470,465.00 VND Previous pric</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
@@ -1946,17 +1946,17 @@
       </c>
       <c r="H32" s="4" t="inlineStr">
         <is>
-          <t>Đặt câu hỏi trúng nỗi đau thường ngày: 'Tại sao không ai nói cho tôi biết món đồ này sớm hơn?!'</t>
+          <t>So sánh âm thanh: 'Bật lọc tạp âm và nói chuyện giữa chợ ồn ào xem micro này xịn cỡ nào!'</t>
         </is>
       </c>
       <c r="I32" s="4" t="inlineStr">
         <is>
-          <t>Khách hàng mua sắm ngẫu hứng (Impulse Buyers) trên TikTok Shop US độ tuổi 18 - 45.</t>
+          <t>Học sinh, Gen Z làm bullet journal, Content Creator quay video TikTok / Vlog tại US.</t>
         </is>
       </c>
       <c r="J32" s="5" t="inlineStr">
         <is>
-          <t>https://www.ebay.com/itm/157632501279</t>
+          <t>https://www.ebay.com/itm/370786315096</t>
         </is>
       </c>
     </row>
@@ -2012,8 +2012,8 @@
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>Apple iPhone 16 Pro Max All Colours26,609,000.00 VND
-eBay Refurbished</t>
+          <t>Apple iPhone 16 Pro - 1TB - All Colours21,127,615.38 VND34,657,692.31 VND Previous price: 34,657,692.31 VND 39% off
+eBay</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
@@ -2039,17 +2039,17 @@
       </c>
       <c r="H34" s="4" t="inlineStr">
         <is>
-          <t>Âm thanh bấm nút nhả cả búi lông chó rụng chỉ trong 1 giây: 'Mùa rụng lông không còn là ác mộng!'</t>
+          <t>Đặt câu hỏi trúng nỗi đau thường ngày: 'Tại sao không ai nói cho tôi biết món đồ này sớm hơn?!'</t>
         </is>
       </c>
       <c r="I34" s="4" t="inlineStr">
         <is>
-          <t>Hội những người 'nghiện' chó mèo (Dog/Cat Parents) tại US, chi tiêu mạnh tay cho thú cưng.</t>
+          <t>Khách hàng mua sắm ngẫu hứng (Impulse Buyers) trên TikTok Shop US độ tuổi 18 - 45.</t>
         </is>
       </c>
       <c r="J34" s="5" t="inlineStr">
         <is>
-          <t>https://www.ebay.com/itm/257723314310</t>
+          <t>https://www.ebay.com/itm/297648174804</t>
         </is>
       </c>
     </row>
@@ -2059,7 +2059,7 @@
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>Apple iPhone 16 Pro - 1TB - All Colours21,821,461.54 VNDeBay Refurbished</t>
+          <t>Apple iPhone 16 Pro - 128GB 256GB 512GB 1TB - All Colours - Unlocked - Good20,780,692.31 VNDeBay Refurbished</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
@@ -2095,7 +2095,7 @@
       </c>
       <c r="J35" s="5" t="inlineStr">
         <is>
-          <t>https://www.ebay.com/itm/257132401723</t>
+          <t>https://www.ebay.com/itm/257132422991</t>
         </is>
       </c>
     </row>
@@ -2105,7 +2105,7 @@
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>Apple iPhone 16 Pro Max - 256GB 512GB 1TB- All Colours - Good25,013,153.85 VNDeBay Refurbished</t>
+          <t>Prada Bonnie large leather handbag Brown44,641,373.08 VNDAlmost gone</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
@@ -2131,17 +2131,17 @@
       </c>
       <c r="H36" s="4" t="inlineStr">
         <is>
-          <t>Âm thanh bấm nút nhả cả búi lông chó rụng chỉ trong 1 giây: 'Mùa rụng lông không còn là ác mộng!'</t>
+          <t>Đặt câu hỏi trúng nỗi đau thường ngày: 'Tại sao không ai nói cho tôi biết món đồ này sớm hơn?!'</t>
         </is>
       </c>
       <c r="I36" s="4" t="inlineStr">
         <is>
-          <t>Hội những người 'nghiện' chó mèo (Dog/Cat Parents) tại US, chi tiêu mạnh tay cho thú cưng.</t>
+          <t>Khách hàng mua sắm ngẫu hứng (Impulse Buyers) trên TikTok Shop US độ tuổi 18 - 45.</t>
         </is>
       </c>
       <c r="J36" s="5" t="inlineStr">
         <is>
-          <t>https://www.ebay.com/itm/298645175829</t>
+          <t>https://www.ebay.com/itm/206266648571</t>
         </is>
       </c>
     </row>
@@ -2151,7 +2151,7 @@
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>Lederweste Bikerweste Motorrad Kutte Biker Chopper Rockerweste mit Taschen2,679,971.42 VNDPremium Velour Fußmatten kompl</t>
+          <t>Giubbotto Blauer nero donna con brillantini2,370,549.23 VND</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
@@ -2187,7 +2187,7 @@
       </c>
       <c r="J37" s="5" t="inlineStr">
         <is>
-          <t>https://www.ebay.com/itm/291771387455</t>
+          <t>https://www.ebay.com/itm/306843251511</t>
         </is>
       </c>
     </row>
@@ -2197,7 +2197,7 @@
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>Birne 6000K H13 E-PRÜFZEICHEN 12V 60/55W E-Prüfzeichen XENON SUPER WHITE HALOGEN625,693.96 VND</t>
+          <t>Birne 6000K H13 E-PRÜFZEICHEN 12V 60/55W E-Prüfzeichen XENON SUPER WHITE HALOGEN625,693.96 VNDLederweste Bikerweste Moto</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
@@ -2243,12 +2243,12 @@
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>500 Abarth Orig Competizione 595 695 Braking Kit Bremsscheiben Kit Va 305x28mm11,286,911.54 VNDShop all 90Parts &amp; Access</t>
+          <t>Premium Velour Fußmatten komplett für VW T6.1 California Coast Küche ab Bj.20208,037,829.62 VND</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>Pet Supplies</t>
+          <t>All Trending Deals</t>
         </is>
       </c>
       <c r="D39" s="3" t="n">
@@ -2269,17 +2269,17 @@
       </c>
       <c r="H39" s="4" t="inlineStr">
         <is>
-          <t>Âm thanh bấm nút nhả cả búi lông chó rụng chỉ trong 1 giây: 'Mùa rụng lông không còn là ác mộng!'</t>
+          <t>Đặt câu hỏi trúng nỗi đau thường ngày: 'Tại sao không ai nói cho tôi biết món đồ này sớm hơn?!'</t>
         </is>
       </c>
       <c r="I39" s="4" t="inlineStr">
         <is>
-          <t>Hội những người 'nghiện' chó mèo (Dog/Cat Parents) tại US, chi tiêu mạnh tay cho thú cưng.</t>
+          <t>Khách hàng mua sắm ngẫu hứng (Impulse Buyers) trên TikTok Shop US độ tuổi 18 - 45.</t>
         </is>
       </c>
       <c r="J39" s="5" t="inlineStr">
         <is>
-          <t>https://www.ebay.com/itm/285765031424</t>
+          <t>https://www.ebay.com/itm/124122083146</t>
         </is>
       </c>
     </row>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>CASIO WATCH SWIMMING 100 METRES WATER RESISTANT W-800 W-800H-1AV W8001,025,371.15 VND1,102,618.85 VND | 7% offPrevious p</t>
+          <t>Biker Kutte Lederkutte Lederweste Clubweste Rockerweste Herren Chopper Motorrad2,679,971.42 VNDShop all 91Parts &amp; Access</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
@@ -2315,17 +2315,17 @@
       </c>
       <c r="H40" s="4" t="inlineStr">
         <is>
-          <t>So sánh âm thanh: 'Bật lọc tạp âm và nói chuyện giữa chợ ồn ào xem micro này xịn cỡ nào!'</t>
+          <t>Đặt câu hỏi trúng nỗi đau thường ngày: 'Tại sao không ai nói cho tôi biết món đồ này sớm hơn?!'</t>
         </is>
       </c>
       <c r="I40" s="4" t="inlineStr">
         <is>
-          <t>Học sinh, Gen Z làm bullet journal, Content Creator quay video TikTok / Vlog tại US.</t>
+          <t>Khách hàng mua sắm ngẫu hứng (Impulse Buyers) trên TikTok Shop US độ tuổi 18 - 45.</t>
         </is>
       </c>
       <c r="J40" s="5" t="inlineStr">
         <is>
-          <t>https://www.ebay.com/itm/371175182923</t>
+          <t>https://www.ebay.com/itm/302258284099</t>
         </is>
       </c>
     </row>
@@ -2335,12 +2335,12 @@
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>YHG Wetsuit 3mm Neoprene Diving Tops Pants Men Women Swim Surfing Snorkeling AU735,508.38 VND</t>
+          <t>CASIO CALCULATOR WATCH CA53, CA-53, CA-53WB,CA53WF VINTAGE RETRO UNISEX DATABANK785,903.31 VND845,126.54 VND | 7% offPre</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>Kitchenware</t>
+          <t>All Trending Deals</t>
         </is>
       </c>
       <c r="D41" s="3" t="n">
@@ -2361,17 +2361,17 @@
       </c>
       <c r="H41" s="4" t="inlineStr">
         <is>
-          <t>Đặt câu hỏi trúng nỗi đau thường ngày: 'Tại sao không ai nói cho tôi biết món đồ này sớm hơn?!'</t>
+          <t>So sánh âm thanh: 'Bật lọc tạp âm và nói chuyện giữa chợ ồn ào xem micro này xịn cỡ nào!'</t>
         </is>
       </c>
       <c r="I41" s="4" t="inlineStr">
         <is>
-          <t>Khách hàng mua sắm ngẫu hứng (Impulse Buyers) trên TikTok Shop US độ tuổi 18 - 45.</t>
+          <t>Học sinh, Gen Z làm bullet journal, Content Creator quay video TikTok / Vlog tại US.</t>
         </is>
       </c>
       <c r="J41" s="5" t="inlineStr">
         <is>
-          <t>https://www.ebay.com/itm/157344373567</t>
+          <t>https://www.ebay.com/itm/284719252501</t>
         </is>
       </c>
     </row>
@@ -2381,12 +2381,12 @@
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">True Temper Dynamic Gold TOUR ISSUE Limited Edition USA Golf Iron Shaft .355 Tip923,076.92 VND1,153,846.15 VND Previous </t>
+          <t>Graphite Crucible for Induction Melting Furnace735,508.38 VND</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>Phones &amp; Electronics</t>
+          <t>All Trending Deals</t>
         </is>
       </c>
       <c r="D42" s="3" t="n">
@@ -2407,17 +2407,17 @@
       </c>
       <c r="H42" s="4" t="inlineStr">
         <is>
-          <t>So sánh âm thanh: 'Bật lọc tạp âm và nói chuyện giữa chợ ồn ào xem micro này xịn cỡ nào!'</t>
+          <t>Âm thanh bấm nút nhả cả búi lông chó rụng chỉ trong 1 giây: 'Mùa rụng lông không còn là ác mộng!'</t>
         </is>
       </c>
       <c r="I42" s="4" t="inlineStr">
         <is>
-          <t>Học sinh, Gen Z làm bullet journal, Content Creator quay video TikTok / Vlog tại US.</t>
+          <t>Hội những người 'nghiện' chó mèo (Dog/Cat Parents) tại US, chi tiêu mạnh tay cho thú cưng.</t>
         </is>
       </c>
       <c r="J42" s="5" t="inlineStr">
         <is>
-          <t>https://www.ebay.com/itm/186144334386</t>
+          <t>https://www.ebay.com/itm/187799864164</t>
         </is>
       </c>
     </row>
@@ -2427,12 +2427,12 @@
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>Veto Pro Pac MP3 EVO Tool Pouch EVO System Electrician Networking Technician3,203,846.15 VND24x Kerzen 80x40mm/8x4cm 1.W</t>
+          <t>28" 30" 31" Carbon Arrows 4" Feather SP500 Archery Recurve Compound Bow Hunting691,366.85 VND735,508.38 VND | 6% offPrev</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>All Trending Deals</t>
+          <t>Automotive &amp; Motorcycle</t>
         </is>
       </c>
       <c r="D43" s="3" t="n">
@@ -2463,7 +2463,7 @@
       </c>
       <c r="J43" s="5" t="inlineStr">
         <is>
-          <t>https://www.ebay.com/itm/366448929530</t>
+          <t>https://www.ebay.com/itm/267490959027</t>
         </is>
       </c>
     </row>
@@ -2473,7 +2473,7 @@
       </c>
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t>Bankerlampe Tischleuchte Bürolampe Jugendstil Schreibtischlampe weiss silber neu2,024,794.50 VND</t>
+          <t>Veto Pro Pac MP3 EVO Tool Pouch EVO System Electrician Networking Technician3,203,846.15 VNDBankerlampe Tischleuchte Bür</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
@@ -2509,7 +2509,7 @@
       </c>
       <c r="J44" s="5" t="inlineStr">
         <is>
-          <t>https://www.ebay.com/itm/194675348414</t>
+          <t>https://www.ebay.com/itm/366448929530</t>
         </is>
       </c>
     </row>
@@ -2519,7 +2519,7 @@
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>3 Paar Zedernholzsohlen - Zedernsohlen - Einlegesohlen aus Holz890,445.00 VNDAlmost goneShop all 88Home &amp; Garden</t>
+          <t>24x Kerzen 80x40mm/8x4cm 1.Wahl Qualität / Kerzen Wiedemann / neue Farben 2025935,711.77 VND</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
@@ -2555,7 +2555,7 @@
       </c>
       <c r="J45" s="5" t="inlineStr">
         <is>
-          <t>https://www.ebay.com/itm/276726430861</t>
+          <t>https://www.ebay.com/itm/351764643068</t>
         </is>
       </c>
     </row>
@@ -2565,12 +2565,12 @@
       </c>
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Opis PushMeFon mobile - Retro 2G Tischhandy Mobil-Telefon mit Metallklingel3,841,719.23 VNDNokia 6700 Classic 5MP Handy </t>
+          <t>Tischglocke Christkindl Klang Messing Weihnachtsglocke Handglocke Dekoration601,273.73 VNDShop all 88Home &amp; Garden</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>Tech &amp; Gadgets</t>
+          <t>All Trending Deals</t>
         </is>
       </c>
       <c r="D46" s="3" t="n">
@@ -2601,7 +2601,7 @@
       </c>
       <c r="J46" s="5" t="inlineStr">
         <is>
-          <t>https://www.ebay.com/itm/324428697438</t>
+          <t>https://www.ebay.com/itm/284215623617</t>
         </is>
       </c>
     </row>
@@ -2611,7 +2611,7 @@
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>Nokia C2-01  (Ohne Simlock)  Frei für alle Sim-Karten Neu schwarz2,379,483.46 VND</t>
+          <t xml:space="preserve">Opis PushMeFon mobile - Retro 2G Tischhandy Mobil-Telefon mit Metallklingel3,841,719.23 VNDNokia 6700 Classic 5MP Handy </t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
@@ -2647,7 +2647,7 @@
       </c>
       <c r="J47" s="5" t="inlineStr">
         <is>
-          <t>https://www.ebay.com/itm/202995946783</t>
+          <t>https://www.ebay.com/itm/324428697438</t>
         </is>
       </c>
     </row>
@@ -2657,7 +2657,7 @@
       </c>
       <c r="B48" s="4" t="inlineStr">
         <is>
-          <t>Opis 60s mobile - Das  Retro 2G Tischhandy mit Wählscheibe &amp; Metallklingel3,841,719.23 VNDShop all 8Cell Phones</t>
+          <t>Nokia C2-01  (Ohne Simlock)  Frei für alle Sim-Karten Neu schwarz2,379,483.46 VND</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
@@ -2693,7 +2693,7 @@
       </c>
       <c r="J48" s="5" t="inlineStr">
         <is>
-          <t>https://www.ebay.com/itm/324427595994</t>
+          <t>https://www.ebay.com/itm/202995946783</t>
         </is>
       </c>
     </row>
@@ -2703,7 +2703,7 @@
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>NEUWARE ORIGINAL METZ Fernbedienung RM18 RM 18 SCHNELLER VERSAND2,054,873.08 VNDAlmost goneORIGINAL SONY Fernbedienung R</t>
+          <t>Opis 60s mobile - Das  Retro 2G Tischhandy mit Wählscheibe &amp; Metallklingel3,841,719.23 VNDShop all 8Cell Phones</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
@@ -2739,7 +2739,7 @@
       </c>
       <c r="J49" s="5" t="inlineStr">
         <is>
-          <t>https://www.ebay.com/itm/392040705358</t>
+          <t>https://www.ebay.com/itm/324427595994</t>
         </is>
       </c>
     </row>
@@ -2749,7 +2749,7 @@
       </c>
       <c r="B50" s="4" t="inlineStr">
         <is>
-          <t>ORIGINAL METZ Fernbedienung für Metz Blue MOC9001 MUC8001 MUC7001 MUC7111 NEU1,009,568.08 VND</t>
+          <t>NEUWARE ORIGINAL METZ Fernbedienung RM18 RM 18 SCHNELLER VERSAND2,054,873.08 VNDAlmost goneORIGINAL SONY Fernbedienung R</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
@@ -2785,7 +2785,7 @@
       </c>
       <c r="J50" s="5" t="inlineStr">
         <is>
-          <t>https://www.ebay.com/itm/393858887603</t>
+          <t>https://www.ebay.com/itm/392040705358</t>
         </is>
       </c>
     </row>
@@ -2795,7 +2795,7 @@
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>NEU ORIGINAL SAMSUNG Fernbedienung für UE40ES6100WXZG UE40ES6100 UE40ES6100W652,198.85 VNDShop all 7TV, Video &amp; Home Aud</t>
+          <t>ORIGINAL METZ Fernbedienung für Metz Blue MOC9001 MUC8001 MUC7001 MUC7111 NEU1,009,568.08 VND</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="J51" s="5" t="inlineStr">
         <is>
-          <t>https://www.ebay.com/itm/392224499242</t>
+          <t>https://www.ebay.com/itm/393858887603</t>
         </is>
       </c>
     </row>
@@ -2841,7 +2841,7 @@
       </c>
       <c r="B52" s="4" t="inlineStr">
         <is>
-          <t>Sony Playstation 5 Controller-TMR Sticks-Top Zustand-alle Farben2,380,972.50 VNDWii - Nintendo Wii Konsole Weiß mit Remo</t>
+          <t>NEU ORIGINAL SAMSUNG Fernbedienung für UE40ES6100WXZG UE40ES6100 UE40ES6100W652,198.85 VNDShop all 7TV, Video &amp; Home Aud</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
@@ -2877,7 +2877,7 @@
       </c>
       <c r="J52" s="5" t="inlineStr">
         <is>
-          <t>https://www.ebay.com/itm/365967503388</t>
+          <t>https://www.ebay.com/itm/392224499242</t>
         </is>
       </c>
     </row>
@@ -2887,7 +2887,7 @@
       </c>
       <c r="B53" s="4" t="inlineStr">
         <is>
-          <t>SW - Nintendo Switch-Konsole Neon-Rot/Neon-Blau (guter Zustand)5,656,857.12 VNDeBay Refurbished</t>
+          <t>Sony Playstation 5 Controller-TMR Sticks-Top Zustand-alle Farben2,380,972.50 VNDWii - Nintendo Wii Konsole Weiß mit Remo</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
@@ -2913,17 +2913,17 @@
       </c>
       <c r="H53" s="4" t="inlineStr">
         <is>
-          <t>Âm thanh bấm nút nhả cả búi lông chó rụng chỉ trong 1 giây: 'Mùa rụng lông không còn là ác mộng!'</t>
+          <t>Đặt câu hỏi trúng nỗi đau thường ngày: 'Tại sao không ai nói cho tôi biết món đồ này sớm hơn?!'</t>
         </is>
       </c>
       <c r="I53" s="4" t="inlineStr">
         <is>
-          <t>Hội những người 'nghiện' chó mèo (Dog/Cat Parents) tại US, chi tiêu mạnh tay cho thú cưng.</t>
+          <t>Khách hàng mua sắm ngẫu hứng (Impulse Buyers) trên TikTok Shop US độ tuổi 18 - 45.</t>
         </is>
       </c>
       <c r="J53" s="5" t="inlineStr">
         <is>
-          <t>https://www.ebay.com/itm/187974010368</t>
+          <t>https://www.ebay.com/itm/365967503388</t>
         </is>
       </c>
     </row>
@@ -2933,7 +2933,7 @@
       </c>
       <c r="B54" s="4" t="inlineStr">
         <is>
-          <t>PlayStation 3 MINECRAFT Deutsch625,098.35 VNDShop all 27Video Games &amp; Consoles</t>
+          <t>SW - Nintendo Switch-Konsole Neon-Rot/Neon-Blau (guter Zustand)5,656,857.12 VNDeBay Refurbished</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
@@ -2959,17 +2959,17 @@
       </c>
       <c r="H54" s="4" t="inlineStr">
         <is>
-          <t>Đặt câu hỏi trúng nỗi đau thường ngày: 'Tại sao không ai nói cho tôi biết món đồ này sớm hơn?!'</t>
+          <t>Âm thanh bấm nút nhả cả búi lông chó rụng chỉ trong 1 giây: 'Mùa rụng lông không còn là ác mộng!'</t>
         </is>
       </c>
       <c r="I54" s="4" t="inlineStr">
         <is>
-          <t>Khách hàng mua sắm ngẫu hứng (Impulse Buyers) trên TikTok Shop US độ tuổi 18 - 45.</t>
+          <t>Hội những người 'nghiện' chó mèo (Dog/Cat Parents) tại US, chi tiêu mạnh tay cho thú cưng.</t>
         </is>
       </c>
       <c r="J54" s="5" t="inlineStr">
         <is>
-          <t>https://www.ebay.com/itm/351153701373</t>
+          <t>https://www.ebay.com/itm/187974010368</t>
         </is>
       </c>
     </row>
@@ -2979,7 +2979,7 @@
       </c>
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t>Personalisierte Schutzhülle für iPhone Handytasche Hülle eigenes Foto Bild Druck744,221.42 VNDHandy Tasche für Samsung G</t>
+          <t>PlayStation 3 MINECRAFT Deutsch625,098.35 VNDShop all 27Video Games &amp; Consoles</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
@@ -3015,7 +3015,7 @@
       </c>
       <c r="J55" s="5" t="inlineStr">
         <is>
-          <t>https://www.ebay.com/itm/272724943549</t>
+          <t>https://www.ebay.com/itm/351153701373</t>
         </is>
       </c>
     </row>
@@ -3025,12 +3025,12 @@
       </c>
       <c r="B56" s="4" t="inlineStr">
         <is>
-          <t>Handy Tasche für Samsung Galaxy A55 5G Schutzhülle Book Case Dünn Handy Hülle774,002.19 VNDFree shipping</t>
+          <t>Personalisierte Schutzhülle für iPhone Handytasche Hülle eigenes Foto Bild Druck744,221.42 VNDHandy Tasche für Samsung G</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>Books, Magazines &amp; Audio</t>
+          <t>Tech &amp; Gadgets</t>
         </is>
       </c>
       <c r="D56" s="3" t="n">
@@ -3061,7 +3061,7 @@
       </c>
       <c r="J56" s="5" t="inlineStr">
         <is>
-          <t>https://www.ebay.com/itm/285825152658</t>
+          <t>https://www.ebay.com/itm/272724943549</t>
         </is>
       </c>
     </row>
@@ -3071,12 +3071,12 @@
       </c>
       <c r="B57" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Handy Hülle mit Band für Samsung Galaxy A55 5G Handy Kette Case zum Umhängen714,440.65 VNDFree shippingShop all 33Phone </t>
+          <t>Handy Tasche für Samsung Galaxy A55 5G Schutzhülle Book Case Dünn Handy Hülle774,002.19 VNDFree shipping</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>Tech &amp; Gadgets</t>
+          <t>Books, Magazines &amp; Audio</t>
         </is>
       </c>
       <c r="D57" s="3" t="n">
@@ -3107,7 +3107,7 @@
       </c>
       <c r="J57" s="5" t="inlineStr">
         <is>
-          <t>https://www.ebay.com/itm/204763504739</t>
+          <t>https://www.ebay.com/itm/285825152658</t>
         </is>
       </c>
     </row>
@@ -3117,7 +3117,7 @@
       </c>
       <c r="B58" s="4" t="inlineStr">
         <is>
-          <t>Original Tinte EPSON Stylus Pro 9800 7800 / T6031 T6032 T6034 -T6039 T603B T603C2,650,488.46 VNDOriginal EPSON Tinte Sty</t>
+          <t xml:space="preserve">Handy Hülle mit Band für Samsung Galaxy A55 5G Handy Kette Case zum Umhängen714,440.65 VNDFree shippingShop all 33Phone </t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
@@ -3153,7 +3153,7 @@
       </c>
       <c r="J58" s="5" t="inlineStr">
         <is>
-          <t>https://www.ebay.com/itm/222635235522</t>
+          <t>https://www.ebay.com/itm/204763504739</t>
         </is>
       </c>
     </row>
@@ -3163,7 +3163,7 @@
       </c>
       <c r="B59" s="4" t="inlineStr">
         <is>
-          <t>Tinte für Canon iPF6400 iPF6400S iPF6450 / PFI-206MBK 206BK 206GY 206C 206M 206Y2,677,291.15 VND</t>
+          <t>Original Tinte EPSON Stylus Pro 9800 7800 / T6031 T6032 T6034 -T6039 T603B T603C2,650,488.46 VNDOriginal EPSON Tinte Sty</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
@@ -3199,7 +3199,7 @@
       </c>
       <c r="J59" s="5" t="inlineStr">
         <is>
-          <t>https://www.ebay.com/itm/352159188925</t>
+          <t>https://www.ebay.com/itm/222635235522</t>
         </is>
       </c>
     </row>
@@ -3209,7 +3209,7 @@
       </c>
       <c r="B60" s="4" t="inlineStr">
         <is>
-          <t>JK-B2A8S20P Smart BMS 4-8S 200A Active Balance 2A BMS LiFePo4 Li-ion LTO Battery1,766,923.08 VND1,920,512.82 VND | 8% of</t>
+          <t>Tinte für Canon iPF6400 iPF6400S iPF6450 / PFI-206MBK 206BK 206GY 206C 206M 206Y2,677,291.15 VND</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
@@ -3245,7 +3245,7 @@
       </c>
       <c r="J60" s="5" t="inlineStr">
         <is>
-          <t>https://www.ebay.com/itm/236864278279</t>
+          <t>https://www.ebay.com/itm/352159188925</t>
         </is>
       </c>
     </row>
@@ -3255,7 +3255,7 @@
       </c>
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t>ORIGINAL SONY Fernbedienung RMT-TX102D KDL40R45XC KDL40R55XC KDL40R550C NEUWARE652,198.85 VND</t>
+          <t>Für Xiaomi Redmi Pad Pro 12.1 Kontrast Robot Silikon Hybrid Hülle Blau / Schwarz713,249.42 VNDAlmost goneLeder Tablet Co</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
@@ -3291,7 +3291,7 @@
       </c>
       <c r="J61" s="5" t="inlineStr">
         <is>
-          <t>https://www.ebay.com/itm/373982552937</t>
+          <t>https://www.ebay.com/itm/176622603332</t>
         </is>
       </c>
     </row>
@@ -3301,7 +3301,7 @@
       </c>
       <c r="B62" s="4" t="inlineStr">
         <is>
-          <t>Für Xiaomi Redmi Pad Pro 12.1 Kontrast Robot Silikon Hybrid Hülle Blau / Schwarz713,249.42 VNDAlmost goneLeder Tablet Co</t>
+          <t>Leder Tablet Cover Samsung Galaxy Tab S7 FE SM-T733/T736 Stand Case Schutzhülle676,619.08 VND</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
@@ -3337,7 +3337,7 @@
       </c>
       <c r="J62" s="5" t="inlineStr">
         <is>
-          <t>https://www.ebay.com/itm/176622603332</t>
+          <t>https://www.ebay.com/itm/304338719356</t>
         </is>
       </c>
     </row>
@@ -3347,7 +3347,7 @@
       </c>
       <c r="B63" s="4" t="inlineStr">
         <is>
-          <t>Leder Tablet Cover Samsung Galaxy Tab S7 FE SM-T733/T736 Stand Case Schutzhülle676,619.08 VND</t>
+          <t>Premium Leder Cover Apple iPad Pro 12.9"  2015-17 Tablet Schutzhülle Case Tasche729,033.23 VND828,501.00 VND | 12% offPr</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
@@ -3383,7 +3383,7 @@
       </c>
       <c r="J63" s="5" t="inlineStr">
         <is>
-          <t>https://www.ebay.com/itm/304338719356</t>
+          <t>https://www.ebay.com/itm/234304242705</t>
         </is>
       </c>
     </row>
@@ -3393,7 +3393,7 @@
       </c>
       <c r="B64" s="4" t="inlineStr">
         <is>
-          <t>Premium Leder Cover Apple iPad Pro 12.9"  2015-17 Tablet Schutzhülle Case Tasche729,033.23 VND828,501.00 VND | 12% offPr</t>
+          <t>Cisco SFP-H10GB-CU3M 37-0961-03 SFP+ 10G Passive DAC Twinax Cable NEW897,435.90 VNDMcAfee Total Protection - 5 Devices -</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
@@ -3429,7 +3429,7 @@
       </c>
       <c r="J64" s="5" t="inlineStr">
         <is>
-          <t>https://www.ebay.com/itm/234304242705</t>
+          <t>https://www.ebay.com/itm/157632501279</t>
         </is>
       </c>
     </row>
@@ -3439,7 +3439,7 @@
       </c>
       <c r="B65" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Display für Samsung A53 5G A536 OLED AMOLED LCD Bildschirm Touch Screen + Kleber1,188,252.69 VNDDisplay für Samsung A53 </t>
+          <t>Display für Samsung A53 5G A536 OLED AMOLED LCD Bildschirm Touch Screen + Kleber1,188,252.69 VND</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
@@ -3485,12 +3485,12 @@
       </c>
       <c r="B66" s="4" t="inlineStr">
         <is>
-          <t>Display für Samsung A51 A515F HD LCD Touch Screen Glas + Kleber &amp; Tools Neu741,541.15 VND</t>
+          <t xml:space="preserve">Display für Samsung A53 5G A536B 2022 HD LCD Bildschirm Touch Screen + Rahmen1,069,129.62 VNDAlmost goneShop all 50More </t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>Tech &amp; Gadgets</t>
+          <t>Menswear &amp; Underwear</t>
         </is>
       </c>
       <c r="D66" s="3" t="n">
@@ -3521,7 +3521,7 @@
       </c>
       <c r="J66" s="5" t="inlineStr">
         <is>
-          <t>https://www.ebay.com/itm/305047092563</t>
+          <t>https://www.ebay.com/itm/295846639825</t>
         </is>
       </c>
     </row>
@@ -3531,12 +3531,12 @@
       </c>
       <c r="B67" s="4" t="inlineStr">
         <is>
-          <t>Display Für Samsung A55 / A556 5G OLED Bildschirm LCD mit  Rahmen + Tools Neu1,932,771.92 VNDShop all 48More Computer Ac</t>
+          <t>2 1/2ct Black Diamond Screw Back Studs Womens Earrings 14K White Gold8,546,666.67 VND26,805,641.03 VND Previous price: 2</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>Menswear &amp; Underwear</t>
+          <t>Jewelry Accessories &amp; Derivatives</t>
         </is>
       </c>
       <c r="D67" s="3" t="n">
@@ -3567,7 +3567,7 @@
       </c>
       <c r="J67" s="5" t="inlineStr">
         <is>
-          <t>https://www.ebay.com/itm/306193635449</t>
+          <t>https://www.ebay.com/itm/355504570491</t>
         </is>
       </c>
     </row>
@@ -3577,12 +3577,12 @@
       </c>
       <c r="B68" s="4" t="inlineStr">
         <is>
-          <t>2 1/2ct Black Diamond Screw Back Studs Womens Earrings 14K White Gold8,546,666.67 VND26,805,641.03 VND Previous price: 2</t>
+          <t>1/4 - 2 Ct T.W. Natural Diamond Solitaire Pendant in 14k White or Yellow Gold4,358,717.95 VND</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
-          <t>Jewelry Accessories &amp; Derivatives</t>
+          <t>Books, Magazines &amp; Audio</t>
         </is>
       </c>
       <c r="D68" s="3" t="n">
@@ -3613,7 +3613,7 @@
       </c>
       <c r="J68" s="5" t="inlineStr">
         <is>
-          <t>https://www.ebay.com/itm/355504570491</t>
+          <t>https://www.ebay.com/itm/353815614085</t>
         </is>
       </c>
     </row>
@@ -3623,12 +3623,12 @@
       </c>
       <c r="B69" s="4" t="inlineStr">
         <is>
-          <t>1/4 - 2 Ct T.W. Natural Diamond Solitaire Pendant in 14k White or Yellow Gold4,358,717.95 VND</t>
+          <t>925 Sterlingsilber Silber Anhänger DAVIDSTERN Hexagramm Charm Kette 20x20mm 50661,780,592.19 VNDAlmost goneShop all 22Fi</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>Books, Magazines &amp; Audio</t>
+          <t>Fashion &amp; Apparel</t>
         </is>
       </c>
       <c r="D69" s="3" t="n">
@@ -3659,7 +3659,7 @@
       </c>
       <c r="J69" s="5" t="inlineStr">
         <is>
-          <t>https://www.ebay.com/itm/353815614085</t>
+          <t>https://www.ebay.com/itm/271569399778</t>
         </is>
       </c>
     </row>
@@ -3669,12 +3669,12 @@
       </c>
       <c r="B70" s="4" t="inlineStr">
         <is>
-          <t>925 Sterlingsilber Silber Anhänger DAVIDSTERN Hexagramm Charm Kette 20x20mm 50661,780,592.19 VNDAlmost goneShop all 22Fi</t>
+          <t>Panzerkette 4 mm Halskette Echt 750er Gold 18Karat vergoldet Damen Herren K1808906,824.42 VND</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
         <is>
-          <t>Fashion &amp; Apparel</t>
+          <t>Kitchenware</t>
         </is>
       </c>
       <c r="D70" s="3" t="n">
@@ -3705,7 +3705,7 @@
       </c>
       <c r="J70" s="5" t="inlineStr">
         <is>
-          <t>https://www.ebay.com/itm/271569399778</t>
+          <t>https://www.ebay.com/itm/125770552175</t>
         </is>
       </c>
     </row>
@@ -3715,12 +3715,12 @@
       </c>
       <c r="B71" s="4" t="inlineStr">
         <is>
-          <t>Panzerkette 4 mm Halskette Echt 750er Gold 18Karat vergoldet Damen Herren K1808906,824.42 VND</t>
+          <t>Set Damenkette Schlüssel Anhänger Zirkonia weiß 750 Gold 18Karat vergoldet A1127595,615.38 VNDAlmost goneHerz Anhänger K</t>
         </is>
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>Kitchenware</t>
+          <t>Menswear &amp; Underwear</t>
         </is>
       </c>
       <c r="D71" s="3" t="n">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="J71" s="5" t="inlineStr">
         <is>
-          <t>https://www.ebay.com/itm/125770552175</t>
+          <t>https://www.ebay.com/itm/125770529088</t>
         </is>
       </c>
     </row>
@@ -3761,12 +3761,12 @@
       </c>
       <c r="B72" s="4" t="inlineStr">
         <is>
-          <t>Set Damenkette Schlüssel Anhänger Zirkonia weiß 750 Gold 18Karat vergoldet A1127595,615.38 VNDAlmost goneHerz Anhänger K</t>
+          <t>Löwenzahn Kapseln mit 500 mg 10:1 Wurzelextrakt - vegan - Vitamineule744,221.42 VNDFree shippingBrokkoli Sulforaphan Kap</t>
         </is>
       </c>
       <c r="C72" s="4" t="inlineStr">
         <is>
-          <t>Menswear &amp; Underwear</t>
+          <t>Health</t>
         </is>
       </c>
       <c r="D72" s="3" t="n">
@@ -3797,7 +3797,7 @@
       </c>
       <c r="J72" s="5" t="inlineStr">
         <is>
-          <t>https://www.ebay.com/itm/125770529088</t>
+          <t>https://www.ebay.com/itm/125306609308</t>
         </is>
       </c>
     </row>
@@ -3807,12 +3807,12 @@
       </c>
       <c r="B73" s="4" t="inlineStr">
         <is>
-          <t>300mg Benfotiamine 3 x 120 Capsules Fat Soluble Thiamine Vitamin B1 Supplement991,345.38 VNDFree shippingLöwenzahn Kapse</t>
+          <t>Curcuma Extrakt Kapseln - hochdosiert - 350 mg Curcuminoide - Vitamineule744,221.42 VNDFree shipping</t>
         </is>
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
-          <t>Menswear &amp; Underwear</t>
+          <t>Health</t>
         </is>
       </c>
       <c r="D73" s="3" t="n">
@@ -3843,7 +3843,7 @@
       </c>
       <c r="J73" s="5" t="inlineStr">
         <is>
-          <t>https://www.ebay.com/itm/357242424467</t>
+          <t>https://www.ebay.com/itm/123839173201</t>
         </is>
       </c>
     </row>
@@ -3853,7 +3853,7 @@
       </c>
       <c r="B74" s="4" t="inlineStr">
         <is>
-          <t>Curcuma Extrakt Kapseln - hochdosiert - 350 mg Curcuminoide - Vitamineule744,221.42 VNDFree shipping</t>
+          <t>Jod Kapseln aus Bio Kelp / Tabletten - 400µg aus Bio Kelp Extrakt - Vitamineule774,002.19 VNDFree shippingShop all 30Bea</t>
         </is>
       </c>
       <c r="C74" s="4" t="inlineStr">
@@ -3889,7 +3889,7 @@
       </c>
       <c r="J74" s="5" t="inlineStr">
         <is>
-          <t>https://www.ebay.com/itm/123839173201</t>
+          <t>https://www.ebay.com/itm/124078773818</t>
         </is>
       </c>
     </row>
@@ -3899,12 +3899,12 @@
       </c>
       <c r="B75" s="4" t="inlineStr">
         <is>
-          <t>Jod Kapseln aus Bio Kelp / Tabletten - 400µg aus Bio Kelp Extrakt - Vitamineule774,002.19 VNDFree shippingShop all 31Bea</t>
+          <t>Lonsdale Navy Blue Baseball Cap Hat Embroidered Logo Adjustable Kappe Mütze741,541.15 VND</t>
         </is>
       </c>
       <c r="C75" s="4" t="inlineStr">
         <is>
-          <t>Health</t>
+          <t>Fashion &amp; Apparel</t>
         </is>
       </c>
       <c r="D75" s="3" t="n">
@@ -3935,7 +3935,7 @@
       </c>
       <c r="J75" s="5" t="inlineStr">
         <is>
-          <t>https://www.ebay.com/itm/124078773818</t>
+          <t>https://www.ebay.com/itm/296106350225</t>
         </is>
       </c>
     </row>
@@ -3945,12 +3945,12 @@
       </c>
       <c r="B76" s="4" t="inlineStr">
         <is>
-          <t>Lonsdale Navy Blue Baseball Cap Hat Embroidered Logo Adjustable Kappe Mütze741,541.15 VND</t>
+          <t>Puma Speedcat OG team royal white Schuhe Sneaker Motorsport F1 398846-183,275,586.81 VNDShop all 12Men's Shoes &amp; Accesso</t>
         </is>
       </c>
       <c r="C76" s="4" t="inlineStr">
         <is>
-          <t>Fashion &amp; Apparel</t>
+          <t>Pet Supplies</t>
         </is>
       </c>
       <c r="D76" s="3" t="n">
@@ -3971,17 +3971,17 @@
       </c>
       <c r="H76" s="4" t="inlineStr">
         <is>
-          <t>Đặt câu hỏi trúng nỗi đau thường ngày: 'Tại sao không ai nói cho tôi biết món đồ này sớm hơn?!'</t>
+          <t>Âm thanh bấm nút nhả cả búi lông chó rụng chỉ trong 1 giây: 'Mùa rụng lông không còn là ác mộng!'</t>
         </is>
       </c>
       <c r="I76" s="4" t="inlineStr">
         <is>
-          <t>Khách hàng mua sắm ngẫu hứng (Impulse Buyers) trên TikTok Shop US độ tuổi 18 - 45.</t>
+          <t>Hội những người 'nghiện' chó mèo (Dog/Cat Parents) tại US, chi tiêu mạnh tay cho thú cưng.</t>
         </is>
       </c>
       <c r="J76" s="5" t="inlineStr">
         <is>
-          <t>https://www.ebay.com/itm/296106350225</t>
+          <t>https://www.ebay.com/itm/156805882161</t>
         </is>
       </c>
     </row>
@@ -3991,12 +3991,12 @@
       </c>
       <c r="B77" s="4" t="inlineStr">
         <is>
-          <t>Puma Speedcat OG team royal white Schuhe Sneaker Motorsport F1 398846-183,275,586.81 VNDShop all 12Men's Shoes &amp; Accesso</t>
+          <t>Lederweste Bikerweste Motorrad Kutte Biker Chopper Rockerweste mit Taschen2,679,971.42 VNDBiker Kutte Lederkutte Lederwe</t>
         </is>
       </c>
       <c r="C77" s="4" t="inlineStr">
         <is>
-          <t>Pet Supplies</t>
+          <t>Fashion &amp; Apparel</t>
         </is>
       </c>
       <c r="D77" s="3" t="n">
@@ -4017,17 +4017,17 @@
       </c>
       <c r="H77" s="4" t="inlineStr">
         <is>
-          <t>Âm thanh bấm nút nhả cả búi lông chó rụng chỉ trong 1 giây: 'Mùa rụng lông không còn là ác mộng!'</t>
+          <t>Đặt câu hỏi trúng nỗi đau thường ngày: 'Tại sao không ai nói cho tôi biết món đồ này sớm hơn?!'</t>
         </is>
       </c>
       <c r="I77" s="4" t="inlineStr">
         <is>
-          <t>Hội những người 'nghiện' chó mèo (Dog/Cat Parents) tại US, chi tiêu mạnh tay cho thú cưng.</t>
+          <t>Khách hàng mua sắm ngẫu hứng (Impulse Buyers) trên TikTok Shop US độ tuổi 18 - 45.</t>
         </is>
       </c>
       <c r="J77" s="5" t="inlineStr">
         <is>
-          <t>https://www.ebay.com/itm/156805882161</t>
+          <t>https://www.ebay.com/itm/291771387455</t>
         </is>
       </c>
     </row>
@@ -4037,7 +4037,7 @@
       </c>
       <c r="B78" s="4" t="inlineStr">
         <is>
-          <t>Biker Kutte Lederkutte Lederweste Clubweste Rockerweste Herren Chopper Motorrad2,679,971.42 VND</t>
+          <t>Schwarze Lederkutte mit blau Umrandungen Kutte Biker Motorrad Rocker Clubweste2,679,971.42 VND</t>
         </is>
       </c>
       <c r="C78" s="4" t="inlineStr">
@@ -4073,7 +4073,7 @@
       </c>
       <c r="J78" s="5" t="inlineStr">
         <is>
-          <t>https://www.ebay.com/itm/302258284099</t>
+          <t>https://www.ebay.com/itm/301897675077</t>
         </is>
       </c>
     </row>
@@ -4083,7 +4083,7 @@
       </c>
       <c r="B79" s="4" t="inlineStr">
         <is>
-          <t>Schwarze Lederkutte mit blau Umrandungen Kutte Biker Motorrad Rocker Clubweste2,679,971.42 VNDShop all 68Men's Clothing</t>
+          <t>Bikerweste Lederweste Rockerweste Lederkutte Kutte Chopperweste Clubweste2,382,163.73 VNDShop all 67Men's Clothing</t>
         </is>
       </c>
       <c r="C79" s="4" t="inlineStr">
@@ -4119,7 +4119,7 @@
       </c>
       <c r="J79" s="5" t="inlineStr">
         <is>
-          <t>https://www.ebay.com/itm/301897675077</t>
+          <t>https://www.ebay.com/itm/303349551958</t>
         </is>
       </c>
     </row>
@@ -4129,7 +4129,7 @@
       </c>
       <c r="B80" s="4" t="inlineStr">
         <is>
-          <t>Unterbrustkorsett Schwarz Leder Corsage Gothic Korsett Underbust Leather Corsets2,178,463.27 VND2,293,119.23 VND | 5% of</t>
+          <t>Unterbrustkorsett Rot Lack Corsage tolles Taillen training PVC Underbust Corsets1,980,421.15 VND2,084,653.85 VND | 5% of</t>
         </is>
       </c>
       <c r="C80" s="4" t="inlineStr">
@@ -4165,7 +4165,7 @@
       </c>
       <c r="J80" s="5" t="inlineStr">
         <is>
-          <t>https://www.ebay.com/itm/362632687305</t>
+          <t>https://www.ebay.com/itm/363166536187</t>
         </is>
       </c>
     </row>
@@ -4175,12 +4175,12 @@
       </c>
       <c r="B81" s="4" t="inlineStr">
         <is>
-          <t>Satin Vollbrustkorsett Schnürkorsett Korsett Mieder Corset Corsage Schwarz LANG2,084,653.85 VND</t>
+          <t>Leder Taillenkorsett Schwarz Schnür Gothic Damen | Leather Waist Corset1,980,421.15 VND2,084,653.85 VND | 5% offPrevious</t>
         </is>
       </c>
       <c r="C81" s="4" t="inlineStr">
         <is>
-          <t>Fashion &amp; Apparel</t>
+          <t>Menswear &amp; Underwear</t>
         </is>
       </c>
       <c r="D81" s="3" t="n">
@@ -4211,7 +4211,7 @@
       </c>
       <c r="J81" s="5" t="inlineStr">
         <is>
-          <t>https://www.ebay.com/itm/362636865751</t>
+          <t>https://www.ebay.com/itm/364907426887</t>
         </is>
       </c>
     </row>
@@ -4221,12 +4221,12 @@
       </c>
       <c r="B82" s="4" t="inlineStr">
         <is>
-          <t>Unterbrustkorsett Rot Lack Corsage tolles Taillen training PVC Underbust Corsets1,980,421.15 VND2,084,653.85 VND | 5% of</t>
+          <t>Unterbrustkorsett Schwarz Baumwolle Corsage Underbust  Wider Hips Corset Hi-441,935,750.00 VNDShop all 35Women's Clothin</t>
         </is>
       </c>
       <c r="C82" s="4" t="inlineStr">
         <is>
-          <t>Fashion &amp; Apparel</t>
+          <t>Menswear &amp; Underwear</t>
         </is>
       </c>
       <c r="D82" s="3" t="n">
@@ -4257,7 +4257,7 @@
       </c>
       <c r="J82" s="5" t="inlineStr">
         <is>
-          <t>https://www.ebay.com/itm/363166536187</t>
+          <t>https://www.ebay.com/itm/362618056873</t>
         </is>
       </c>
     </row>
@@ -4267,12 +4267,12 @@
       </c>
       <c r="B83" s="4" t="inlineStr">
         <is>
-          <t>New Omega Seamaster Diver 300M Automatic Green Men's Watch 210.90.42.20.10.001266,769,230.77 VND320,512,820.51 VND Previ</t>
+          <t>Breitling TransOcean Chrono Quartz 40mm Iced 13ct Diamond Black Dial A530401166,641,025.64 VNDAlmost gone</t>
         </is>
       </c>
       <c r="C83" s="4" t="inlineStr">
         <is>
-          <t>Menswear &amp; Underwear</t>
+          <t>Fashion &amp; Apparel</t>
         </is>
       </c>
       <c r="D83" s="3" t="n">
@@ -4293,17 +4293,17 @@
       </c>
       <c r="H83" s="4" t="inlineStr">
         <is>
-          <t>So sánh âm thanh: 'Bật lọc tạp âm và nói chuyện giữa chợ ồn ào xem micro này xịn cỡ nào!'</t>
+          <t>Đặt câu hỏi trúng nỗi đau thường ngày: 'Tại sao không ai nói cho tôi biết món đồ này sớm hơn?!'</t>
         </is>
       </c>
       <c r="I83" s="4" t="inlineStr">
         <is>
-          <t>Học sinh, Gen Z làm bullet journal, Content Creator quay video TikTok / Vlog tại US.</t>
+          <t>Khách hàng mua sắm ngẫu hứng (Impulse Buyers) trên TikTok Shop US độ tuổi 18 - 45.</t>
         </is>
       </c>
       <c r="J83" s="5" t="inlineStr">
         <is>
-          <t>https://www.ebay.com/itm/357622544308</t>
+          <t>https://www.ebay.com/itm/146360754668</t>
         </is>
       </c>
     </row>
@@ -4401,7 +4401,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I32"/>
+  <dimension ref="A1:I31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4506,7 +4506,7 @@
       </c>
       <c r="I3" s="5" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/Mighty-Patch-Hydrocolloid-Absorbing-count/dp/B074PVTPBW/ref=zg_bs_g_beauty_d_sccl_5/142-8547974-1409324</t>
+          <t>https://www.amazon.com/Mighty-Patch-Hydrocolloid-Absorbing-count/dp/B074PVTPBW/ref=zg_bs_g_beauty_d_sccl_5/134-1887633-9887334</t>
         </is>
       </c>
     </row>
@@ -4516,28 +4516,28 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>STANLEY IceFlow 2.0 Flip Straw Tumbler, 30 oz, Black 2.0 | Easy Carry Handle | Twist On Lid and Flip Up Straw | Leak Resistant Wat</t>
+          <t>Clean Skin Club Clean Towels XL®, 100% USDA Biobased Face Towel, Disposable Face Towelette, Eczema Association Accepted, Makeup Re</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>Kitchenware</t>
+          <t>Beauty &amp; Personal Care</t>
         </is>
       </c>
       <c r="D4" s="3" t="n">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="E4" s="3" t="n">
         <v>92</v>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>70% - 85% (Source $3.5 - $6.0 -&gt; Bán $18.99 - $24.99)</t>
+          <t>70% - 82% (Source $3.5 - $5.0 -&gt; Bán $15.95 - $17.95)</t>
         </is>
       </c>
       <c r="G4" s="4" t="inlineStr">
         <is>
-          <t>Before/After Macro Skin Texture Zoom (Cận cảnh bề mặt da)</t>
+          <t>Problem - Agitate - Solution (So sánh vi khuẩn kính hiển vi)</t>
         </is>
       </c>
       <c r="H4" s="4" t="inlineStr">
@@ -4547,7 +4547,7 @@
       </c>
       <c r="I4" s="5" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/STANLEY-IceFlow-Straw-Tumbler-Black/dp/B0DR9PMK1W/ref=zg_bs_g_kitchen_d_sccl_6/142-8547974-1409324</t>
+          <t>https://www.amazon.com/Clean-Skin-Club-Disposable-Sensitive/dp/B07PBXXNCY/ref=zg_bs_g_beauty_d_sccl_4/134-1887633-9887334</t>
         </is>
       </c>
     </row>
@@ -4557,12 +4557,12 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>Clean Skin Club Clean Towels XL®, 100% USDA Biobased Face Towel, Disposable Face Towelette, Eczema Association Accepted, Makeup Re</t>
+          <t>Owala FreeSip Stainless Steel Water Bottle 24 oz Denim</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>Beauty &amp; Personal Care</t>
+          <t>Kitchenware</t>
         </is>
       </c>
       <c r="D5" s="3" t="n">
@@ -4573,22 +4573,22 @@
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>70% - 82% (Source $3.5 - $5.0 -&gt; Bán $15.95 - $17.95)</t>
+          <t>60% - 75% (Source $6.0 - $9.0 -&gt; Bán $24.99 - $37.99)</t>
         </is>
       </c>
       <c r="G5" s="4" t="inlineStr">
         <is>
-          <t>Problem - Agitate - Solution (So sánh vi khuẩn kính hiển vi)</t>
+          <t>Drop Test &amp; Leak-proof Challenge (Thử thách va đập &amp; chống đổ nước)</t>
         </is>
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>Bấm vào giỏ hàng màu vàng góc dưới nhận voucher freeship hôm nay!</t>
+          <t>Màu hot này liên tục cháy hàng, click giỏ hàng đặt ngay kẻo hết size!</t>
         </is>
       </c>
       <c r="I5" s="5" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/Clean-Skin-Club-Disposable-Sensitive/dp/B07PBXXNCY/ref=zg_bs_g_beauty_d_sccl_4/142-8547974-1409324</t>
+          <t>https://www.amazon.com/Owala-FreeSip-Insulated-Stainless-BPA-Free/dp/B0BZYCJK89/ref=zg_bs_g_kitchen_d_sccl_1/134-1887633-9887334</t>
         </is>
       </c>
     </row>
@@ -4629,7 +4629,7 @@
       </c>
       <c r="I6" s="5" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/Owala-FreeSip-Insulated-Stainless-BPA-Free/dp/B0BZYCJK89/ref=zg_bs_g_kitchen_d_sccl_1/142-8547974-1409324</t>
+          <t>https://www.amazon.com/Owala-FreeSip-Insulated-Stainless-BPA-Free/dp/B0BZYCJK89/ref=zg_bs_g_home-garden_d_sccl_2/134-1887633-9887334</t>
         </is>
       </c>
     </row>
@@ -4639,7 +4639,7 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>Owala FreeSip Stainless Steel Water Bottle 24 oz Denim</t>
+          <t xml:space="preserve">Owala SmoothSip Slider Insulated Stainless Steel Coffee Tumbler, Reusable Iced Coffee Cup, Hot Coffee Travel Mug, BPA Free 20 oz, </t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
@@ -4648,7 +4648,7 @@
         </is>
       </c>
       <c r="D7" s="3" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="E7" s="3" t="n">
         <v>92</v>
@@ -4670,7 +4670,7 @@
       </c>
       <c r="I7" s="5" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/Owala-FreeSip-Insulated-Stainless-BPA-Free/dp/B0BZYCJK89/ref=zg_bs_g_home-garden_d_sccl_1/142-8547974-1409324</t>
+          <t>https://www.amazon.com/Owala-SmoothSip-Insulated-Stainless-Reusable/dp/B0DF3M7V3T/ref=zg_bs_g_kitchen_d_sccl_5/134-1887633-9887334</t>
         </is>
       </c>
     </row>
@@ -4680,38 +4680,38 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Owala SmoothSip Slider Insulated Stainless Steel Coffee Tumbler, Reusable Iced Coffee Cup, Hot Coffee Travel Mug, BPA Free 20 oz, </t>
+          <t>eos Shea Better Body Lotion- Vanilla Cashmere, 24-Hour Moisture, 16 fl oz</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>Kitchenware</t>
+          <t>Beauty &amp; Skincare</t>
         </is>
       </c>
       <c r="D8" s="3" t="n">
-        <v>90</v>
+        <v>97</v>
       </c>
       <c r="E8" s="3" t="n">
         <v>92</v>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>60% - 75% (Source $6.0 - $9.0 -&gt; Bán $24.99 - $37.99)</t>
+          <t>70% - 85% (Source $3.5 - $6.0 -&gt; Bán $18.99 - $24.99)</t>
         </is>
       </c>
       <c r="G8" s="4" t="inlineStr">
         <is>
-          <t>Drop Test &amp; Leak-proof Challenge (Thử thách va đập &amp; chống đổ nước)</t>
+          <t>Before/After Macro Skin Texture Zoom (Cận cảnh bề mặt da)</t>
         </is>
       </c>
       <c r="H8" s="4" t="inlineStr">
         <is>
-          <t>Màu hot này liên tục cháy hàng, click giỏ hàng đặt ngay kẻo hết size!</t>
+          <t>Bấm vào giỏ hàng màu vàng góc dưới nhận voucher freeship hôm nay!</t>
         </is>
       </c>
       <c r="I8" s="5" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/Owala-SmoothSip-Insulated-Stainless-Reusable/dp/B0DF3M7V3T/ref=zg_bs_g_kitchen_d_sccl_5/142-8547974-1409324</t>
+          <t>https://www.amazon.com/eos-Cashmere-Moisture-Lightweight-Non-Greasy/dp/B08KT2Z93D/ref=zg_bs_g_beauty_d_sccl_1/134-1887633-9887334</t>
         </is>
       </c>
     </row>
@@ -4721,12 +4721,12 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>eos Shea Better Body Lotion- Vanilla Cashmere, 24-Hour Moisture, 16 fl oz</t>
+          <t>TERRO Liquid Ant Killer Bait Stations, 12-Pack, Indoor Ant Traps, T300B | Borax Formula, Kills the Queen &amp; the Entire Colony, Liqu</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>Beauty &amp; Skincare</t>
+          <t>Home Gadgets</t>
         </is>
       </c>
       <c r="D9" s="3" t="n">
@@ -4737,22 +4737,22 @@
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>70% - 85% (Source $3.5 - $6.0 -&gt; Bán $18.99 - $24.99)</t>
+          <t>65% - 75% (Ước tính giá bán $15 - $29)</t>
         </is>
       </c>
       <c r="G9" s="4" t="inlineStr">
         <is>
-          <t>Before/After Macro Skin Texture Zoom (Cận cảnh bề mặt da)</t>
+          <t>TikTok Made Me Buy It / Honest Review</t>
         </is>
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>Bấm vào giỏ hàng màu vàng góc dưới nhận voucher freeship hôm nay!</t>
+          <t>Xem ngay giá ưu đãi độc quyền hôm nay trên TikTok Shop!</t>
         </is>
       </c>
       <c r="I9" s="5" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/eos-Cashmere-Moisture-Lightweight-Non-Greasy/dp/B08KT2Z93D/ref=zg_bs_g_beauty_d_sccl_1/142-8547974-1409324</t>
+          <t>https://www.amazon.com/TERRO-T300-2-2-Pack-Liquid-Baits/dp/B00E4GACB8/ref=zg_bs_g_home-garden_d_sccl_1/134-1887633-9887334</t>
         </is>
       </c>
     </row>
@@ -4762,12 +4762,12 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Neutrogena Makeup Remover Micellar Wipes, 2 Pack of 25 Ct | Plant-Based Micellar Water Cleansing Cloths, Gently Removes Oil, Dirt </t>
+          <t xml:space="preserve">Queen Size 4 Piece Sheet Set - Comfy Breathable &amp; Cooling Sheets - White | Hotel Luxury Bed Sheets for Women &amp; Men, Deep Pockets, </t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>Home Supplies</t>
+          <t>Menswear &amp; Underwear</t>
         </is>
       </c>
       <c r="D10" s="3" t="n">
@@ -4778,22 +4778,22 @@
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>70% - 85% (Source $3.5 - $6.0 -&gt; Bán $18.99 - $24.99)</t>
+          <t>65% - 75% (Ước tính giá bán $15 - $29)</t>
         </is>
       </c>
       <c r="G10" s="4" t="inlineStr">
         <is>
-          <t>Before/After Macro Skin Texture Zoom (Cận cảnh bề mặt da)</t>
+          <t>TikTok Made Me Buy It / Honest Review</t>
         </is>
       </c>
       <c r="H10" s="4" t="inlineStr">
         <is>
-          <t>Bấm vào giỏ hàng màu vàng góc dưới nhận voucher freeship hôm nay!</t>
+          <t>Xem ngay giá ưu đãi độc quyền hôm nay trên TikTok Shop!</t>
         </is>
       </c>
       <c r="I10" s="5" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/Neutrogena-Makeup-Remover-Micellar-Wipes/dp/B00U2VQZDS/ref=zg_bs_g_beauty_d_sccl_6/142-8547974-1409324</t>
+          <t>https://www.amazon.com/Queen-Size-Piece-Sheet-Set/dp/B01M16WBW1/ref=zg_bs_g_home-garden_d_sccl_3/134-1887633-9887334</t>
         </is>
       </c>
     </row>
@@ -4803,12 +4803,12 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>TERRO Liquid Ant Killer Bait Stations, 12-Pack, Indoor Ant Traps, T300B | Borax Formula, Kills the Queen &amp; the Entire Colony, Liqu</t>
+          <t>Dr. Elsey's Ultra UnScented Clumping Clay Cat Litter 40 lb. Bag</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>Home Gadgets</t>
+          <t>Pet Supplies</t>
         </is>
       </c>
       <c r="D11" s="3" t="n">
@@ -4819,22 +4819,22 @@
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>65% - 75% (Ước tính giá bán $15 - $29)</t>
+          <t>75% - 85% (Source $2.0 - $4.0 -&gt; Bán $11.99 - $16.99)</t>
         </is>
       </c>
       <c r="G11" s="4" t="inlineStr">
         <is>
-          <t>TikTok Made Me Buy It / Honest Review</t>
+          <t>Emotional Reaction &amp; Satisfying Fur Release ASMR</t>
         </is>
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>Xem ngay giá ưu đãi độc quyền hôm nay trên TikTok Shop!</t>
+          <t>Bảo vệ đường hô hấp cho cả nhà, sắm ngay chiếc lược tự nhả lông này!</t>
         </is>
       </c>
       <c r="I11" s="5" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/TERRO-T300-2-2-Pack-Liquid-Baits/dp/B00E4GACB8/ref=zg_bs_g_home-garden_d_sccl_2/142-8547974-1409324</t>
+          <t>https://www.amazon.com/Dr-Elseys-Premium-Clumping-Litter/dp/B0009X29WK/ref=zg_bs_g_pet-supplies_d_sccl_1/134-1887633-9887334</t>
         </is>
       </c>
     </row>
@@ -4844,12 +4844,12 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>Amazon Basics Lightweight Super Soft Breathable Wrinkle-Resistant Microfiber 4-Piece Bed Sheet Set with 14-Inch Deep Pockets, Quee</t>
+          <t>Amazon Basics Leak-Proof Dog and Puppy Potty Training Pee Pads with Quick-Dry 5-Layer Super Absorbent Design, Regular Size 22 x 22</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>Phones &amp; Electronics</t>
+          <t>Pet Supplies</t>
         </is>
       </c>
       <c r="D12" s="3" t="n">
@@ -4860,22 +4860,22 @@
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>68% - 78% (Source $4.0 - $7.5 -&gt; Bán $19.99 - $29.99)</t>
+          <t>75% - 85% (Source $2.0 - $4.0 -&gt; Bán $11.99 - $16.99)</t>
         </is>
       </c>
       <c r="G12" s="4" t="inlineStr">
         <is>
-          <t>Side-by-side Live Demo &amp; Unboxing ASMR</t>
+          <t>Emotional Reaction &amp; Satisfying Fur Release ASMR</t>
         </is>
       </c>
       <c r="H12" s="4" t="inlineStr">
         <is>
-          <t>Phụ kiện bắt buộc cho dân làm video TikTok, bấm góc trái đặt hàng liền tay!</t>
+          <t>Bảo vệ đường hô hấp cho cả nhà, sắm ngay chiếc lược tự nhả lông này!</t>
         </is>
       </c>
       <c r="I12" s="5" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/Amazon-Basics-Microfiber-Lightweight-Wrinkle-free/dp/B0154ASID6/ref=zg_bs_g_home-garden_d_sccl_3/142-8547974-1409324</t>
+          <t>https://www.amazon.com/Amazon-Basics-Leak-Proof-Quick-Dry-Absorbency/dp/B00MW8G62E/ref=zg_bs_g_pet-supplies_d_sccl_2/134-1887633-9887334</t>
         </is>
       </c>
     </row>
@@ -4885,7 +4885,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Dr. Elsey's Ultra UnScented Clumping Clay Cat Litter 40 lb. Bag</t>
+          <t>Purina Fancy Feast Gravy Lovers Wet Cat Food, 3 oz Cans, 30-Pack | Variety Pack with poultry and beef grilled gourmet recipes, mad</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
@@ -4916,7 +4916,7 @@
       </c>
       <c r="I13" s="5" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/Dr-Elseys-Premium-Clumping-Litter/dp/B0009X29WK/ref=zg_bs_g_pet-supplies_d_sccl_1/142-8547974-1409324</t>
+          <t>https://www.amazon.com/Purina-Fancy-Feast-Poultry-Collection/dp/B00JN9IWNG/ref=zg_bs_g_pet-supplies_d_sccl_3/134-1887633-9887334</t>
         </is>
       </c>
     </row>
@@ -4926,38 +4926,38 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>Amazon Basics Leak-Proof Dog and Puppy Potty Training Pee Pads with Quick-Dry 5-Layer Super Absorbent Design, Regular Size 22 x 22</t>
+          <t>Amazon Basics Double-Tipped Cotton Swabs for Personal Hygiene and Baby Care, Cotton, Versatile, Baby Safe, 500 Count</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>Pet Supplies</t>
+          <t>Automotive &amp; Motorcycle</t>
         </is>
       </c>
       <c r="D14" s="3" t="n">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="E14" s="3" t="n">
         <v>92</v>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>75% - 85% (Source $2.0 - $4.0 -&gt; Bán $11.99 - $16.99)</t>
+          <t>70% - 85% (Source $3.5 - $6.0 -&gt; Bán $18.99 - $24.99)</t>
         </is>
       </c>
       <c r="G14" s="4" t="inlineStr">
         <is>
-          <t>Emotional Reaction &amp; Satisfying Fur Release ASMR</t>
+          <t>Before/After Macro Skin Texture Zoom (Cận cảnh bề mặt da)</t>
         </is>
       </c>
       <c r="H14" s="4" t="inlineStr">
         <is>
-          <t>Bảo vệ đường hô hấp cho cả nhà, sắm ngay chiếc lược tự nhả lông này!</t>
+          <t>Bấm vào giỏ hàng màu vàng góc dưới nhận voucher freeship hôm nay!</t>
         </is>
       </c>
       <c r="I14" s="5" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/Amazon-Basics-Leak-Proof-Quick-Dry-Absorbency/dp/B00MW8G62E/ref=zg_bs_g_pet-supplies_d_sccl_2/142-8547974-1409324</t>
+          <t>https://www.amazon.com/Amazon-Basics-Cotton-Swabs-500ct/dp/B09541P9WH/ref=zg_bs_g_beauty_d_sccl_3/134-1887633-9887334</t>
         </is>
       </c>
     </row>
@@ -4967,38 +4967,38 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Purina Fancy Feast Gravy Lovers Wet Cat Food, 3 oz Cans, 30-Pack | Variety Pack with poultry and beef grilled gourmet recipes, mad</t>
+          <t>blink plus plan with monthly auto-renewal</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>Pet Supplies</t>
+          <t>Tech Gadgets</t>
         </is>
       </c>
       <c r="D15" s="3" t="n">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="E15" s="3" t="n">
         <v>92</v>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>75% - 85% (Source $2.0 - $4.0 -&gt; Bán $11.99 - $16.99)</t>
+          <t>65% - 75% (Ước tính giá bán $15 - $29)</t>
         </is>
       </c>
       <c r="G15" s="4" t="inlineStr">
         <is>
-          <t>Emotional Reaction &amp; Satisfying Fur Release ASMR</t>
+          <t>TikTok Made Me Buy It / Honest Review</t>
         </is>
       </c>
       <c r="H15" s="4" t="inlineStr">
         <is>
-          <t>Bảo vệ đường hô hấp cho cả nhà, sắm ngay chiếc lược tự nhả lông này!</t>
+          <t>Xem ngay giá ưu đãi độc quyền hôm nay trên TikTok Shop!</t>
         </is>
       </c>
       <c r="I15" s="5" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/Purina-Fancy-Feast-Poultry-Collection/dp/B00JN9IWNG/ref=zg_bs_g_pet-supplies_d_sccl_3/142-8547974-1409324</t>
+          <t>https://www.amazon.com/Blink-Plus-Plan-monthly-auto-renewal/dp/B08JHCVHTY/ref=zg_bs_g_electronics_d_sccl_1/134-1887633-9887334</t>
         </is>
       </c>
     </row>
@@ -5008,19 +5008,19 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>Amazon Basics Double-Tipped Cotton Swabs for Personal Hygiene and Baby Care, Cotton, Versatile, Baby Safe, 500 Count</t>
+          <t>Amazon Essentials 100% Cotton Rounds, 100 Count (Previously Amazon Basics)</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>Automotive &amp; Motorcycle</t>
+          <t>Beauty &amp; Skincare</t>
         </is>
       </c>
       <c r="D16" s="3" t="n">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
@@ -5039,7 +5039,7 @@
       </c>
       <c r="I16" s="5" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/Amazon-Basics-Cotton-Swabs-500ct/dp/B09541P9WH/ref=zg_bs_g_beauty_d_sccl_3/142-8547974-1409324</t>
+          <t>https://www.amazon.com/Amazon-Basics-Cotton-Rounds-Count/dp/B09542G9ZN/ref=zg_bs_g_beauty_d_sccl_6/134-1887633-9887334</t>
         </is>
       </c>
     </row>
@@ -5049,19 +5049,19 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>blink plus plan with monthly auto-renewal</t>
+          <t>Etekcity Food Kitchen Scale, Digital Grams and Ounces, 11lb | Tare function, ideal for baking, weight loss, keto, meal prep, packa</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>Tech Gadgets</t>
+          <t>Home &amp; Kitchen</t>
         </is>
       </c>
       <c r="D17" s="3" t="n">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
@@ -5080,7 +5080,7 @@
       </c>
       <c r="I17" s="5" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/Blink-Plus-Plan-monthly-auto-renewal/dp/B08JHCVHTY/ref=zg_bs_g_electronics_d_sccl_1/142-8547974-1409324</t>
+          <t>https://www.amazon.com/Etekcity-Multifunction-Stainless-Batteries-Included/dp/B0113UZJE2/ref=zg_bs_g_kitchen_d_sccl_4/134-1887633-9887334</t>
         </is>
       </c>
     </row>
@@ -5090,12 +5090,12 @@
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>Etekcity Food Kitchen Scale, Digital Grams and Ounces, 11lb | Tare function, ideal for baking, weight loss, keto, meal prep, packa</t>
+          <t>Amazon Basics Lightweight Super Soft Breathable Wrinkle-Resistant Microfiber 4-Piece Bed Sheet Set with 14-Inch Deep Pockets, Quee</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>Home &amp; Kitchen</t>
+          <t>Phones &amp; Electronics</t>
         </is>
       </c>
       <c r="D18" s="3" t="n">
@@ -5106,22 +5106,22 @@
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t>65% - 75% (Ước tính giá bán $15 - $29)</t>
+          <t>68% - 78% (Source $4.0 - $7.5 -&gt; Bán $19.99 - $29.99)</t>
         </is>
       </c>
       <c r="G18" s="4" t="inlineStr">
         <is>
-          <t>TikTok Made Me Buy It / Honest Review</t>
+          <t>Side-by-side Live Demo &amp; Unboxing ASMR</t>
         </is>
       </c>
       <c r="H18" s="4" t="inlineStr">
         <is>
-          <t>Xem ngay giá ưu đãi độc quyền hôm nay trên TikTok Shop!</t>
+          <t>Phụ kiện bắt buộc cho dân làm video TikTok, bấm góc trái đặt hàng liền tay!</t>
         </is>
       </c>
       <c r="I18" s="5" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/Etekcity-Multifunction-Stainless-Batteries-Included/dp/B0113UZJE2/ref=zg_bs_g_kitchen_d_sccl_4/142-8547974-1409324</t>
+          <t>https://www.amazon.com/Amazon-Basics-Microfiber-Lightweight-Wrinkle-free/dp/B0154ASID6/ref=zg_bs_g_home-garden_d_sccl_4/134-1887633-9887334</t>
         </is>
       </c>
     </row>
@@ -5131,12 +5131,12 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Queen Size 4 Piece Sheet Set - Comfy Breathable &amp; Cooling Sheets - White | Hotel Luxury Bed Sheets for Women &amp; Men, Deep Pockets, </t>
+          <t>Zevo Flying Insect Trap for Fruit Flies &amp; Gnats, 1 Plug-in Base &amp; 1 Refills | Catches Fruit Flies &amp; Gnats Near Fruit Bowls &amp; Trash</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>Menswear &amp; Underwear</t>
+          <t>Pet Supplies</t>
         </is>
       </c>
       <c r="D19" s="3" t="n">
@@ -5147,22 +5147,22 @@
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t>65% - 75% (Ước tính giá bán $15 - $29)</t>
+          <t>75% - 85% (Source $2.0 - $4.0 -&gt; Bán $11.99 - $16.99)</t>
         </is>
       </c>
       <c r="G19" s="4" t="inlineStr">
         <is>
-          <t>TikTok Made Me Buy It / Honest Review</t>
+          <t>Emotional Reaction &amp; Satisfying Fur Release ASMR</t>
         </is>
       </c>
       <c r="H19" s="4" t="inlineStr">
         <is>
-          <t>Xem ngay giá ưu đãi độc quyền hôm nay trên TikTok Shop!</t>
+          <t>Bảo vệ đường hô hấp cho cả nhà, sắm ngay chiếc lược tự nhả lông này!</t>
         </is>
       </c>
       <c r="I19" s="5" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/Queen-Size-Piece-Sheet-Set/dp/B01M16WBW1/ref=zg_bs_g_home-garden_d_sccl_4/142-8547974-1409324</t>
+          <t>https://www.amazon.com/Electric-Flying-Insect-Trap-Starter/dp/B07T869RNY/ref=zg_bs_g_home-garden_d_sccl_6/134-1887633-9887334</t>
         </is>
       </c>
     </row>
@@ -5172,7 +5172,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>Zevo Flying Insect Trap for Fruit Flies &amp; Gnats, 1 Plug-in Base &amp; 1 Refills | Catches Fruit Flies &amp; Gnats Near Fruit Bowls &amp; Trash</t>
+          <t>Earth Rated Dog Poop Bags on Refill Rolls, 270 Bags, Lavender | Guaranteed Leak Proof and Extra Thick Waste Bag Refill Rolls</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
@@ -5203,7 +5203,7 @@
       </c>
       <c r="I20" s="5" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/Electric-Flying-Insect-Trap-Starter/dp/B07T869RNY/ref=zg_bs_g_home-garden_d_sccl_6/142-8547974-1409324</t>
+          <t>https://www.amazon.com/Earth-Rated-Lavender-Scented-Completely/dp/B00BSYR7K8/ref=zg_bs_g_pet-supplies_d_sccl_5/134-1887633-9887334</t>
         </is>
       </c>
     </row>
@@ -5213,38 +5213,38 @@
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>Earth Rated Dog Poop Bags on Refill Rolls, 270 Bags, Lavender | Guaranteed Leak Proof and Extra Thick Waste Bag Refill Rolls</t>
+          <t>bella Fits-Anywhere™ 2-Slice Slim Toaster, Long Slot &amp; Extra Wide, Oatmilk</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>Pet Supplies</t>
+          <t>Home &amp; Kitchen</t>
         </is>
       </c>
       <c r="D21" s="3" t="n">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="E21" s="3" t="n">
         <v>86</v>
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t>75% - 85% (Source $2.0 - $4.0 -&gt; Bán $11.99 - $16.99)</t>
+          <t>65% - 75% (Ước tính giá bán $15 - $29)</t>
         </is>
       </c>
       <c r="G21" s="4" t="inlineStr">
         <is>
-          <t>Emotional Reaction &amp; Satisfying Fur Release ASMR</t>
+          <t>TikTok Made Me Buy It / Honest Review</t>
         </is>
       </c>
       <c r="H21" s="4" t="inlineStr">
         <is>
-          <t>Bảo vệ đường hô hấp cho cả nhà, sắm ngay chiếc lược tự nhả lông này!</t>
+          <t>Xem ngay giá ưu đãi độc quyền hôm nay trên TikTok Shop!</t>
         </is>
       </c>
       <c r="I21" s="5" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/Earth-Rated-Lavender-Scented-Completely/dp/B00BSYR7K8/ref=zg_bs_g_pet-supplies_d_sccl_5/142-8547974-1409324</t>
+          <t>https://www.amazon.com/Toaster-Fits-anywhereTM-Kitchenware-Setting-Removable/dp/B0CYJBB2JQ/ref=zg_bs_g_kitchen_d_sccl_6/134-1887633-9887334</t>
         </is>
       </c>
     </row>
@@ -5285,7 +5285,7 @@
       </c>
       <c r="I22" s="5" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/ZEVO-Flying-Insect-Refills-Indoor/dp/B0C3FTCYZL/ref=zg_bs_g_home-garden_d_sccl_5/142-8547974-1409324</t>
+          <t>https://www.amazon.com/ZEVO-Flying-Insect-Refills-Indoor/dp/B0C3FTCYZL/ref=zg_bs_g_home-garden_d_sccl_5/134-1887633-9887334</t>
         </is>
       </c>
     </row>
@@ -5295,12 +5295,12 @@
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>Apple AirPods 4 Wireless Earbuds | Bluetooth Headphones, Personalized Spatial Audio, Sweat &amp; Water Resistant, USB-C Charging Case,</t>
+          <t>INABA Churu Cat Treats, Lickable, Squeezable Creamy Purée Cat Treat with Green Tea Extract &amp; Taurine, 0.5 Ounces Each Tube, 20 Tub</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>Phones &amp; Electronics</t>
+          <t>Pet Supplies</t>
         </is>
       </c>
       <c r="D23" s="3" t="n">
@@ -5311,22 +5311,22 @@
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t>68% - 78% (Source $4.0 - $7.5 -&gt; Bán $19.99 - $29.99)</t>
+          <t>75% - 85% (Source $2.0 - $4.0 -&gt; Bán $11.99 - $16.99)</t>
         </is>
       </c>
       <c r="G23" s="4" t="inlineStr">
         <is>
-          <t>Side-by-side Live Demo &amp; Unboxing ASMR</t>
+          <t>Emotional Reaction &amp; Satisfying Fur Release ASMR</t>
         </is>
       </c>
       <c r="H23" s="4" t="inlineStr">
         <is>
-          <t>Phụ kiện bắt buộc cho dân làm video TikTok, bấm góc trái đặt hàng liền tay!</t>
+          <t>Bảo vệ đường hô hấp cho cả nhà, sắm ngay chiếc lược tự nhả lông này!</t>
         </is>
       </c>
       <c r="I23" s="5" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/Apple-Bluetooth-Headphones-Personalized-Effortless/dp/B0DGHMNQ5Z/ref=zg_bs_g_electronics_d_sccl_6/142-8547974-1409324</t>
+          <t>https://www.amazon.com/INABA-Grain-Free-Lickable-Squeezable-Vitamin/dp/B0B52D7BBD/ref=zg_bs_g_pet-supplies_d_sccl_4/134-1887633-9887334</t>
         </is>
       </c>
     </row>
@@ -5336,7 +5336,7 @@
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>Greenies Pill Pockets Large Size Dog Treats, Peanut Butter, 15.8 oz | Vet-recommended, masks pill smell &amp; taste, moldable texture,</t>
+          <t xml:space="preserve">Greenies Pill Pockets Large Size Dog Treats, Peanut Butter, 7.9 oz | Vet-recommended, masks pill smell &amp; taste, moldable texture, </t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
@@ -5367,7 +5367,7 @@
       </c>
       <c r="I24" s="5" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/Greenies-Pockets-Natural-Treats-Capsule/dp/B07S2TDDCK/ref=zg_bs_g_pet-supplies_d_sccl_4/142-8547974-1409324</t>
+          <t>https://www.amazon.com/Greenies-Pill-Pockets-Ingredients-Nutrients/dp/B008GRONV6/ref=zg_bs_g_pet-supplies_d_sccl_6/134-1887633-9887334</t>
         </is>
       </c>
     </row>
@@ -5377,38 +5377,38 @@
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>INABA Churu Cat Treats, Lickable, Squeezable Creamy Purée Cat Treat with Green Tea Extract &amp; Taurine, 0.5 Ounces Each Tube, 50 Tub</t>
+          <t>ICED 10k White Gold DIAMOND Curb Link HEAVY 44gr Bracelet Jewelry136,393,589.74 VNDPanzerkette Halskette 5 mm Echt 750er</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>Pet Supplies</t>
+          <t>Kitchenware</t>
         </is>
       </c>
       <c r="D25" s="3" t="n">
         <v>90</v>
       </c>
       <c r="E25" s="3" t="n">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t>75% - 85% (Source $2.0 - $4.0 -&gt; Bán $11.99 - $16.99)</t>
+          <t>65% - 75% (Ước tính giá bán $15 - $29)</t>
         </is>
       </c>
       <c r="G25" s="4" t="inlineStr">
         <is>
-          <t>Emotional Reaction &amp; Satisfying Fur Release ASMR</t>
+          <t>TikTok Made Me Buy It / Honest Review</t>
         </is>
       </c>
       <c r="H25" s="4" t="inlineStr">
         <is>
-          <t>Bảo vệ đường hô hấp cho cả nhà, sắm ngay chiếc lược tự nhả lông này!</t>
+          <t>Xem ngay giá ưu đãi độc quyền hôm nay trên TikTok Shop!</t>
         </is>
       </c>
       <c r="I25" s="5" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/INABA-Chicken-Lickable-Creamy-Variety/dp/B07D323MFZ/ref=zg_bs_g_pet-supplies_d_sccl_6/142-8547974-1409324</t>
+          <t>https://www.ebay.com/itm/298332862724</t>
         </is>
       </c>
     </row>
@@ -5418,38 +5418,38 @@
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>ICED 10k White Gold DIAMOND Curb Link HEAVY 44gr Bracelet Jewelry136,393,589.74 VNDPanzerkette Halskette 5 mm Echt 750er</t>
+          <t>Custom Name Birth Flower Bar Necklace &amp; Personalized Jewelry</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>Kitchenware</t>
+          <t>Jewelry Accessories &amp; Derivatives</t>
         </is>
       </c>
       <c r="D26" s="3" t="n">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="E26" s="3" t="n">
-        <v>76</v>
+        <v>50</v>
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
-          <t>65% - 75% (Ước tính giá bán $15 - $29)</t>
+          <t>75% - 85%</t>
         </is>
       </c>
       <c r="G26" s="4" t="inlineStr">
         <is>
-          <t>TikTok Made Me Buy It / Honest Review</t>
+          <t>Behind The Scenes Crafting &amp; Emotional Gift Unboxing</t>
         </is>
       </c>
       <c r="H26" s="4" t="inlineStr">
         <is>
-          <t>Xem ngay giá ưu đãi độc quyền hôm nay trên TikTok Shop!</t>
+          <t>Gõ tên người bạn muốn khắc vào ghi chú đơn hàng ngay dưới video!</t>
         </is>
       </c>
       <c r="I26" s="5" t="inlineStr">
         <is>
-          <t>https://www.ebay.com/itm/298332862724</t>
+          <t>https://www.etsy.com/market/birth_flower_necklace</t>
         </is>
       </c>
     </row>
@@ -5459,12 +5459,12 @@
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>Custom Name Birth Flower Bar Necklace &amp; Personalized Jewelry</t>
+          <t>Personalized Wooden Docking Station &amp; Desk Organizer for Men</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>Jewelry Accessories &amp; Derivatives</t>
+          <t>Menswear &amp; Underwear</t>
         </is>
       </c>
       <c r="D27" s="3" t="n">
@@ -5475,7 +5475,7 @@
       </c>
       <c r="F27" s="3" t="inlineStr">
         <is>
-          <t>75% - 85%</t>
+          <t>65% - 75%</t>
         </is>
       </c>
       <c r="G27" s="4" t="inlineStr">
@@ -5490,7 +5490,7 @@
       </c>
       <c r="I27" s="5" t="inlineStr">
         <is>
-          <t>https://www.etsy.com/market/birth_flower_necklace</t>
+          <t>https://www.etsy.com/market/wooden_docking_station</t>
         </is>
       </c>
     </row>
@@ -5500,12 +5500,12 @@
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>Personalized Wooden Docking Station &amp; Desk Organizer for Men</t>
+          <t>Minimalist Custom Acrylic Wall Calendar &amp; Family Command Center</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>Menswear &amp; Underwear</t>
+          <t>Home Supplies</t>
         </is>
       </c>
       <c r="D28" s="3" t="n">
@@ -5516,7 +5516,7 @@
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
-          <t>65% - 75%</t>
+          <t>70% - 80%</t>
         </is>
       </c>
       <c r="G28" s="4" t="inlineStr">
@@ -5531,7 +5531,7 @@
       </c>
       <c r="I28" s="5" t="inlineStr">
         <is>
-          <t>https://www.etsy.com/market/wooden_docking_station</t>
+          <t>https://www.etsy.com/market/acrylic_calendar</t>
         </is>
       </c>
     </row>
@@ -5541,12 +5541,12 @@
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>Minimalist Custom Acrylic Wall Calendar &amp; Family Command Center</t>
+          <t>Engraved Olive Wood Cutting Board &amp; Charcuterie Serving Platter</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>Home Supplies</t>
+          <t>Kitchenware</t>
         </is>
       </c>
       <c r="D29" s="3" t="n">
@@ -5557,7 +5557,7 @@
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
-          <t>70% - 80%</t>
+          <t>70%</t>
         </is>
       </c>
       <c r="G29" s="4" t="inlineStr">
@@ -5572,7 +5572,7 @@
       </c>
       <c r="I29" s="5" t="inlineStr">
         <is>
-          <t>https://www.etsy.com/market/acrylic_calendar</t>
+          <t>https://www.etsy.com/market/personalized_cutting_board</t>
         </is>
       </c>
     </row>
@@ -5582,12 +5582,12 @@
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>Engraved Olive Wood Cutting Board &amp; Charcuterie Serving Platter</t>
+          <t>Custom Pet Portrait Sweatshirt &amp; Embroidered Dog Mom Hoodie</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>Kitchenware</t>
+          <t>Pet Supplies</t>
         </is>
       </c>
       <c r="D30" s="3" t="n">
@@ -5598,22 +5598,22 @@
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
-          <t>70%</t>
+          <t>75% - 85% (Source $2.0 - $4.0 -&gt; Bán $11.99 - $16.99)</t>
         </is>
       </c>
       <c r="G30" s="4" t="inlineStr">
         <is>
-          <t>Behind The Scenes Crafting &amp; Emotional Gift Unboxing</t>
+          <t>Emotional Reaction &amp; Satisfying Fur Release ASMR</t>
         </is>
       </c>
       <c r="H30" s="4" t="inlineStr">
         <is>
-          <t>Gõ tên người bạn muốn khắc vào ghi chú đơn hàng ngay dưới video!</t>
+          <t>Bảo vệ đường hô hấp cho cả nhà, sắm ngay chiếc lược tự nhả lông này!</t>
         </is>
       </c>
       <c r="I30" s="5" t="inlineStr">
         <is>
-          <t>https://www.etsy.com/market/personalized_cutting_board</t>
+          <t>https://www.etsy.com/market/custom_pet_sweatshirt</t>
         </is>
       </c>
     </row>
@@ -5623,12 +5623,12 @@
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>Custom Pet Portrait Sweatshirt &amp; Embroidered Dog Mom Hoodie</t>
+          <t>Handmade Organic Soy Aromatherapy Candle in Amber Glass Jar</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>Pet Supplies</t>
+          <t>Home Supplies</t>
         </is>
       </c>
       <c r="D31" s="3" t="n">
@@ -5639,61 +5639,20 @@
       </c>
       <c r="F31" s="3" t="inlineStr">
         <is>
-          <t>75% - 85% (Source $2.0 - $4.0 -&gt; Bán $11.99 - $16.99)</t>
+          <t>80%</t>
         </is>
       </c>
       <c r="G31" s="4" t="inlineStr">
         <is>
-          <t>Emotional Reaction &amp; Satisfying Fur Release ASMR</t>
+          <t>TikTok Made Me Buy It / Honest Review</t>
         </is>
       </c>
       <c r="H31" s="4" t="inlineStr">
         <is>
-          <t>Bảo vệ đường hô hấp cho cả nhà, sắm ngay chiếc lược tự nhả lông này!</t>
+          <t>Xem ngay giá ưu đãi độc quyền hôm nay trên TikTok Shop!</t>
         </is>
       </c>
       <c r="I31" s="5" t="inlineStr">
-        <is>
-          <t>https://www.etsy.com/market/custom_pet_sweatshirt</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="22" customHeight="1">
-      <c r="A32" s="3" t="n">
-        <v>30</v>
-      </c>
-      <c r="B32" s="4" t="inlineStr">
-        <is>
-          <t>Handmade Organic Soy Aromatherapy Candle in Amber Glass Jar</t>
-        </is>
-      </c>
-      <c r="C32" s="4" t="inlineStr">
-        <is>
-          <t>Home Supplies</t>
-        </is>
-      </c>
-      <c r="D32" s="3" t="n">
-        <v>94</v>
-      </c>
-      <c r="E32" s="3" t="n">
-        <v>50</v>
-      </c>
-      <c r="F32" s="3" t="inlineStr">
-        <is>
-          <t>80%</t>
-        </is>
-      </c>
-      <c r="G32" s="4" t="inlineStr">
-        <is>
-          <t>TikTok Made Me Buy It / Honest Review</t>
-        </is>
-      </c>
-      <c r="H32" s="4" t="inlineStr">
-        <is>
-          <t>Xem ngay giá ưu đãi độc quyền hôm nay trên TikTok Shop!</t>
-        </is>
-      </c>
-      <c r="I32" s="5" t="inlineStr">
         <is>
           <t>https://www.etsy.com/market/soy_candle</t>
         </is>
@@ -5730,7 +5689,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I29" r:id="rId27"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I30" r:id="rId28"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I31" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I32" r:id="rId30"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5742,7 +5700,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L113"/>
+  <dimension ref="A1:L112"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5752,7 +5710,7 @@
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="14" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="25" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
     <col width="25" customWidth="1" min="9" max="9"/>
     <col width="48" customWidth="1" min="10" max="10"/>
     <col width="48" customWidth="1" min="11" max="11"/>
@@ -6266,7 +6224,7 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>STANLEY Quencher H2.0 Tumbler with Handle and Straw 30 oz | Flowstate 3-Position Lid | Cup Holder Compatible for Travel | Insulate</t>
+          <t>STANLEY Quencher H2.0 Flow State Tumbler, 40 oz, Rose Quartz 2.0 | Handle and Straw | 3-Position Lid | Cup Holder Compatible for T</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
@@ -6310,7 +6268,7 @@
       </c>
       <c r="L11" s="5" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/STANLEY-Flowstate-3-Position-Compatible-Insulated/dp/B0CP9YB3Q4/ref=zg_bs_g_kitchen_d_sccl_2/142-8547974-1409324</t>
+          <t>https://www.amazon.com/STANLEY-Quencher-State-Tumbler-Quartz/dp/B0CP9Z56SW/ref=zg_bs_g_kitchen_d_sccl_2/134-1887633-9887334</t>
         </is>
       </c>
     </row>
@@ -6364,7 +6322,7 @@
       </c>
       <c r="L12" s="5" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/Medicube-Zero-Pore-Pads-Dual-Textured/dp/B09V7Z4TJG/ref=zg_bs_g_beauty_d_sccl_2/142-8547974-1409324</t>
+          <t>https://www.amazon.com/Medicube-Zero-Pore-Pads-Dual-Textured/dp/B09V7Z4TJG/ref=zg_bs_g_beauty_d_sccl_2/134-1887633-9887334</t>
         </is>
       </c>
     </row>
@@ -6418,7 +6376,7 @@
       </c>
       <c r="L13" s="5" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/HydroJug-Traveler-Resistant-Bottle-Reusable-Insulated/dp/B0CQVWT2NH/ref=zg_bs_g_kitchen_d_sccl_3/142-8547974-1409324</t>
+          <t>https://www.amazon.com/HydroJug-Traveler-Resistant-Bottle-Reusable-Insulated/dp/B0CQVWT2NH/ref=zg_bs_g_kitchen_d_sccl_3/134-1887633-9887334</t>
         </is>
       </c>
     </row>
@@ -6472,7 +6430,7 @@
       </c>
       <c r="L14" s="5" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/Mighty-Patch-Hydrocolloid-Absorbing-count/dp/B074PVTPBW/ref=zg_bs_g_beauty_d_sccl_5/142-8547974-1409324</t>
+          <t>https://www.amazon.com/Mighty-Patch-Hydrocolloid-Absorbing-count/dp/B074PVTPBW/ref=zg_bs_g_beauty_d_sccl_5/134-1887633-9887334</t>
         </is>
       </c>
     </row>
@@ -6482,7 +6440,7 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>STANLEY IceFlow 2.0 Flip Straw Tumbler, 30 oz, Black 2.0 | Easy Carry Handle | Twist On Lid and Flip Up Straw | Leak Resistant Wat</t>
+          <t>Clean Skin Club Clean Towels XL®, 100% USDA Biobased Face Towel, Disposable Face Towelette, Eczema Association Accepted, Makeup Re</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
@@ -6492,17 +6450,17 @@
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>Kitchenware</t>
+          <t>Beauty &amp; Personal Care</t>
         </is>
       </c>
       <c r="E15" s="3" t="n">
-        <v>99.2</v>
+        <v>98.3</v>
       </c>
       <c r="F15" s="3" t="n">
         <v>92</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
@@ -6521,12 +6479,12 @@
       </c>
       <c r="K15" s="4" t="inlineStr">
         <is>
-          <t>Before/After Macro Skin Texture Zoom (Cận cảnh bề mặt da)</t>
+          <t>Problem - Agitate - Solution (So sánh vi khuẩn kính hiển vi)</t>
         </is>
       </c>
       <c r="L15" s="5" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/STANLEY-IceFlow-Straw-Tumbler-Black/dp/B0DR9PMK1W/ref=zg_bs_g_kitchen_d_sccl_6/142-8547974-1409324</t>
+          <t>https://www.amazon.com/Clean-Skin-Club-Disposable-Sensitive/dp/B07PBXXNCY/ref=zg_bs_g_beauty_d_sccl_4/134-1887633-9887334</t>
         </is>
       </c>
     </row>
@@ -6536,7 +6494,7 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>Clean Skin Club Clean Towels XL®, 100% USDA Biobased Face Towel, Disposable Face Towelette, Eczema Association Accepted, Makeup Re</t>
+          <t>Owala FreeSip Stainless Steel Water Bottle 24 oz Denim</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
@@ -6546,7 +6504,7 @@
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>Beauty &amp; Personal Care</t>
+          <t>Kitchenware</t>
         </is>
       </c>
       <c r="E16" s="3" t="n">
@@ -6575,12 +6533,12 @@
       </c>
       <c r="K16" s="4" t="inlineStr">
         <is>
-          <t>Problem - Agitate - Solution (So sánh vi khuẩn kính hiển vi)</t>
+          <t>Drop Test &amp; Leak-proof Challenge (Thử thách va đập &amp; chống đổ nước)</t>
         </is>
       </c>
       <c r="L16" s="5" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/Clean-Skin-Club-Disposable-Sensitive/dp/B07PBXXNCY/ref=zg_bs_g_beauty_d_sccl_4/142-8547974-1409324</t>
+          <t>https://www.amazon.com/Owala-FreeSip-Insulated-Stainless-BPA-Free/dp/B0BZYCJK89/ref=zg_bs_g_kitchen_d_sccl_1/134-1887633-9887334</t>
         </is>
       </c>
     </row>
@@ -6634,7 +6592,7 @@
       </c>
       <c r="L17" s="5" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/Owala-FreeSip-Insulated-Stainless-BPA-Free/dp/B0BZYCJK89/ref=zg_bs_g_kitchen_d_sccl_1/142-8547974-1409324</t>
+          <t>https://www.amazon.com/Owala-FreeSip-Insulated-Stainless-BPA-Free/dp/B0BZYCJK89/ref=zg_bs_g_home-garden_d_sccl_2/134-1887633-9887334</t>
         </is>
       </c>
     </row>
@@ -6644,7 +6602,7 @@
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>Owala FreeSip Stainless Steel Water Bottle 24 oz Denim</t>
+          <t xml:space="preserve">Owala SmoothSip Slider Insulated Stainless Steel Coffee Tumbler, Reusable Iced Coffee Cup, Hot Coffee Travel Mug, BPA Free 20 oz, </t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
@@ -6658,17 +6616,17 @@
         </is>
       </c>
       <c r="E18" s="3" t="n">
-        <v>98.3</v>
+        <v>96.09999999999999</v>
       </c>
       <c r="F18" s="3" t="n">
         <v>92</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="H18" s="3" t="inlineStr">
         <is>
-          <t>1 offer from $29.99</t>
+          <t>$19.99</t>
         </is>
       </c>
       <c r="I18" s="4" t="inlineStr">
@@ -6688,7 +6646,7 @@
       </c>
       <c r="L18" s="5" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/Owala-FreeSip-Insulated-Stainless-BPA-Free/dp/B0BZYCJK89/ref=zg_bs_g_home-garden_d_sccl_1/142-8547974-1409324</t>
+          <t>https://www.amazon.com/Owala-SmoothSip-Insulated-Stainless-Reusable/dp/B0DF3M7V3T/ref=zg_bs_g_kitchen_d_sccl_5/134-1887633-9887334</t>
         </is>
       </c>
     </row>
@@ -6698,7 +6656,7 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Owala SmoothSip Slider Insulated Stainless Steel Coffee Tumbler, Reusable Iced Coffee Cup, Hot Coffee Travel Mug, BPA Free 20 oz, </t>
+          <t>eos Shea Better Body Lotion- Vanilla Cashmere, 24-Hour Moisture, 16 fl oz</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
@@ -6708,17 +6666,17 @@
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>Kitchenware</t>
+          <t>Beauty &amp; Skincare</t>
         </is>
       </c>
       <c r="E19" s="3" t="n">
-        <v>96.09999999999999</v>
+        <v>94.2</v>
       </c>
       <c r="F19" s="3" t="n">
         <v>92</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>90</v>
+        <v>97</v>
       </c>
       <c r="H19" s="3" t="inlineStr">
         <is>
@@ -6732,17 +6690,17 @@
       </c>
       <c r="J19" s="4" t="inlineStr">
         <is>
-          <t>Amazon Best Sellers, Amazon US, TikTok Trend Validated</t>
+          <t>Amazon Best Sellers, Amazon US</t>
         </is>
       </c>
       <c r="K19" s="4" t="inlineStr">
         <is>
-          <t>Drop Test &amp; Leak-proof Challenge (Thử thách va đập &amp; chống đổ nước)</t>
+          <t>Before/After Macro Skin Texture Zoom (Cận cảnh bề mặt da)</t>
         </is>
       </c>
       <c r="L19" s="5" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/Owala-SmoothSip-Insulated-Stainless-Reusable/dp/B0DF3M7V3T/ref=zg_bs_g_kitchen_d_sccl_5/142-8547974-1409324</t>
+          <t>https://www.amazon.com/eos-Cashmere-Moisture-Lightweight-Non-Greasy/dp/B08KT2Z93D/ref=zg_bs_g_beauty_d_sccl_1/134-1887633-9887334</t>
         </is>
       </c>
     </row>
@@ -6752,7 +6710,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>eos Shea Better Body Lotion- Vanilla Cashmere, 24-Hour Moisture, 16 fl oz</t>
+          <t>TERRO Liquid Ant Killer Bait Stations, 12-Pack, Indoor Ant Traps, T300B | Borax Formula, Kills the Queen &amp; the Entire Colony, Liqu</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
@@ -6762,7 +6720,7 @@
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>Beauty &amp; Skincare</t>
+          <t>Home Gadgets</t>
         </is>
       </c>
       <c r="E20" s="3" t="n">
@@ -6791,12 +6749,12 @@
       </c>
       <c r="K20" s="4" t="inlineStr">
         <is>
-          <t>Before/After Macro Skin Texture Zoom (Cận cảnh bề mặt da)</t>
+          <t>TikTok Made Me Buy It / Honest Review</t>
         </is>
       </c>
       <c r="L20" s="5" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/eos-Cashmere-Moisture-Lightweight-Non-Greasy/dp/B08KT2Z93D/ref=zg_bs_g_beauty_d_sccl_1/142-8547974-1409324</t>
+          <t>https://www.amazon.com/TERRO-T300-2-2-Pack-Liquid-Baits/dp/B00E4GACB8/ref=zg_bs_g_home-garden_d_sccl_1/134-1887633-9887334</t>
         </is>
       </c>
     </row>
@@ -6806,7 +6764,7 @@
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Neutrogena Makeup Remover Micellar Wipes, 2 Pack of 25 Ct | Plant-Based Micellar Water Cleansing Cloths, Gently Removes Oil, Dirt </t>
+          <t xml:space="preserve">Queen Size 4 Piece Sheet Set - Comfy Breathable &amp; Cooling Sheets - White | Hotel Luxury Bed Sheets for Women &amp; Men, Deep Pockets, </t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
@@ -6816,7 +6774,7 @@
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>Home Supplies</t>
+          <t>Menswear &amp; Underwear</t>
         </is>
       </c>
       <c r="E21" s="3" t="n">
@@ -6845,12 +6803,12 @@
       </c>
       <c r="K21" s="4" t="inlineStr">
         <is>
-          <t>Before/After Macro Skin Texture Zoom (Cận cảnh bề mặt da)</t>
+          <t>TikTok Made Me Buy It / Honest Review</t>
         </is>
       </c>
       <c r="L21" s="5" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/Neutrogena-Makeup-Remover-Micellar-Wipes/dp/B00U2VQZDS/ref=zg_bs_g_beauty_d_sccl_6/142-8547974-1409324</t>
+          <t>https://www.amazon.com/Queen-Size-Piece-Sheet-Set/dp/B01M16WBW1/ref=zg_bs_g_home-garden_d_sccl_3/134-1887633-9887334</t>
         </is>
       </c>
     </row>
@@ -6860,7 +6818,7 @@
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>TERRO Liquid Ant Killer Bait Stations, 12-Pack, Indoor Ant Traps, T300B | Borax Formula, Kills the Queen &amp; the Entire Colony, Liqu</t>
+          <t>Dr. Elsey's Ultra UnScented Clumping Clay Cat Litter 40 lb. Bag</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
@@ -6870,7 +6828,7 @@
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>Home Gadgets</t>
+          <t>Pet Supplies</t>
         </is>
       </c>
       <c r="E22" s="3" t="n">
@@ -6884,7 +6842,7 @@
       </c>
       <c r="H22" s="3" t="inlineStr">
         <is>
-          <t>8 offers from $7.09</t>
+          <t>$19.99</t>
         </is>
       </c>
       <c r="I22" s="4" t="inlineStr">
@@ -6899,12 +6857,12 @@
       </c>
       <c r="K22" s="4" t="inlineStr">
         <is>
-          <t>TikTok Made Me Buy It / Honest Review</t>
+          <t>Emotional Reaction &amp; Satisfying Fur Release ASMR</t>
         </is>
       </c>
       <c r="L22" s="5" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/TERRO-T300-2-2-Pack-Liquid-Baits/dp/B00E4GACB8/ref=zg_bs_g_home-garden_d_sccl_2/142-8547974-1409324</t>
+          <t>https://www.amazon.com/Dr-Elseys-Premium-Clumping-Litter/dp/B0009X29WK/ref=zg_bs_g_pet-supplies_d_sccl_1/134-1887633-9887334</t>
         </is>
       </c>
     </row>
@@ -6914,7 +6872,7 @@
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>Amazon Basics Lightweight Super Soft Breathable Wrinkle-Resistant Microfiber 4-Piece Bed Sheet Set with 14-Inch Deep Pockets, Quee</t>
+          <t>Amazon Basics Leak-Proof Dog and Puppy Potty Training Pee Pads with Quick-Dry 5-Layer Super Absorbent Design, Regular Size 22 x 22</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
@@ -6924,7 +6882,7 @@
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>Phones &amp; Electronics</t>
+          <t>Pet Supplies</t>
         </is>
       </c>
       <c r="E23" s="3" t="n">
@@ -6938,7 +6896,7 @@
       </c>
       <c r="H23" s="3" t="inlineStr">
         <is>
-          <t>7 offers from $13.44</t>
+          <t>$19.99</t>
         </is>
       </c>
       <c r="I23" s="4" t="inlineStr">
@@ -6953,12 +6911,12 @@
       </c>
       <c r="K23" s="4" t="inlineStr">
         <is>
-          <t>Side-by-side Live Demo &amp; Unboxing ASMR</t>
+          <t>Emotional Reaction &amp; Satisfying Fur Release ASMR</t>
         </is>
       </c>
       <c r="L23" s="5" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/Amazon-Basics-Microfiber-Lightweight-Wrinkle-free/dp/B0154ASID6/ref=zg_bs_g_home-garden_d_sccl_3/142-8547974-1409324</t>
+          <t>https://www.amazon.com/Amazon-Basics-Leak-Proof-Quick-Dry-Absorbency/dp/B00MW8G62E/ref=zg_bs_g_pet-supplies_d_sccl_2/134-1887633-9887334</t>
         </is>
       </c>
     </row>
@@ -6968,7 +6926,7 @@
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>Dr. Elsey's Ultra UnScented Clumping Clay Cat Litter 40 lb. Bag</t>
+          <t>Purina Fancy Feast Gravy Lovers Wet Cat Food, 3 oz Cans, 30-Pack | Variety Pack with poultry and beef grilled gourmet recipes, mad</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
@@ -6992,7 +6950,7 @@
       </c>
       <c r="H24" s="3" t="inlineStr">
         <is>
-          <t>$22.99</t>
+          <t>$19.99</t>
         </is>
       </c>
       <c r="I24" s="4" t="inlineStr">
@@ -7012,7 +6970,7 @@
       </c>
       <c r="L24" s="5" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/Dr-Elseys-Premium-Clumping-Litter/dp/B0009X29WK/ref=zg_bs_g_pet-supplies_d_sccl_1/142-8547974-1409324</t>
+          <t>https://www.amazon.com/Purina-Fancy-Feast-Poultry-Collection/dp/B00JN9IWNG/ref=zg_bs_g_pet-supplies_d_sccl_3/134-1887633-9887334</t>
         </is>
       </c>
     </row>
@@ -7022,7 +6980,7 @@
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>Amazon Basics Leak-Proof Dog and Puppy Potty Training Pee Pads with Quick-Dry 5-Layer Super Absorbent Design, Regular Size 22 x 22</t>
+          <t>Amazon Basics Double-Tipped Cotton Swabs for Personal Hygiene and Baby Care, Cotton, Versatile, Baby Safe, 500 Count</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
@@ -7032,21 +6990,21 @@
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>Pet Supplies</t>
+          <t>Automotive &amp; Motorcycle</t>
         </is>
       </c>
       <c r="E25" s="3" t="n">
-        <v>94.2</v>
+        <v>93.3</v>
       </c>
       <c r="F25" s="3" t="n">
         <v>92</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="H25" s="3" t="inlineStr">
         <is>
-          <t>1 offer from $18.99</t>
+          <t>$19.99</t>
         </is>
       </c>
       <c r="I25" s="4" t="inlineStr">
@@ -7061,12 +7019,12 @@
       </c>
       <c r="K25" s="4" t="inlineStr">
         <is>
-          <t>Emotional Reaction &amp; Satisfying Fur Release ASMR</t>
+          <t>Before/After Macro Skin Texture Zoom (Cận cảnh bề mặt da)</t>
         </is>
       </c>
       <c r="L25" s="5" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/Amazon-Basics-Leak-Proof-Quick-Dry-Absorbency/dp/B00MW8G62E/ref=zg_bs_g_pet-supplies_d_sccl_2/142-8547974-1409324</t>
+          <t>https://www.amazon.com/Amazon-Basics-Cotton-Swabs-500ct/dp/B09541P9WH/ref=zg_bs_g_beauty_d_sccl_3/134-1887633-9887334</t>
         </is>
       </c>
     </row>
@@ -7076,7 +7034,7 @@
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>Purina Fancy Feast Gravy Lovers Wet Cat Food, 3 oz Cans, 30-Pack | Variety Pack with poultry and beef grilled gourmet recipes, mad</t>
+          <t>blink plus plan with monthly auto-renewal</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
@@ -7086,21 +7044,21 @@
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>Pet Supplies</t>
+          <t>Tech Gadgets</t>
         </is>
       </c>
       <c r="E26" s="3" t="n">
-        <v>94.2</v>
+        <v>92</v>
       </c>
       <c r="F26" s="3" t="n">
         <v>92</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="H26" s="3" t="inlineStr">
         <is>
-          <t>6 offers from $28.06</t>
+          <t>$19.99</t>
         </is>
       </c>
       <c r="I26" s="4" t="inlineStr">
@@ -7115,12 +7073,12 @@
       </c>
       <c r="K26" s="4" t="inlineStr">
         <is>
-          <t>Emotional Reaction &amp; Satisfying Fur Release ASMR</t>
+          <t>TikTok Made Me Buy It / Honest Review</t>
         </is>
       </c>
       <c r="L26" s="5" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/Purina-Fancy-Feast-Poultry-Collection/dp/B00JN9IWNG/ref=zg_bs_g_pet-supplies_d_sccl_3/142-8547974-1409324</t>
+          <t>https://www.amazon.com/Blink-Plus-Plan-monthly-auto-renewal/dp/B08JHCVHTY/ref=zg_bs_g_electronics_d_sccl_1/134-1887633-9887334</t>
         </is>
       </c>
     </row>
@@ -7130,27 +7088,27 @@
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>Amazon Basics Double-Tipped Cotton Swabs for Personal Hygiene and Baby Care, Cotton, Versatile, Baby Safe, 500 Count</t>
+          <t>Apple EarPods Headphones with USB-C Plug, Wired Ear Buds with Built-in Remote to Control Music, Phone Calls, and Volume</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>🌲 Evergreen Bền Vững</t>
+          <t>🔥 Bùng Nổ 24h (Viral Spike)</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>Automotive &amp; Motorcycle</t>
+          <t>Phones &amp; Electronics</t>
         </is>
       </c>
       <c r="E27" s="3" t="n">
-        <v>93.3</v>
+        <v>88.8</v>
       </c>
       <c r="F27" s="3" t="n">
         <v>92</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="H27" s="3" t="inlineStr">
         <is>
@@ -7169,12 +7127,12 @@
       </c>
       <c r="K27" s="4" t="inlineStr">
         <is>
-          <t>Before/After Macro Skin Texture Zoom (Cận cảnh bề mặt da)</t>
+          <t>TikTok Made Me Buy It / Honest Review</t>
         </is>
       </c>
       <c r="L27" s="5" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/Amazon-Basics-Cotton-Swabs-500ct/dp/B09541P9WH/ref=zg_bs_g_beauty_d_sccl_3/142-8547974-1409324</t>
+          <t>https://www.amazon.com/Apple-EarPods-Headphones-Built-Control/dp/B0DCH8VDXF/ref=zg_bs_g_electronics_d_sccl_2/134-1887633-9887334</t>
         </is>
       </c>
     </row>
@@ -7184,31 +7142,31 @@
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>blink plus plan with monthly auto-renewal</t>
+          <t>Apple AirTag (2nd Generation): Tracker for Keychain, Wallet, and More; Locator with Sound; Simple One-Tap Setup with iPhone or iPa</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>🌲 Evergreen Bền Vững</t>
+          <t>🔥 Bùng Nổ 24h (Viral Spike)</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>Tech Gadgets</t>
+          <t>Pet Supplies</t>
         </is>
       </c>
       <c r="E28" s="3" t="n">
-        <v>92</v>
+        <v>88.8</v>
       </c>
       <c r="F28" s="3" t="n">
         <v>92</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="H28" s="3" t="inlineStr">
         <is>
-          <t>$11.99</t>
+          <t>$19.99</t>
         </is>
       </c>
       <c r="I28" s="4" t="inlineStr">
@@ -7223,12 +7181,12 @@
       </c>
       <c r="K28" s="4" t="inlineStr">
         <is>
-          <t>TikTok Made Me Buy It / Honest Review</t>
+          <t>Emotional Reaction &amp; Satisfying Fur Release ASMR</t>
         </is>
       </c>
       <c r="L28" s="5" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/Blink-Plus-Plan-monthly-auto-renewal/dp/B08JHCVHTY/ref=zg_bs_g_electronics_d_sccl_1/142-8547974-1409324</t>
+          <t>https://www.amazon.com/Apple-AirTag-2nd-Generation-Precision/dp/B0GJTFXNRX/ref=zg_bs_g_electronics_d_sccl_3/134-1887633-9887334</t>
         </is>
       </c>
     </row>
@@ -7238,31 +7196,31 @@
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>Apple EarPods Headphones with USB-C Plug, Wired Ear Buds with Built-in Remote to Control Music, Phone Calls, and Volume</t>
+          <t>Amazon Essentials 100% Cotton Rounds, 100 Count (Previously Amazon Basics)</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>🔥 Bùng Nổ 24h (Viral Spike)</t>
+          <t>🌲 Evergreen Bền Vững</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>Phones &amp; Electronics</t>
+          <t>Beauty &amp; Skincare</t>
         </is>
       </c>
       <c r="E29" s="3" t="n">
-        <v>88.8</v>
+        <v>91</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>85</v>
+        <v>97</v>
       </c>
       <c r="H29" s="3" t="inlineStr">
         <is>
-          <t>18 offers from $17.87</t>
+          <t>$19.99</t>
         </is>
       </c>
       <c r="I29" s="4" t="inlineStr">
@@ -7277,12 +7235,12 @@
       </c>
       <c r="K29" s="4" t="inlineStr">
         <is>
-          <t>TikTok Made Me Buy It / Honest Review</t>
+          <t>Before/After Macro Skin Texture Zoom (Cận cảnh bề mặt da)</t>
         </is>
       </c>
       <c r="L29" s="5" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/Apple-EarPods-Headphones-Built-Control/dp/B0DCH8VDXF/ref=zg_bs_g_electronics_d_sccl_2/142-8547974-1409324</t>
+          <t>https://www.amazon.com/Amazon-Basics-Cotton-Rounds-Count/dp/B09542G9ZN/ref=zg_bs_g_beauty_d_sccl_6/134-1887633-9887334</t>
         </is>
       </c>
     </row>
@@ -7292,31 +7250,31 @@
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>Apple AirTag (2nd Generation): Tracker for Keychain, Wallet, and More; Locator with Sound; Simple One-Tap Setup with iPhone or iPa</t>
+          <t>Etekcity Food Kitchen Scale, Digital Grams and Ounces, 11lb | Tare function, ideal for baking, weight loss, keto, meal prep, packa</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>🔥 Bùng Nổ 24h (Viral Spike)</t>
+          <t>🌲 Evergreen Bền Vững</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>Pet Supplies</t>
+          <t>Home &amp; Kitchen</t>
         </is>
       </c>
       <c r="E30" s="3" t="n">
-        <v>88.8</v>
+        <v>91</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>85</v>
+        <v>97</v>
       </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
-          <t>10 offers from $22.32</t>
+          <t>$19.99</t>
         </is>
       </c>
       <c r="I30" s="4" t="inlineStr">
@@ -7331,12 +7289,12 @@
       </c>
       <c r="K30" s="4" t="inlineStr">
         <is>
-          <t>Emotional Reaction &amp; Satisfying Fur Release ASMR</t>
+          <t>TikTok Made Me Buy It / Honest Review</t>
         </is>
       </c>
       <c r="L30" s="5" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/Apple-AirTag-2nd-Generation-Precision/dp/B0GJTFXNRX/ref=zg_bs_g_electronics_d_sccl_3/142-8547974-1409324</t>
+          <t>https://www.amazon.com/Etekcity-Multifunction-Stainless-Batteries-Included/dp/B0113UZJE2/ref=zg_bs_g_kitchen_d_sccl_4/134-1887633-9887334</t>
         </is>
       </c>
     </row>
@@ -7346,7 +7304,7 @@
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>Etekcity Food Kitchen Scale, Digital Grams and Ounces, 11lb | Tare function, ideal for baking, weight loss, keto, meal prep, packa</t>
+          <t>Amazon Basics Lightweight Super Soft Breathable Wrinkle-Resistant Microfiber 4-Piece Bed Sheet Set with 14-Inch Deep Pockets, Quee</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
@@ -7356,7 +7314,7 @@
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>Home &amp; Kitchen</t>
+          <t>Phones &amp; Electronics</t>
         </is>
       </c>
       <c r="E31" s="3" t="n">
@@ -7385,12 +7343,12 @@
       </c>
       <c r="K31" s="4" t="inlineStr">
         <is>
-          <t>TikTok Made Me Buy It / Honest Review</t>
+          <t>Side-by-side Live Demo &amp; Unboxing ASMR</t>
         </is>
       </c>
       <c r="L31" s="5" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/Etekcity-Multifunction-Stainless-Batteries-Included/dp/B0113UZJE2/ref=zg_bs_g_kitchen_d_sccl_4/142-8547974-1409324</t>
+          <t>https://www.amazon.com/Amazon-Basics-Microfiber-Lightweight-Wrinkle-free/dp/B0154ASID6/ref=zg_bs_g_home-garden_d_sccl_4/134-1887633-9887334</t>
         </is>
       </c>
     </row>
@@ -7400,7 +7358,7 @@
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Queen Size 4 Piece Sheet Set - Comfy Breathable &amp; Cooling Sheets - White | Hotel Luxury Bed Sheets for Women &amp; Men, Deep Pockets, </t>
+          <t>Zevo Flying Insect Trap for Fruit Flies &amp; Gnats, 1 Plug-in Base &amp; 1 Refills | Catches Fruit Flies &amp; Gnats Near Fruit Bowls &amp; Trash</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
@@ -7410,7 +7368,7 @@
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>Menswear &amp; Underwear</t>
+          <t>Pet Supplies</t>
         </is>
       </c>
       <c r="E32" s="3" t="n">
@@ -7424,7 +7382,7 @@
       </c>
       <c r="H32" s="3" t="inlineStr">
         <is>
-          <t>$24.99</t>
+          <t>$19.99</t>
         </is>
       </c>
       <c r="I32" s="4" t="inlineStr">
@@ -7439,12 +7397,12 @@
       </c>
       <c r="K32" s="4" t="inlineStr">
         <is>
-          <t>TikTok Made Me Buy It / Honest Review</t>
+          <t>Emotional Reaction &amp; Satisfying Fur Release ASMR</t>
         </is>
       </c>
       <c r="L32" s="5" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/Queen-Size-Piece-Sheet-Set/dp/B01M16WBW1/ref=zg_bs_g_home-garden_d_sccl_4/142-8547974-1409324</t>
+          <t>https://www.amazon.com/Electric-Flying-Insect-Trap-Starter/dp/B07T869RNY/ref=zg_bs_g_home-garden_d_sccl_6/134-1887633-9887334</t>
         </is>
       </c>
     </row>
@@ -7454,7 +7412,7 @@
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>Zevo Flying Insect Trap for Fruit Flies &amp; Gnats, 1 Plug-in Base &amp; 1 Refills | Catches Fruit Flies &amp; Gnats Near Fruit Bowls &amp; Trash</t>
+          <t>Earth Rated Dog Poop Bags on Refill Rolls, 270 Bags, Lavender | Guaranteed Leak Proof and Extra Thick Waste Bag Refill Rolls</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
@@ -7478,7 +7436,7 @@
       </c>
       <c r="H33" s="3" t="inlineStr">
         <is>
-          <t>$19.97</t>
+          <t>$19.99</t>
         </is>
       </c>
       <c r="I33" s="4" t="inlineStr">
@@ -7498,7 +7456,7 @@
       </c>
       <c r="L33" s="5" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/Electric-Flying-Insect-Trap-Starter/dp/B07T869RNY/ref=zg_bs_g_home-garden_d_sccl_6/142-8547974-1409324</t>
+          <t>https://www.amazon.com/Earth-Rated-Lavender-Scented-Completely/dp/B00BSYR7K8/ref=zg_bs_g_pet-supplies_d_sccl_5/134-1887633-9887334</t>
         </is>
       </c>
     </row>
@@ -7508,7 +7466,7 @@
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>Earth Rated Dog Poop Bags on Refill Rolls, 270 Bags, Lavender | Guaranteed Leak Proof and Extra Thick Waste Bag Refill Rolls</t>
+          <t>bella Fits-Anywhere™ 2-Slice Slim Toaster, Long Slot &amp; Extra Wide, Oatmilk</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
@@ -7518,21 +7476,21 @@
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>Pet Supplies</t>
+          <t>Home &amp; Kitchen</t>
         </is>
       </c>
       <c r="E34" s="3" t="n">
-        <v>91</v>
+        <v>87.8</v>
       </c>
       <c r="F34" s="3" t="n">
         <v>86</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="H34" s="3" t="inlineStr">
         <is>
-          <t>1 offer from $14.99</t>
+          <t>$19.99</t>
         </is>
       </c>
       <c r="I34" s="4" t="inlineStr">
@@ -7547,12 +7505,12 @@
       </c>
       <c r="K34" s="4" t="inlineStr">
         <is>
-          <t>Emotional Reaction &amp; Satisfying Fur Release ASMR</t>
+          <t>TikTok Made Me Buy It / Honest Review</t>
         </is>
       </c>
       <c r="L34" s="5" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/Earth-Rated-Lavender-Scented-Completely/dp/B00BSYR7K8/ref=zg_bs_g_pet-supplies_d_sccl_5/142-8547974-1409324</t>
+          <t>https://www.amazon.com/Toaster-Fits-anywhereTM-Kitchenware-Setting-Removable/dp/B0CYJBB2JQ/ref=zg_bs_g_kitchen_d_sccl_6/134-1887633-9887334</t>
         </is>
       </c>
     </row>
@@ -7586,7 +7544,7 @@
       </c>
       <c r="H35" s="3" t="inlineStr">
         <is>
-          <t>$14.97</t>
+          <t>$19.99</t>
         </is>
       </c>
       <c r="I35" s="4" t="inlineStr">
@@ -7606,7 +7564,7 @@
       </c>
       <c r="L35" s="5" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/ZEVO-Flying-Insect-Refills-Indoor/dp/B0C3FTCYZL/ref=zg_bs_g_home-garden_d_sccl_5/142-8547974-1409324</t>
+          <t>https://www.amazon.com/ZEVO-Flying-Insect-Refills-Indoor/dp/B0C3FTCYZL/ref=zg_bs_g_home-garden_d_sccl_5/134-1887633-9887334</t>
         </is>
       </c>
     </row>
@@ -7616,7 +7574,7 @@
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>Apple AirPods 4 Wireless Earbuds | Bluetooth Headphones, Personalized Spatial Audio, Sweat &amp; Water Resistant, USB-C Charging Case,</t>
+          <t>INABA Churu Cat Treats, Lickable, Squeezable Creamy Purée Cat Treat with Green Tea Extract &amp; Taurine, 0.5 Ounces Each Tube, 20 Tub</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
@@ -7626,7 +7584,7 @@
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>Phones &amp; Electronics</t>
+          <t>Pet Supplies</t>
         </is>
       </c>
       <c r="E36" s="3" t="n">
@@ -7640,7 +7598,7 @@
       </c>
       <c r="H36" s="3" t="inlineStr">
         <is>
-          <t>47 offers from $91.26</t>
+          <t>$19.99</t>
         </is>
       </c>
       <c r="I36" s="4" t="inlineStr">
@@ -7655,12 +7613,12 @@
       </c>
       <c r="K36" s="4" t="inlineStr">
         <is>
-          <t>Side-by-side Live Demo &amp; Unboxing ASMR</t>
+          <t>Emotional Reaction &amp; Satisfying Fur Release ASMR</t>
         </is>
       </c>
       <c r="L36" s="5" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/Apple-Bluetooth-Headphones-Personalized-Effortless/dp/B0DGHMNQ5Z/ref=zg_bs_g_electronics_d_sccl_6/142-8547974-1409324</t>
+          <t>https://www.amazon.com/INABA-Grain-Free-Lickable-Squeezable-Vitamin/dp/B0B52D7BBD/ref=zg_bs_g_pet-supplies_d_sccl_4/134-1887633-9887334</t>
         </is>
       </c>
     </row>
@@ -7670,7 +7628,7 @@
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>Greenies Pill Pockets Large Size Dog Treats, Peanut Butter, 15.8 oz | Vet-recommended, masks pill smell &amp; taste, moldable texture,</t>
+          <t xml:space="preserve">Greenies Pill Pockets Large Size Dog Treats, Peanut Butter, 7.9 oz | Vet-recommended, masks pill smell &amp; taste, moldable texture, </t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
@@ -7694,7 +7652,7 @@
       </c>
       <c r="H37" s="3" t="inlineStr">
         <is>
-          <t>4 offers from $21.99</t>
+          <t>$19.99</t>
         </is>
       </c>
       <c r="I37" s="4" t="inlineStr">
@@ -7714,7 +7672,7 @@
       </c>
       <c r="L37" s="5" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/Greenies-Pockets-Natural-Treats-Capsule/dp/B07S2TDDCK/ref=zg_bs_g_pet-supplies_d_sccl_4/142-8547974-1409324</t>
+          <t>https://www.amazon.com/Greenies-Pill-Pockets-Ingredients-Nutrients/dp/B008GRONV6/ref=zg_bs_g_pet-supplies_d_sccl_6/134-1887633-9887334</t>
         </is>
       </c>
     </row>
@@ -7724,31 +7682,31 @@
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>INABA Churu Cat Treats, Lickable, Squeezable Creamy Purée Cat Treat with Green Tea Extract &amp; Taurine, 0.5 Ounces Each Tube, 50 Tub</t>
+          <t>Apple AirPods Pro 3 Wireless Earbuds with Active Noise Cancellation | Live Translation, Heart Rate Sensing, Hearing Aid Feature, B</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>🌲 Evergreen Bền Vững</t>
+          <t>🔥 Xu Hướng Tăng Trưởng</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>Pet Supplies</t>
+          <t>Jewelry Accessories &amp; Derivatives</t>
         </is>
       </c>
       <c r="E38" s="3" t="n">
-        <v>87.8</v>
+        <v>85.59999999999999</v>
       </c>
       <c r="F38" s="3" t="n">
         <v>86</v>
       </c>
       <c r="G38" s="3" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="H38" s="3" t="inlineStr">
         <is>
-          <t>3 offers from $32.96</t>
+          <t>$19.99</t>
         </is>
       </c>
       <c r="I38" s="4" t="inlineStr">
@@ -7763,12 +7721,12 @@
       </c>
       <c r="K38" s="4" t="inlineStr">
         <is>
-          <t>Emotional Reaction &amp; Satisfying Fur Release ASMR</t>
+          <t>Side-by-side Live Demo &amp; Unboxing ASMR</t>
         </is>
       </c>
       <c r="L38" s="5" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/INABA-Chicken-Lickable-Creamy-Variety/dp/B07D323MFZ/ref=zg_bs_g_pet-supplies_d_sccl_6/142-8547974-1409324</t>
+          <t>https://www.amazon.com/Apple-Cancellation-Translation-Headphones-High-Fidelity/dp/B0FQFB8FMG/ref=zg_bs_g_electronics_d_sccl_4/134-1887633-9887334</t>
         </is>
       </c>
     </row>
@@ -7778,7 +7736,7 @@
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>Amazon Fire TV Stick 4K Select (newest model), start streaming in 4K, AI-powered search, and free &amp; live TV, find shows faster wit</t>
+          <t xml:space="preserve">Roku Streaming Stick HD with Voice Remote | Compact 4K Streaming Device for TV with Roku Voice Remote &amp; Long-Range Wi-Fi - Free &amp; </t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
@@ -7802,7 +7760,7 @@
       </c>
       <c r="H39" s="3" t="inlineStr">
         <is>
-          <t>1 offer from $49.99</t>
+          <t>$19.99</t>
         </is>
       </c>
       <c r="I39" s="4" t="inlineStr">
@@ -7822,7 +7780,7 @@
       </c>
       <c r="L39" s="5" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/amazon-fire-tv-stick-4K-select/dp/B0C6W3D4RM/ref=zg_bs_g_electronics_d_sccl_4/142-8547974-1409324</t>
+          <t>https://www.amazon.com/Roku-Streaming-Stick-HD-2025/dp/B0DXXYS4BJ/ref=zg_bs_g_electronics_d_sccl_5/134-1887633-9887334</t>
         </is>
       </c>
     </row>
@@ -7832,7 +7790,7 @@
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>Apple AirPods Pro 3 Wireless Earbuds with Active Noise Cancellation | Live Translation, Heart Rate Sensing, Hearing Aid Feature, B</t>
+          <t>Amazon Fire TV Stick 4K Select (newest model), start streaming in 4K, AI-powered search, and free &amp; live TV, find shows faster wit</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
@@ -7842,7 +7800,7 @@
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>Jewelry Accessories &amp; Derivatives</t>
+          <t>Tech Gadgets</t>
         </is>
       </c>
       <c r="E40" s="3" t="n">
@@ -7856,7 +7814,7 @@
       </c>
       <c r="H40" s="3" t="inlineStr">
         <is>
-          <t>12 offers from $183.44</t>
+          <t>$19.99</t>
         </is>
       </c>
       <c r="I40" s="4" t="inlineStr">
@@ -7871,12 +7829,12 @@
       </c>
       <c r="K40" s="4" t="inlineStr">
         <is>
-          <t>Side-by-side Live Demo &amp; Unboxing ASMR</t>
+          <t>TikTok Made Me Buy It / Honest Review</t>
         </is>
       </c>
       <c r="L40" s="5" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/Apple-Cancellation-Translation-Headphones-High-Fidelity/dp/B0FQFB8FMG/ref=zg_bs_g_electronics_d_sccl_5/142-8547974-1409324</t>
+          <t>https://www.amazon.com/amazon-fire-tv-stick-4K-select/dp/B0C6W3D4RM/ref=zg_bs_g_electronics_d_sccl_6/134-1887633-9887334</t>
         </is>
       </c>
     </row>
@@ -7940,7 +7898,7 @@
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>15%OFF UGG Slippers Australian Sheepskin Wool Warm House Slip On Scuff Women Men1,084,962.23 VNDADIDAS SCHUHE SPEZIALIST</t>
+          <t>Womens Mens UGG Mini Short Tall Classic Boots Chestnut Genuine Sheepskin Wool1,636,731.46 VNDADIDAS SCHUHE SPEZIALIST 42</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
@@ -7979,12 +7937,12 @@
       </c>
       <c r="K42" s="4" t="inlineStr">
         <is>
-          <t>Before/After Macro Skin Texture Zoom (Cận cảnh bề mặt da)</t>
+          <t>TikTok Made Me Buy It / Honest Review</t>
         </is>
       </c>
       <c r="L42" s="5" t="inlineStr">
         <is>
-          <t>https://www.ebay.com/itm/385963123229</t>
+          <t>https://www.ebay.com/itm/385738675527</t>
         </is>
       </c>
     </row>
@@ -7994,7 +7952,7 @@
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>red alert</t>
+          <t>erin napier</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
@@ -8004,17 +7962,17 @@
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>Pets &amp; Animals</t>
+          <t>General Trend</t>
         </is>
       </c>
       <c r="E43" s="3" t="n">
-        <v>65.40000000000001</v>
+        <v>63.2</v>
       </c>
       <c r="F43" s="3" t="n">
         <v>78</v>
       </c>
       <c r="G43" s="3" t="n">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="H43" s="3" t="inlineStr">
         <is>
@@ -8033,12 +7991,12 @@
       </c>
       <c r="K43" s="4" t="inlineStr">
         <is>
-          <t>Emotional Reaction &amp; Satisfying Fur Release ASMR</t>
+          <t>TikTok Made Me Buy It / Honest Review</t>
         </is>
       </c>
       <c r="L43" s="5" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?geo=US&amp;q=red%20alert</t>
+          <t>https://trends.google.com/trends/explore?geo=US&amp;q=erin%20napier</t>
         </is>
       </c>
     </row>
@@ -8048,7 +8006,7 @@
       </c>
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t>mlb wildcard standings</t>
+          <t>blake lively</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
@@ -8058,17 +8016,17 @@
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>Automotive &amp; Motorcycle</t>
+          <t>General Trend</t>
         </is>
       </c>
       <c r="E44" s="3" t="n">
-        <v>65.40000000000001</v>
+        <v>63.2</v>
       </c>
       <c r="F44" s="3" t="n">
         <v>78</v>
       </c>
       <c r="G44" s="3" t="n">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="H44" s="3" t="inlineStr">
         <is>
@@ -8092,7 +8050,7 @@
       </c>
       <c r="L44" s="5" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?geo=US&amp;q=mlb%20wildcard%20standings</t>
+          <t>https://trends.google.com/trends/explore?geo=US&amp;q=blake%20lively</t>
         </is>
       </c>
     </row>
@@ -8102,7 +8060,7 @@
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>pak vs eng</t>
+          <t>mitch mcconnell</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
@@ -8112,7 +8070,7 @@
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>General Trend</t>
+          <t>Fashion &amp; Apparel</t>
         </is>
       </c>
       <c r="E45" s="3" t="n">
@@ -8146,7 +8104,7 @@
       </c>
       <c r="L45" s="5" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?geo=US&amp;q=pak%20vs%20eng</t>
+          <t>https://trends.google.com/trends/explore?geo=US&amp;q=mitch%20mcconnell</t>
         </is>
       </c>
     </row>
@@ -8156,7 +8114,7 @@
       </c>
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t>michelle obama chanel us open</t>
+          <t>the falling man</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
@@ -8166,7 +8124,7 @@
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>Phones &amp; Electronics</t>
+          <t>Fashion &amp; Apparel</t>
         </is>
       </c>
       <c r="E46" s="3" t="n">
@@ -8195,12 +8153,12 @@
       </c>
       <c r="K46" s="4" t="inlineStr">
         <is>
-          <t>Side-by-side Live Demo &amp; Unboxing ASMR</t>
+          <t>TikTok Made Me Buy It / Honest Review</t>
         </is>
       </c>
       <c r="L46" s="5" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?geo=US&amp;q=michelle%20obama%20chanel%20us%20open</t>
+          <t>https://trends.google.com/trends/explore?geo=US&amp;q=the%20falling%20man</t>
         </is>
       </c>
     </row>
@@ -8210,7 +8168,7 @@
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>meghan</t>
+          <t>gas prices</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
@@ -8220,7 +8178,7 @@
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>Health &amp; Fitness</t>
+          <t>Fashion &amp; Apparel</t>
         </is>
       </c>
       <c r="E47" s="3" t="n">
@@ -8254,7 +8212,7 @@
       </c>
       <c r="L47" s="5" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?geo=US&amp;q=meghan</t>
+          <t>https://trends.google.com/trends/explore?geo=US&amp;q=gas%20prices</t>
         </is>
       </c>
     </row>
@@ -8264,7 +8222,7 @@
       </c>
       <c r="B48" s="4" t="inlineStr">
         <is>
-          <t>ukraine</t>
+          <t>weather today</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
@@ -8308,7 +8266,7 @@
       </c>
       <c r="L48" s="5" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?geo=US&amp;q=ukraine</t>
+          <t>https://trends.google.com/trends/explore?geo=US&amp;q=weather%20today</t>
         </is>
       </c>
     </row>
@@ -8318,7 +8276,7 @@
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>irish open 2026</t>
+          <t>spacex</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
@@ -8328,7 +8286,7 @@
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>Books, Magazines &amp; Audio</t>
+          <t>General Trend</t>
         </is>
       </c>
       <c r="E49" s="3" t="n">
@@ -8362,7 +8320,7 @@
       </c>
       <c r="L49" s="5" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?geo=US&amp;q=irish%20open%202026</t>
+          <t>https://trends.google.com/trends/explore?geo=US&amp;q=spacex</t>
         </is>
       </c>
     </row>
@@ -8372,7 +8330,7 @@
       </c>
       <c r="B50" s="4" t="inlineStr">
         <is>
-          <t>indianapolis weather</t>
+          <t>costco rationing oil</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
@@ -8382,7 +8340,7 @@
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>General Trend</t>
+          <t>Beauty &amp; Personal Care</t>
         </is>
       </c>
       <c r="E50" s="3" t="n">
@@ -8411,12 +8369,12 @@
       </c>
       <c r="K50" s="4" t="inlineStr">
         <is>
-          <t>TikTok Made Me Buy It / Honest Review</t>
+          <t>Before/After Macro Skin Texture Zoom (Cận cảnh bề mặt da)</t>
         </is>
       </c>
       <c r="L50" s="5" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?geo=US&amp;q=indianapolis%20weather</t>
+          <t>https://trends.google.com/trends/explore?geo=US&amp;q=costco%20rationing%20oil</t>
         </is>
       </c>
     </row>
@@ -8426,7 +8384,7 @@
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>adam levy</t>
+          <t>sharon horgan</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
@@ -8436,7 +8394,7 @@
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>Fashion &amp; Apparel</t>
+          <t>General Trend</t>
         </is>
       </c>
       <c r="E51" s="3" t="n">
@@ -8470,7 +8428,7 @@
       </c>
       <c r="L51" s="5" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?geo=US&amp;q=adam%20levy</t>
+          <t>https://trends.google.com/trends/explore?geo=US&amp;q=sharon%20horgan</t>
         </is>
       </c>
     </row>
@@ -8480,7 +8438,7 @@
       </c>
       <c r="B52" s="4" t="inlineStr">
         <is>
-          <t>jason bard yarmosky</t>
+          <t>the walking dead: dead city</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
@@ -8490,7 +8448,7 @@
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>Fashion &amp; Apparel</t>
+          <t>Gadgets &amp; Electronics</t>
         </is>
       </c>
       <c r="E52" s="3" t="n">
@@ -8524,7 +8482,7 @@
       </c>
       <c r="L52" s="5" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?geo=US&amp;q=jason%20bard%20yarmosky</t>
+          <t>https://trends.google.com/trends/explore?geo=US&amp;q=the%20walking%20dead%3A%20dead%20city</t>
         </is>
       </c>
     </row>
@@ -8588,7 +8546,7 @@
       </c>
       <c r="B54" s="4" t="inlineStr">
         <is>
-          <t>Spotlight DealCASIO WATCH CALCULATOR VINTAGE RETRO 80's CA-53W-1Z CA53 CA-53 AUSSIE SELLER838,137.46 VND1,470,465.00 VND</t>
+          <t>Spotlight DealGE ECG Leadwire Set 3 Lead Grabber AHA 51in REF 2106390-0021,538,461.54 VND</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
@@ -8627,12 +8585,12 @@
       </c>
       <c r="K54" s="4" t="inlineStr">
         <is>
-          <t>Side-by-side Live Demo &amp; Unboxing ASMR</t>
+          <t>TikTok Made Me Buy It / Honest Review</t>
         </is>
       </c>
       <c r="L54" s="5" t="inlineStr">
         <is>
-          <t>https://www.ebay.com/itm/370786315096</t>
+          <t>https://www.ebay.com/itm/178382893222</t>
         </is>
       </c>
     </row>
@@ -8642,7 +8600,7 @@
       </c>
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t>CASIO WATCH VINTAGE RETRO ORIGINAL F-91W-1 F91 F91W F-91 WARANTY666,169.38 VND734,772.69 VND | 9% offPrevious price: 734</t>
+          <t>CASIO WATCH CALCULATOR VINTAGE RETRO 80's CA-53W-1Z CA53 CA-53 AUSSIE SELLER838,137.46 VND1,470,465.00 VND Previous pric</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
@@ -8686,7 +8644,7 @@
       </c>
       <c r="L55" s="5" t="inlineStr">
         <is>
-          <t>https://www.ebay.com/itm/370816923572</t>
+          <t>https://www.ebay.com/itm/370786315096</t>
         </is>
       </c>
     </row>
@@ -8696,7 +8654,7 @@
       </c>
       <c r="B56" s="4" t="inlineStr">
         <is>
-          <t>Cisco SFP-H10GB-CU3M 37-0961-03 SFP+ 10G Passive DAC Twinax Cable NEW897,435.90 VND</t>
+          <t>NZG 1:18 Mercedes-Benz AMG G63 4x4² 2023 W463 Alloy Diecast Car Model6,641,025.64 VND9,025,641.03 VND Previous price: 9,</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
@@ -8706,7 +8664,7 @@
       </c>
       <c r="D56" s="4" t="inlineStr">
         <is>
-          <t>All Trending Deals</t>
+          <t>Automotive &amp; Motorcycle</t>
         </is>
       </c>
       <c r="E56" s="3" t="n">
@@ -8740,7 +8698,7 @@
       </c>
       <c r="L56" s="5" t="inlineStr">
         <is>
-          <t>https://www.ebay.com/itm/157632501279</t>
+          <t>https://www.ebay.com/itm/298638189628</t>
         </is>
       </c>
     </row>
@@ -8750,7 +8708,8 @@
       </c>
       <c r="B57" s="4" t="inlineStr">
         <is>
-          <t>NZG 1:18 Mercedes-Benz AMG G63 4x4² 2023 W463 Alloy Diecast Car Model6,641,025.64 VND9,025,641.03 VND Previous price: 9,</t>
+          <t>Apple iPhone 16 Pro - 1TB - All Colours21,127,615.38 VND34,657,692.31 VND Previous price: 34,657,692.31 VND 39% off
+eBay</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
@@ -8760,7 +8719,7 @@
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>Automotive &amp; Motorcycle</t>
+          <t>All Trending Deals</t>
         </is>
       </c>
       <c r="E57" s="3" t="n">
@@ -8794,7 +8753,7 @@
       </c>
       <c r="L57" s="5" t="inlineStr">
         <is>
-          <t>https://www.ebay.com/itm/298638189628</t>
+          <t>https://www.ebay.com/itm/297648174804</t>
         </is>
       </c>
     </row>
@@ -8804,8 +8763,7 @@
       </c>
       <c r="B58" s="4" t="inlineStr">
         <is>
-          <t>Apple iPhone 16 Pro Max All Colours26,609,000.00 VND
-eBay Refurbished</t>
+          <t>Apple iPhone 16 Pro - 128GB 256GB 512GB 1TB - All Colours - Unlocked - Good20,780,692.31 VNDeBay Refurbished</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
@@ -8849,7 +8807,7 @@
       </c>
       <c r="L58" s="5" t="inlineStr">
         <is>
-          <t>https://www.ebay.com/itm/257723314310</t>
+          <t>https://www.ebay.com/itm/257132422991</t>
         </is>
       </c>
     </row>
@@ -8859,7 +8817,7 @@
       </c>
       <c r="B59" s="4" t="inlineStr">
         <is>
-          <t>Apple iPhone 16 Pro - 1TB - All Colours21,821,461.54 VNDeBay Refurbished</t>
+          <t>Prada Bonnie large leather handbag Brown44,641,373.08 VNDAlmost gone</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
@@ -8898,12 +8856,12 @@
       </c>
       <c r="K59" s="4" t="inlineStr">
         <is>
-          <t>Emotional Reaction &amp; Satisfying Fur Release ASMR</t>
+          <t>TikTok Made Me Buy It / Honest Review</t>
         </is>
       </c>
       <c r="L59" s="5" t="inlineStr">
         <is>
-          <t>https://www.ebay.com/itm/257132401723</t>
+          <t>https://www.ebay.com/itm/206266648571</t>
         </is>
       </c>
     </row>
@@ -8913,7 +8871,7 @@
       </c>
       <c r="B60" s="4" t="inlineStr">
         <is>
-          <t>Apple iPhone 16 Pro Max - 256GB 512GB 1TB- All Colours - Good25,013,153.85 VNDeBay Refurbished</t>
+          <t>Giubbotto Blauer nero donna con brillantini2,370,549.23 VND</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
@@ -8952,12 +8910,12 @@
       </c>
       <c r="K60" s="4" t="inlineStr">
         <is>
-          <t>Emotional Reaction &amp; Satisfying Fur Release ASMR</t>
+          <t>TikTok Made Me Buy It / Honest Review</t>
         </is>
       </c>
       <c r="L60" s="5" t="inlineStr">
         <is>
-          <t>https://www.ebay.com/itm/298645175829</t>
+          <t>https://www.ebay.com/itm/306843251511</t>
         </is>
       </c>
     </row>
@@ -8967,7 +8925,7 @@
       </c>
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t>Lederweste Bikerweste Motorrad Kutte Biker Chopper Rockerweste mit Taschen2,679,971.42 VNDPremium Velour Fußmatten kompl</t>
+          <t>Birne 6000K H13 E-PRÜFZEICHEN 12V 60/55W E-Prüfzeichen XENON SUPER WHITE HALOGEN625,693.96 VNDLederweste Bikerweste Moto</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
@@ -9011,7 +8969,7 @@
       </c>
       <c r="L61" s="5" t="inlineStr">
         <is>
-          <t>https://www.ebay.com/itm/291771387455</t>
+          <t>https://www.ebay.com/itm/133242757435</t>
         </is>
       </c>
     </row>
@@ -9021,7 +8979,7 @@
       </c>
       <c r="B62" s="4" t="inlineStr">
         <is>
-          <t>Birne 6000K H13 E-PRÜFZEICHEN 12V 60/55W E-Prüfzeichen XENON SUPER WHITE HALOGEN625,693.96 VND</t>
+          <t>Premium Velour Fußmatten komplett für VW T6.1 California Coast Küche ab Bj.20208,037,829.62 VND</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
@@ -9065,7 +9023,7 @@
       </c>
       <c r="L62" s="5" t="inlineStr">
         <is>
-          <t>https://www.ebay.com/itm/133242757435</t>
+          <t>https://www.ebay.com/itm/124122083146</t>
         </is>
       </c>
     </row>
@@ -9075,7 +9033,7 @@
       </c>
       <c r="B63" s="4" t="inlineStr">
         <is>
-          <t>500 Abarth Orig Competizione 595 695 Braking Kit Bremsscheiben Kit Va 305x28mm11,286,911.54 VNDShop all 90Parts &amp; Access</t>
+          <t>Biker Kutte Lederkutte Lederweste Clubweste Rockerweste Herren Chopper Motorrad2,679,971.42 VNDShop all 91Parts &amp; Access</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
@@ -9085,7 +9043,7 @@
       </c>
       <c r="D63" s="4" t="inlineStr">
         <is>
-          <t>Pet Supplies</t>
+          <t>All Trending Deals</t>
         </is>
       </c>
       <c r="E63" s="3" t="n">
@@ -9114,12 +9072,12 @@
       </c>
       <c r="K63" s="4" t="inlineStr">
         <is>
-          <t>Emotional Reaction &amp; Satisfying Fur Release ASMR</t>
+          <t>TikTok Made Me Buy It / Honest Review</t>
         </is>
       </c>
       <c r="L63" s="5" t="inlineStr">
         <is>
-          <t>https://www.ebay.com/itm/285765031424</t>
+          <t>https://www.ebay.com/itm/302258284099</t>
         </is>
       </c>
     </row>
@@ -9129,7 +9087,7 @@
       </c>
       <c r="B64" s="4" t="inlineStr">
         <is>
-          <t>CASIO WATCH SWIMMING 100 METRES WATER RESISTANT W-800 W-800H-1AV W8001,025,371.15 VND1,102,618.85 VND | 7% offPrevious p</t>
+          <t>CASIO CALCULATOR WATCH CA53, CA-53, CA-53WB,CA53WF VINTAGE RETRO UNISEX DATABANK785,903.31 VND845,126.54 VND | 7% offPre</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
@@ -9173,7 +9131,7 @@
       </c>
       <c r="L64" s="5" t="inlineStr">
         <is>
-          <t>https://www.ebay.com/itm/371175182923</t>
+          <t>https://www.ebay.com/itm/284719252501</t>
         </is>
       </c>
     </row>
@@ -9183,7 +9141,7 @@
       </c>
       <c r="B65" s="4" t="inlineStr">
         <is>
-          <t>YHG Wetsuit 3mm Neoprene Diving Tops Pants Men Women Swim Surfing Snorkeling AU735,508.38 VND</t>
+          <t>Graphite Crucible for Induction Melting Furnace735,508.38 VND</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
@@ -9193,7 +9151,7 @@
       </c>
       <c r="D65" s="4" t="inlineStr">
         <is>
-          <t>Kitchenware</t>
+          <t>All Trending Deals</t>
         </is>
       </c>
       <c r="E65" s="3" t="n">
@@ -9222,12 +9180,12 @@
       </c>
       <c r="K65" s="4" t="inlineStr">
         <is>
-          <t>TikTok Made Me Buy It / Honest Review</t>
+          <t>Emotional Reaction &amp; Satisfying Fur Release ASMR</t>
         </is>
       </c>
       <c r="L65" s="5" t="inlineStr">
         <is>
-          <t>https://www.ebay.com/itm/157344373567</t>
+          <t>https://www.ebay.com/itm/187799864164</t>
         </is>
       </c>
     </row>
@@ -9237,7 +9195,7 @@
       </c>
       <c r="B66" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">True Temper Dynamic Gold TOUR ISSUE Limited Edition USA Golf Iron Shaft .355 Tip923,076.92 VND1,153,846.15 VND Previous </t>
+          <t>28" 30" 31" Carbon Arrows 4" Feather SP500 Archery Recurve Compound Bow Hunting691,366.85 VND735,508.38 VND | 6% offPrev</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
@@ -9247,7 +9205,7 @@
       </c>
       <c r="D66" s="4" t="inlineStr">
         <is>
-          <t>Phones &amp; Electronics</t>
+          <t>Automotive &amp; Motorcycle</t>
         </is>
       </c>
       <c r="E66" s="3" t="n">
@@ -9276,12 +9234,12 @@
       </c>
       <c r="K66" s="4" t="inlineStr">
         <is>
-          <t>Side-by-side Live Demo &amp; Unboxing ASMR</t>
+          <t>TikTok Made Me Buy It / Honest Review</t>
         </is>
       </c>
       <c r="L66" s="5" t="inlineStr">
         <is>
-          <t>https://www.ebay.com/itm/186144334386</t>
+          <t>https://www.ebay.com/itm/267490959027</t>
         </is>
       </c>
     </row>
@@ -9291,7 +9249,7 @@
       </c>
       <c r="B67" s="4" t="inlineStr">
         <is>
-          <t>Veto Pro Pac MP3 EVO Tool Pouch EVO System Electrician Networking Technician3,203,846.15 VND24x Kerzen 80x40mm/8x4cm 1.W</t>
+          <t>Veto Pro Pac MP3 EVO Tool Pouch EVO System Electrician Networking Technician3,203,846.15 VNDBankerlampe Tischleuchte Bür</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
@@ -9345,7 +9303,7 @@
       </c>
       <c r="B68" s="4" t="inlineStr">
         <is>
-          <t>Bankerlampe Tischleuchte Bürolampe Jugendstil Schreibtischlampe weiss silber neu2,024,794.50 VND</t>
+          <t>24x Kerzen 80x40mm/8x4cm 1.Wahl Qualität / Kerzen Wiedemann / neue Farben 2025935,711.77 VND</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
@@ -9389,7 +9347,7 @@
       </c>
       <c r="L68" s="5" t="inlineStr">
         <is>
-          <t>https://www.ebay.com/itm/194675348414</t>
+          <t>https://www.ebay.com/itm/351764643068</t>
         </is>
       </c>
     </row>
@@ -9399,7 +9357,7 @@
       </c>
       <c r="B69" s="4" t="inlineStr">
         <is>
-          <t>3 Paar Zedernholzsohlen - Zedernsohlen - Einlegesohlen aus Holz890,445.00 VNDAlmost goneShop all 88Home &amp; Garden</t>
+          <t>Tischglocke Christkindl Klang Messing Weihnachtsglocke Handglocke Dekoration601,273.73 VNDShop all 88Home &amp; Garden</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
@@ -9443,7 +9401,7 @@
       </c>
       <c r="L69" s="5" t="inlineStr">
         <is>
-          <t>https://www.ebay.com/itm/276726430861</t>
+          <t>https://www.ebay.com/itm/284215623617</t>
         </is>
       </c>
     </row>
@@ -10209,7 +10167,7 @@
       </c>
       <c r="B84" s="4" t="inlineStr">
         <is>
-          <t>JK-B2A8S20P Smart BMS 4-8S 200A Active Balance 2A BMS LiFePo4 Li-ion LTO Battery1,766,923.08 VND1,920,512.82 VND | 8% of</t>
+          <t>Für Xiaomi Redmi Pad Pro 12.1 Kontrast Robot Silikon Hybrid Hülle Blau / Schwarz713,249.42 VNDAlmost goneLeder Tablet Co</t>
         </is>
       </c>
       <c r="C84" s="4" t="inlineStr">
@@ -10253,7 +10211,7 @@
       </c>
       <c r="L84" s="5" t="inlineStr">
         <is>
-          <t>https://www.ebay.com/itm/236864278279</t>
+          <t>https://www.ebay.com/itm/176622603332</t>
         </is>
       </c>
     </row>
@@ -10263,7 +10221,7 @@
       </c>
       <c r="B85" s="4" t="inlineStr">
         <is>
-          <t>ORIGINAL SONY Fernbedienung RMT-TX102D KDL40R45XC KDL40R55XC KDL40R550C NEUWARE652,198.85 VND</t>
+          <t>Leder Tablet Cover Samsung Galaxy Tab S7 FE SM-T733/T736 Stand Case Schutzhülle676,619.08 VND</t>
         </is>
       </c>
       <c r="C85" s="4" t="inlineStr">
@@ -10307,7 +10265,7 @@
       </c>
       <c r="L85" s="5" t="inlineStr">
         <is>
-          <t>https://www.ebay.com/itm/373982552937</t>
+          <t>https://www.ebay.com/itm/304338719356</t>
         </is>
       </c>
     </row>
@@ -10317,7 +10275,7 @@
       </c>
       <c r="B86" s="4" t="inlineStr">
         <is>
-          <t>Für Xiaomi Redmi Pad Pro 12.1 Kontrast Robot Silikon Hybrid Hülle Blau / Schwarz713,249.42 VNDAlmost goneLeder Tablet Co</t>
+          <t>Premium Leder Cover Apple iPad Pro 12.9"  2015-17 Tablet Schutzhülle Case Tasche729,033.23 VND828,501.00 VND | 12% offPr</t>
         </is>
       </c>
       <c r="C86" s="4" t="inlineStr">
@@ -10361,7 +10319,7 @@
       </c>
       <c r="L86" s="5" t="inlineStr">
         <is>
-          <t>https://www.ebay.com/itm/176622603332</t>
+          <t>https://www.ebay.com/itm/234304242705</t>
         </is>
       </c>
     </row>
@@ -10371,7 +10329,7 @@
       </c>
       <c r="B87" s="4" t="inlineStr">
         <is>
-          <t>Leder Tablet Cover Samsung Galaxy Tab S7 FE SM-T733/T736 Stand Case Schutzhülle676,619.08 VND</t>
+          <t>Cisco SFP-H10GB-CU3M 37-0961-03 SFP+ 10G Passive DAC Twinax Cable NEW897,435.90 VNDMcAfee Total Protection - 5 Devices -</t>
         </is>
       </c>
       <c r="C87" s="4" t="inlineStr">
@@ -10415,7 +10373,7 @@
       </c>
       <c r="L87" s="5" t="inlineStr">
         <is>
-          <t>https://www.ebay.com/itm/304338719356</t>
+          <t>https://www.ebay.com/itm/157632501279</t>
         </is>
       </c>
     </row>
@@ -10425,7 +10383,7 @@
       </c>
       <c r="B88" s="4" t="inlineStr">
         <is>
-          <t>Premium Leder Cover Apple iPad Pro 12.9"  2015-17 Tablet Schutzhülle Case Tasche729,033.23 VND828,501.00 VND | 12% offPr</t>
+          <t>Display für Samsung A53 5G A536 OLED AMOLED LCD Bildschirm Touch Screen + Kleber1,188,252.69 VND</t>
         </is>
       </c>
       <c r="C88" s="4" t="inlineStr">
@@ -10469,7 +10427,7 @@
       </c>
       <c r="L88" s="5" t="inlineStr">
         <is>
-          <t>https://www.ebay.com/itm/234304242705</t>
+          <t>https://www.ebay.com/itm/305041451782</t>
         </is>
       </c>
     </row>
@@ -10479,7 +10437,7 @@
       </c>
       <c r="B89" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Display für Samsung A53 5G A536 OLED AMOLED LCD Bildschirm Touch Screen + Kleber1,188,252.69 VNDDisplay für Samsung A53 </t>
+          <t xml:space="preserve">Display für Samsung A53 5G A536B 2022 HD LCD Bildschirm Touch Screen + Rahmen1,069,129.62 VNDAlmost goneShop all 50More </t>
         </is>
       </c>
       <c r="C89" s="4" t="inlineStr">
@@ -10489,7 +10447,7 @@
       </c>
       <c r="D89" s="4" t="inlineStr">
         <is>
-          <t>Tech &amp; Gadgets</t>
+          <t>Menswear &amp; Underwear</t>
         </is>
       </c>
       <c r="E89" s="3" t="n">
@@ -10523,7 +10481,7 @@
       </c>
       <c r="L89" s="5" t="inlineStr">
         <is>
-          <t>https://www.ebay.com/itm/305041451782</t>
+          <t>https://www.ebay.com/itm/295846639825</t>
         </is>
       </c>
     </row>
@@ -10533,7 +10491,7 @@
       </c>
       <c r="B90" s="4" t="inlineStr">
         <is>
-          <t>Display für Samsung A51 A515F HD LCD Touch Screen Glas + Kleber &amp; Tools Neu741,541.15 VND</t>
+          <t>2 1/2ct Black Diamond Screw Back Studs Womens Earrings 14K White Gold8,546,666.67 VND26,805,641.03 VND Previous price: 2</t>
         </is>
       </c>
       <c r="C90" s="4" t="inlineStr">
@@ -10543,7 +10501,7 @@
       </c>
       <c r="D90" s="4" t="inlineStr">
         <is>
-          <t>Tech &amp; Gadgets</t>
+          <t>Jewelry Accessories &amp; Derivatives</t>
         </is>
       </c>
       <c r="E90" s="3" t="n">
@@ -10577,7 +10535,7 @@
       </c>
       <c r="L90" s="5" t="inlineStr">
         <is>
-          <t>https://www.ebay.com/itm/305047092563</t>
+          <t>https://www.ebay.com/itm/355504570491</t>
         </is>
       </c>
     </row>
@@ -10587,7 +10545,7 @@
       </c>
       <c r="B91" s="4" t="inlineStr">
         <is>
-          <t>Display Für Samsung A55 / A556 5G OLED Bildschirm LCD mit  Rahmen + Tools Neu1,932,771.92 VNDShop all 48More Computer Ac</t>
+          <t>1/4 - 2 Ct T.W. Natural Diamond Solitaire Pendant in 14k White or Yellow Gold4,358,717.95 VND</t>
         </is>
       </c>
       <c r="C91" s="4" t="inlineStr">
@@ -10597,7 +10555,7 @@
       </c>
       <c r="D91" s="4" t="inlineStr">
         <is>
-          <t>Menswear &amp; Underwear</t>
+          <t>Books, Magazines &amp; Audio</t>
         </is>
       </c>
       <c r="E91" s="3" t="n">
@@ -10631,7 +10589,7 @@
       </c>
       <c r="L91" s="5" t="inlineStr">
         <is>
-          <t>https://www.ebay.com/itm/306193635449</t>
+          <t>https://www.ebay.com/itm/353815614085</t>
         </is>
       </c>
     </row>
@@ -10641,7 +10599,7 @@
       </c>
       <c r="B92" s="4" t="inlineStr">
         <is>
-          <t>2 1/2ct Black Diamond Screw Back Studs Womens Earrings 14K White Gold8,546,666.67 VND26,805,641.03 VND Previous price: 2</t>
+          <t>925 Sterlingsilber Silber Anhänger DAVIDSTERN Hexagramm Charm Kette 20x20mm 50661,780,592.19 VNDAlmost goneShop all 22Fi</t>
         </is>
       </c>
       <c r="C92" s="4" t="inlineStr">
@@ -10651,7 +10609,7 @@
       </c>
       <c r="D92" s="4" t="inlineStr">
         <is>
-          <t>Jewelry Accessories &amp; Derivatives</t>
+          <t>Fashion &amp; Apparel</t>
         </is>
       </c>
       <c r="E92" s="3" t="n">
@@ -10685,7 +10643,7 @@
       </c>
       <c r="L92" s="5" t="inlineStr">
         <is>
-          <t>https://www.ebay.com/itm/355504570491</t>
+          <t>https://www.ebay.com/itm/271569399778</t>
         </is>
       </c>
     </row>
@@ -10695,7 +10653,7 @@
       </c>
       <c r="B93" s="4" t="inlineStr">
         <is>
-          <t>1/4 - 2 Ct T.W. Natural Diamond Solitaire Pendant in 14k White or Yellow Gold4,358,717.95 VND</t>
+          <t>Panzerkette 4 mm Halskette Echt 750er Gold 18Karat vergoldet Damen Herren K1808906,824.42 VND</t>
         </is>
       </c>
       <c r="C93" s="4" t="inlineStr">
@@ -10705,7 +10663,7 @@
       </c>
       <c r="D93" s="4" t="inlineStr">
         <is>
-          <t>Books, Magazines &amp; Audio</t>
+          <t>Kitchenware</t>
         </is>
       </c>
       <c r="E93" s="3" t="n">
@@ -10739,7 +10697,7 @@
       </c>
       <c r="L93" s="5" t="inlineStr">
         <is>
-          <t>https://www.ebay.com/itm/353815614085</t>
+          <t>https://www.ebay.com/itm/125770552175</t>
         </is>
       </c>
     </row>
@@ -10749,7 +10707,7 @@
       </c>
       <c r="B94" s="4" t="inlineStr">
         <is>
-          <t>925 Sterlingsilber Silber Anhänger DAVIDSTERN Hexagramm Charm Kette 20x20mm 50661,780,592.19 VNDAlmost goneShop all 22Fi</t>
+          <t>Set Damenkette Schlüssel Anhänger Zirkonia weiß 750 Gold 18Karat vergoldet A1127595,615.38 VNDAlmost goneHerz Anhänger K</t>
         </is>
       </c>
       <c r="C94" s="4" t="inlineStr">
@@ -10759,7 +10717,7 @@
       </c>
       <c r="D94" s="4" t="inlineStr">
         <is>
-          <t>Fashion &amp; Apparel</t>
+          <t>Menswear &amp; Underwear</t>
         </is>
       </c>
       <c r="E94" s="3" t="n">
@@ -10793,7 +10751,7 @@
       </c>
       <c r="L94" s="5" t="inlineStr">
         <is>
-          <t>https://www.ebay.com/itm/271569399778</t>
+          <t>https://www.ebay.com/itm/125770529088</t>
         </is>
       </c>
     </row>
@@ -10803,7 +10761,7 @@
       </c>
       <c r="B95" s="4" t="inlineStr">
         <is>
-          <t>Panzerkette 4 mm Halskette Echt 750er Gold 18Karat vergoldet Damen Herren K1808906,824.42 VND</t>
+          <t>Löwenzahn Kapseln mit 500 mg 10:1 Wurzelextrakt - vegan - Vitamineule744,221.42 VNDFree shippingBrokkoli Sulforaphan Kap</t>
         </is>
       </c>
       <c r="C95" s="4" t="inlineStr">
@@ -10813,7 +10771,7 @@
       </c>
       <c r="D95" s="4" t="inlineStr">
         <is>
-          <t>Kitchenware</t>
+          <t>Health</t>
         </is>
       </c>
       <c r="E95" s="3" t="n">
@@ -10847,7 +10805,7 @@
       </c>
       <c r="L95" s="5" t="inlineStr">
         <is>
-          <t>https://www.ebay.com/itm/125770552175</t>
+          <t>https://www.ebay.com/itm/125306609308</t>
         </is>
       </c>
     </row>
@@ -10857,7 +10815,7 @@
       </c>
       <c r="B96" s="4" t="inlineStr">
         <is>
-          <t>Set Damenkette Schlüssel Anhänger Zirkonia weiß 750 Gold 18Karat vergoldet A1127595,615.38 VNDAlmost goneHerz Anhänger K</t>
+          <t>Curcuma Extrakt Kapseln - hochdosiert - 350 mg Curcuminoide - Vitamineule744,221.42 VNDFree shipping</t>
         </is>
       </c>
       <c r="C96" s="4" t="inlineStr">
@@ -10867,7 +10825,7 @@
       </c>
       <c r="D96" s="4" t="inlineStr">
         <is>
-          <t>Menswear &amp; Underwear</t>
+          <t>Health</t>
         </is>
       </c>
       <c r="E96" s="3" t="n">
@@ -10901,7 +10859,7 @@
       </c>
       <c r="L96" s="5" t="inlineStr">
         <is>
-          <t>https://www.ebay.com/itm/125770529088</t>
+          <t>https://www.ebay.com/itm/123839173201</t>
         </is>
       </c>
     </row>
@@ -10911,7 +10869,7 @@
       </c>
       <c r="B97" s="4" t="inlineStr">
         <is>
-          <t>300mg Benfotiamine 3 x 120 Capsules Fat Soluble Thiamine Vitamin B1 Supplement991,345.38 VNDFree shippingLöwenzahn Kapse</t>
+          <t>Jod Kapseln aus Bio Kelp / Tabletten - 400µg aus Bio Kelp Extrakt - Vitamineule774,002.19 VNDFree shippingShop all 30Bea</t>
         </is>
       </c>
       <c r="C97" s="4" t="inlineStr">
@@ -10921,7 +10879,7 @@
       </c>
       <c r="D97" s="4" t="inlineStr">
         <is>
-          <t>Menswear &amp; Underwear</t>
+          <t>Health</t>
         </is>
       </c>
       <c r="E97" s="3" t="n">
@@ -10955,7 +10913,7 @@
       </c>
       <c r="L97" s="5" t="inlineStr">
         <is>
-          <t>https://www.ebay.com/itm/357242424467</t>
+          <t>https://www.ebay.com/itm/124078773818</t>
         </is>
       </c>
     </row>
@@ -10965,7 +10923,7 @@
       </c>
       <c r="B98" s="4" t="inlineStr">
         <is>
-          <t>Curcuma Extrakt Kapseln - hochdosiert - 350 mg Curcuminoide - Vitamineule744,221.42 VNDFree shipping</t>
+          <t>Lonsdale Navy Blue Baseball Cap Hat Embroidered Logo Adjustable Kappe Mütze741,541.15 VND</t>
         </is>
       </c>
       <c r="C98" s="4" t="inlineStr">
@@ -10975,7 +10933,7 @@
       </c>
       <c r="D98" s="4" t="inlineStr">
         <is>
-          <t>Health</t>
+          <t>Fashion &amp; Apparel</t>
         </is>
       </c>
       <c r="E98" s="3" t="n">
@@ -11009,7 +10967,7 @@
       </c>
       <c r="L98" s="5" t="inlineStr">
         <is>
-          <t>https://www.ebay.com/itm/123839173201</t>
+          <t>https://www.ebay.com/itm/296106350225</t>
         </is>
       </c>
     </row>
@@ -11019,7 +10977,7 @@
       </c>
       <c r="B99" s="4" t="inlineStr">
         <is>
-          <t>Jod Kapseln aus Bio Kelp / Tabletten - 400µg aus Bio Kelp Extrakt - Vitamineule774,002.19 VNDFree shippingShop all 31Bea</t>
+          <t>Puma Speedcat OG team royal white Schuhe Sneaker Motorsport F1 398846-183,275,586.81 VNDShop all 12Men's Shoes &amp; Accesso</t>
         </is>
       </c>
       <c r="C99" s="4" t="inlineStr">
@@ -11029,7 +10987,7 @@
       </c>
       <c r="D99" s="4" t="inlineStr">
         <is>
-          <t>Health</t>
+          <t>Pet Supplies</t>
         </is>
       </c>
       <c r="E99" s="3" t="n">
@@ -11058,12 +11016,12 @@
       </c>
       <c r="K99" s="4" t="inlineStr">
         <is>
-          <t>TikTok Made Me Buy It / Honest Review</t>
+          <t>Emotional Reaction &amp; Satisfying Fur Release ASMR</t>
         </is>
       </c>
       <c r="L99" s="5" t="inlineStr">
         <is>
-          <t>https://www.ebay.com/itm/124078773818</t>
+          <t>https://www.ebay.com/itm/156805882161</t>
         </is>
       </c>
     </row>
@@ -11073,7 +11031,7 @@
       </c>
       <c r="B100" s="4" t="inlineStr">
         <is>
-          <t>Lonsdale Navy Blue Baseball Cap Hat Embroidered Logo Adjustable Kappe Mütze741,541.15 VND</t>
+          <t>Lederweste Bikerweste Motorrad Kutte Biker Chopper Rockerweste mit Taschen2,679,971.42 VNDBiker Kutte Lederkutte Lederwe</t>
         </is>
       </c>
       <c r="C100" s="4" t="inlineStr">
@@ -11117,7 +11075,7 @@
       </c>
       <c r="L100" s="5" t="inlineStr">
         <is>
-          <t>https://www.ebay.com/itm/296106350225</t>
+          <t>https://www.ebay.com/itm/291771387455</t>
         </is>
       </c>
     </row>
@@ -11127,7 +11085,7 @@
       </c>
       <c r="B101" s="4" t="inlineStr">
         <is>
-          <t>Puma Speedcat OG team royal white Schuhe Sneaker Motorsport F1 398846-183,275,586.81 VNDShop all 12Men's Shoes &amp; Accesso</t>
+          <t>Schwarze Lederkutte mit blau Umrandungen Kutte Biker Motorrad Rocker Clubweste2,679,971.42 VND</t>
         </is>
       </c>
       <c r="C101" s="4" t="inlineStr">
@@ -11137,7 +11095,7 @@
       </c>
       <c r="D101" s="4" t="inlineStr">
         <is>
-          <t>Pet Supplies</t>
+          <t>Fashion &amp; Apparel</t>
         </is>
       </c>
       <c r="E101" s="3" t="n">
@@ -11166,12 +11124,12 @@
       </c>
       <c r="K101" s="4" t="inlineStr">
         <is>
-          <t>Emotional Reaction &amp; Satisfying Fur Release ASMR</t>
+          <t>TikTok Made Me Buy It / Honest Review</t>
         </is>
       </c>
       <c r="L101" s="5" t="inlineStr">
         <is>
-          <t>https://www.ebay.com/itm/156805882161</t>
+          <t>https://www.ebay.com/itm/301897675077</t>
         </is>
       </c>
     </row>
@@ -11181,7 +11139,7 @@
       </c>
       <c r="B102" s="4" t="inlineStr">
         <is>
-          <t>Biker Kutte Lederkutte Lederweste Clubweste Rockerweste Herren Chopper Motorrad2,679,971.42 VND</t>
+          <t>Bikerweste Lederweste Rockerweste Lederkutte Kutte Chopperweste Clubweste2,382,163.73 VNDShop all 67Men's Clothing</t>
         </is>
       </c>
       <c r="C102" s="4" t="inlineStr">
@@ -11191,7 +11149,7 @@
       </c>
       <c r="D102" s="4" t="inlineStr">
         <is>
-          <t>Fashion &amp; Apparel</t>
+          <t>Menswear &amp; Underwear</t>
         </is>
       </c>
       <c r="E102" s="3" t="n">
@@ -11225,7 +11183,7 @@
       </c>
       <c r="L102" s="5" t="inlineStr">
         <is>
-          <t>https://www.ebay.com/itm/302258284099</t>
+          <t>https://www.ebay.com/itm/303349551958</t>
         </is>
       </c>
     </row>
@@ -11235,7 +11193,7 @@
       </c>
       <c r="B103" s="4" t="inlineStr">
         <is>
-          <t>Schwarze Lederkutte mit blau Umrandungen Kutte Biker Motorrad Rocker Clubweste2,679,971.42 VNDShop all 68Men's Clothing</t>
+          <t>Unterbrustkorsett Rot Lack Corsage tolles Taillen training PVC Underbust Corsets1,980,421.15 VND2,084,653.85 VND | 5% of</t>
         </is>
       </c>
       <c r="C103" s="4" t="inlineStr">
@@ -11245,7 +11203,7 @@
       </c>
       <c r="D103" s="4" t="inlineStr">
         <is>
-          <t>Menswear &amp; Underwear</t>
+          <t>Fashion &amp; Apparel</t>
         </is>
       </c>
       <c r="E103" s="3" t="n">
@@ -11279,7 +11237,7 @@
       </c>
       <c r="L103" s="5" t="inlineStr">
         <is>
-          <t>https://www.ebay.com/itm/301897675077</t>
+          <t>https://www.ebay.com/itm/363166536187</t>
         </is>
       </c>
     </row>
@@ -11289,7 +11247,7 @@
       </c>
       <c r="B104" s="4" t="inlineStr">
         <is>
-          <t>Unterbrustkorsett Schwarz Leder Corsage Gothic Korsett Underbust Leather Corsets2,178,463.27 VND2,293,119.23 VND | 5% of</t>
+          <t>Leder Taillenkorsett Schwarz Schnür Gothic Damen | Leather Waist Corset1,980,421.15 VND2,084,653.85 VND | 5% offPrevious</t>
         </is>
       </c>
       <c r="C104" s="4" t="inlineStr">
@@ -11299,7 +11257,7 @@
       </c>
       <c r="D104" s="4" t="inlineStr">
         <is>
-          <t>Fashion &amp; Apparel</t>
+          <t>Menswear &amp; Underwear</t>
         </is>
       </c>
       <c r="E104" s="3" t="n">
@@ -11333,7 +11291,7 @@
       </c>
       <c r="L104" s="5" t="inlineStr">
         <is>
-          <t>https://www.ebay.com/itm/362632687305</t>
+          <t>https://www.ebay.com/itm/364907426887</t>
         </is>
       </c>
     </row>
@@ -11343,7 +11301,7 @@
       </c>
       <c r="B105" s="4" t="inlineStr">
         <is>
-          <t>Satin Vollbrustkorsett Schnürkorsett Korsett Mieder Corset Corsage Schwarz LANG2,084,653.85 VND</t>
+          <t>Unterbrustkorsett Schwarz Baumwolle Corsage Underbust  Wider Hips Corset Hi-441,935,750.00 VNDShop all 35Women's Clothin</t>
         </is>
       </c>
       <c r="C105" s="4" t="inlineStr">
@@ -11353,7 +11311,7 @@
       </c>
       <c r="D105" s="4" t="inlineStr">
         <is>
-          <t>Fashion &amp; Apparel</t>
+          <t>Menswear &amp; Underwear</t>
         </is>
       </c>
       <c r="E105" s="3" t="n">
@@ -11387,7 +11345,7 @@
       </c>
       <c r="L105" s="5" t="inlineStr">
         <is>
-          <t>https://www.ebay.com/itm/362636865751</t>
+          <t>https://www.ebay.com/itm/362618056873</t>
         </is>
       </c>
     </row>
@@ -11397,7 +11355,7 @@
       </c>
       <c r="B106" s="4" t="inlineStr">
         <is>
-          <t>Unterbrustkorsett Rot Lack Corsage tolles Taillen training PVC Underbust Corsets1,980,421.15 VND2,084,653.85 VND | 5% of</t>
+          <t>Breitling TransOcean Chrono Quartz 40mm Iced 13ct Diamond Black Dial A530401166,641,025.64 VNDAlmost gone</t>
         </is>
       </c>
       <c r="C106" s="4" t="inlineStr">
@@ -11441,7 +11399,7 @@
       </c>
       <c r="L106" s="5" t="inlineStr">
         <is>
-          <t>https://www.ebay.com/itm/363166536187</t>
+          <t>https://www.ebay.com/itm/146360754668</t>
         </is>
       </c>
     </row>
@@ -11451,51 +11409,51 @@
       </c>
       <c r="B107" s="4" t="inlineStr">
         <is>
-          <t>New Omega Seamaster Diver 300M Automatic Green Men's Watch 210.90.42.20.10.001266,769,230.77 VND320,512,820.51 VND Previ</t>
+          <t>Custom Name Birth Flower Bar Necklace &amp; Personalized Jewelry</t>
         </is>
       </c>
       <c r="C107" s="4" t="inlineStr">
         <is>
-          <t>🔥 Xu Hướng Tăng Trưởng</t>
+          <t>🌲 Evergreen Bền Vững</t>
         </is>
       </c>
       <c r="D107" s="4" t="inlineStr">
         <is>
-          <t>Menswear &amp; Underwear</t>
+          <t>Jewelry Accessories &amp; Derivatives</t>
         </is>
       </c>
       <c r="E107" s="3" t="n">
-        <v>74.2</v>
+        <v>74.8</v>
       </c>
       <c r="F107" s="3" t="n">
-        <v>76</v>
+        <v>50</v>
       </c>
       <c r="G107" s="3" t="n">
-        <v>72</v>
+        <v>94</v>
       </c>
       <c r="H107" s="3" t="inlineStr">
         <is>
-          <t>$19.99</t>
+          <t>$24.00 - $38.00</t>
         </is>
       </c>
       <c r="I107" s="4" t="inlineStr">
         <is>
-          <t>eBay US</t>
+          <t>Etsy US Trending</t>
         </is>
       </c>
       <c r="J107" s="4" t="inlineStr">
         <is>
-          <t>eBay US Deals</t>
+          <t>Etsy US, Handmade/POD, TikTok Gift Trend</t>
         </is>
       </c>
       <c r="K107" s="4" t="inlineStr">
         <is>
-          <t>Side-by-side Live Demo &amp; Unboxing ASMR</t>
+          <t>Behind The Scenes Crafting &amp; Emotional Gift Unboxing</t>
         </is>
       </c>
       <c r="L107" s="5" t="inlineStr">
         <is>
-          <t>https://www.ebay.com/itm/357622544308</t>
+          <t>https://www.etsy.com/market/birth_flower_necklace</t>
         </is>
       </c>
     </row>
@@ -11505,7 +11463,7 @@
       </c>
       <c r="B108" s="4" t="inlineStr">
         <is>
-          <t>Custom Name Birth Flower Bar Necklace &amp; Personalized Jewelry</t>
+          <t>Personalized Wooden Docking Station &amp; Desk Organizer for Men</t>
         </is>
       </c>
       <c r="C108" s="4" t="inlineStr">
@@ -11515,7 +11473,7 @@
       </c>
       <c r="D108" s="4" t="inlineStr">
         <is>
-          <t>Jewelry Accessories &amp; Derivatives</t>
+          <t>Menswear &amp; Underwear</t>
         </is>
       </c>
       <c r="E108" s="3" t="n">
@@ -11529,7 +11487,7 @@
       </c>
       <c r="H108" s="3" t="inlineStr">
         <is>
-          <t>$24.00 - $38.00</t>
+          <t>$29.50 - $45.00</t>
         </is>
       </c>
       <c r="I108" s="4" t="inlineStr">
@@ -11549,7 +11507,7 @@
       </c>
       <c r="L108" s="5" t="inlineStr">
         <is>
-          <t>https://www.etsy.com/market/birth_flower_necklace</t>
+          <t>https://www.etsy.com/market/wooden_docking_station</t>
         </is>
       </c>
     </row>
@@ -11559,7 +11517,7 @@
       </c>
       <c r="B109" s="4" t="inlineStr">
         <is>
-          <t>Personalized Wooden Docking Station &amp; Desk Organizer for Men</t>
+          <t>Minimalist Custom Acrylic Wall Calendar &amp; Family Command Center</t>
         </is>
       </c>
       <c r="C109" s="4" t="inlineStr">
@@ -11569,7 +11527,7 @@
       </c>
       <c r="D109" s="4" t="inlineStr">
         <is>
-          <t>Menswear &amp; Underwear</t>
+          <t>Home Supplies</t>
         </is>
       </c>
       <c r="E109" s="3" t="n">
@@ -11583,7 +11541,7 @@
       </c>
       <c r="H109" s="3" t="inlineStr">
         <is>
-          <t>$29.50 - $45.00</t>
+          <t>$39.00 - $69.00</t>
         </is>
       </c>
       <c r="I109" s="4" t="inlineStr">
@@ -11603,7 +11561,7 @@
       </c>
       <c r="L109" s="5" t="inlineStr">
         <is>
-          <t>https://www.etsy.com/market/wooden_docking_station</t>
+          <t>https://www.etsy.com/market/acrylic_calendar</t>
         </is>
       </c>
     </row>
@@ -11613,7 +11571,7 @@
       </c>
       <c r="B110" s="4" t="inlineStr">
         <is>
-          <t>Minimalist Custom Acrylic Wall Calendar &amp; Family Command Center</t>
+          <t>Engraved Olive Wood Cutting Board &amp; Charcuterie Serving Platter</t>
         </is>
       </c>
       <c r="C110" s="4" t="inlineStr">
@@ -11623,7 +11581,7 @@
       </c>
       <c r="D110" s="4" t="inlineStr">
         <is>
-          <t>Home Supplies</t>
+          <t>Kitchenware</t>
         </is>
       </c>
       <c r="E110" s="3" t="n">
@@ -11637,7 +11595,7 @@
       </c>
       <c r="H110" s="3" t="inlineStr">
         <is>
-          <t>$39.00 - $69.00</t>
+          <t>$32.00 - $55.00</t>
         </is>
       </c>
       <c r="I110" s="4" t="inlineStr">
@@ -11657,7 +11615,7 @@
       </c>
       <c r="L110" s="5" t="inlineStr">
         <is>
-          <t>https://www.etsy.com/market/acrylic_calendar</t>
+          <t>https://www.etsy.com/market/personalized_cutting_board</t>
         </is>
       </c>
     </row>
@@ -11667,7 +11625,7 @@
       </c>
       <c r="B111" s="4" t="inlineStr">
         <is>
-          <t>Engraved Olive Wood Cutting Board &amp; Charcuterie Serving Platter</t>
+          <t>Custom Pet Portrait Sweatshirt &amp; Embroidered Dog Mom Hoodie</t>
         </is>
       </c>
       <c r="C111" s="4" t="inlineStr">
@@ -11677,11 +11635,11 @@
       </c>
       <c r="D111" s="4" t="inlineStr">
         <is>
-          <t>Kitchenware</t>
+          <t>Pet Supplies</t>
         </is>
       </c>
       <c r="E111" s="3" t="n">
-        <v>74.8</v>
+        <v>69.8</v>
       </c>
       <c r="F111" s="3" t="n">
         <v>50</v>
@@ -11691,7 +11649,7 @@
       </c>
       <c r="H111" s="3" t="inlineStr">
         <is>
-          <t>$32.00 - $55.00</t>
+          <t>$34.00 - $48.00</t>
         </is>
       </c>
       <c r="I111" s="4" t="inlineStr">
@@ -11701,17 +11659,17 @@
       </c>
       <c r="J111" s="4" t="inlineStr">
         <is>
-          <t>Etsy US, Handmade/POD, TikTok Gift Trend</t>
+          <t>Etsy US, Handmade/POD</t>
         </is>
       </c>
       <c r="K111" s="4" t="inlineStr">
         <is>
-          <t>Behind The Scenes Crafting &amp; Emotional Gift Unboxing</t>
+          <t>Emotional Reaction &amp; Satisfying Fur Release ASMR</t>
         </is>
       </c>
       <c r="L111" s="5" t="inlineStr">
         <is>
-          <t>https://www.etsy.com/market/personalized_cutting_board</t>
+          <t>https://www.etsy.com/market/custom_pet_sweatshirt</t>
         </is>
       </c>
     </row>
@@ -11721,7 +11679,7 @@
       </c>
       <c r="B112" s="4" t="inlineStr">
         <is>
-          <t>Custom Pet Portrait Sweatshirt &amp; Embroidered Dog Mom Hoodie</t>
+          <t>Handmade Organic Soy Aromatherapy Candle in Amber Glass Jar</t>
         </is>
       </c>
       <c r="C112" s="4" t="inlineStr">
@@ -11731,7 +11689,7 @@
       </c>
       <c r="D112" s="4" t="inlineStr">
         <is>
-          <t>Pet Supplies</t>
+          <t>Home Supplies</t>
         </is>
       </c>
       <c r="E112" s="3" t="n">
@@ -11745,7 +11703,7 @@
       </c>
       <c r="H112" s="3" t="inlineStr">
         <is>
-          <t>$34.00 - $48.00</t>
+          <t>$18.00 - $26.00</t>
         </is>
       </c>
       <c r="I112" s="4" t="inlineStr">
@@ -11760,64 +11718,10 @@
       </c>
       <c r="K112" s="4" t="inlineStr">
         <is>
-          <t>Emotional Reaction &amp; Satisfying Fur Release ASMR</t>
+          <t>TikTok Made Me Buy It / Honest Review</t>
         </is>
       </c>
       <c r="L112" s="5" t="inlineStr">
-        <is>
-          <t>https://www.etsy.com/market/custom_pet_sweatshirt</t>
-        </is>
-      </c>
-    </row>
-    <row r="113" ht="22" customHeight="1">
-      <c r="A113" s="3" t="n">
-        <v>111</v>
-      </c>
-      <c r="B113" s="4" t="inlineStr">
-        <is>
-          <t>Handmade Organic Soy Aromatherapy Candle in Amber Glass Jar</t>
-        </is>
-      </c>
-      <c r="C113" s="4" t="inlineStr">
-        <is>
-          <t>🌲 Evergreen Bền Vững</t>
-        </is>
-      </c>
-      <c r="D113" s="4" t="inlineStr">
-        <is>
-          <t>Home Supplies</t>
-        </is>
-      </c>
-      <c r="E113" s="3" t="n">
-        <v>69.8</v>
-      </c>
-      <c r="F113" s="3" t="n">
-        <v>50</v>
-      </c>
-      <c r="G113" s="3" t="n">
-        <v>94</v>
-      </c>
-      <c r="H113" s="3" t="inlineStr">
-        <is>
-          <t>$18.00 - $26.00</t>
-        </is>
-      </c>
-      <c r="I113" s="4" t="inlineStr">
-        <is>
-          <t>Etsy US Trending</t>
-        </is>
-      </c>
-      <c r="J113" s="4" t="inlineStr">
-        <is>
-          <t>Etsy US, Handmade/POD</t>
-        </is>
-      </c>
-      <c r="K113" s="4" t="inlineStr">
-        <is>
-          <t>TikTok Made Me Buy It / Honest Review</t>
-        </is>
-      </c>
-      <c r="L113" s="5" t="inlineStr">
         <is>
           <t>https://www.etsy.com/market/soy_candle</t>
         </is>
@@ -11935,7 +11839,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L110" r:id="rId108"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L111" r:id="rId109"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L112" r:id="rId110"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L113" r:id="rId111"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/exports/TikTok_Shop_US_Latest_Trends.xlsx
+++ b/exports/TikTok_Shop_US_Latest_Trends.xlsx
@@ -1410,7 +1410,7 @@
       </c>
       <c r="J21" s="5" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/STANLEY-Quencher-State-Tumbler-Quartz/dp/B0CP9Z56SW/ref=zg_bs_g_kitchen_d_sccl_2/134-3113057-6761362</t>
+          <t>https://www.amazon.com/STANLEY-Quencher-State-Tumbler-Quartz/dp/B0CP9Z56SW/ref=zg_bs_g_kitchen_d_sccl_2/134-1095087-0412057</t>
         </is>
       </c>
     </row>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="J22" s="5" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/Medicube-Zero-Pore-Pads-Dual-Textured/dp/B09V7Z4TJG/ref=zg_bs_g_beauty_d_sccl_2/134-3113057-6761362</t>
+          <t>https://www.amazon.com/Medicube-Zero-Pore-Pads-Dual-Textured/dp/B09V7Z4TJG/ref=zg_bs_g_beauty_d_sccl_2/134-1095087-0412057</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="J23" s="5" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/HydroJug-Traveler-Resistant-Bottle-Reusable-Insulated/dp/B0CQVWT2NH/ref=zg_bs_g_kitchen_d_sccl_3/134-3113057-6761362</t>
+          <t>https://www.amazon.com/HydroJug-Traveler-Resistant-Bottle-Reusable-Insulated/dp/B0CQVWT2NH/ref=zg_bs_g_kitchen_d_sccl_3/134-1095087-0412057</t>
         </is>
       </c>
     </row>
@@ -1590,7 +1590,7 @@
       </c>
       <c r="J25" s="5" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/Apple-EarPods-Headphones-Built-Control/dp/B0DCH8VDXF/ref=zg_bs_g_electronics_d_sccl_2/134-3113057-6761362</t>
+          <t>https://www.amazon.com/Apple-EarPods-Headphones-Built-Control/dp/B0DCH8VDXF/ref=zg_bs_g_electronics_d_sccl_2/134-1095087-0412057</t>
         </is>
       </c>
     </row>
@@ -1636,7 +1636,7 @@
       </c>
       <c r="J26" s="5" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/Apple-AirTag-2nd-Generation-Precision/dp/B0GJTFXNRX/ref=zg_bs_g_electronics_d_sccl_3/134-3113057-6761362</t>
+          <t>https://www.amazon.com/Apple-AirTag-2nd-Generation-Precision/dp/B0GJTFXNRX/ref=zg_bs_g_electronics_d_sccl_3/134-1095087-0412057</t>
         </is>
       </c>
     </row>
@@ -1724,7 +1724,7 @@
       </c>
       <c r="J28" s="5" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/Apple-Cancellation-Translation-Headphones-High-Fidelity/dp/B0FQFB8FMG/ref=zg_bs_g_electronics_d_sccl_4/134-3113057-6761362</t>
+          <t>https://www.amazon.com/Apple-Cancellation-Translation-Headphones-High-Fidelity/dp/B0FQFB8FMG/ref=zg_bs_g_electronics_d_sccl_4/134-1095087-0412057</t>
         </is>
       </c>
     </row>
@@ -1770,7 +1770,7 @@
       </c>
       <c r="J29" s="5" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/Roku-Streaming-Stick-HD-2025/dp/B0DXXYS4BJ/ref=zg_bs_g_electronics_d_sccl_5/134-3113057-6761362</t>
+          <t>https://www.amazon.com/Roku-Streaming-Stick-HD-2025/dp/B0DXXYS4BJ/ref=zg_bs_g_electronics_d_sccl_5/134-1095087-0412057</t>
         </is>
       </c>
     </row>
@@ -1816,7 +1816,7 @@
       </c>
       <c r="J30" s="5" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/amazon-fire-tv-stick-4K-select/dp/B0C6W3D4RM/ref=zg_bs_g_electronics_d_sccl_6/134-3113057-6761362</t>
+          <t>https://www.amazon.com/amazon-fire-tv-stick-4K-select/dp/B0C6W3D4RM/ref=zg_bs_g_electronics_d_sccl_6/134-1095087-0412057</t>
         </is>
       </c>
     </row>
@@ -2128,19 +2128,19 @@
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>xrp price</t>
+          <t>dave franco</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>Beauty &amp; Personal Care</t>
+          <t>Pet Supplies</t>
         </is>
       </c>
       <c r="D38" s="3" t="n">
         <v>78</v>
       </c>
       <c r="E38" s="3" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="F38" s="3" t="inlineStr">
         <is>
@@ -2154,17 +2154,17 @@
       </c>
       <c r="H38" s="4" t="inlineStr">
         <is>
-          <t>Đặt câu hỏi trúng nỗi đau thường ngày: 'Tại sao không ai nói cho tôi biết món đồ này sớm hơn?!'</t>
+          <t>Âm thanh bấm nút nhả cả búi lông chó rụng chỉ trong 1 giây: 'Mùa rụng lông không còn là ác mộng!'</t>
         </is>
       </c>
       <c r="I38" s="4" t="inlineStr">
         <is>
-          <t>Khách hàng mua sắm ngẫu hứng (Impulse Buyers) trên TikTok Shop US độ tuổi 18 - 45.</t>
+          <t>Hội những người 'nghiện' chó mèo (Dog/Cat Parents) tại US, chi tiêu mạnh tay cho thú cưng.</t>
         </is>
       </c>
       <c r="J38" s="5" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?geo=US&amp;q=xrp%20price</t>
+          <t>https://trends.google.com/trends/explore?geo=US&amp;q=dave%20franco</t>
         </is>
       </c>
     </row>
@@ -2174,7 +2174,7 @@
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>omaha weather</t>
+          <t>goog stock</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
@@ -2210,7 +2210,7 @@
       </c>
       <c r="J39" s="5" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?geo=US&amp;q=omaha%20weather</t>
+          <t>https://trends.google.com/trends/explore?geo=US&amp;q=goog%20stock</t>
         </is>
       </c>
     </row>
@@ -2220,7 +2220,7 @@
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>oil prices</t>
+          <t>aaron gordon</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
@@ -2246,17 +2246,17 @@
       </c>
       <c r="H40" s="4" t="inlineStr">
         <is>
-          <t>Before &amp; After cận cảnh lỗ chân lông: 'Dừng ngay nếu bạn vẫn đang nặn mụn hoặc dùng tẩy tế bào chết hạt to!'</t>
+          <t>Đặt câu hỏi trúng nỗi đau thường ngày: 'Tại sao không ai nói cho tôi biết món đồ này sớm hơn?!'</t>
         </is>
       </c>
       <c r="I40" s="4" t="inlineStr">
         <is>
-          <t>Gen Z &amp; Millennials (18-34 tuổi), Chăm sóc da mụn, tín đồ Skincare &amp; 'Clean Girl' aesthetic US.</t>
+          <t>Khách hàng mua sắm ngẫu hứng (Impulse Buyers) trên TikTok Shop US độ tuổi 18 - 45.</t>
         </is>
       </c>
       <c r="J40" s="5" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?geo=US&amp;q=oil%20prices</t>
+          <t>https://trends.google.com/trends/explore?geo=US&amp;q=aaron%20gordon</t>
         </is>
       </c>
     </row>
@@ -2266,12 +2266,12 @@
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>temperature</t>
+          <t>todd blanche joe digenova call</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>DIY, Craft &amp; POD</t>
+          <t>Gadgets &amp; Electronics</t>
         </is>
       </c>
       <c r="D41" s="3" t="n">
@@ -2292,17 +2292,17 @@
       </c>
       <c r="H41" s="4" t="inlineStr">
         <is>
-          <t>Quá trình máy khắc laser tên khách hàng lên gỗ/kim loại: 'Làm món quà độc nhất vô nhị tặng mẹ...'</t>
+          <t>Đặt câu hỏi trúng nỗi đau thường ngày: 'Tại sao không ai nói cho tôi biết món đồ này sớm hơn?!'</t>
         </is>
       </c>
       <c r="I41" s="4" t="inlineStr">
         <is>
-          <t>Người tìm quà tặng sinh nhật, kỷ niệm, Mother's Day, quà tân gia ý nghĩa quanh năm.</t>
+          <t>Khách hàng mua sắm ngẫu hứng (Impulse Buyers) trên TikTok Shop US độ tuổi 18 - 45.</t>
         </is>
       </c>
       <c r="J41" s="5" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?geo=US&amp;q=temperature</t>
+          <t>https://trends.google.com/trends/explore?geo=US&amp;q=todd%20blanche%20joe%20digenova%20call</t>
         </is>
       </c>
     </row>
@@ -2312,12 +2312,12 @@
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>clarity act</t>
+          <t>tropical storm weather forecast</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>DIY, Craft &amp; POD</t>
+          <t>Beauty &amp; Personal Care</t>
         </is>
       </c>
       <c r="D42" s="3" t="n">
@@ -2338,17 +2338,17 @@
       </c>
       <c r="H42" s="4" t="inlineStr">
         <is>
-          <t>Quá trình máy khắc laser tên khách hàng lên gỗ/kim loại: 'Làm món quà độc nhất vô nhị tặng mẹ...'</t>
+          <t>Đặt câu hỏi trúng nỗi đau thường ngày: 'Tại sao không ai nói cho tôi biết món đồ này sớm hơn?!'</t>
         </is>
       </c>
       <c r="I42" s="4" t="inlineStr">
         <is>
-          <t>Người tìm quà tặng sinh nhật, kỷ niệm, Mother's Day, quà tân gia ý nghĩa quanh năm.</t>
+          <t>Khách hàng mua sắm ngẫu hứng (Impulse Buyers) trên TikTok Shop US độ tuổi 18 - 45.</t>
         </is>
       </c>
       <c r="J42" s="5" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?geo=US&amp;q=clarity%20act</t>
+          <t>https://trends.google.com/trends/explore?geo=US&amp;q=tropical%20storm%20weather%20forecast</t>
         </is>
       </c>
     </row>
@@ -2358,7 +2358,7 @@
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>npr</t>
+          <t>nvda</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
@@ -2394,7 +2394,7 @@
       </c>
       <c r="J43" s="5" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?geo=US&amp;q=npr</t>
+          <t>https://trends.google.com/trends/explore?geo=US&amp;q=nvda</t>
         </is>
       </c>
     </row>
@@ -2404,7 +2404,7 @@
       </c>
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t>kaley cuoco</t>
+          <t>omaha weather</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
@@ -2440,7 +2440,7 @@
       </c>
       <c r="J44" s="5" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?geo=US&amp;q=kaley%20cuoco</t>
+          <t>https://trends.google.com/trends/explore?geo=US&amp;q=omaha%20weather</t>
         </is>
       </c>
     </row>
@@ -2450,12 +2450,12 @@
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>reba mcentire dolly parton emmy tribute</t>
+          <t>xrp price</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>DIY, Craft &amp; POD</t>
+          <t>Beauty &amp; Personal Care</t>
         </is>
       </c>
       <c r="D45" s="3" t="n">
@@ -2476,17 +2476,17 @@
       </c>
       <c r="H45" s="4" t="inlineStr">
         <is>
-          <t>Quá trình máy khắc laser tên khách hàng lên gỗ/kim loại: 'Làm món quà độc nhất vô nhị tặng mẹ...'</t>
+          <t>Đặt câu hỏi trúng nỗi đau thường ngày: 'Tại sao không ai nói cho tôi biết món đồ này sớm hơn?!'</t>
         </is>
       </c>
       <c r="I45" s="4" t="inlineStr">
         <is>
-          <t>Người tìm quà tặng sinh nhật, kỷ niệm, Mother's Day, quà tân gia ý nghĩa quanh năm.</t>
+          <t>Khách hàng mua sắm ngẫu hứng (Impulse Buyers) trên TikTok Shop US độ tuổi 18 - 45.</t>
         </is>
       </c>
       <c r="J45" s="5" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?geo=US&amp;q=reba%20mcentire%20dolly%20parton%20emmy%20tribute</t>
+          <t>https://trends.google.com/trends/explore?geo=US&amp;q=xrp%20price</t>
         </is>
       </c>
     </row>
@@ -2496,7 +2496,7 @@
       </c>
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t>erin napier</t>
+          <t>clarity act</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
@@ -2532,7 +2532,7 @@
       </c>
       <c r="J46" s="5" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?geo=US&amp;q=erin%20napier</t>
+          <t>https://trends.google.com/trends/explore?geo=US&amp;q=clarity%20act</t>
         </is>
       </c>
     </row>
@@ -2542,12 +2542,12 @@
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>blake lively</t>
+          <t>temperature</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>Beauty &amp; Personal Care</t>
+          <t>DIY, Craft &amp; POD</t>
         </is>
       </c>
       <c r="D47" s="3" t="n">
@@ -2568,17 +2568,17 @@
       </c>
       <c r="H47" s="4" t="inlineStr">
         <is>
-          <t>Đặt câu hỏi trúng nỗi đau thường ngày: 'Tại sao không ai nói cho tôi biết món đồ này sớm hơn?!'</t>
+          <t>Quá trình máy khắc laser tên khách hàng lên gỗ/kim loại: 'Làm món quà độc nhất vô nhị tặng mẹ...'</t>
         </is>
       </c>
       <c r="I47" s="4" t="inlineStr">
         <is>
-          <t>Khách hàng mua sắm ngẫu hứng (Impulse Buyers) trên TikTok Shop US độ tuổi 18 - 45.</t>
+          <t>Người tìm quà tặng sinh nhật, kỷ niệm, Mother's Day, quà tân gia ý nghĩa quanh năm.</t>
         </is>
       </c>
       <c r="J47" s="5" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?geo=US&amp;q=blake%20lively</t>
+          <t>https://trends.google.com/trends/explore?geo=US&amp;q=temperature</t>
         </is>
       </c>
     </row>
@@ -5257,7 +5257,7 @@
       </c>
       <c r="I3" s="5" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/eos-Cashmere-Moisture-Lightweight-Non-Greasy/dp/B08KT2Z93D/ref=zg_bs_g_beauty_d_sccl_1/134-3113057-6761362</t>
+          <t>https://www.amazon.com/eos-Cashmere-Moisture-Lightweight-Non-Greasy/dp/B08KT2Z93D/ref=zg_bs_g_beauty_d_sccl_1/134-1095087-0412057</t>
         </is>
       </c>
     </row>
@@ -5298,7 +5298,7 @@
       </c>
       <c r="I4" s="5" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/Mighty-Patch-Hydrocolloid-Absorbing-count/dp/B074PVTPBW/ref=zg_bs_g_beauty_d_sccl_5/134-3113057-6761362</t>
+          <t>https://www.amazon.com/Mighty-Patch-Hydrocolloid-Absorbing-count/dp/B074PVTPBW/ref=zg_bs_g_beauty_d_sccl_5/134-1095087-0412057</t>
         </is>
       </c>
     </row>
@@ -5339,7 +5339,7 @@
       </c>
       <c r="I5" s="5" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/TERRO-T300-2-2-Pack-Liquid-Baits/dp/B00E4GACB8/ref=zg_bs_g_home-garden_d_sccl_1/134-3113057-6761362</t>
+          <t>https://www.amazon.com/TERRO-T300-2-2-Pack-Liquid-Baits/dp/B00E4GACB8/ref=zg_bs_g_home-garden_d_sccl_1/134-1095087-0412057</t>
         </is>
       </c>
     </row>
@@ -5380,7 +5380,7 @@
       </c>
       <c r="I6" s="5" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/Queen-Size-Piece-Sheet-Set/dp/B01M16WBW1/ref=zg_bs_g_home-garden_d_sccl_3/134-3113057-6761362</t>
+          <t>https://www.amazon.com/Queen-Size-Piece-Sheet-Set/dp/B01M16WBW1/ref=zg_bs_g_home-garden_d_sccl_3/134-1095087-0412057</t>
         </is>
       </c>
     </row>
@@ -5421,7 +5421,7 @@
       </c>
       <c r="I7" s="5" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/Dr-Elseys-Premium-Clumping-Litter/dp/B0009X29WK/ref=zg_bs_g_pet-supplies_d_sccl_1/134-3113057-6761362</t>
+          <t>https://www.amazon.com/Dr-Elseys-Premium-Clumping-Litter/dp/B0009X29WK/ref=zg_bs_g_pet-supplies_d_sccl_1/134-1095087-0412057</t>
         </is>
       </c>
     </row>
@@ -5462,7 +5462,7 @@
       </c>
       <c r="I8" s="5" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/Amazon-Basics-Leak-Proof-Quick-Dry-Absorbency/dp/B00MW8G62E/ref=zg_bs_g_pet-supplies_d_sccl_2/134-3113057-6761362</t>
+          <t>https://www.amazon.com/Amazon-Basics-Leak-Proof-Quick-Dry-Absorbency/dp/B00MW8G62E/ref=zg_bs_g_pet-supplies_d_sccl_2/134-1095087-0412057</t>
         </is>
       </c>
     </row>
@@ -5503,7 +5503,7 @@
       </c>
       <c r="I9" s="5" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/Purina-Fancy-Feast-Poultry-Collection/dp/B00JN9IWNG/ref=zg_bs_g_pet-supplies_d_sccl_3/134-3113057-6761362</t>
+          <t>https://www.amazon.com/Purina-Fancy-Feast-Poultry-Collection/dp/B00JN9IWNG/ref=zg_bs_g_pet-supplies_d_sccl_3/134-1095087-0412057</t>
         </is>
       </c>
     </row>
@@ -5544,7 +5544,7 @@
       </c>
       <c r="I10" s="5" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/Amazon-Basics-Cotton-Swabs-500ct/dp/B09541P9WH/ref=zg_bs_g_beauty_d_sccl_3/134-3113057-6761362</t>
+          <t>https://www.amazon.com/Amazon-Basics-Cotton-Swabs-500ct/dp/B09541P9WH/ref=zg_bs_g_beauty_d_sccl_3/134-1095087-0412057</t>
         </is>
       </c>
     </row>
@@ -5585,7 +5585,7 @@
       </c>
       <c r="I11" s="5" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/Clean-Skin-Club-Disposable-Sensitive/dp/B07PBXXNCY/ref=zg_bs_g_beauty_d_sccl_4/134-3113057-6761362</t>
+          <t>https://www.amazon.com/Clean-Skin-Club-Disposable-Sensitive/dp/B07PBXXNCY/ref=zg_bs_g_beauty_d_sccl_4/134-1095087-0412057</t>
         </is>
       </c>
     </row>
@@ -5626,7 +5626,7 @@
       </c>
       <c r="I12" s="5" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/Owala-FreeSip-Insulated-Stainless-BPA-Free/dp/B0BZYCJK89/ref=zg_bs_g_kitchen_d_sccl_1/134-3113057-6761362</t>
+          <t>https://www.amazon.com/Owala-FreeSip-Insulated-Stainless-BPA-Free/dp/B0BZYCJK89/ref=zg_bs_g_kitchen_d_sccl_1/134-1095087-0412057</t>
         </is>
       </c>
     </row>
@@ -5667,7 +5667,7 @@
       </c>
       <c r="I13" s="5" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/Owala-FreeSip-Insulated-Stainless-BPA-Free/dp/B0BZYCJK89/ref=zg_bs_g_home-garden_d_sccl_2/134-3113057-6761362</t>
+          <t>https://www.amazon.com/Owala-FreeSip-Insulated-Stainless-BPA-Free/dp/B0BZYCJK89/ref=zg_bs_g_home-garden_d_sccl_2/134-1095087-0412057</t>
         </is>
       </c>
     </row>
@@ -5708,7 +5708,7 @@
       </c>
       <c r="I14" s="5" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/Blink-Plus-Plan-monthly-auto-renewal/dp/B08JHCVHTY/ref=zg_bs_g_electronics_d_sccl_1/134-3113057-6761362</t>
+          <t>https://www.amazon.com/Blink-Plus-Plan-monthly-auto-renewal/dp/B08JHCVHTY/ref=zg_bs_g_electronics_d_sccl_1/134-1095087-0412057</t>
         </is>
       </c>
     </row>
@@ -5749,7 +5749,7 @@
       </c>
       <c r="I15" s="5" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/Owala-SmoothSip-Insulated-Stainless-Reusable/dp/B0DF3M7V3T/ref=zg_bs_g_kitchen_d_sccl_5/134-3113057-6761362</t>
+          <t>https://www.amazon.com/Owala-SmoothSip-Insulated-Stainless-Reusable/dp/B0DF3M7V3T/ref=zg_bs_g_kitchen_d_sccl_5/134-1095087-0412057</t>
         </is>
       </c>
     </row>
@@ -5790,7 +5790,7 @@
       </c>
       <c r="I16" s="5" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/Amazon-Basics-Cotton-Rounds-Count/dp/B09542G9ZN/ref=zg_bs_g_beauty_d_sccl_6/134-3113057-6761362</t>
+          <t>https://www.amazon.com/Amazon-Basics-Cotton-Rounds-Count/dp/B09542G9ZN/ref=zg_bs_g_beauty_d_sccl_6/134-1095087-0412057</t>
         </is>
       </c>
     </row>
@@ -5831,7 +5831,7 @@
       </c>
       <c r="I17" s="5" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/Etekcity-Multifunction-Stainless-Batteries-Included/dp/B0113UZJE2/ref=zg_bs_g_kitchen_d_sccl_4/134-3113057-6761362</t>
+          <t>https://www.amazon.com/Etekcity-Multifunction-Stainless-Batteries-Included/dp/B0113UZJE2/ref=zg_bs_g_kitchen_d_sccl_4/134-1095087-0412057</t>
         </is>
       </c>
     </row>
@@ -5872,7 +5872,7 @@
       </c>
       <c r="I18" s="5" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/Amazon-Basics-Microfiber-Lightweight-Wrinkle-free/dp/B0154ASID6/ref=zg_bs_g_home-garden_d_sccl_4/134-3113057-6761362</t>
+          <t>https://www.amazon.com/Amazon-Basics-Microfiber-Lightweight-Wrinkle-free/dp/B0154ASID6/ref=zg_bs_g_home-garden_d_sccl_4/134-1095087-0412057</t>
         </is>
       </c>
     </row>
@@ -5913,7 +5913,7 @@
       </c>
       <c r="I19" s="5" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/Electric-Flying-Insect-Trap-Starter/dp/B07T869RNY/ref=zg_bs_g_home-garden_d_sccl_6/134-3113057-6761362</t>
+          <t>https://www.amazon.com/Electric-Flying-Insect-Trap-Starter/dp/B07T869RNY/ref=zg_bs_g_home-garden_d_sccl_6/134-1095087-0412057</t>
         </is>
       </c>
     </row>
@@ -5954,7 +5954,7 @@
       </c>
       <c r="I20" s="5" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/Earth-Rated-Lavender-Scented-Completely/dp/B00BSYR7K8/ref=zg_bs_g_pet-supplies_d_sccl_5/134-3113057-6761362</t>
+          <t>https://www.amazon.com/Earth-Rated-Lavender-Scented-Completely/dp/B00BSYR7K8/ref=zg_bs_g_pet-supplies_d_sccl_5/134-1095087-0412057</t>
         </is>
       </c>
     </row>
@@ -5995,7 +5995,7 @@
       </c>
       <c r="I21" s="5" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/Toaster-Fits-anywhereTM-Kitchenware-Setting-Removable/dp/B0CYJBB2JQ/ref=zg_bs_g_kitchen_d_sccl_6/134-3113057-6761362</t>
+          <t>https://www.amazon.com/Toaster-Fits-anywhereTM-Kitchenware-Setting-Removable/dp/B0CYJBB2JQ/ref=zg_bs_g_kitchen_d_sccl_6/134-1095087-0412057</t>
         </is>
       </c>
     </row>
@@ -6036,7 +6036,7 @@
       </c>
       <c r="I22" s="5" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/ZEVO-Flying-Insect-Refills-Indoor/dp/B0C3FTCYZL/ref=zg_bs_g_home-garden_d_sccl_5/134-3113057-6761362</t>
+          <t>https://www.amazon.com/ZEVO-Flying-Insect-Refills-Indoor/dp/B0C3FTCYZL/ref=zg_bs_g_home-garden_d_sccl_5/134-1095087-0412057</t>
         </is>
       </c>
     </row>
@@ -6077,7 +6077,7 @@
       </c>
       <c r="I23" s="5" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/INABA-Grain-Free-Lickable-Squeezable-Vitamin/dp/B0B52D7BBD/ref=zg_bs_g_pet-supplies_d_sccl_4/134-3113057-6761362</t>
+          <t>https://www.amazon.com/INABA-Grain-Free-Lickable-Squeezable-Vitamin/dp/B0B52D7BBD/ref=zg_bs_g_pet-supplies_d_sccl_4/134-1095087-0412057</t>
         </is>
       </c>
     </row>
@@ -6118,7 +6118,7 @@
       </c>
       <c r="I24" s="5" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/Greenies-Pill-Pockets-Ingredients-Nutrients/dp/B008GRONV6/ref=zg_bs_g_pet-supplies_d_sccl_6/134-3113057-6761362</t>
+          <t>https://www.amazon.com/Greenies-Pill-Pockets-Ingredients-Nutrients/dp/B008GRONV6/ref=zg_bs_g_pet-supplies_d_sccl_6/134-1095087-0412057</t>
         </is>
       </c>
     </row>
@@ -7556,7 +7556,7 @@
       </c>
       <c r="L21" s="5" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/STANLEY-Quencher-State-Tumbler-Quartz/dp/B0CP9Z56SW/ref=zg_bs_g_kitchen_d_sccl_2/134-3113057-6761362</t>
+          <t>https://www.amazon.com/STANLEY-Quencher-State-Tumbler-Quartz/dp/B0CP9Z56SW/ref=zg_bs_g_kitchen_d_sccl_2/134-1095087-0412057</t>
         </is>
       </c>
     </row>
@@ -7610,7 +7610,7 @@
       </c>
       <c r="L22" s="5" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/Medicube-Zero-Pore-Pads-Dual-Textured/dp/B09V7Z4TJG/ref=zg_bs_g_beauty_d_sccl_2/134-3113057-6761362</t>
+          <t>https://www.amazon.com/Medicube-Zero-Pore-Pads-Dual-Textured/dp/B09V7Z4TJG/ref=zg_bs_g_beauty_d_sccl_2/134-1095087-0412057</t>
         </is>
       </c>
     </row>
@@ -7664,7 +7664,7 @@
       </c>
       <c r="L23" s="5" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/HydroJug-Traveler-Resistant-Bottle-Reusable-Insulated/dp/B0CQVWT2NH/ref=zg_bs_g_kitchen_d_sccl_3/134-3113057-6761362</t>
+          <t>https://www.amazon.com/HydroJug-Traveler-Resistant-Bottle-Reusable-Insulated/dp/B0CQVWT2NH/ref=zg_bs_g_kitchen_d_sccl_3/134-1095087-0412057</t>
         </is>
       </c>
     </row>
@@ -7768,7 +7768,7 @@
       </c>
       <c r="L25" s="5" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/eos-Cashmere-Moisture-Lightweight-Non-Greasy/dp/B08KT2Z93D/ref=zg_bs_g_beauty_d_sccl_1/134-3113057-6761362</t>
+          <t>https://www.amazon.com/eos-Cashmere-Moisture-Lightweight-Non-Greasy/dp/B08KT2Z93D/ref=zg_bs_g_beauty_d_sccl_1/134-1095087-0412057</t>
         </is>
       </c>
     </row>
@@ -7822,7 +7822,7 @@
       </c>
       <c r="L26" s="5" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/Mighty-Patch-Hydrocolloid-Absorbing-count/dp/B074PVTPBW/ref=zg_bs_g_beauty_d_sccl_5/134-3113057-6761362</t>
+          <t>https://www.amazon.com/Mighty-Patch-Hydrocolloid-Absorbing-count/dp/B074PVTPBW/ref=zg_bs_g_beauty_d_sccl_5/134-1095087-0412057</t>
         </is>
       </c>
     </row>
@@ -7876,7 +7876,7 @@
       </c>
       <c r="L27" s="5" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/TERRO-T300-2-2-Pack-Liquid-Baits/dp/B00E4GACB8/ref=zg_bs_g_home-garden_d_sccl_1/134-3113057-6761362</t>
+          <t>https://www.amazon.com/TERRO-T300-2-2-Pack-Liquid-Baits/dp/B00E4GACB8/ref=zg_bs_g_home-garden_d_sccl_1/134-1095087-0412057</t>
         </is>
       </c>
     </row>
@@ -7930,7 +7930,7 @@
       </c>
       <c r="L28" s="5" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/Queen-Size-Piece-Sheet-Set/dp/B01M16WBW1/ref=zg_bs_g_home-garden_d_sccl_3/134-3113057-6761362</t>
+          <t>https://www.amazon.com/Queen-Size-Piece-Sheet-Set/dp/B01M16WBW1/ref=zg_bs_g_home-garden_d_sccl_3/134-1095087-0412057</t>
         </is>
       </c>
     </row>
@@ -7984,7 +7984,7 @@
       </c>
       <c r="L29" s="5" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/Dr-Elseys-Premium-Clumping-Litter/dp/B0009X29WK/ref=zg_bs_g_pet-supplies_d_sccl_1/134-3113057-6761362</t>
+          <t>https://www.amazon.com/Dr-Elseys-Premium-Clumping-Litter/dp/B0009X29WK/ref=zg_bs_g_pet-supplies_d_sccl_1/134-1095087-0412057</t>
         </is>
       </c>
     </row>
@@ -8038,7 +8038,7 @@
       </c>
       <c r="L30" s="5" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/Amazon-Basics-Leak-Proof-Quick-Dry-Absorbency/dp/B00MW8G62E/ref=zg_bs_g_pet-supplies_d_sccl_2/134-3113057-6761362</t>
+          <t>https://www.amazon.com/Amazon-Basics-Leak-Proof-Quick-Dry-Absorbency/dp/B00MW8G62E/ref=zg_bs_g_pet-supplies_d_sccl_2/134-1095087-0412057</t>
         </is>
       </c>
     </row>
@@ -8092,7 +8092,7 @@
       </c>
       <c r="L31" s="5" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/Purina-Fancy-Feast-Poultry-Collection/dp/B00JN9IWNG/ref=zg_bs_g_pet-supplies_d_sccl_3/134-3113057-6761362</t>
+          <t>https://www.amazon.com/Purina-Fancy-Feast-Poultry-Collection/dp/B00JN9IWNG/ref=zg_bs_g_pet-supplies_d_sccl_3/134-1095087-0412057</t>
         </is>
       </c>
     </row>
@@ -8146,7 +8146,7 @@
       </c>
       <c r="L32" s="5" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/Amazon-Basics-Cotton-Swabs-500ct/dp/B09541P9WH/ref=zg_bs_g_beauty_d_sccl_3/134-3113057-6761362</t>
+          <t>https://www.amazon.com/Amazon-Basics-Cotton-Swabs-500ct/dp/B09541P9WH/ref=zg_bs_g_beauty_d_sccl_3/134-1095087-0412057</t>
         </is>
       </c>
     </row>
@@ -8200,7 +8200,7 @@
       </c>
       <c r="L33" s="5" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/Clean-Skin-Club-Disposable-Sensitive/dp/B07PBXXNCY/ref=zg_bs_g_beauty_d_sccl_4/134-3113057-6761362</t>
+          <t>https://www.amazon.com/Clean-Skin-Club-Disposable-Sensitive/dp/B07PBXXNCY/ref=zg_bs_g_beauty_d_sccl_4/134-1095087-0412057</t>
         </is>
       </c>
     </row>
@@ -8254,7 +8254,7 @@
       </c>
       <c r="L34" s="5" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/Owala-FreeSip-Insulated-Stainless-BPA-Free/dp/B0BZYCJK89/ref=zg_bs_g_kitchen_d_sccl_1/134-3113057-6761362</t>
+          <t>https://www.amazon.com/Owala-FreeSip-Insulated-Stainless-BPA-Free/dp/B0BZYCJK89/ref=zg_bs_g_kitchen_d_sccl_1/134-1095087-0412057</t>
         </is>
       </c>
     </row>
@@ -8308,7 +8308,7 @@
       </c>
       <c r="L35" s="5" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/Owala-FreeSip-Insulated-Stainless-BPA-Free/dp/B0BZYCJK89/ref=zg_bs_g_home-garden_d_sccl_2/134-3113057-6761362</t>
+          <t>https://www.amazon.com/Owala-FreeSip-Insulated-Stainless-BPA-Free/dp/B0BZYCJK89/ref=zg_bs_g_home-garden_d_sccl_2/134-1095087-0412057</t>
         </is>
       </c>
     </row>
@@ -8362,7 +8362,7 @@
       </c>
       <c r="L36" s="5" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/Blink-Plus-Plan-monthly-auto-renewal/dp/B08JHCVHTY/ref=zg_bs_g_electronics_d_sccl_1/134-3113057-6761362</t>
+          <t>https://www.amazon.com/Blink-Plus-Plan-monthly-auto-renewal/dp/B08JHCVHTY/ref=zg_bs_g_electronics_d_sccl_1/134-1095087-0412057</t>
         </is>
       </c>
     </row>
@@ -8416,7 +8416,7 @@
       </c>
       <c r="L37" s="5" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/Owala-SmoothSip-Insulated-Stainless-Reusable/dp/B0DF3M7V3T/ref=zg_bs_g_kitchen_d_sccl_5/134-3113057-6761362</t>
+          <t>https://www.amazon.com/Owala-SmoothSip-Insulated-Stainless-Reusable/dp/B0DF3M7V3T/ref=zg_bs_g_kitchen_d_sccl_5/134-1095087-0412057</t>
         </is>
       </c>
     </row>
@@ -8470,7 +8470,7 @@
       </c>
       <c r="L38" s="5" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/Apple-EarPods-Headphones-Built-Control/dp/B0DCH8VDXF/ref=zg_bs_g_electronics_d_sccl_2/134-3113057-6761362</t>
+          <t>https://www.amazon.com/Apple-EarPods-Headphones-Built-Control/dp/B0DCH8VDXF/ref=zg_bs_g_electronics_d_sccl_2/134-1095087-0412057</t>
         </is>
       </c>
     </row>
@@ -8524,7 +8524,7 @@
       </c>
       <c r="L39" s="5" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/Apple-AirTag-2nd-Generation-Precision/dp/B0GJTFXNRX/ref=zg_bs_g_electronics_d_sccl_3/134-3113057-6761362</t>
+          <t>https://www.amazon.com/Apple-AirTag-2nd-Generation-Precision/dp/B0GJTFXNRX/ref=zg_bs_g_electronics_d_sccl_3/134-1095087-0412057</t>
         </is>
       </c>
     </row>
@@ -8628,7 +8628,7 @@
       </c>
       <c r="L41" s="5" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/Amazon-Basics-Cotton-Rounds-Count/dp/B09542G9ZN/ref=zg_bs_g_beauty_d_sccl_6/134-3113057-6761362</t>
+          <t>https://www.amazon.com/Amazon-Basics-Cotton-Rounds-Count/dp/B09542G9ZN/ref=zg_bs_g_beauty_d_sccl_6/134-1095087-0412057</t>
         </is>
       </c>
     </row>
@@ -8682,7 +8682,7 @@
       </c>
       <c r="L42" s="5" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/Etekcity-Multifunction-Stainless-Batteries-Included/dp/B0113UZJE2/ref=zg_bs_g_kitchen_d_sccl_4/134-3113057-6761362</t>
+          <t>https://www.amazon.com/Etekcity-Multifunction-Stainless-Batteries-Included/dp/B0113UZJE2/ref=zg_bs_g_kitchen_d_sccl_4/134-1095087-0412057</t>
         </is>
       </c>
     </row>
@@ -8736,7 +8736,7 @@
       </c>
       <c r="L43" s="5" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/Amazon-Basics-Microfiber-Lightweight-Wrinkle-free/dp/B0154ASID6/ref=zg_bs_g_home-garden_d_sccl_4/134-3113057-6761362</t>
+          <t>https://www.amazon.com/Amazon-Basics-Microfiber-Lightweight-Wrinkle-free/dp/B0154ASID6/ref=zg_bs_g_home-garden_d_sccl_4/134-1095087-0412057</t>
         </is>
       </c>
     </row>
@@ -8790,7 +8790,7 @@
       </c>
       <c r="L44" s="5" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/Electric-Flying-Insect-Trap-Starter/dp/B07T869RNY/ref=zg_bs_g_home-garden_d_sccl_6/134-3113057-6761362</t>
+          <t>https://www.amazon.com/Electric-Flying-Insect-Trap-Starter/dp/B07T869RNY/ref=zg_bs_g_home-garden_d_sccl_6/134-1095087-0412057</t>
         </is>
       </c>
     </row>
@@ -8844,7 +8844,7 @@
       </c>
       <c r="L45" s="5" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/Earth-Rated-Lavender-Scented-Completely/dp/B00BSYR7K8/ref=zg_bs_g_pet-supplies_d_sccl_5/134-3113057-6761362</t>
+          <t>https://www.amazon.com/Earth-Rated-Lavender-Scented-Completely/dp/B00BSYR7K8/ref=zg_bs_g_pet-supplies_d_sccl_5/134-1095087-0412057</t>
         </is>
       </c>
     </row>
@@ -8898,7 +8898,7 @@
       </c>
       <c r="L46" s="5" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/Toaster-Fits-anywhereTM-Kitchenware-Setting-Removable/dp/B0CYJBB2JQ/ref=zg_bs_g_kitchen_d_sccl_6/134-3113057-6761362</t>
+          <t>https://www.amazon.com/Toaster-Fits-anywhereTM-Kitchenware-Setting-Removable/dp/B0CYJBB2JQ/ref=zg_bs_g_kitchen_d_sccl_6/134-1095087-0412057</t>
         </is>
       </c>
     </row>
@@ -8952,7 +8952,7 @@
       </c>
       <c r="L47" s="5" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/ZEVO-Flying-Insect-Refills-Indoor/dp/B0C3FTCYZL/ref=zg_bs_g_home-garden_d_sccl_5/134-3113057-6761362</t>
+          <t>https://www.amazon.com/ZEVO-Flying-Insect-Refills-Indoor/dp/B0C3FTCYZL/ref=zg_bs_g_home-garden_d_sccl_5/134-1095087-0412057</t>
         </is>
       </c>
     </row>
@@ -9006,7 +9006,7 @@
       </c>
       <c r="L48" s="5" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/INABA-Grain-Free-Lickable-Squeezable-Vitamin/dp/B0B52D7BBD/ref=zg_bs_g_pet-supplies_d_sccl_4/134-3113057-6761362</t>
+          <t>https://www.amazon.com/INABA-Grain-Free-Lickable-Squeezable-Vitamin/dp/B0B52D7BBD/ref=zg_bs_g_pet-supplies_d_sccl_4/134-1095087-0412057</t>
         </is>
       </c>
     </row>
@@ -9060,7 +9060,7 @@
       </c>
       <c r="L49" s="5" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/Greenies-Pill-Pockets-Ingredients-Nutrients/dp/B008GRONV6/ref=zg_bs_g_pet-supplies_d_sccl_6/134-3113057-6761362</t>
+          <t>https://www.amazon.com/Greenies-Pill-Pockets-Ingredients-Nutrients/dp/B008GRONV6/ref=zg_bs_g_pet-supplies_d_sccl_6/134-1095087-0412057</t>
         </is>
       </c>
     </row>
@@ -9114,7 +9114,7 @@
       </c>
       <c r="L50" s="5" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/Apple-Cancellation-Translation-Headphones-High-Fidelity/dp/B0FQFB8FMG/ref=zg_bs_g_electronics_d_sccl_4/134-3113057-6761362</t>
+          <t>https://www.amazon.com/Apple-Cancellation-Translation-Headphones-High-Fidelity/dp/B0FQFB8FMG/ref=zg_bs_g_electronics_d_sccl_4/134-1095087-0412057</t>
         </is>
       </c>
     </row>
@@ -9168,7 +9168,7 @@
       </c>
       <c r="L51" s="5" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/Roku-Streaming-Stick-HD-2025/dp/B0DXXYS4BJ/ref=zg_bs_g_electronics_d_sccl_5/134-3113057-6761362</t>
+          <t>https://www.amazon.com/Roku-Streaming-Stick-HD-2025/dp/B0DXXYS4BJ/ref=zg_bs_g_electronics_d_sccl_5/134-1095087-0412057</t>
         </is>
       </c>
     </row>
@@ -9222,7 +9222,7 @@
       </c>
       <c r="L52" s="5" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/amazon-fire-tv-stick-4K-select/dp/B0C6W3D4RM/ref=zg_bs_g_electronics_d_sccl_6/134-3113057-6761362</t>
+          <t>https://www.amazon.com/amazon-fire-tv-stick-4K-select/dp/B0C6W3D4RM/ref=zg_bs_g_electronics_d_sccl_6/134-1095087-0412057</t>
         </is>
       </c>
     </row>
@@ -9590,7 +9590,7 @@
       </c>
       <c r="B60" s="4" t="inlineStr">
         <is>
-          <t>xrp price</t>
+          <t>dave franco</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
@@ -9600,17 +9600,17 @@
       </c>
       <c r="D60" s="4" t="inlineStr">
         <is>
-          <t>Beauty &amp; Personal Care</t>
+          <t>Pet Supplies</t>
         </is>
       </c>
       <c r="E60" s="3" t="n">
-        <v>63.2</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="F60" s="3" t="n">
         <v>78</v>
       </c>
       <c r="G60" s="3" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="H60" s="3" t="inlineStr">
         <is>
@@ -9629,12 +9629,12 @@
       </c>
       <c r="K60" s="4" t="inlineStr">
         <is>
-          <t>TikTok Made Me Buy It / Honest Review</t>
+          <t>Emotional Reaction &amp; Satisfying Fur Release ASMR</t>
         </is>
       </c>
       <c r="L60" s="5" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?geo=US&amp;q=xrp%20price</t>
+          <t>https://trends.google.com/trends/explore?geo=US&amp;q=dave%20franco</t>
         </is>
       </c>
     </row>
@@ -9644,7 +9644,7 @@
       </c>
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t>omaha weather</t>
+          <t>goog stock</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
@@ -9688,7 +9688,7 @@
       </c>
       <c r="L61" s="5" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?geo=US&amp;q=omaha%20weather</t>
+          <t>https://trends.google.com/trends/explore?geo=US&amp;q=goog%20stock</t>
         </is>
       </c>
     </row>
@@ -9698,7 +9698,7 @@
       </c>
       <c r="B62" s="4" t="inlineStr">
         <is>
-          <t>oil prices</t>
+          <t>aaron gordon</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
@@ -9737,12 +9737,12 @@
       </c>
       <c r="K62" s="4" t="inlineStr">
         <is>
-          <t>Before/After Macro Skin Texture Zoom (Cận cảnh bề mặt da)</t>
+          <t>TikTok Made Me Buy It / Honest Review</t>
         </is>
       </c>
       <c r="L62" s="5" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?geo=US&amp;q=oil%20prices</t>
+          <t>https://trends.google.com/trends/explore?geo=US&amp;q=aaron%20gordon</t>
         </is>
       </c>
     </row>
@@ -9752,7 +9752,7 @@
       </c>
       <c r="B63" s="4" t="inlineStr">
         <is>
-          <t>temperature</t>
+          <t>todd blanche joe digenova call</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
@@ -9762,7 +9762,7 @@
       </c>
       <c r="D63" s="4" t="inlineStr">
         <is>
-          <t>DIY, Craft &amp; POD</t>
+          <t>Gadgets &amp; Electronics</t>
         </is>
       </c>
       <c r="E63" s="3" t="n">
@@ -9791,12 +9791,12 @@
       </c>
       <c r="K63" s="4" t="inlineStr">
         <is>
-          <t>Behind The Scenes Crafting &amp; Emotional Gift Unboxing</t>
+          <t>TikTok Made Me Buy It / Honest Review</t>
         </is>
       </c>
       <c r="L63" s="5" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?geo=US&amp;q=temperature</t>
+          <t>https://trends.google.com/trends/explore?geo=US&amp;q=todd%20blanche%20joe%20digenova%20call</t>
         </is>
       </c>
     </row>
@@ -9806,7 +9806,7 @@
       </c>
       <c r="B64" s="4" t="inlineStr">
         <is>
-          <t>clarity act</t>
+          <t>tropical storm weather forecast</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
@@ -9816,7 +9816,7 @@
       </c>
       <c r="D64" s="4" t="inlineStr">
         <is>
-          <t>DIY, Craft &amp; POD</t>
+          <t>Beauty &amp; Personal Care</t>
         </is>
       </c>
       <c r="E64" s="3" t="n">
@@ -9845,12 +9845,12 @@
       </c>
       <c r="K64" s="4" t="inlineStr">
         <is>
-          <t>Behind The Scenes Crafting &amp; Emotional Gift Unboxing</t>
+          <t>TikTok Made Me Buy It / Honest Review</t>
         </is>
       </c>
       <c r="L64" s="5" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?geo=US&amp;q=clarity%20act</t>
+          <t>https://trends.google.com/trends/explore?geo=US&amp;q=tropical%20storm%20weather%20forecast</t>
         </is>
       </c>
     </row>
@@ -9860,7 +9860,7 @@
       </c>
       <c r="B65" s="4" t="inlineStr">
         <is>
-          <t>npr</t>
+          <t>nvda</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
@@ -9904,7 +9904,7 @@
       </c>
       <c r="L65" s="5" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?geo=US&amp;q=npr</t>
+          <t>https://trends.google.com/trends/explore?geo=US&amp;q=nvda</t>
         </is>
       </c>
     </row>
@@ -9914,7 +9914,7 @@
       </c>
       <c r="B66" s="4" t="inlineStr">
         <is>
-          <t>kaley cuoco</t>
+          <t>omaha weather</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
@@ -9958,7 +9958,7 @@
       </c>
       <c r="L66" s="5" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?geo=US&amp;q=kaley%20cuoco</t>
+          <t>https://trends.google.com/trends/explore?geo=US&amp;q=omaha%20weather</t>
         </is>
       </c>
     </row>
@@ -9968,7 +9968,7 @@
       </c>
       <c r="B67" s="4" t="inlineStr">
         <is>
-          <t>reba mcentire dolly parton emmy tribute</t>
+          <t>xrp price</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
@@ -9978,7 +9978,7 @@
       </c>
       <c r="D67" s="4" t="inlineStr">
         <is>
-          <t>DIY, Craft &amp; POD</t>
+          <t>Beauty &amp; Personal Care</t>
         </is>
       </c>
       <c r="E67" s="3" t="n">
@@ -10007,12 +10007,12 @@
       </c>
       <c r="K67" s="4" t="inlineStr">
         <is>
-          <t>Behind The Scenes Crafting &amp; Emotional Gift Unboxing</t>
+          <t>TikTok Made Me Buy It / Honest Review</t>
         </is>
       </c>
       <c r="L67" s="5" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?geo=US&amp;q=reba%20mcentire%20dolly%20parton%20emmy%20tribute</t>
+          <t>https://trends.google.com/trends/explore?geo=US&amp;q=xrp%20price</t>
         </is>
       </c>
     </row>
@@ -10022,7 +10022,7 @@
       </c>
       <c r="B68" s="4" t="inlineStr">
         <is>
-          <t>erin napier</t>
+          <t>clarity act</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
@@ -10066,7 +10066,7 @@
       </c>
       <c r="L68" s="5" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?geo=US&amp;q=erin%20napier</t>
+          <t>https://trends.google.com/trends/explore?geo=US&amp;q=clarity%20act</t>
         </is>
       </c>
     </row>
@@ -10076,7 +10076,7 @@
       </c>
       <c r="B69" s="4" t="inlineStr">
         <is>
-          <t>blake lively</t>
+          <t>temperature</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
@@ -10086,7 +10086,7 @@
       </c>
       <c r="D69" s="4" t="inlineStr">
         <is>
-          <t>Beauty &amp; Personal Care</t>
+          <t>DIY, Craft &amp; POD</t>
         </is>
       </c>
       <c r="E69" s="3" t="n">
@@ -10115,12 +10115,12 @@
       </c>
       <c r="K69" s="4" t="inlineStr">
         <is>
-          <t>TikTok Made Me Buy It / Honest Review</t>
+          <t>Behind The Scenes Crafting &amp; Emotional Gift Unboxing</t>
         </is>
       </c>
       <c r="L69" s="5" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?geo=US&amp;q=blake%20lively</t>
+          <t>https://trends.google.com/trends/explore?geo=US&amp;q=temperature</t>
         </is>
       </c>
     </row>

--- a/exports/TikTok_Shop_US_Latest_Trends.xlsx
+++ b/exports/TikTok_Shop_US_Latest_Trends.xlsx
@@ -1410,7 +1410,7 @@
       </c>
       <c r="J21" s="5" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/STANLEY-Quencher-State-Tumbler-Quartz/dp/B0CP9Z56SW/ref=zg_bs_g_kitchen_d_sccl_2/134-1095087-0412057</t>
+          <t>https://www.amazon.com/STANLEY-Quencher-State-Tumbler-Quartz/dp/B0CP9Z56SW/ref=zg_bs_g_kitchen_d_sccl_2/143-7478900-6733836</t>
         </is>
       </c>
     </row>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="J22" s="5" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/Medicube-Zero-Pore-Pads-Dual-Textured/dp/B09V7Z4TJG/ref=zg_bs_g_beauty_d_sccl_2/134-1095087-0412057</t>
+          <t>https://www.amazon.com/Medicube-Zero-Pore-Pads-Dual-Textured/dp/B09V7Z4TJG/ref=zg_bs_g_beauty_d_sccl_2/143-7478900-6733836</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="J23" s="5" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/HydroJug-Traveler-Resistant-Bottle-Reusable-Insulated/dp/B0CQVWT2NH/ref=zg_bs_g_kitchen_d_sccl_3/134-1095087-0412057</t>
+          <t>https://www.amazon.com/HydroJug-Traveler-Resistant-Bottle-Reusable-Insulated/dp/B0CQVWT2NH/ref=zg_bs_g_kitchen_d_sccl_3/143-7478900-6733836</t>
         </is>
       </c>
     </row>
@@ -1590,7 +1590,7 @@
       </c>
       <c r="J25" s="5" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/Apple-EarPods-Headphones-Built-Control/dp/B0DCH8VDXF/ref=zg_bs_g_electronics_d_sccl_2/134-1095087-0412057</t>
+          <t>https://www.amazon.com/Apple-EarPods-Headphones-Built-Control/dp/B0DCH8VDXF/ref=zg_bs_g_electronics_d_sccl_2/143-7478900-6733836</t>
         </is>
       </c>
     </row>
@@ -1636,7 +1636,7 @@
       </c>
       <c r="J26" s="5" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/Apple-AirTag-2nd-Generation-Precision/dp/B0GJTFXNRX/ref=zg_bs_g_electronics_d_sccl_3/134-1095087-0412057</t>
+          <t>https://www.amazon.com/Apple-AirTag-2nd-Generation-Precision/dp/B0GJTFXNRX/ref=zg_bs_g_electronics_d_sccl_3/143-7478900-6733836</t>
         </is>
       </c>
     </row>
@@ -1724,7 +1724,7 @@
       </c>
       <c r="J28" s="5" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/Apple-Cancellation-Translation-Headphones-High-Fidelity/dp/B0FQFB8FMG/ref=zg_bs_g_electronics_d_sccl_4/134-1095087-0412057</t>
+          <t>https://www.amazon.com/Apple-Cancellation-Translation-Headphones-High-Fidelity/dp/B0FQFB8FMG/ref=zg_bs_g_electronics_d_sccl_4/143-7478900-6733836</t>
         </is>
       </c>
     </row>
@@ -1770,7 +1770,7 @@
       </c>
       <c r="J29" s="5" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/Roku-Streaming-Stick-HD-2025/dp/B0DXXYS4BJ/ref=zg_bs_g_electronics_d_sccl_5/134-1095087-0412057</t>
+          <t>https://www.amazon.com/Roku-Streaming-Stick-HD-2025/dp/B0DXXYS4BJ/ref=zg_bs_g_electronics_d_sccl_5/143-7478900-6733836</t>
         </is>
       </c>
     </row>
@@ -1816,7 +1816,7 @@
       </c>
       <c r="J30" s="5" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/amazon-fire-tv-stick-4K-select/dp/B0C6W3D4RM/ref=zg_bs_g_electronics_d_sccl_6/134-1095087-0412057</t>
+          <t>https://www.amazon.com/amazon-fire-tv-stick-4K-select/dp/B0C6W3D4RM/ref=zg_bs_g_electronics_d_sccl_6/143-7478900-6733836</t>
         </is>
       </c>
     </row>
@@ -2174,7 +2174,7 @@
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>goog stock</t>
+          <t>hugging face incident</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
@@ -2210,7 +2210,7 @@
       </c>
       <c r="J39" s="5" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?geo=US&amp;q=goog%20stock</t>
+          <t>https://trends.google.com/trends/explore?geo=US&amp;q=hugging%20face%20incident</t>
         </is>
       </c>
     </row>
@@ -2220,12 +2220,12 @@
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>aaron gordon</t>
+          <t>michael j fox</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>Beauty &amp; Personal Care</t>
+          <t>Phones &amp; Electronics</t>
         </is>
       </c>
       <c r="D40" s="3" t="n">
@@ -2246,17 +2246,17 @@
       </c>
       <c r="H40" s="4" t="inlineStr">
         <is>
-          <t>Đặt câu hỏi trúng nỗi đau thường ngày: 'Tại sao không ai nói cho tôi biết món đồ này sớm hơn?!'</t>
+          <t>So sánh âm thanh: 'Bật lọc tạp âm và nói chuyện giữa chợ ồn ào xem micro này xịn cỡ nào!'</t>
         </is>
       </c>
       <c r="I40" s="4" t="inlineStr">
         <is>
-          <t>Khách hàng mua sắm ngẫu hứng (Impulse Buyers) trên TikTok Shop US độ tuổi 18 - 45.</t>
+          <t>Học sinh, Gen Z làm bullet journal, Content Creator quay video TikTok / Vlog tại US.</t>
         </is>
       </c>
       <c r="J40" s="5" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?geo=US&amp;q=aaron%20gordon</t>
+          <t>https://trends.google.com/trends/explore?geo=US&amp;q=michael%20j%20fox</t>
         </is>
       </c>
     </row>
@@ -2266,12 +2266,12 @@
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>todd blanche joe digenova call</t>
+          <t>oracle layoffs</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>Gadgets &amp; Electronics</t>
+          <t>Beauty &amp; Personal Care</t>
         </is>
       </c>
       <c r="D41" s="3" t="n">
@@ -2302,7 +2302,7 @@
       </c>
       <c r="J41" s="5" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?geo=US&amp;q=todd%20blanche%20joe%20digenova%20call</t>
+          <t>https://trends.google.com/trends/explore?geo=US&amp;q=oracle%20layoffs</t>
         </is>
       </c>
     </row>
@@ -2312,7 +2312,7 @@
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>tropical storm weather forecast</t>
+          <t>mta</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
@@ -2338,17 +2338,17 @@
       </c>
       <c r="H42" s="4" t="inlineStr">
         <is>
-          <t>Đặt câu hỏi trúng nỗi đau thường ngày: 'Tại sao không ai nói cho tôi biết món đồ này sớm hơn?!'</t>
+          <t>Before &amp; After cận cảnh lỗ chân lông: 'Dừng ngay nếu bạn vẫn đang nặn mụn hoặc dùng tẩy tế bào chết hạt to!'</t>
         </is>
       </c>
       <c r="I42" s="4" t="inlineStr">
         <is>
-          <t>Khách hàng mua sắm ngẫu hứng (Impulse Buyers) trên TikTok Shop US độ tuổi 18 - 45.</t>
+          <t>Gen Z &amp; Millennials (18-34 tuổi), Chăm sóc da mụn, tín đồ Skincare &amp; 'Clean Girl' aesthetic US.</t>
         </is>
       </c>
       <c r="J42" s="5" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?geo=US&amp;q=tropical%20storm%20weather%20forecast</t>
+          <t>https://trends.google.com/trends/explore?geo=US&amp;q=mta</t>
         </is>
       </c>
     </row>
@@ -2358,7 +2358,7 @@
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>nvda</t>
+          <t>goog stock</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
@@ -2394,7 +2394,7 @@
       </c>
       <c r="J43" s="5" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?geo=US&amp;q=nvda</t>
+          <t>https://trends.google.com/trends/explore?geo=US&amp;q=goog%20stock</t>
         </is>
       </c>
     </row>
@@ -2404,7 +2404,7 @@
       </c>
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t>omaha weather</t>
+          <t>aaron gordon</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
@@ -2440,7 +2440,7 @@
       </c>
       <c r="J44" s="5" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?geo=US&amp;q=omaha%20weather</t>
+          <t>https://trends.google.com/trends/explore?geo=US&amp;q=aaron%20gordon</t>
         </is>
       </c>
     </row>
@@ -2450,12 +2450,12 @@
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>xrp price</t>
+          <t>todd blanche joe digenova call</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>Beauty &amp; Personal Care</t>
+          <t>Gadgets &amp; Electronics</t>
         </is>
       </c>
       <c r="D45" s="3" t="n">
@@ -2486,7 +2486,7 @@
       </c>
       <c r="J45" s="5" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?geo=US&amp;q=xrp%20price</t>
+          <t>https://trends.google.com/trends/explore?geo=US&amp;q=todd%20blanche%20joe%20digenova%20call</t>
         </is>
       </c>
     </row>
@@ -2496,7 +2496,7 @@
       </c>
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t>clarity act</t>
+          <t>tropical storm weather forecast</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
@@ -2532,7 +2532,7 @@
       </c>
       <c r="J46" s="5" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?geo=US&amp;q=clarity%20act</t>
+          <t>https://trends.google.com/trends/explore?geo=US&amp;q=tropical%20storm%20weather%20forecast</t>
         </is>
       </c>
     </row>
@@ -2542,12 +2542,12 @@
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>temperature</t>
+          <t>dominick bianchi</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>DIY, Craft &amp; POD</t>
+          <t>Beauty &amp; Personal Care</t>
         </is>
       </c>
       <c r="D47" s="3" t="n">
@@ -2568,17 +2568,17 @@
       </c>
       <c r="H47" s="4" t="inlineStr">
         <is>
-          <t>Quá trình máy khắc laser tên khách hàng lên gỗ/kim loại: 'Làm món quà độc nhất vô nhị tặng mẹ...'</t>
+          <t>Đặt câu hỏi trúng nỗi đau thường ngày: 'Tại sao không ai nói cho tôi biết món đồ này sớm hơn?!'</t>
         </is>
       </c>
       <c r="I47" s="4" t="inlineStr">
         <is>
-          <t>Người tìm quà tặng sinh nhật, kỷ niệm, Mother's Day, quà tân gia ý nghĩa quanh năm.</t>
+          <t>Khách hàng mua sắm ngẫu hứng (Impulse Buyers) trên TikTok Shop US độ tuổi 18 - 45.</t>
         </is>
       </c>
       <c r="J47" s="5" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?geo=US&amp;q=temperature</t>
+          <t>https://trends.google.com/trends/explore?geo=US&amp;q=dominick%20bianchi</t>
         </is>
       </c>
     </row>
@@ -5257,7 +5257,7 @@
       </c>
       <c r="I3" s="5" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/eos-Cashmere-Moisture-Lightweight-Non-Greasy/dp/B08KT2Z93D/ref=zg_bs_g_beauty_d_sccl_1/134-1095087-0412057</t>
+          <t>https://www.amazon.com/eos-Cashmere-Moisture-Lightweight-Non-Greasy/dp/B08KT2Z93D/ref=zg_bs_g_beauty_d_sccl_1/143-7478900-6733836</t>
         </is>
       </c>
     </row>
@@ -5298,7 +5298,7 @@
       </c>
       <c r="I4" s="5" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/Mighty-Patch-Hydrocolloid-Absorbing-count/dp/B074PVTPBW/ref=zg_bs_g_beauty_d_sccl_5/134-1095087-0412057</t>
+          <t>https://www.amazon.com/Mighty-Patch-Hydrocolloid-Absorbing-count/dp/B074PVTPBW/ref=zg_bs_g_beauty_d_sccl_5/143-7478900-6733836</t>
         </is>
       </c>
     </row>
@@ -5339,7 +5339,7 @@
       </c>
       <c r="I5" s="5" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/TERRO-T300-2-2-Pack-Liquid-Baits/dp/B00E4GACB8/ref=zg_bs_g_home-garden_d_sccl_1/134-1095087-0412057</t>
+          <t>https://www.amazon.com/TERRO-T300-2-2-Pack-Liquid-Baits/dp/B00E4GACB8/ref=zg_bs_g_home-garden_d_sccl_1/143-7478900-6733836</t>
         </is>
       </c>
     </row>
@@ -5380,7 +5380,7 @@
       </c>
       <c r="I6" s="5" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/Queen-Size-Piece-Sheet-Set/dp/B01M16WBW1/ref=zg_bs_g_home-garden_d_sccl_3/134-1095087-0412057</t>
+          <t>https://www.amazon.com/Queen-Size-Piece-Sheet-Set/dp/B01M16WBW1/ref=zg_bs_g_home-garden_d_sccl_3/143-7478900-6733836</t>
         </is>
       </c>
     </row>
@@ -5421,7 +5421,7 @@
       </c>
       <c r="I7" s="5" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/Dr-Elseys-Premium-Clumping-Litter/dp/B0009X29WK/ref=zg_bs_g_pet-supplies_d_sccl_1/134-1095087-0412057</t>
+          <t>https://www.amazon.com/Dr-Elseys-Premium-Clumping-Litter/dp/B0009X29WK/ref=zg_bs_g_pet-supplies_d_sccl_1/143-7478900-6733836</t>
         </is>
       </c>
     </row>
@@ -5462,7 +5462,7 @@
       </c>
       <c r="I8" s="5" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/Amazon-Basics-Leak-Proof-Quick-Dry-Absorbency/dp/B00MW8G62E/ref=zg_bs_g_pet-supplies_d_sccl_2/134-1095087-0412057</t>
+          <t>https://www.amazon.com/Amazon-Basics-Leak-Proof-Quick-Dry-Absorbency/dp/B00MW8G62E/ref=zg_bs_g_pet-supplies_d_sccl_2/143-7478900-6733836</t>
         </is>
       </c>
     </row>
@@ -5503,7 +5503,7 @@
       </c>
       <c r="I9" s="5" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/Purina-Fancy-Feast-Poultry-Collection/dp/B00JN9IWNG/ref=zg_bs_g_pet-supplies_d_sccl_3/134-1095087-0412057</t>
+          <t>https://www.amazon.com/Purina-Fancy-Feast-Poultry-Collection/dp/B00JN9IWNG/ref=zg_bs_g_pet-supplies_d_sccl_3/143-7478900-6733836</t>
         </is>
       </c>
     </row>
@@ -5544,7 +5544,7 @@
       </c>
       <c r="I10" s="5" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/Amazon-Basics-Cotton-Swabs-500ct/dp/B09541P9WH/ref=zg_bs_g_beauty_d_sccl_3/134-1095087-0412057</t>
+          <t>https://www.amazon.com/Amazon-Basics-Cotton-Swabs-500ct/dp/B09541P9WH/ref=zg_bs_g_beauty_d_sccl_3/143-7478900-6733836</t>
         </is>
       </c>
     </row>
@@ -5585,7 +5585,7 @@
       </c>
       <c r="I11" s="5" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/Clean-Skin-Club-Disposable-Sensitive/dp/B07PBXXNCY/ref=zg_bs_g_beauty_d_sccl_4/134-1095087-0412057</t>
+          <t>https://www.amazon.com/Clean-Skin-Club-Disposable-Sensitive/dp/B07PBXXNCY/ref=zg_bs_g_beauty_d_sccl_4/143-7478900-6733836</t>
         </is>
       </c>
     </row>
@@ -5626,7 +5626,7 @@
       </c>
       <c r="I12" s="5" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/Owala-FreeSip-Insulated-Stainless-BPA-Free/dp/B0BZYCJK89/ref=zg_bs_g_kitchen_d_sccl_1/134-1095087-0412057</t>
+          <t>https://www.amazon.com/Owala-FreeSip-Insulated-Stainless-BPA-Free/dp/B0BZYCJK89/ref=zg_bs_g_kitchen_d_sccl_1/143-7478900-6733836</t>
         </is>
       </c>
     </row>
@@ -5667,7 +5667,7 @@
       </c>
       <c r="I13" s="5" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/Owala-FreeSip-Insulated-Stainless-BPA-Free/dp/B0BZYCJK89/ref=zg_bs_g_home-garden_d_sccl_2/134-1095087-0412057</t>
+          <t>https://www.amazon.com/Owala-FreeSip-Insulated-Stainless-BPA-Free/dp/B0BZYCJK89/ref=zg_bs_g_home-garden_d_sccl_2/143-7478900-6733836</t>
         </is>
       </c>
     </row>
@@ -5708,7 +5708,7 @@
       </c>
       <c r="I14" s="5" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/Blink-Plus-Plan-monthly-auto-renewal/dp/B08JHCVHTY/ref=zg_bs_g_electronics_d_sccl_1/134-1095087-0412057</t>
+          <t>https://www.amazon.com/Blink-Plus-Plan-monthly-auto-renewal/dp/B08JHCVHTY/ref=zg_bs_g_electronics_d_sccl_1/143-7478900-6733836</t>
         </is>
       </c>
     </row>
@@ -5749,7 +5749,7 @@
       </c>
       <c r="I15" s="5" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/Owala-SmoothSip-Insulated-Stainless-Reusable/dp/B0DF3M7V3T/ref=zg_bs_g_kitchen_d_sccl_5/134-1095087-0412057</t>
+          <t>https://www.amazon.com/Owala-SmoothSip-Insulated-Stainless-Reusable/dp/B0DF3M7V3T/ref=zg_bs_g_kitchen_d_sccl_5/143-7478900-6733836</t>
         </is>
       </c>
     </row>
@@ -5790,7 +5790,7 @@
       </c>
       <c r="I16" s="5" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/Amazon-Basics-Cotton-Rounds-Count/dp/B09542G9ZN/ref=zg_bs_g_beauty_d_sccl_6/134-1095087-0412057</t>
+          <t>https://www.amazon.com/Amazon-Basics-Cotton-Rounds-Count/dp/B09542G9ZN/ref=zg_bs_g_beauty_d_sccl_6/143-7478900-6733836</t>
         </is>
       </c>
     </row>
@@ -5831,7 +5831,7 @@
       </c>
       <c r="I17" s="5" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/Etekcity-Multifunction-Stainless-Batteries-Included/dp/B0113UZJE2/ref=zg_bs_g_kitchen_d_sccl_4/134-1095087-0412057</t>
+          <t>https://www.amazon.com/Etekcity-Multifunction-Stainless-Batteries-Included/dp/B0113UZJE2/ref=zg_bs_g_kitchen_d_sccl_4/143-7478900-6733836</t>
         </is>
       </c>
     </row>
@@ -5872,7 +5872,7 @@
       </c>
       <c r="I18" s="5" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/Amazon-Basics-Microfiber-Lightweight-Wrinkle-free/dp/B0154ASID6/ref=zg_bs_g_home-garden_d_sccl_4/134-1095087-0412057</t>
+          <t>https://www.amazon.com/Amazon-Basics-Microfiber-Lightweight-Wrinkle-free/dp/B0154ASID6/ref=zg_bs_g_home-garden_d_sccl_4/143-7478900-6733836</t>
         </is>
       </c>
     </row>
@@ -5913,7 +5913,7 @@
       </c>
       <c r="I19" s="5" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/Electric-Flying-Insect-Trap-Starter/dp/B07T869RNY/ref=zg_bs_g_home-garden_d_sccl_6/134-1095087-0412057</t>
+          <t>https://www.amazon.com/Electric-Flying-Insect-Trap-Starter/dp/B07T869RNY/ref=zg_bs_g_home-garden_d_sccl_6/143-7478900-6733836</t>
         </is>
       </c>
     </row>
@@ -5954,7 +5954,7 @@
       </c>
       <c r="I20" s="5" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/Earth-Rated-Lavender-Scented-Completely/dp/B00BSYR7K8/ref=zg_bs_g_pet-supplies_d_sccl_5/134-1095087-0412057</t>
+          <t>https://www.amazon.com/Earth-Rated-Lavender-Scented-Completely/dp/B00BSYR7K8/ref=zg_bs_g_pet-supplies_d_sccl_5/143-7478900-6733836</t>
         </is>
       </c>
     </row>
@@ -5995,7 +5995,7 @@
       </c>
       <c r="I21" s="5" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/Toaster-Fits-anywhereTM-Kitchenware-Setting-Removable/dp/B0CYJBB2JQ/ref=zg_bs_g_kitchen_d_sccl_6/134-1095087-0412057</t>
+          <t>https://www.amazon.com/Toaster-Fits-anywhereTM-Kitchenware-Setting-Removable/dp/B0CYJBB2JQ/ref=zg_bs_g_kitchen_d_sccl_6/143-7478900-6733836</t>
         </is>
       </c>
     </row>
@@ -6036,7 +6036,7 @@
       </c>
       <c r="I22" s="5" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/ZEVO-Flying-Insect-Refills-Indoor/dp/B0C3FTCYZL/ref=zg_bs_g_home-garden_d_sccl_5/134-1095087-0412057</t>
+          <t>https://www.amazon.com/ZEVO-Flying-Insect-Refills-Indoor/dp/B0C3FTCYZL/ref=zg_bs_g_home-garden_d_sccl_5/143-7478900-6733836</t>
         </is>
       </c>
     </row>
@@ -6077,7 +6077,7 @@
       </c>
       <c r="I23" s="5" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/INABA-Grain-Free-Lickable-Squeezable-Vitamin/dp/B0B52D7BBD/ref=zg_bs_g_pet-supplies_d_sccl_4/134-1095087-0412057</t>
+          <t>https://www.amazon.com/INABA-Grain-Free-Lickable-Squeezable-Vitamin/dp/B0B52D7BBD/ref=zg_bs_g_pet-supplies_d_sccl_4/143-7478900-6733836</t>
         </is>
       </c>
     </row>
@@ -6118,7 +6118,7 @@
       </c>
       <c r="I24" s="5" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/Greenies-Pill-Pockets-Ingredients-Nutrients/dp/B008GRONV6/ref=zg_bs_g_pet-supplies_d_sccl_6/134-1095087-0412057</t>
+          <t>https://www.amazon.com/Greenies-Pill-Pockets-Ingredients-Nutrients/dp/B008GRONV6/ref=zg_bs_g_pet-supplies_d_sccl_6/143-7478900-6733836</t>
         </is>
       </c>
     </row>
@@ -7556,7 +7556,7 @@
       </c>
       <c r="L21" s="5" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/STANLEY-Quencher-State-Tumbler-Quartz/dp/B0CP9Z56SW/ref=zg_bs_g_kitchen_d_sccl_2/134-1095087-0412057</t>
+          <t>https://www.amazon.com/STANLEY-Quencher-State-Tumbler-Quartz/dp/B0CP9Z56SW/ref=zg_bs_g_kitchen_d_sccl_2/143-7478900-6733836</t>
         </is>
       </c>
     </row>
@@ -7610,7 +7610,7 @@
       </c>
       <c r="L22" s="5" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/Medicube-Zero-Pore-Pads-Dual-Textured/dp/B09V7Z4TJG/ref=zg_bs_g_beauty_d_sccl_2/134-1095087-0412057</t>
+          <t>https://www.amazon.com/Medicube-Zero-Pore-Pads-Dual-Textured/dp/B09V7Z4TJG/ref=zg_bs_g_beauty_d_sccl_2/143-7478900-6733836</t>
         </is>
       </c>
     </row>
@@ -7664,7 +7664,7 @@
       </c>
       <c r="L23" s="5" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/HydroJug-Traveler-Resistant-Bottle-Reusable-Insulated/dp/B0CQVWT2NH/ref=zg_bs_g_kitchen_d_sccl_3/134-1095087-0412057</t>
+          <t>https://www.amazon.com/HydroJug-Traveler-Resistant-Bottle-Reusable-Insulated/dp/B0CQVWT2NH/ref=zg_bs_g_kitchen_d_sccl_3/143-7478900-6733836</t>
         </is>
       </c>
     </row>
@@ -7768,7 +7768,7 @@
       </c>
       <c r="L25" s="5" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/eos-Cashmere-Moisture-Lightweight-Non-Greasy/dp/B08KT2Z93D/ref=zg_bs_g_beauty_d_sccl_1/134-1095087-0412057</t>
+          <t>https://www.amazon.com/eos-Cashmere-Moisture-Lightweight-Non-Greasy/dp/B08KT2Z93D/ref=zg_bs_g_beauty_d_sccl_1/143-7478900-6733836</t>
         </is>
       </c>
     </row>
@@ -7822,7 +7822,7 @@
       </c>
       <c r="L26" s="5" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/Mighty-Patch-Hydrocolloid-Absorbing-count/dp/B074PVTPBW/ref=zg_bs_g_beauty_d_sccl_5/134-1095087-0412057</t>
+          <t>https://www.amazon.com/Mighty-Patch-Hydrocolloid-Absorbing-count/dp/B074PVTPBW/ref=zg_bs_g_beauty_d_sccl_5/143-7478900-6733836</t>
         </is>
       </c>
     </row>
@@ -7876,7 +7876,7 @@
       </c>
       <c r="L27" s="5" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/TERRO-T300-2-2-Pack-Liquid-Baits/dp/B00E4GACB8/ref=zg_bs_g_home-garden_d_sccl_1/134-1095087-0412057</t>
+          <t>https://www.amazon.com/TERRO-T300-2-2-Pack-Liquid-Baits/dp/B00E4GACB8/ref=zg_bs_g_home-garden_d_sccl_1/143-7478900-6733836</t>
         </is>
       </c>
     </row>
@@ -7930,7 +7930,7 @@
       </c>
       <c r="L28" s="5" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/Queen-Size-Piece-Sheet-Set/dp/B01M16WBW1/ref=zg_bs_g_home-garden_d_sccl_3/134-1095087-0412057</t>
+          <t>https://www.amazon.com/Queen-Size-Piece-Sheet-Set/dp/B01M16WBW1/ref=zg_bs_g_home-garden_d_sccl_3/143-7478900-6733836</t>
         </is>
       </c>
     </row>
@@ -7984,7 +7984,7 @@
       </c>
       <c r="L29" s="5" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/Dr-Elseys-Premium-Clumping-Litter/dp/B0009X29WK/ref=zg_bs_g_pet-supplies_d_sccl_1/134-1095087-0412057</t>
+          <t>https://www.amazon.com/Dr-Elseys-Premium-Clumping-Litter/dp/B0009X29WK/ref=zg_bs_g_pet-supplies_d_sccl_1/143-7478900-6733836</t>
         </is>
       </c>
     </row>
@@ -8038,7 +8038,7 @@
       </c>
       <c r="L30" s="5" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/Amazon-Basics-Leak-Proof-Quick-Dry-Absorbency/dp/B00MW8G62E/ref=zg_bs_g_pet-supplies_d_sccl_2/134-1095087-0412057</t>
+          <t>https://www.amazon.com/Amazon-Basics-Leak-Proof-Quick-Dry-Absorbency/dp/B00MW8G62E/ref=zg_bs_g_pet-supplies_d_sccl_2/143-7478900-6733836</t>
         </is>
       </c>
     </row>
@@ -8092,7 +8092,7 @@
       </c>
       <c r="L31" s="5" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/Purina-Fancy-Feast-Poultry-Collection/dp/B00JN9IWNG/ref=zg_bs_g_pet-supplies_d_sccl_3/134-1095087-0412057</t>
+          <t>https://www.amazon.com/Purina-Fancy-Feast-Poultry-Collection/dp/B00JN9IWNG/ref=zg_bs_g_pet-supplies_d_sccl_3/143-7478900-6733836</t>
         </is>
       </c>
     </row>
@@ -8146,7 +8146,7 @@
       </c>
       <c r="L32" s="5" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/Amazon-Basics-Cotton-Swabs-500ct/dp/B09541P9WH/ref=zg_bs_g_beauty_d_sccl_3/134-1095087-0412057</t>
+          <t>https://www.amazon.com/Amazon-Basics-Cotton-Swabs-500ct/dp/B09541P9WH/ref=zg_bs_g_beauty_d_sccl_3/143-7478900-6733836</t>
         </is>
       </c>
     </row>
@@ -8200,7 +8200,7 @@
       </c>
       <c r="L33" s="5" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/Clean-Skin-Club-Disposable-Sensitive/dp/B07PBXXNCY/ref=zg_bs_g_beauty_d_sccl_4/134-1095087-0412057</t>
+          <t>https://www.amazon.com/Clean-Skin-Club-Disposable-Sensitive/dp/B07PBXXNCY/ref=zg_bs_g_beauty_d_sccl_4/143-7478900-6733836</t>
         </is>
       </c>
     </row>
@@ -8254,7 +8254,7 @@
       </c>
       <c r="L34" s="5" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/Owala-FreeSip-Insulated-Stainless-BPA-Free/dp/B0BZYCJK89/ref=zg_bs_g_kitchen_d_sccl_1/134-1095087-0412057</t>
+          <t>https://www.amazon.com/Owala-FreeSip-Insulated-Stainless-BPA-Free/dp/B0BZYCJK89/ref=zg_bs_g_kitchen_d_sccl_1/143-7478900-6733836</t>
         </is>
       </c>
     </row>
@@ -8308,7 +8308,7 @@
       </c>
       <c r="L35" s="5" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/Owala-FreeSip-Insulated-Stainless-BPA-Free/dp/B0BZYCJK89/ref=zg_bs_g_home-garden_d_sccl_2/134-1095087-0412057</t>
+          <t>https://www.amazon.com/Owala-FreeSip-Insulated-Stainless-BPA-Free/dp/B0BZYCJK89/ref=zg_bs_g_home-garden_d_sccl_2/143-7478900-6733836</t>
         </is>
       </c>
     </row>
@@ -8362,7 +8362,7 @@
       </c>
       <c r="L36" s="5" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/Blink-Plus-Plan-monthly-auto-renewal/dp/B08JHCVHTY/ref=zg_bs_g_electronics_d_sccl_1/134-1095087-0412057</t>
+          <t>https://www.amazon.com/Blink-Plus-Plan-monthly-auto-renewal/dp/B08JHCVHTY/ref=zg_bs_g_electronics_d_sccl_1/143-7478900-6733836</t>
         </is>
       </c>
     </row>
@@ -8416,7 +8416,7 @@
       </c>
       <c r="L37" s="5" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/Owala-SmoothSip-Insulated-Stainless-Reusable/dp/B0DF3M7V3T/ref=zg_bs_g_kitchen_d_sccl_5/134-1095087-0412057</t>
+          <t>https://www.amazon.com/Owala-SmoothSip-Insulated-Stainless-Reusable/dp/B0DF3M7V3T/ref=zg_bs_g_kitchen_d_sccl_5/143-7478900-6733836</t>
         </is>
       </c>
     </row>
@@ -8470,7 +8470,7 @@
       </c>
       <c r="L38" s="5" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/Apple-EarPods-Headphones-Built-Control/dp/B0DCH8VDXF/ref=zg_bs_g_electronics_d_sccl_2/134-1095087-0412057</t>
+          <t>https://www.amazon.com/Apple-EarPods-Headphones-Built-Control/dp/B0DCH8VDXF/ref=zg_bs_g_electronics_d_sccl_2/143-7478900-6733836</t>
         </is>
       </c>
     </row>
@@ -8524,7 +8524,7 @@
       </c>
       <c r="L39" s="5" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/Apple-AirTag-2nd-Generation-Precision/dp/B0GJTFXNRX/ref=zg_bs_g_electronics_d_sccl_3/134-1095087-0412057</t>
+          <t>https://www.amazon.com/Apple-AirTag-2nd-Generation-Precision/dp/B0GJTFXNRX/ref=zg_bs_g_electronics_d_sccl_3/143-7478900-6733836</t>
         </is>
       </c>
     </row>
@@ -8628,7 +8628,7 @@
       </c>
       <c r="L41" s="5" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/Amazon-Basics-Cotton-Rounds-Count/dp/B09542G9ZN/ref=zg_bs_g_beauty_d_sccl_6/134-1095087-0412057</t>
+          <t>https://www.amazon.com/Amazon-Basics-Cotton-Rounds-Count/dp/B09542G9ZN/ref=zg_bs_g_beauty_d_sccl_6/143-7478900-6733836</t>
         </is>
       </c>
     </row>
@@ -8682,7 +8682,7 @@
       </c>
       <c r="L42" s="5" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/Etekcity-Multifunction-Stainless-Batteries-Included/dp/B0113UZJE2/ref=zg_bs_g_kitchen_d_sccl_4/134-1095087-0412057</t>
+          <t>https://www.amazon.com/Etekcity-Multifunction-Stainless-Batteries-Included/dp/B0113UZJE2/ref=zg_bs_g_kitchen_d_sccl_4/143-7478900-6733836</t>
         </is>
       </c>
     </row>
@@ -8736,7 +8736,7 @@
       </c>
       <c r="L43" s="5" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/Amazon-Basics-Microfiber-Lightweight-Wrinkle-free/dp/B0154ASID6/ref=zg_bs_g_home-garden_d_sccl_4/134-1095087-0412057</t>
+          <t>https://www.amazon.com/Amazon-Basics-Microfiber-Lightweight-Wrinkle-free/dp/B0154ASID6/ref=zg_bs_g_home-garden_d_sccl_4/143-7478900-6733836</t>
         </is>
       </c>
     </row>
@@ -8790,7 +8790,7 @@
       </c>
       <c r="L44" s="5" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/Electric-Flying-Insect-Trap-Starter/dp/B07T869RNY/ref=zg_bs_g_home-garden_d_sccl_6/134-1095087-0412057</t>
+          <t>https://www.amazon.com/Electric-Flying-Insect-Trap-Starter/dp/B07T869RNY/ref=zg_bs_g_home-garden_d_sccl_6/143-7478900-6733836</t>
         </is>
       </c>
     </row>
@@ -8844,7 +8844,7 @@
       </c>
       <c r="L45" s="5" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/Earth-Rated-Lavender-Scented-Completely/dp/B00BSYR7K8/ref=zg_bs_g_pet-supplies_d_sccl_5/134-1095087-0412057</t>
+          <t>https://www.amazon.com/Earth-Rated-Lavender-Scented-Completely/dp/B00BSYR7K8/ref=zg_bs_g_pet-supplies_d_sccl_5/143-7478900-6733836</t>
         </is>
       </c>
     </row>
@@ -8898,7 +8898,7 @@
       </c>
       <c r="L46" s="5" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/Toaster-Fits-anywhereTM-Kitchenware-Setting-Removable/dp/B0CYJBB2JQ/ref=zg_bs_g_kitchen_d_sccl_6/134-1095087-0412057</t>
+          <t>https://www.amazon.com/Toaster-Fits-anywhereTM-Kitchenware-Setting-Removable/dp/B0CYJBB2JQ/ref=zg_bs_g_kitchen_d_sccl_6/143-7478900-6733836</t>
         </is>
       </c>
     </row>
@@ -8952,7 +8952,7 @@
       </c>
       <c r="L47" s="5" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/ZEVO-Flying-Insect-Refills-Indoor/dp/B0C3FTCYZL/ref=zg_bs_g_home-garden_d_sccl_5/134-1095087-0412057</t>
+          <t>https://www.amazon.com/ZEVO-Flying-Insect-Refills-Indoor/dp/B0C3FTCYZL/ref=zg_bs_g_home-garden_d_sccl_5/143-7478900-6733836</t>
         </is>
       </c>
     </row>
@@ -9006,7 +9006,7 @@
       </c>
       <c r="L48" s="5" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/INABA-Grain-Free-Lickable-Squeezable-Vitamin/dp/B0B52D7BBD/ref=zg_bs_g_pet-supplies_d_sccl_4/134-1095087-0412057</t>
+          <t>https://www.amazon.com/INABA-Grain-Free-Lickable-Squeezable-Vitamin/dp/B0B52D7BBD/ref=zg_bs_g_pet-supplies_d_sccl_4/143-7478900-6733836</t>
         </is>
       </c>
     </row>
@@ -9060,7 +9060,7 @@
       </c>
       <c r="L49" s="5" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/Greenies-Pill-Pockets-Ingredients-Nutrients/dp/B008GRONV6/ref=zg_bs_g_pet-supplies_d_sccl_6/134-1095087-0412057</t>
+          <t>https://www.amazon.com/Greenies-Pill-Pockets-Ingredients-Nutrients/dp/B008GRONV6/ref=zg_bs_g_pet-supplies_d_sccl_6/143-7478900-6733836</t>
         </is>
       </c>
     </row>
@@ -9114,7 +9114,7 @@
       </c>
       <c r="L50" s="5" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/Apple-Cancellation-Translation-Headphones-High-Fidelity/dp/B0FQFB8FMG/ref=zg_bs_g_electronics_d_sccl_4/134-1095087-0412057</t>
+          <t>https://www.amazon.com/Apple-Cancellation-Translation-Headphones-High-Fidelity/dp/B0FQFB8FMG/ref=zg_bs_g_electronics_d_sccl_4/143-7478900-6733836</t>
         </is>
       </c>
     </row>
@@ -9168,7 +9168,7 @@
       </c>
       <c r="L51" s="5" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/Roku-Streaming-Stick-HD-2025/dp/B0DXXYS4BJ/ref=zg_bs_g_electronics_d_sccl_5/134-1095087-0412057</t>
+          <t>https://www.amazon.com/Roku-Streaming-Stick-HD-2025/dp/B0DXXYS4BJ/ref=zg_bs_g_electronics_d_sccl_5/143-7478900-6733836</t>
         </is>
       </c>
     </row>
@@ -9222,7 +9222,7 @@
       </c>
       <c r="L52" s="5" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/amazon-fire-tv-stick-4K-select/dp/B0C6W3D4RM/ref=zg_bs_g_electronics_d_sccl_6/134-1095087-0412057</t>
+          <t>https://www.amazon.com/amazon-fire-tv-stick-4K-select/dp/B0C6W3D4RM/ref=zg_bs_g_electronics_d_sccl_6/143-7478900-6733836</t>
         </is>
       </c>
     </row>
@@ -9644,7 +9644,7 @@
       </c>
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t>goog stock</t>
+          <t>hugging face incident</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
@@ -9688,7 +9688,7 @@
       </c>
       <c r="L61" s="5" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?geo=US&amp;q=goog%20stock</t>
+          <t>https://trends.google.com/trends/explore?geo=US&amp;q=hugging%20face%20incident</t>
         </is>
       </c>
     </row>
@@ -9698,7 +9698,7 @@
       </c>
       <c r="B62" s="4" t="inlineStr">
         <is>
-          <t>aaron gordon</t>
+          <t>michael j fox</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
@@ -9708,7 +9708,7 @@
       </c>
       <c r="D62" s="4" t="inlineStr">
         <is>
-          <t>Beauty &amp; Personal Care</t>
+          <t>Phones &amp; Electronics</t>
         </is>
       </c>
       <c r="E62" s="3" t="n">
@@ -9737,12 +9737,12 @@
       </c>
       <c r="K62" s="4" t="inlineStr">
         <is>
-          <t>TikTok Made Me Buy It / Honest Review</t>
+          <t>Side-by-side Live Demo &amp; Unboxing ASMR</t>
         </is>
       </c>
       <c r="L62" s="5" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?geo=US&amp;q=aaron%20gordon</t>
+          <t>https://trends.google.com/trends/explore?geo=US&amp;q=michael%20j%20fox</t>
         </is>
       </c>
     </row>
@@ -9752,7 +9752,7 @@
       </c>
       <c r="B63" s="4" t="inlineStr">
         <is>
-          <t>todd blanche joe digenova call</t>
+          <t>oracle layoffs</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
@@ -9762,7 +9762,7 @@
       </c>
       <c r="D63" s="4" t="inlineStr">
         <is>
-          <t>Gadgets &amp; Electronics</t>
+          <t>Beauty &amp; Personal Care</t>
         </is>
       </c>
       <c r="E63" s="3" t="n">
@@ -9796,7 +9796,7 @@
       </c>
       <c r="L63" s="5" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?geo=US&amp;q=todd%20blanche%20joe%20digenova%20call</t>
+          <t>https://trends.google.com/trends/explore?geo=US&amp;q=oracle%20layoffs</t>
         </is>
       </c>
     </row>
@@ -9806,7 +9806,7 @@
       </c>
       <c r="B64" s="4" t="inlineStr">
         <is>
-          <t>tropical storm weather forecast</t>
+          <t>mta</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
@@ -9845,12 +9845,12 @@
       </c>
       <c r="K64" s="4" t="inlineStr">
         <is>
-          <t>TikTok Made Me Buy It / Honest Review</t>
+          <t>Before/After Macro Skin Texture Zoom (Cận cảnh bề mặt da)</t>
         </is>
       </c>
       <c r="L64" s="5" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?geo=US&amp;q=tropical%20storm%20weather%20forecast</t>
+          <t>https://trends.google.com/trends/explore?geo=US&amp;q=mta</t>
         </is>
       </c>
     </row>
@@ -9860,7 +9860,7 @@
       </c>
       <c r="B65" s="4" t="inlineStr">
         <is>
-          <t>nvda</t>
+          <t>goog stock</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
@@ -9904,7 +9904,7 @@
       </c>
       <c r="L65" s="5" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?geo=US&amp;q=nvda</t>
+          <t>https://trends.google.com/trends/explore?geo=US&amp;q=goog%20stock</t>
         </is>
       </c>
     </row>
@@ -9914,7 +9914,7 @@
       </c>
       <c r="B66" s="4" t="inlineStr">
         <is>
-          <t>omaha weather</t>
+          <t>aaron gordon</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
@@ -9958,7 +9958,7 @@
       </c>
       <c r="L66" s="5" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?geo=US&amp;q=omaha%20weather</t>
+          <t>https://trends.google.com/trends/explore?geo=US&amp;q=aaron%20gordon</t>
         </is>
       </c>
     </row>
@@ -9968,7 +9968,7 @@
       </c>
       <c r="B67" s="4" t="inlineStr">
         <is>
-          <t>xrp price</t>
+          <t>todd blanche joe digenova call</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
@@ -9978,7 +9978,7 @@
       </c>
       <c r="D67" s="4" t="inlineStr">
         <is>
-          <t>Beauty &amp; Personal Care</t>
+          <t>Gadgets &amp; Electronics</t>
         </is>
       </c>
       <c r="E67" s="3" t="n">
@@ -10012,7 +10012,7 @@
       </c>
       <c r="L67" s="5" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?geo=US&amp;q=xrp%20price</t>
+          <t>https://trends.google.com/trends/explore?geo=US&amp;q=todd%20blanche%20joe%20digenova%20call</t>
         </is>
       </c>
     </row>
@@ -10022,7 +10022,7 @@
       </c>
       <c r="B68" s="4" t="inlineStr">
         <is>
-          <t>clarity act</t>
+          <t>tropical storm weather forecast</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
@@ -10066,7 +10066,7 @@
       </c>
       <c r="L68" s="5" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?geo=US&amp;q=clarity%20act</t>
+          <t>https://trends.google.com/trends/explore?geo=US&amp;q=tropical%20storm%20weather%20forecast</t>
         </is>
       </c>
     </row>
@@ -10076,7 +10076,7 @@
       </c>
       <c r="B69" s="4" t="inlineStr">
         <is>
-          <t>temperature</t>
+          <t>dominick bianchi</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
@@ -10086,7 +10086,7 @@
       </c>
       <c r="D69" s="4" t="inlineStr">
         <is>
-          <t>DIY, Craft &amp; POD</t>
+          <t>Beauty &amp; Personal Care</t>
         </is>
       </c>
       <c r="E69" s="3" t="n">
@@ -10115,12 +10115,12 @@
       </c>
       <c r="K69" s="4" t="inlineStr">
         <is>
-          <t>Behind The Scenes Crafting &amp; Emotional Gift Unboxing</t>
+          <t>TikTok Made Me Buy It / Honest Review</t>
         </is>
       </c>
       <c r="L69" s="5" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?geo=US&amp;q=temperature</t>
+          <t>https://trends.google.com/trends/explore?geo=US&amp;q=dominick%20bianchi</t>
         </is>
       </c>
     </row>
@@ -13723,7 +13723,7 @@
       </c>
       <c r="L3" s="5" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@thebeachwaver/video/741982736192</t>
+          <t>https://www.tiktok.com/search?q=Beachwaver%20S1.25%20Dual%20Voltage%20Automatic%20Rotating%20Ceramic%20Curling%20Wand</t>
         </is>
       </c>
     </row>
@@ -13781,7 +13781,7 @@
       </c>
       <c r="L4" s="5" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@cleanwithme_asmr/video/7410982736192</t>
+          <t>https://www.tiktok.com/search?q=thebeachwaver%20Electric%20Spin%20Scrubber%20360%20Cordless%20Power%20Shower%20Cleaner%20Brush</t>
         </is>
       </c>
     </row>
@@ -13811,7 +13811,7 @@
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>@owala_official</t>
+          <t>@owalalife</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
@@ -13839,7 +13839,7 @@
       </c>
       <c r="L5" s="5" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@owala_official/video/749982736192</t>
+          <t>https://www.tiktok.com/search?q=cleanwithme_asmr%20Owala%20FreeSip%2032oz%20Insulated%20Stainless%20Steel%20Water%20Bottle%20Tumbler</t>
         </is>
       </c>
     </row>
@@ -13869,7 +13869,7 @@
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>@keychron_official</t>
+          <t>@keychron</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
@@ -13897,7 +13897,7 @@
       </c>
       <c r="L6" s="5" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@keychron_official/video/7415982736192</t>
+          <t>https://www.tiktok.com/search?q=owalalife%20Wireless%20Custom%20Mechanical%20Keyboard%20RGB%20Hot-Swappable%20Gateron%20Pro</t>
         </is>
       </c>
     </row>
@@ -13955,7 +13955,7 @@
       </c>
       <c r="L7" s="5" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@ergonomic_living/video/7418982736192</t>
+          <t>https://www.tiktok.com/search?q=keychron%20Breathable%20Mesh%20Ergonomic%20Office%20Chair%20with%203D%20Lumbar%20Support</t>
         </is>
       </c>
     </row>
@@ -14013,7 +14013,7 @@
       </c>
       <c r="L8" s="5" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@thebeachwaver/video/7534817293019</t>
+          <t>https://www.tiktok.com/search?q=ergonomic_living%20Beachwaver%20S1.25%20Dual%20Voltage%20Automatic%20Rotating%20Ceramic%20Curling%20Wand</t>
         </is>
       </c>
     </row>
@@ -14071,7 +14071,7 @@
       </c>
       <c r="L9" s="5" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@led_vibes_room/video/7420982736192</t>
+          <t>https://www.tiktok.com/search?q=thebeachwaver_reviews%20Smart%20WiFi%20COB%20Flexible%20Neon%20Rope%20LED%20Strip%20Light%2016.4ft%20Music%20Sync</t>
         </is>
       </c>
     </row>
@@ -14129,7 +14129,7 @@
       </c>
       <c r="L10" s="5" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@cleanwithme_asmr/video/7543817293019</t>
+          <t>https://www.tiktok.com/search?q=led_vibes_room%20Electric%20Spin%20Scrubber%20360%20Cordless%20Power%20Shower%20Cleaner%20Brush</t>
         </is>
       </c>
     </row>
@@ -14187,7 +14187,7 @@
       </c>
       <c r="L11" s="5" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@wavytalkofficial/video/744982736192</t>
+          <t>https://www.tiktok.com/search?q=cleanwithme_asmr_reviews%20Wavytalk%20Thermal%20Round%20Brush%201.5%20Inch%20Ceramic%20Heated%20Blowout%20Brush</t>
         </is>
       </c>
     </row>
@@ -14245,7 +14245,7 @@
       </c>
       <c r="L12" s="5" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@owala_official/video/7542817293019</t>
+          <t>https://www.tiktok.com/search?q=wavytalkofficial%20Owala%20FreeSip%2032oz%20Insulated%20Stainless%20Steel%20Water%20Bottle%20Tumbler</t>
         </is>
       </c>
     </row>
@@ -14303,7 +14303,7 @@
       </c>
       <c r="L13" s="5" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@urban_threads_men/video/7425982736192</t>
+          <t>https://www.tiktok.com/search?q=owala_official_reviews%20Baggy%20Parachute%20Cargo%20Streetwear%20Pants%20Multi-Pocket%20Tactical%20Fit</t>
         </is>
       </c>
     </row>
@@ -14361,7 +14361,7 @@
       </c>
       <c r="L14" s="5" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@personalized_glam/video/7422982736192</t>
+          <t>https://www.tiktok.com/search?q=urban_threads_men%20Custom%20Birth%20Flower%20Bar%20Name%20Pendant%20Necklace%2018K%20Gold%20Plated</t>
         </is>
       </c>
     </row>
@@ -14419,7 +14419,7 @@
       </c>
       <c r="L15" s="5" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@health_gurus_us/video/7419982736192</t>
+          <t>https://www.tiktok.com/search?q=personalized_glam%20Magnesium%20Glycinate%20Deep%20Sleep%20Relax%20Gummies%2060ct%20High%20Absorption</t>
         </is>
       </c>
     </row>
@@ -14477,7 +14477,7 @@
       </c>
       <c r="L16" s="5" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@halara_official/video/745982736192</t>
+          <t>https://www.tiktok.com/search?q=health_gurus_us%20Halara%20High%20Waisted%20Crossover%20Side%20Pocket%20Flared%20Casual%20Leggings</t>
         </is>
       </c>
     </row>
@@ -14535,7 +14535,7 @@
       </c>
       <c r="L17" s="5" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@cloud_cushion_slides/video/7428982736192</t>
+          <t>https://www.tiktok.com/search?q=halara_official%20Ultra-Thick%20Cloud%20Cushion%20Ergonomic%20Recovery%20Slides%20Anti-Slip</t>
         </is>
       </c>
     </row>
@@ -14593,7 +14593,7 @@
       </c>
       <c r="L18" s="5" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@keychron_official/video/7548817293019</t>
+          <t>https://www.tiktok.com/search?q=cloud_cushion_slides%20Wireless%20Custom%20Mechanical%20Keyboard%20RGB%20Hot-Swappable%20Gateron%20Pro</t>
         </is>
       </c>
     </row>
@@ -14651,7 +14651,7 @@
       </c>
       <c r="L19" s="5" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@ergonomic_living/video/7551817293019</t>
+          <t>https://www.tiktok.com/search?q=keychron_official_reviews%20Breathable%20Mesh%20Ergonomic%20Office%20Chair%20with%203D%20Lumbar%20Support</t>
         </is>
       </c>
     </row>
@@ -14709,7 +14709,7 @@
       </c>
       <c r="L20" s="5" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@vintage_vault_us/video/7427982736192</t>
+          <t>https://www.tiktok.com/search?q=ergonomic_living_reviews%20Authentic%2090s%20Carhartt%20Detroit%20Jacket%20Vintage%20Distressed%20Blanket%20Lined</t>
         </is>
       </c>
     </row>
@@ -14767,7 +14767,7 @@
       </c>
       <c r="L21" s="5" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@tartecosmetics/video/746982736192</t>
+          <t>https://www.tiktok.com/search?q=vintage_vault_us%20Tarte%20Maracuja%20Juicy%20Lip%20Plump%20Viral%20Hydrating%20Gloss</t>
         </is>
       </c>
     </row>
@@ -14825,7 +14825,7 @@
       </c>
       <c r="L22" s="5" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@brookemonk_/video/748982736192</t>
+          <t>https://www.tiktok.com/search?q=tartecosmetics%20Anker%20MagGo%20Qi2%20Ultra-Fast%20Magnetic%20Power%20Bank%2010000mAh</t>
         </is>
       </c>
     </row>
@@ -14883,7 +14883,7 @@
       </c>
       <c r="L23" s="5" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@led_vibes_room/video/7553817293019</t>
+          <t>https://www.tiktok.com/search?q=brookemonk_%20Smart%20WiFi%20COB%20Flexible%20Neon%20Rope%20LED%20Strip%20Light%2016.4ft%20Music%20Sync</t>
         </is>
       </c>
     </row>
@@ -14941,7 +14941,7 @@
       </c>
       <c r="L24" s="5" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@neatfreak_home/video/7421982736192</t>
+          <t>https://www.tiktok.com/search?q=led_vibes_room_reviews%20Foldable%20Handheld%20Garment%20Clothes%20Steamer%201000W%20Fast%20Heat</t>
         </is>
       </c>
     </row>
@@ -14999,7 +14999,7 @@
       </c>
       <c r="L25" s="5" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@everyday_carry_us/video/7424982736192</t>
+          <t>https://www.tiktok.com/search?q=neatfreak_home%20Everyday%20Everywhere%20Water-Resistant%20Crossbody%20Belt%20Bag%20Adjustable</t>
         </is>
       </c>
     </row>
@@ -15057,7 +15057,7 @@
       </c>
       <c r="L26" s="5" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@wavytalkofficial/video/7537817293019</t>
+          <t>https://www.tiktok.com/search?q=everyday_carry_us%20Wavytalk%20Thermal%20Round%20Brush%201.5%20Inch%20Ceramic%20Heated%20Blowout%20Brush</t>
         </is>
       </c>
     </row>
@@ -15115,7 +15115,7 @@
       </c>
       <c r="L27" s="5" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@gurunanda.official/video/742982736192</t>
+          <t>https://www.tiktok.com/search?q=wavytalkofficial_reviews%20GuruNanda%20Cocomint%20Coconut%20Pulling%20Oil%20with%20Tongue%20Scraper</t>
         </is>
       </c>
     </row>
@@ -15173,7 +15173,7 @@
       </c>
       <c r="L28" s="5" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@urban_threads_men/video/7558817293019</t>
+          <t>https://www.tiktok.com/search?q=gurunanda.official%20Baggy%20Parachute%20Cargo%20Streetwear%20Pants%20Multi-Pocket%20Tactical%20Fit</t>
         </is>
       </c>
     </row>
@@ -15231,7 +15231,7 @@
       </c>
       <c r="L29" s="5" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@personalized_glam/video/7555817293019</t>
+          <t>https://www.tiktok.com/search?q=urban_threads_men_reviews%20Custom%20Birth%20Flower%20Bar%20Name%20Pendant%20Necklace%2018K%20Gold%20Plated</t>
         </is>
       </c>
     </row>
@@ -15289,7 +15289,7 @@
       </c>
       <c r="L30" s="5" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@health_gurus_us/video/7552817293019</t>
+          <t>https://www.tiktok.com/search?q=personalized_glam_reviews%20Magnesium%20Glycinate%20Deep%20Sleep%20Relax%20Gummies%2060ct%20High%20Absorption</t>
         </is>
       </c>
     </row>
@@ -15347,7 +15347,7 @@
       </c>
       <c r="L31" s="5" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@tool_master_diy/video/7431982736192</t>
+          <t>https://www.tiktok.com/search?q=health_gurus_us_reviews%204V%20Cordless%20Electric%20Screwdriver%20Rechargeable%2036%20Bit%20Set%20Magnetic%20Head</t>
         </is>
       </c>
     </row>
@@ -15405,7 +15405,7 @@
       </c>
       <c r="L32" s="5" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@fanttik_official/video/7411982736192</t>
+          <t>https://www.tiktok.com/search?q=tool_master_diy%20Portable%20Cordless%20Smart%20Tire%20Inflator%20%26%20Digital%20Air%20Compressor%20150%20PSI</t>
         </is>
       </c>
     </row>
@@ -15463,7 +15463,7 @@
       </c>
       <c r="L33" s="5" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@cleanskinclub/video/743982736192</t>
+          <t>https://www.tiktok.com/search?q=fanttik_official%20Clean%20Skin%20Club%20Clean%20Towels%20XL%20100%25%20Biobased%20Disposable%20Face%20Towels</t>
         </is>
       </c>
     </row>
@@ -15521,7 +15521,7 @@
       </c>
       <c r="L34" s="5" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@halara_official/video/7538817293019</t>
+          <t>https://www.tiktok.com/search?q=cleanskinclub%20Halara%20High%20Waisted%20Crossover%20Side%20Pocket%20Flared%20Casual%20Leggings</t>
         </is>
       </c>
     </row>
@@ -15579,7 +15579,7 @@
       </c>
       <c r="L35" s="5" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@cloud_cushion_slides/video/7561817293019</t>
+          <t>https://www.tiktok.com/search?q=halara_official_reviews%20Ultra-Thick%20Cloud%20Cushion%20Ergonomic%20Recovery%20Slides%20Anti-Slip</t>
         </is>
       </c>
     </row>
@@ -15637,7 +15637,7 @@
       </c>
       <c r="L36" s="5" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@crunchycandylab/video/7417982736192</t>
+          <t>https://www.tiktok.com/search?q=cloud_cushion_slides_reviews%20Freeze%20Dried%20Rainbow%20Crunch%20Crunchy%20Candy%208oz%20Party%20Pack</t>
         </is>
       </c>
     </row>
@@ -15695,7 +15695,7 @@
       </c>
       <c r="L37" s="5" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@vintage_vault_us/video/7560817293019</t>
+          <t>https://www.tiktok.com/search?q=crunchycandylab%20Authentic%2090s%20Carhartt%20Detroit%20Jacket%20Vintage%20Distressed%20Blanket%20Lined</t>
         </is>
       </c>
     </row>
@@ -15753,7 +15753,7 @@
       </c>
       <c r="L38" s="5" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@tartecosmetics/video/7539817293019</t>
+          <t>https://www.tiktok.com/search?q=vintage_vault_us_reviews%20Tarte%20Maracuja%20Juicy%20Lip%20Plump%20Viral%20Hydrating%20Gloss</t>
         </is>
       </c>
     </row>
@@ -15811,7 +15811,7 @@
       </c>
       <c r="L39" s="5" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@brookemonk_/video/7541817293019</t>
+          <t>https://www.tiktok.com/search?q=tartecosmetics_reviews%20Anker%20MagGo%20Qi2%20Ultra-Fast%20Magnetic%20Power%20Bank%2010000mAh</t>
         </is>
       </c>
     </row>
@@ -15869,7 +15869,7 @@
       </c>
       <c r="L40" s="5" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@neatfreak_home/video/7554817293019</t>
+          <t>https://www.tiktok.com/search?q=brookemonk__reviews%20Foldable%20Handheld%20Garment%20Clothes%20Steamer%201000W%20Fast%20Heat</t>
         </is>
       </c>
     </row>
@@ -15927,7 +15927,7 @@
       </c>
       <c r="L41" s="5" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@everyday_carry_us/video/7557817293019</t>
+          <t>https://www.tiktok.com/search?q=neatfreak_home_reviews%20Everyday%20Everywhere%20Water-Resistant%20Crossbody%20Belt%20Bag%20Adjustable</t>
         </is>
       </c>
     </row>
@@ -15985,7 +15985,7 @@
       </c>
       <c r="L42" s="5" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@gurunanda.official/video/7535817293019</t>
+          <t>https://www.tiktok.com/search?q=everyday_carry_us_reviews%20GuruNanda%20Cocomint%20Coconut%20Pulling%20Oil%20with%20Tongue%20Scraper</t>
         </is>
       </c>
     </row>
@@ -16043,7 +16043,7 @@
       </c>
       <c r="L43" s="5" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@popflexactive/video/7429982736192</t>
+          <t>https://www.tiktok.com/search?q=gurunanda.official_reviews%20Wide%20Band%20Non-Slip%20Booty%20Fabric%20Resistance%20Bands%203pk%20Heavy%20Duty</t>
         </is>
       </c>
     </row>
@@ -16101,7 +16101,7 @@
       </c>
       <c r="L44" s="5" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@fanttik_official/video/7544817293019</t>
+          <t>https://www.tiktok.com/search?q=popflexactive%20Portable%20Cordless%20Smart%20Tire%20Inflator%20%26%20Digital%20Air%20Compressor%20150%20PSI</t>
         </is>
       </c>
     </row>
@@ -16159,7 +16159,7 @@
       </c>
       <c r="L45" s="5" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@cleanskinclub/video/7536817293019</t>
+          <t>https://www.tiktok.com/search?q=fanttik_official_reviews%20Clean%20Skin%20Club%20Clean%20Towels%20XL%20100%25%20Biobased%20Disposable%20Face%20Towels</t>
         </is>
       </c>
     </row>
@@ -16217,7 +16217,7 @@
       </c>
       <c r="L46" s="5" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@crunchycandylab/video/7550817293019</t>
+          <t>https://www.tiktok.com/search?q=cleanskinclub_reviews%20Freeze%20Dried%20Rainbow%20Crunch%20Crunchy%20Candy%208oz%20Party%20Pack</t>
         </is>
       </c>
     </row>
@@ -16275,7 +16275,7 @@
       </c>
       <c r="L47" s="5" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@y2k_retro_shades/video/7416982736192</t>
+          <t>https://www.tiktok.com/search?q=crunchycandylab_reviews%20Retro%20Oval%20Chunky%20Y2K%20Polarized%20UV400%20Sunglasses</t>
         </is>
       </c>
     </row>
@@ -16333,7 +16333,7 @@
       </c>
       <c r="L48" s="5" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@brodiethatdood/video/747982736192</t>
+          <t>https://www.tiktok.com/search?q=y2k_retro_shades%20Aumuca%20Self-Cleaning%20Slicker%20Deshedding%20Brush%20for%20Dogs%20and%20Cats</t>
         </is>
       </c>
     </row>
@@ -16391,7 +16391,7 @@
       </c>
       <c r="L49" s="5" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@tiny_trends_kids/video/7423982736192</t>
+          <t>https://www.tiktok.com/search?q=brodiethatdood%20Toddler%202-Piece%20Waffle%20Knit%20Loungewear%20Set%20Soft%20Organic%20Cotton</t>
         </is>
       </c>
     </row>
@@ -16449,7 +16449,7 @@
       </c>
       <c r="L50" s="5" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@card_collector_us/video/7414982736192</t>
+          <t>https://www.tiktok.com/search?q=tiny_trends_kids%20Pokemon%20PTCG%20Booster%20Binder%20%26%20Magnetic%20Acrylic%20Storage%20Cases</t>
         </is>
       </c>
     </row>
@@ -16507,7 +16507,7 @@
       </c>
       <c r="L51" s="5" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@digital_planner_club/video/7433982736192</t>
+          <t>https://www.tiktok.com/search?q=card_collector_us%20Ultimate%20Life%20OS%20All-in-One%20Notion%20Template%202026%20Daily%20Habit%20Tracker</t>
         </is>
       </c>
     </row>
@@ -16565,7 +16565,7 @@
       </c>
       <c r="L52" s="5" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@aesthetic_home_rugs/video/7430982736192</t>
+          <t>https://www.tiktok.com/search?q=digital_planner_club%20Super%20Absorbent%20Visual%20Memory%20Foam%20Floor%20Mat%20Instant%20Dry%20Bathroom%20Rug</t>
         </is>
       </c>
     </row>
@@ -16623,7 +16623,7 @@
       </c>
       <c r="L53" s="5" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@popflexactive/video/7562817293019</t>
+          <t>https://www.tiktok.com/search?q=aesthetic_home_rugs%20Wide%20Band%20Non-Slip%20Booty%20Fabric%20Resistance%20Bands%203pk%20Heavy%20Duty</t>
         </is>
       </c>
     </row>
@@ -16681,7 +16681,7 @@
       </c>
       <c r="L54" s="5" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@mommy_finds_daily/video/7412982736192</t>
+          <t>https://www.tiktok.com/search?q=popflexactive_reviews%20Silicone%20Pull%20String%20Sensory%20Montessori%20Teething%20Toy%20for%20Babies</t>
         </is>
       </c>
     </row>
@@ -16739,7 +16739,7 @@
       </c>
       <c r="L55" s="5" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@fidget_satisfying/video/7432982736192</t>
+          <t>https://www.tiktok.com/search?q=mommy_finds_daily%20Steamed%20Bun%20Dumpling%20Squishy%20Stress%20Relief%20Slow-Rise%20Sensory%20Toy</t>
         </is>
       </c>
     </row>
@@ -16797,7 +16797,7 @@
       </c>
       <c r="L56" s="5" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@modest_chic_us/video/7426982736192</t>
+          <t>https://www.tiktok.com/search?q=fidget_satisfying%20Premium%20Modal%20Cotton%20Jersey%20Breathable%20Instant%20Hijab%20Scarf</t>
         </is>
       </c>
     </row>
@@ -16855,7 +16855,7 @@
       </c>
       <c r="L57" s="5" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@y2k_retro_shades/video/7549817293019</t>
+          <t>https://www.tiktok.com/search?q=modest_chic_us%20Retro%20Oval%20Chunky%20Y2K%20Polarized%20UV400%20Sunglasses</t>
         </is>
       </c>
     </row>
@@ -16913,7 +16913,7 @@
       </c>
       <c r="L58" s="5" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@brodiethatdood/video/7540817293019</t>
+          <t>https://www.tiktok.com/search?q=y2k_retro_shades_reviews%20Aumuca%20Self-Cleaning%20Slicker%20Deshedding%20Brush%20for%20Dogs%20and%20Cats</t>
         </is>
       </c>
     </row>
@@ -16971,7 +16971,7 @@
       </c>
       <c r="L59" s="5" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@tiny_trends_kids/video/7556817293019</t>
+          <t>https://www.tiktok.com/search?q=brodiethatdood_reviews%20Toddler%202-Piece%20Waffle%20Knit%20Loungewear%20Set%20Soft%20Organic%20Cotton</t>
         </is>
       </c>
     </row>
@@ -17029,7 +17029,7 @@
       </c>
       <c r="L60" s="5" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@card_collector_us/video/7547817293019</t>
+          <t>https://www.tiktok.com/search?q=tiny_trends_kids_reviews%20Pokemon%20PTCG%20Booster%20Binder%20%26%20Magnetic%20Acrylic%20Storage%20Cases</t>
         </is>
       </c>
     </row>
@@ -17087,7 +17087,7 @@
       </c>
       <c r="L61" s="5" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@journaling_aesthetic/video/7413982736192</t>
+          <t>https://www.tiktok.com/search?q=card_collector_us_reviews%20Vintage%20Embossed%20Hardcover%20Lock%20Journal%20%26%20Planner%20with%20Metal%20Clasp</t>
         </is>
       </c>
     </row>
@@ -17145,7 +17145,7 @@
       </c>
       <c r="L62" s="5" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@mommy_finds_daily/video/7545817293019</t>
+          <t>https://www.tiktok.com/search?q=journaling_aesthetic%20Silicone%20Pull%20String%20Sensory%20Montessori%20Teething%20Toy%20for%20Babies</t>
         </is>
       </c>
     </row>
@@ -17203,7 +17203,7 @@
       </c>
       <c r="L63" s="5" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@modest_chic_us/video/7559817293019</t>
+          <t>https://www.tiktok.com/search?q=mommy_finds_daily_reviews%20Premium%20Modal%20Cotton%20Jersey%20Breathable%20Instant%20Hijab%20Scarf</t>
         </is>
       </c>
     </row>
@@ -17261,7 +17261,7 @@
       </c>
       <c r="L64" s="5" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@journaling_aesthetic/video/7546817293019</t>
+          <t>https://www.tiktok.com/search?q=modest_chic_us_reviews%20Vintage%20Embossed%20Hardcover%20Lock%20Journal%20%26%20Planner%20with%20Metal%20Clasp</t>
         </is>
       </c>
     </row>
@@ -17532,17 +17532,17 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>owala_official</t>
+          <t>Owala’s life</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>@owala_official</t>
+          <t>@owalalife</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>1.2M</t>
+          <t>1.0K</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
@@ -17570,12 +17570,12 @@
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t>10.2%</t>
+          <t>8.5%</t>
         </is>
       </c>
       <c r="K5" s="5" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@owala_official</t>
+          <t>https://www.tiktok.com/@owalalife</t>
         </is>
       </c>
     </row>
@@ -17744,12 +17744,12 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>keychron_official</t>
+          <t>keychron</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>@keychron_official</t>
+          <t>@keychron</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
@@ -17787,7 +17787,7 @@
       </c>
       <c r="K9" s="5" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@keychron_official</t>
+          <t>https://www.tiktok.com/@keychron</t>
         </is>
       </c>
     </row>
